--- a/reports/telegram/aegis_daily_2026-08-06.xlsx
+++ b/reports/telegram/aegis_daily_2026-08-06.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="AV2" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="AV3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AV4" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="AV5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="AV6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="AV7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="AV8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="AV9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="AV10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="AV11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="AV12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="AV13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="AV14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="AV15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="AV16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       <c r="S17" s="4" t="inlineStr"/>
       <c r="T17" s="4" t="inlineStr">
         <is>
-          <t>Rank ↑ 2→1 · Conf 83% · 61d left · → STRONG BUY</t>
+          <t>Rank ↑ 2→1 · Conf 83% · momentum → · 61d left · → STRONG BUY</t>
         </is>
       </c>
       <c r="U17" s="4" t="inlineStr"/>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="W17" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>Calibrated</t>
         </is>
       </c>
       <c r="X17" s="4" t="n">
@@ -3134,10 +3134,10 @@
         <v>1454.6</v>
       </c>
       <c r="AE17" s="4" t="n">
-        <v>1440.05</v>
+        <v>1415</v>
       </c>
       <c r="AF17" s="4" t="n">
-        <v>1469.15</v>
+        <v>1495</v>
       </c>
       <c r="AG17" s="4" t="n">
         <v>1381.87</v>
@@ -3152,10 +3152,10 @@
         <v>5.32</v>
       </c>
       <c r="AK17" s="4" t="n">
-        <v>1672.79</v>
+        <v>1639.24</v>
       </c>
       <c r="AL17" s="4" t="n">
-        <v>15</v>
+        <v>12.69</v>
       </c>
       <c r="AM17" s="4" t="n">
         <v>0.35</v>
@@ -3176,13 +3176,15 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="AT17" s="4" t="inlineStr"/>
+      <c r="AT17" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AU17" s="4" t="n">
         <v>5.32</v>
       </c>
       <c r="AV17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -3238,7 +3240,7 @@
       <c r="S18" s="4" t="inlineStr"/>
       <c r="T18" s="4" t="inlineStr">
         <is>
-          <t>Rank ↓ 1→2 · Conf 88% · 61d left · → STRONG BUY</t>
+          <t>Rank ↓ 1→2 · Conf 88% · momentum → · 61d left · → STRONG BUY</t>
         </is>
       </c>
       <c r="U18" s="4" t="inlineStr"/>
@@ -3247,7 +3249,7 @@
       </c>
       <c r="W18" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>Calibrated</t>
         </is>
       </c>
       <c r="X18" s="4" t="n">
@@ -3272,10 +3274,10 @@
         <v>1964</v>
       </c>
       <c r="AE18" s="4" t="n">
-        <v>1944.36</v>
+        <v>1911</v>
       </c>
       <c r="AF18" s="4" t="n">
-        <v>1983.64</v>
+        <v>2017</v>
       </c>
       <c r="AG18" s="4" t="n">
         <v>1865.8</v>
@@ -3290,10 +3292,10 @@
         <v>4.58</v>
       </c>
       <c r="AK18" s="4" t="n">
-        <v>2258.6</v>
+        <v>2197.78</v>
       </c>
       <c r="AL18" s="4" t="n">
-        <v>15</v>
+        <v>11.9</v>
       </c>
       <c r="AM18" s="4" t="n">
         <v>0.44</v>
@@ -3314,13 +3316,15 @@
           <t>Pharma</t>
         </is>
       </c>
-      <c r="AT18" s="4" t="inlineStr"/>
+      <c r="AT18" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AU18" s="4" t="n">
         <v>4.58</v>
       </c>
       <c r="AV18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3380,7 @@
       <c r="S19" s="4" t="inlineStr"/>
       <c r="T19" s="4" t="inlineStr">
         <is>
-          <t>Rank → 3→3 · Conf 86% · 61d left · → STRONG BUY</t>
+          <t>Rank → 3→3 · Conf 86% · momentum → · 61d left · → STRONG BUY</t>
         </is>
       </c>
       <c r="U19" s="4" t="inlineStr"/>
@@ -3385,7 +3389,7 @@
       </c>
       <c r="W19" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>Calibrated</t>
         </is>
       </c>
       <c r="X19" s="4" t="n">
@@ -3410,10 +3414,10 @@
         <v>1620</v>
       </c>
       <c r="AE19" s="4" t="n">
-        <v>1603.8</v>
+        <v>1569</v>
       </c>
       <c r="AF19" s="4" t="n">
-        <v>1636.2</v>
+        <v>1671</v>
       </c>
       <c r="AG19" s="4" t="n">
         <v>1539</v>
@@ -3428,10 +3432,10 @@
         <v>1.36</v>
       </c>
       <c r="AK19" s="4" t="n">
-        <v>1863</v>
+        <v>1756.94</v>
       </c>
       <c r="AL19" s="4" t="n">
-        <v>15</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AM19" s="4" t="n">
         <v>-1.37</v>
@@ -3452,13 +3456,15 @@
           <t>Chemicals</t>
         </is>
       </c>
-      <c r="AT19" s="4" t="inlineStr"/>
+      <c r="AT19" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AU19" s="4" t="n">
         <v>1.36</v>
       </c>
       <c r="AV19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -3514,7 +3520,7 @@
       <c r="S20" s="4" t="inlineStr"/>
       <c r="T20" s="4" t="inlineStr">
         <is>
-          <t>Rank ↓ 3→4 · Conf 71% · 61d left · → STRONG BUY</t>
+          <t>Rank ↓ 3→4 · Conf 71% · momentum → · 61d left · → STRONG BUY</t>
         </is>
       </c>
       <c r="U20" s="4" t="inlineStr"/>
@@ -3523,7 +3529,7 @@
       </c>
       <c r="W20" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>Calibrated</t>
         </is>
       </c>
       <c r="X20" s="4" t="n">
@@ -3548,10 +3554,10 @@
         <v>2410</v>
       </c>
       <c r="AE20" s="4" t="n">
-        <v>2385.9</v>
+        <v>2349</v>
       </c>
       <c r="AF20" s="4" t="n">
-        <v>2434.1</v>
+        <v>2471</v>
       </c>
       <c r="AG20" s="4" t="n">
         <v>2289.5</v>
@@ -3566,10 +3572,10 @@
         <v>8</v>
       </c>
       <c r="AK20" s="4" t="n">
-        <v>2771.5</v>
+        <v>2784.996000000001</v>
       </c>
       <c r="AL20" s="4" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM20" s="4" t="n">
         <v>1.09</v>
@@ -3590,13 +3596,15 @@
           <t>Pharma</t>
         </is>
       </c>
-      <c r="AT20" s="4" t="inlineStr"/>
+      <c r="AT20" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AU20" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AV20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3660,7 @@
       <c r="S21" s="4" t="inlineStr"/>
       <c r="T21" s="4" t="inlineStr">
         <is>
-          <t>Rank ↓ 4→5 · Conf 72% · 61d left · → STRONG BUY</t>
+          <t>Rank ↓ 4→5 · Conf 72% · momentum → · 61d left · → STRONG BUY</t>
         </is>
       </c>
       <c r="U21" s="4" t="inlineStr"/>
@@ -3661,7 +3669,7 @@
       </c>
       <c r="W21" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>Calibrated</t>
         </is>
       </c>
       <c r="X21" s="4" t="n">
@@ -3686,10 +3694,10 @@
         <v>343.6</v>
       </c>
       <c r="AE21" s="4" t="n">
-        <v>340.16</v>
+        <v>335</v>
       </c>
       <c r="AF21" s="4" t="n">
-        <v>347.04</v>
+        <v>353</v>
       </c>
       <c r="AG21" s="4" t="n">
         <v>326.42</v>
@@ -3704,10 +3712,10 @@
         <v>8</v>
       </c>
       <c r="AK21" s="4" t="n">
-        <v>395.14</v>
+        <v>397.0641600000001</v>
       </c>
       <c r="AL21" s="4" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM21" s="4" t="n">
         <v>-1.04</v>
@@ -3728,13 +3736,15 @@
           <t>Power</t>
         </is>
       </c>
-      <c r="AT21" s="4" t="inlineStr"/>
+      <c r="AT21" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AU21" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AV21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3800,7 @@
       <c r="S22" s="4" t="inlineStr"/>
       <c r="T22" s="4" t="inlineStr">
         <is>
-          <t>Rank ↓ 5→6 · Conf 72% · 61d left · → BUY</t>
+          <t>Rank ↓ 5→6 · Conf 72% · momentum → · 61d left · → BUY</t>
         </is>
       </c>
       <c r="U22" s="4" t="inlineStr"/>
@@ -3799,7 +3809,7 @@
       </c>
       <c r="W22" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>Calibrated</t>
         </is>
       </c>
       <c r="X22" s="4" t="n">
@@ -3824,10 +3834,10 @@
         <v>398</v>
       </c>
       <c r="AE22" s="4" t="n">
-        <v>394.02</v>
+        <v>386</v>
       </c>
       <c r="AF22" s="4" t="n">
-        <v>401.98</v>
+        <v>410</v>
       </c>
       <c r="AG22" s="4" t="n">
         <v>378.1</v>
@@ -3842,10 +3852,10 @@
         <v>8</v>
       </c>
       <c r="AK22" s="4" t="n">
-        <v>457.7</v>
+        <v>459.9288000000001</v>
       </c>
       <c r="AL22" s="4" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM22" s="4" t="n">
         <v>0.25</v>
@@ -3866,13 +3876,15 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="AT22" s="4" t="inlineStr"/>
+      <c r="AT22" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AU22" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AV22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3940,7 @@
       <c r="S23" s="4" t="inlineStr"/>
       <c r="T23" s="4" t="inlineStr">
         <is>
-          <t>Rank → 7→7 · Conf 69% · 61d left · → BUY</t>
+          <t>Rank → 7→7 · Conf 69% · momentum → · 61d left · → BUY</t>
         </is>
       </c>
       <c r="U23" s="4" t="inlineStr"/>
@@ -3937,7 +3949,7 @@
       </c>
       <c r="W23" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>Calibrated</t>
         </is>
       </c>
       <c r="X23" s="4" t="n">
@@ -3962,10 +3974,10 @@
         <v>283.4</v>
       </c>
       <c r="AE23" s="4" t="n">
-        <v>280.57</v>
+        <v>276</v>
       </c>
       <c r="AF23" s="4" t="n">
-        <v>286.23</v>
+        <v>290</v>
       </c>
       <c r="AG23" s="4" t="n">
         <v>269.23</v>
@@ -3980,10 +3992,10 @@
         <v>8</v>
       </c>
       <c r="AK23" s="4" t="n">
-        <v>325.91</v>
+        <v>327.49704</v>
       </c>
       <c r="AL23" s="4" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM23" s="4" t="n">
         <v>-0.86</v>
@@ -4004,13 +4016,15 @@
           <t>Power</t>
         </is>
       </c>
-      <c r="AT23" s="4" t="inlineStr"/>
+      <c r="AT23" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AU23" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AV23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -4066,7 +4080,7 @@
       <c r="S24" s="4" t="inlineStr"/>
       <c r="T24" s="4" t="inlineStr">
         <is>
-          <t>Rank ↓ 7→8 · Conf 67% · 61d left · → HOLD</t>
+          <t>Rank ↓ 7→8 · Conf 67% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="U24" s="4" t="inlineStr"/>
@@ -4075,7 +4089,7 @@
       </c>
       <c r="W24" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>Calibrated</t>
         </is>
       </c>
       <c r="X24" s="4" t="n">
@@ -4100,10 +4114,10 @@
         <v>510.2</v>
       </c>
       <c r="AE24" s="4" t="n">
-        <v>505.1</v>
+        <v>495</v>
       </c>
       <c r="AF24" s="4" t="n">
-        <v>515.3</v>
+        <v>526</v>
       </c>
       <c r="AG24" s="4" t="n">
         <v>484.6899999999999</v>
@@ -4118,10 +4132,10 @@
         <v>8</v>
       </c>
       <c r="AK24" s="4" t="n">
-        <v>586.7299999999999</v>
+        <v>589.5871200000001</v>
       </c>
       <c r="AL24" s="4" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM24" s="4" t="n">
         <v>0.46</v>
@@ -4142,13 +4156,15 @@
           <t>Transport</t>
         </is>
       </c>
-      <c r="AT24" s="4" t="inlineStr"/>
+      <c r="AT24" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AU24" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AV24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -4204,7 +4220,7 @@
       <c r="S25" s="4" t="inlineStr"/>
       <c r="T25" s="4" t="inlineStr">
         <is>
-          <t>Rank ↓ 8→9 · Conf 64% · 61d left · → BUY</t>
+          <t>Rank ↓ 8→9 · Conf 64% · momentum → · 61d left · → BUY</t>
         </is>
       </c>
       <c r="U25" s="4" t="inlineStr"/>
@@ -4213,7 +4229,7 @@
       </c>
       <c r="W25" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>Calibrated</t>
         </is>
       </c>
       <c r="X25" s="4" t="n">
@@ -4238,10 +4254,10 @@
         <v>391.5</v>
       </c>
       <c r="AE25" s="4" t="n">
-        <v>387.58</v>
+        <v>379</v>
       </c>
       <c r="AF25" s="4" t="n">
-        <v>395.42</v>
+        <v>404</v>
       </c>
       <c r="AG25" s="4" t="n">
         <v>371.925</v>
@@ -4256,10 +4272,10 @@
         <v>8</v>
       </c>
       <c r="AK25" s="4" t="n">
-        <v>450.225</v>
+        <v>452.4174000000001</v>
       </c>
       <c r="AL25" s="4" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM25" s="4" t="n">
         <v>0.42</v>
@@ -4280,13 +4296,15 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="AT25" s="4" t="inlineStr"/>
+      <c r="AT25" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AU25" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AV25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4356,7 @@
       <c r="S26" s="4" t="inlineStr"/>
       <c r="T26" s="4" t="inlineStr">
         <is>
-          <t>Rank ↓ 9→10 · Conf 66% · 61d left · → HOLD</t>
+          <t>Rank ↓ 9→10 · Conf 66% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="U26" s="4" t="inlineStr"/>
@@ -4347,7 +4365,7 @@
       </c>
       <c r="W26" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>Calibrated</t>
         </is>
       </c>
       <c r="X26" s="4" t="n">
@@ -4372,10 +4390,10 @@
         <v>5478</v>
       </c>
       <c r="AE26" s="4" t="n">
-        <v>5423.22</v>
+        <v>5335</v>
       </c>
       <c r="AF26" s="4" t="n">
-        <v>5532.78</v>
+        <v>5621</v>
       </c>
       <c r="AG26" s="4" t="n">
         <v>5204.099999999999</v>
@@ -4390,10 +4408,10 @@
         <v>8</v>
       </c>
       <c r="AK26" s="4" t="n">
-        <v>6299.7</v>
+        <v>6330.376800000001</v>
       </c>
       <c r="AL26" s="4" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM26" s="4" t="n">
         <v>0.43</v>
@@ -4414,13 +4432,15 @@
           <t>FMCG</t>
         </is>
       </c>
-      <c r="AT26" s="4" t="inlineStr"/>
+      <c r="AT26" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AU26" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AV26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4496,7 @@
       <c r="S27" s="4" t="inlineStr"/>
       <c r="T27" s="4" t="inlineStr">
         <is>
-          <t>Rank ↓ 10→11 · Conf 66% · 61d left · → BUY</t>
+          <t>Rank ↓ 10→11 · Conf 66% · momentum → · 61d left · → BUY</t>
         </is>
       </c>
       <c r="U27" s="4" t="inlineStr"/>
@@ -4485,7 +4505,7 @@
       </c>
       <c r="W27" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>Calibrated</t>
         </is>
       </c>
       <c r="X27" s="4" t="n">
@@ -4510,10 +4530,10 @@
         <v>417.6</v>
       </c>
       <c r="AE27" s="4" t="n">
-        <v>413.42</v>
+        <v>405</v>
       </c>
       <c r="AF27" s="4" t="n">
-        <v>421.78</v>
+        <v>430</v>
       </c>
       <c r="AG27" s="4" t="n">
         <v>396.72</v>
@@ -4528,10 +4548,10 @@
         <v>8</v>
       </c>
       <c r="AK27" s="4" t="n">
-        <v>480.24</v>
+        <v>482.5785600000001</v>
       </c>
       <c r="AL27" s="4" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM27" s="4" t="n">
         <v>0.59</v>
@@ -4552,13 +4572,15 @@
           <t>Metal</t>
         </is>
       </c>
-      <c r="AT27" s="4" t="inlineStr"/>
+      <c r="AT27" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AU27" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AV27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4740,7 @@
       </c>
       <c r="AV28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4900,7 @@
       </c>
       <c r="AV29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -5042,7 +5064,7 @@
       </c>
       <c r="AV30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -5206,7 +5228,7 @@
       </c>
       <c r="AV31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5394,7 @@
       </c>
       <c r="AV32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5558,7 @@
       </c>
       <c r="AV33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -5702,7 +5724,7 @@
       </c>
       <c r="AV34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -5770,11 +5792,11 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>crude +19.8% (rising) → +1.0pts · 32 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+          <t>crude +19.8% (rising) → +1.0pts · 33 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R35" s="4" t="n">
         <v>0.15</v>
@@ -5868,7 +5890,7 @@
       </c>
       <c r="AV35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6056,7 @@
       </c>
       <c r="AV36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6220,7 @@
       </c>
       <c r="AV37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6384,7 @@
       </c>
       <c r="AV38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -6528,7 +6550,7 @@
       </c>
       <c r="AV39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6716,7 @@
       </c>
       <c r="AV40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -6860,7 +6882,7 @@
       </c>
       <c r="AV41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7048,7 @@
       </c>
       <c r="AV42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_daily_2026-08-06.xlsx
+++ b/reports/telegram/aegis_daily_2026-08-06.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AV$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AV$52</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV42"/>
+  <dimension ref="A1:AV52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="AV2" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="AV3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AV4" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="AV5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="AV6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="AV7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="AV8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="AV9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="AV10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="AV11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="AV12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="AV13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="AV14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="AV15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="AV16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AV17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="AV18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="AV19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="AV20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="AV21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="AV22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="AV23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="AV24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -4304,7 +4304,7 @@
       </c>
       <c r="AV25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="AV26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="AV27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="AV28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -4900,7 +4900,7 @@
       </c>
       <c r="AV29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="AV30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="AV31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="AV32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="AV33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -5724,7 +5724,7 @@
       </c>
       <c r="AV34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AV35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="AV36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="AV37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="AV38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -6550,7 +6550,7 @@
       </c>
       <c r="AV39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="AV40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="AV41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -7048,12 +7048,1562 @@
       </c>
       <c r="AV42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr"/>
+      <c r="H43" s="4" t="inlineStr"/>
+      <c r="I43" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" s="4" t="inlineStr"/>
+      <c r="K43" s="4" t="inlineStr"/>
+      <c r="L43" s="4" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="M43" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N43" s="4" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="O43" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P43" s="4" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="Q43" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R43" s="4" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="S43" s="4" t="inlineStr"/>
+      <c r="T43" s="4" t="inlineStr">
+        <is>
+          <t>Rank #1 · Conf 54% · momentum → · band HOLD · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="U43" s="4" t="inlineStr"/>
+      <c r="V43" s="4" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="W43" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X43" s="4" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="Y43" s="4" t="inlineStr"/>
+      <c r="Z43" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA43" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="AB43" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC43" s="4" t="n">
+        <v>358.56</v>
+      </c>
+      <c r="AD43" s="4" t="n">
+        <v>358.56</v>
+      </c>
+      <c r="AE43" s="4" t="n">
+        <v>351.39</v>
+      </c>
+      <c r="AF43" s="4" t="n">
+        <v>365.73</v>
+      </c>
+      <c r="AG43" s="4" t="n">
+        <v>340.632</v>
+      </c>
+      <c r="AH43" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI43" s="4" t="n">
+        <v>387.2448000000001</v>
+      </c>
+      <c r="AJ43" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK43" s="4" t="n">
+        <v>414.3519360000001</v>
+      </c>
+      <c r="AL43" s="4" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AM43" s="4" t="inlineStr"/>
+      <c r="AN43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO43" s="4" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AP43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ43" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AR43" s="4" t="inlineStr"/>
+      <c r="AS43" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT43" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU43" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV43" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>TRV</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr"/>
+      <c r="H44" s="4" t="inlineStr"/>
+      <c r="I44" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr"/>
+      <c r="K44" s="4" t="inlineStr"/>
+      <c r="L44" s="4" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="M44" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N44" s="4" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="O44" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P44" s="4" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 12 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="Q44" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="R44" s="4" t="inlineStr"/>
+      <c r="S44" s="4" t="inlineStr"/>
+      <c r="T44" s="4" t="inlineStr">
+        <is>
+          <t>Rank #2 · Conf 57% · momentum → · band HOLD · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="U44" s="4" t="inlineStr"/>
+      <c r="V44" s="4" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="W44" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X44" s="4" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="Y44" s="4" t="inlineStr"/>
+      <c r="Z44" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA44" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="AB44" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC44" s="4" t="n">
+        <v>368.98</v>
+      </c>
+      <c r="AD44" s="4" t="n">
+        <v>368.98</v>
+      </c>
+      <c r="AE44" s="4" t="n">
+        <v>365.29</v>
+      </c>
+      <c r="AF44" s="4" t="n">
+        <v>372.67</v>
+      </c>
+      <c r="AG44" s="4" t="n">
+        <v>350.531</v>
+      </c>
+      <c r="AH44" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI44" s="4" t="n">
+        <v>413.26</v>
+      </c>
+      <c r="AJ44" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK44" s="4" t="n">
+        <v>442.1882</v>
+      </c>
+      <c r="AL44" s="4" t="n">
+        <v>19.84</v>
+      </c>
+      <c r="AM44" s="4" t="inlineStr"/>
+      <c r="AN44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO44" s="4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AP44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ44" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AR44" s="4" t="inlineStr"/>
+      <c r="AS44" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT44" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU44" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV44" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr"/>
+      <c r="H45" s="4" t="inlineStr"/>
+      <c r="I45" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr"/>
+      <c r="K45" s="4" t="inlineStr"/>
+      <c r="L45" s="4" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="M45" s="4" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="N45" s="4" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="O45" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P45" s="4" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 21 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="Q45" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="R45" s="4" t="inlineStr"/>
+      <c r="S45" s="4" t="inlineStr"/>
+      <c r="T45" s="4" t="inlineStr">
+        <is>
+          <t>Rank #3 · Conf 47% · momentum → · band WATCH · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="U45" s="4" t="inlineStr"/>
+      <c r="V45" s="4" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="W45" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X45" s="4" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="Y45" s="4" t="inlineStr"/>
+      <c r="Z45" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA45" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="AB45" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC45" s="4" t="n">
+        <v>202.81</v>
+      </c>
+      <c r="AD45" s="4" t="n">
+        <v>202.81</v>
+      </c>
+      <c r="AE45" s="4" t="n">
+        <v>198.75</v>
+      </c>
+      <c r="AF45" s="4" t="n">
+        <v>206.87</v>
+      </c>
+      <c r="AG45" s="4" t="n">
+        <v>192.6695</v>
+      </c>
+      <c r="AH45" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI45" s="4" t="n">
+        <v>219.0348</v>
+      </c>
+      <c r="AJ45" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK45" s="4" t="n">
+        <v>234.367236</v>
+      </c>
+      <c r="AL45" s="4" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AM45" s="4" t="inlineStr"/>
+      <c r="AN45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP45" s="4" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="AQ45" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AR45" s="4" t="inlineStr"/>
+      <c r="AS45" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT45" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU45" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV45" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr"/>
+      <c r="H46" s="4" t="inlineStr"/>
+      <c r="I46" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr"/>
+      <c r="K46" s="4" t="inlineStr"/>
+      <c r="L46" s="4" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="M46" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N46" s="4" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="O46" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P46" s="4" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 33 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="Q46" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="R46" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="S46" s="4" t="inlineStr"/>
+      <c r="T46" s="4" t="inlineStr">
+        <is>
+          <t>Rank #4 · Conf 54% · momentum → · band HOLD · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="U46" s="4" t="inlineStr"/>
+      <c r="V46" s="4" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="W46" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X46" s="4" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="Y46" s="4" t="inlineStr"/>
+      <c r="Z46" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA46" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="AB46" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AC46" s="4" t="n">
+        <v>393.82</v>
+      </c>
+      <c r="AD46" s="4" t="n">
+        <v>393.82</v>
+      </c>
+      <c r="AE46" s="4" t="n">
+        <v>385.94</v>
+      </c>
+      <c r="AF46" s="4" t="n">
+        <v>401.7</v>
+      </c>
+      <c r="AG46" s="4" t="n">
+        <v>374.129</v>
+      </c>
+      <c r="AH46" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI46" s="4" t="n">
+        <v>425.3256</v>
+      </c>
+      <c r="AJ46" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK46" s="4" t="n">
+        <v>455.098392</v>
+      </c>
+      <c r="AL46" s="4" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AM46" s="4" t="inlineStr"/>
+      <c r="AN46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO46" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ46" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AR46" s="4" t="inlineStr"/>
+      <c r="AS46" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT46" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU46" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV46" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Coca-Cola</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr"/>
+      <c r="H47" s="4" t="inlineStr"/>
+      <c r="I47" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr"/>
+      <c r="K47" s="4" t="inlineStr"/>
+      <c r="L47" s="4" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="M47" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N47" s="4" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="O47" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P47" s="4" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 11 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="Q47" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="R47" s="4" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="S47" s="4" t="inlineStr"/>
+      <c r="T47" s="4" t="inlineStr">
+        <is>
+          <t>Rank #5 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U47" s="4" t="inlineStr"/>
+      <c r="V47" s="4" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="W47" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X47" s="4" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="Y47" s="4" t="inlineStr"/>
+      <c r="Z47" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA47" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="AB47" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC47" s="4" t="n">
+        <v>81.56</v>
+      </c>
+      <c r="AD47" s="4" t="n">
+        <v>81.56</v>
+      </c>
+      <c r="AE47" s="4" t="n">
+        <v>79.93000000000001</v>
+      </c>
+      <c r="AF47" s="4" t="n">
+        <v>83.19</v>
+      </c>
+      <c r="AG47" s="4" t="n">
+        <v>77.482</v>
+      </c>
+      <c r="AH47" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI47" s="4" t="n">
+        <v>88.0848</v>
+      </c>
+      <c r="AJ47" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK47" s="4" t="n">
+        <v>94.250736</v>
+      </c>
+      <c r="AL47" s="4" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AM47" s="4" t="inlineStr"/>
+      <c r="AN47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO47" s="4" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="AP47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ47" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AR47" s="4" t="inlineStr"/>
+      <c r="AS47" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT47" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU47" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV47" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Honeywell</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr"/>
+      <c r="H48" s="4" t="inlineStr"/>
+      <c r="I48" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr"/>
+      <c r="K48" s="4" t="inlineStr"/>
+      <c r="L48" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="M48" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N48" s="4" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="O48" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P48" s="4" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 48 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="Q48" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="R48" s="4" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="S48" s="4" t="inlineStr"/>
+      <c r="T48" s="4" t="inlineStr">
+        <is>
+          <t>Rank #6 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U48" s="4" t="inlineStr"/>
+      <c r="V48" s="4" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="W48" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X48" s="4" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="Y48" s="4" t="inlineStr"/>
+      <c r="Z48" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA48" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="AB48" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC48" s="4" t="n">
+        <v>225.02</v>
+      </c>
+      <c r="AD48" s="4" t="n">
+        <v>225.02</v>
+      </c>
+      <c r="AE48" s="4" t="n">
+        <v>220.52</v>
+      </c>
+      <c r="AF48" s="4" t="n">
+        <v>229.52</v>
+      </c>
+      <c r="AG48" s="4" t="n">
+        <v>213.769</v>
+      </c>
+      <c r="AH48" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI48" s="4" t="n">
+        <v>243.0216</v>
+      </c>
+      <c r="AJ48" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK48" s="4" t="n">
+        <v>260.0331120000001</v>
+      </c>
+      <c r="AL48" s="4" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AM48" s="4" t="inlineStr"/>
+      <c r="AN48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO48" s="4" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="AP48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ48" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AR48" s="4" t="inlineStr"/>
+      <c r="AS48" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT48" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU48" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV48" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr"/>
+      <c r="H49" s="4" t="inlineStr"/>
+      <c r="I49" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr"/>
+      <c r="K49" s="4" t="inlineStr"/>
+      <c r="L49" s="4" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="M49" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N49" s="4" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="O49" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P49" s="4" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="Q49" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R49" s="4" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="S49" s="4" t="inlineStr"/>
+      <c r="T49" s="4" t="inlineStr">
+        <is>
+          <t>Rank #7 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U49" s="4" t="inlineStr"/>
+      <c r="V49" s="4" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="W49" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X49" s="4" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="Y49" s="4" t="inlineStr"/>
+      <c r="Z49" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA49" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="AB49" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC49" s="4" t="n">
+        <v>333.74</v>
+      </c>
+      <c r="AD49" s="4" t="n">
+        <v>333.74</v>
+      </c>
+      <c r="AE49" s="4" t="n">
+        <v>327.07</v>
+      </c>
+      <c r="AF49" s="4" t="n">
+        <v>340.41</v>
+      </c>
+      <c r="AG49" s="4" t="n">
+        <v>317.053</v>
+      </c>
+      <c r="AH49" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI49" s="4" t="n">
+        <v>360.4392</v>
+      </c>
+      <c r="AJ49" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK49" s="4" t="n">
+        <v>385.669944</v>
+      </c>
+      <c r="AL49" s="4" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AM49" s="4" t="inlineStr"/>
+      <c r="AN49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP49" s="4" t="n">
+        <v>-7.44</v>
+      </c>
+      <c r="AQ49" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AR49" s="4" t="inlineStr"/>
+      <c r="AS49" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT49" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU49" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV49" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr"/>
+      <c r="H50" s="4" t="inlineStr"/>
+      <c r="I50" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr"/>
+      <c r="K50" s="4" t="inlineStr"/>
+      <c r="L50" s="4" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="M50" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N50" s="4" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="O50" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P50" s="4" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 18 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="Q50" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="R50" s="4" t="inlineStr"/>
+      <c r="S50" s="4" t="inlineStr"/>
+      <c r="T50" s="4" t="inlineStr">
+        <is>
+          <t>Rank #8 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U50" s="4" t="inlineStr"/>
+      <c r="V50" s="4" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="W50" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X50" s="4" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="Y50" s="4" t="inlineStr"/>
+      <c r="Z50" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA50" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="AB50" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC50" s="4" t="n">
+        <v>341.1</v>
+      </c>
+      <c r="AD50" s="4" t="n">
+        <v>341.1</v>
+      </c>
+      <c r="AE50" s="4" t="n">
+        <v>334.28</v>
+      </c>
+      <c r="AF50" s="4" t="n">
+        <v>347.92</v>
+      </c>
+      <c r="AG50" s="4" t="n">
+        <v>324.045</v>
+      </c>
+      <c r="AH50" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI50" s="4" t="n">
+        <v>368.388</v>
+      </c>
+      <c r="AJ50" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK50" s="4" t="n">
+        <v>394.1751600000001</v>
+      </c>
+      <c r="AL50" s="4" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AM50" s="4" t="inlineStr"/>
+      <c r="AN50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO50" s="4" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AP50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ50" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AR50" s="4" t="inlineStr"/>
+      <c r="AS50" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT50" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU50" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV50" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr"/>
+      <c r="H51" s="4" t="inlineStr"/>
+      <c r="I51" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J51" s="4" t="inlineStr"/>
+      <c r="K51" s="4" t="inlineStr"/>
+      <c r="L51" s="4" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="M51" s="4" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="N51" s="4" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="O51" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P51" s="4" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 9 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="Q51" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="R51" s="4" t="inlineStr"/>
+      <c r="S51" s="4" t="inlineStr"/>
+      <c r="T51" s="4" t="inlineStr">
+        <is>
+          <t>Rank #9 · Conf 51% · momentum → · band WATCH · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U51" s="4" t="inlineStr"/>
+      <c r="V51" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="W51" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X51" s="4" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="Y51" s="4" t="inlineStr"/>
+      <c r="Z51" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA51" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="AB51" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC51" s="4" t="n">
+        <v>1065.22</v>
+      </c>
+      <c r="AD51" s="4" t="n">
+        <v>1065.22</v>
+      </c>
+      <c r="AE51" s="4" t="n">
+        <v>1043.92</v>
+      </c>
+      <c r="AF51" s="4" t="n">
+        <v>1086.52</v>
+      </c>
+      <c r="AG51" s="4" t="n">
+        <v>1011.959</v>
+      </c>
+      <c r="AH51" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI51" s="4" t="n">
+        <v>1150.4376</v>
+      </c>
+      <c r="AJ51" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK51" s="4" t="n">
+        <v>1230.968232</v>
+      </c>
+      <c r="AL51" s="4" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AM51" s="4" t="inlineStr"/>
+      <c r="AN51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP51" s="4" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="AQ51" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AR51" s="4" t="inlineStr"/>
+      <c r="AS51" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT51" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU51" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV51" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>MMM</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr"/>
+      <c r="H52" s="4" t="inlineStr"/>
+      <c r="I52" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr"/>
+      <c r="K52" s="4" t="inlineStr"/>
+      <c r="L52" s="4" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="M52" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N52" s="4" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="O52" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P52" s="4" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 15 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="Q52" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="R52" s="4" t="inlineStr"/>
+      <c r="S52" s="4" t="inlineStr"/>
+      <c r="T52" s="4" t="inlineStr">
+        <is>
+          <t>Rank #10 · Conf 54% · momentum → · band HOLD · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U52" s="4" t="inlineStr"/>
+      <c r="V52" s="4" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="W52" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X52" s="4" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="Y52" s="4" t="inlineStr"/>
+      <c r="Z52" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA52" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="AB52" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AC52" s="4" t="n">
+        <v>159.84</v>
+      </c>
+      <c r="AD52" s="4" t="n">
+        <v>159.84</v>
+      </c>
+      <c r="AE52" s="4" t="n">
+        <v>156.64</v>
+      </c>
+      <c r="AF52" s="4" t="n">
+        <v>163.04</v>
+      </c>
+      <c r="AG52" s="4" t="n">
+        <v>151.848</v>
+      </c>
+      <c r="AH52" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI52" s="4" t="n">
+        <v>172.6272</v>
+      </c>
+      <c r="AJ52" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK52" s="4" t="n">
+        <v>184.711104</v>
+      </c>
+      <c r="AL52" s="4" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AM52" s="4" t="inlineStr"/>
+      <c r="AN52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO52" s="4" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="AP52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ52" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AR52" s="4" t="inlineStr"/>
+      <c r="AS52" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT52" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU52" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV52" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AV42"/>
+  <autoFilter ref="A1:AV52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/telegram/aegis_daily_2026-08-06.xlsx
+++ b/reports/telegram/aegis_daily_2026-08-06.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AV$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AX$52</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV52"/>
+  <dimension ref="A1:AX52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -487,41 +487,43 @@
     <col width="8" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="50" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="50" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="60" customWidth="1" min="20" max="20"/>
-    <col width="34" customWidth="1" min="21" max="21"/>
-    <col width="13" customWidth="1" min="22" max="22"/>
-    <col width="11" customWidth="1" min="23" max="23"/>
-    <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="6" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="60" customWidth="1" min="22" max="22"/>
+    <col width="34" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
     <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="10" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
-    <col width="14" customWidth="1" min="29" max="29"/>
-    <col width="12" customWidth="1" min="30" max="30"/>
-    <col width="13" customWidth="1" min="31" max="31"/>
-    <col width="13" customWidth="1" min="32" max="32"/>
-    <col width="11" customWidth="1" min="33" max="33"/>
-    <col width="9" customWidth="1" min="34" max="34"/>
+    <col width="6" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="14" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="13" customWidth="1" min="33" max="33"/>
+    <col width="13" customWidth="1" min="34" max="34"/>
     <col width="11" customWidth="1" min="35" max="35"/>
-    <col width="8" customWidth="1" min="36" max="36"/>
+    <col width="9" customWidth="1" min="36" max="36"/>
     <col width="11" customWidth="1" min="37" max="37"/>
     <col width="8" customWidth="1" min="38" max="38"/>
-    <col width="13" customWidth="1" min="39" max="39"/>
-    <col width="15" customWidth="1" min="40" max="40"/>
-    <col width="12" customWidth="1" min="41" max="41"/>
-    <col width="11" customWidth="1" min="42" max="42"/>
-    <col width="16" customWidth="1" min="43" max="43"/>
-    <col width="32" customWidth="1" min="44" max="44"/>
-    <col width="20" customWidth="1" min="45" max="45"/>
-    <col width="18" customWidth="1" min="46" max="46"/>
-    <col width="17" customWidth="1" min="47" max="47"/>
-    <col width="20" customWidth="1" min="48" max="48"/>
+    <col width="11" customWidth="1" min="39" max="39"/>
+    <col width="8" customWidth="1" min="40" max="40"/>
+    <col width="13" customWidth="1" min="41" max="41"/>
+    <col width="15" customWidth="1" min="42" max="42"/>
+    <col width="12" customWidth="1" min="43" max="43"/>
+    <col width="11" customWidth="1" min="44" max="44"/>
+    <col width="16" customWidth="1" min="45" max="45"/>
+    <col width="32" customWidth="1" min="46" max="46"/>
+    <col width="20" customWidth="1" min="47" max="47"/>
+    <col width="18" customWidth="1" min="48" max="48"/>
+    <col width="17" customWidth="1" min="49" max="49"/>
+    <col width="20" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -592,175 +594,185 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>Risk Meter</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Sector Exposure %</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>Adj Conf</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Ctx Drag</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Ctx Reason</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Insider 90d</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Corr to Uni</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Turnover σ</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Alert</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Confidence %</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Conf Type</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Model Score</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Horizon (d)</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Days Left</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Current Price</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Entry Price</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Buy Zone Low</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Buy Zone High</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Stop Loss</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Risk %</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Target 1</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>T1 %</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Target 2</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>T2 %</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Today Move %</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Current Perf %</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Max Gain %</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Max DD %</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Lifecycle State</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>Top Drivers</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>Portfolio Weight %</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>Expected Alpha %</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Last Updated (UTC)</t>
         </is>
@@ -813,110 +825,116 @@
       </c>
       <c r="M2" s="4" t="inlineStr">
         <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="N2" s="4" t="n">
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O2" s="4" t="inlineStr"/>
+      <c r="P2" s="4" t="n">
         <v>36.6</v>
       </c>
-      <c r="O2" s="4" t="n">
+      <c r="Q2" s="4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="P2" s="4" t="inlineStr">
+      <c r="R2" s="4" t="inlineStr">
         <is>
           <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
-      <c r="Q2" s="4" t="inlineStr"/>
-      <c r="R2" s="4" t="inlineStr"/>
       <c r="S2" s="4" t="inlineStr"/>
-      <c r="T2" s="4" t="inlineStr">
-        <is>
-          <t>Rank ↑ 9→1 · Conf 39% · band WATCH · 10d left · → HOLD</t>
-        </is>
-      </c>
+      <c r="T2" s="4" t="inlineStr"/>
       <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="n">
+      <c r="V2" s="4" t="inlineStr">
+        <is>
+          <t>Rank ↑ 9→1 · Conf 39% · band WATCH→HOLD · 10d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="W2" s="4" t="inlineStr"/>
+      <c r="X2" s="4" t="n">
         <v>39.3</v>
       </c>
-      <c r="W2" s="4" t="inlineStr">
+      <c r="Y2" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X2" s="4" t="n">
+      <c r="Z2" s="4" t="n">
         <v>26.3</v>
       </c>
-      <c r="Y2" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z2" s="4" t="n">
+      <c r="AA2" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB2" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="AA2" s="4" t="n">
+      <c r="AC2" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AB2" s="4" t="inlineStr">
+      <c r="AD2" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="AC2" s="4" t="n">
+      <c r="AE2" s="4" t="n">
         <v>2452.2</v>
       </c>
-      <c r="AD2" s="4" t="n">
+      <c r="AF2" s="4" t="n">
         <v>2452.2</v>
       </c>
-      <c r="AE2" s="4" t="n">
+      <c r="AG2" s="4" t="n">
         <v>2427.68</v>
       </c>
-      <c r="AF2" s="4" t="n">
+      <c r="AH2" s="4" t="n">
         <v>2476.72</v>
       </c>
-      <c r="AG2" s="4" t="n">
+      <c r="AI2" s="4" t="n">
         <v>2329.59</v>
       </c>
-      <c r="AH2" s="4" t="n">
+      <c r="AJ2" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI2" s="4" t="n">
+      <c r="AK2" s="4" t="n">
         <v>2648.38</v>
       </c>
-      <c r="AJ2" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK2" s="4" t="n">
+      <c r="AL2" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM2" s="4" t="n">
         <v>2820.03</v>
       </c>
-      <c r="AL2" s="4" t="n">
+      <c r="AN2" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AM2" s="4" t="n">
+      <c r="AO2" s="4" t="n">
         <v>0.84</v>
       </c>
-      <c r="AN2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" s="4" t="inlineStr"/>
-      <c r="AP2" s="4" t="inlineStr"/>
-      <c r="AQ2" s="4" t="inlineStr">
+      <c r="AP2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" s="4" t="inlineStr"/>
+      <c r="AR2" s="4" t="inlineStr"/>
+      <c r="AS2" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AR2" s="4" t="inlineStr">
+      <c r="AT2" s="4" t="inlineStr">
         <is>
           <t>Quality · Mean Reversion · Ai Hybrid</t>
         </is>
       </c>
-      <c r="AS2" s="4" t="inlineStr"/>
-      <c r="AT2" s="4" t="inlineStr"/>
-      <c r="AU2" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV2" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AU2" s="4" t="inlineStr"/>
+      <c r="AV2" s="4" t="inlineStr"/>
+      <c r="AW2" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX2" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -970,107 +988,113 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N3" s="4" t="n">
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr"/>
+      <c r="P3" s="4" t="n">
         <v>37.8</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="Q3" s="4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr"/>
-      <c r="R3" s="4" t="inlineStr"/>
       <c r="S3" s="4" t="inlineStr"/>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="T3" s="4" t="inlineStr"/>
+      <c r="U3" s="4" t="inlineStr"/>
+      <c r="V3" s="4" t="inlineStr">
         <is>
           <t>Rank → 2→2 · Conf 41% · band HOLD · 10d left · → HOLD</t>
         </is>
       </c>
-      <c r="U3" s="4" t="inlineStr"/>
-      <c r="V3" s="4" t="n">
+      <c r="W3" s="4" t="inlineStr"/>
+      <c r="X3" s="4" t="n">
         <v>40.6</v>
       </c>
-      <c r="W3" s="4" t="inlineStr">
+      <c r="Y3" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="Z3" s="4" t="n">
         <v>26.2</v>
       </c>
-      <c r="Y3" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB3" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AC3" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AB3" s="4" t="inlineStr">
+      <c r="AD3" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="AC3" s="4" t="n">
+      <c r="AE3" s="4" t="n">
         <v>5196.6</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AF3" s="4" t="n">
         <v>5196.6</v>
       </c>
-      <c r="AE3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>5144.63</v>
       </c>
-      <c r="AF3" s="4" t="n">
+      <c r="AH3" s="4" t="n">
         <v>5248.57</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AI3" s="4" t="n">
         <v>4936.77</v>
       </c>
-      <c r="AH3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI3" s="4" t="n">
+      <c r="AK3" s="4" t="n">
         <v>5612.33</v>
       </c>
-      <c r="AJ3" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK3" s="4" t="n">
+      <c r="AL3" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM3" s="4" t="n">
         <v>5976.09</v>
       </c>
-      <c r="AL3" s="4" t="n">
+      <c r="AN3" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AM3" s="4" t="n">
+      <c r="AO3" s="4" t="n">
         <v>1.42</v>
       </c>
-      <c r="AN3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" s="4" t="inlineStr"/>
-      <c r="AP3" s="4" t="inlineStr"/>
-      <c r="AQ3" s="4" t="inlineStr">
+      <c r="AP3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="4" t="inlineStr"/>
+      <c r="AR3" s="4" t="inlineStr"/>
+      <c r="AS3" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AR3" s="4" t="inlineStr">
+      <c r="AT3" s="4" t="inlineStr">
         <is>
           <t>Quality · Growth · Ai Hybrid</t>
         </is>
       </c>
-      <c r="AS3" s="4" t="inlineStr"/>
-      <c r="AT3" s="4" t="inlineStr"/>
-      <c r="AU3" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV3" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AU3" s="4" t="inlineStr"/>
+      <c r="AV3" s="4" t="inlineStr"/>
+      <c r="AW3" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX3" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -1117,110 +1141,116 @@
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="n">
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr"/>
+      <c r="P4" s="4" t="n">
         <v>36.6</v>
       </c>
-      <c r="O4" s="4" t="n">
+      <c r="Q4" s="4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="P4" s="4" t="inlineStr">
+      <c r="R4" s="4" t="inlineStr">
         <is>
           <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
       <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr">
-        <is>
-          <t>Rank → 3→3 · Conf 39% · band WATCH · 54d left · → HOLD</t>
-        </is>
-      </c>
+      <c r="T4" s="4" t="inlineStr"/>
       <c r="U4" s="4" t="inlineStr"/>
-      <c r="V4" s="4" t="n">
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 3→3 · Conf 39% · band WATCH→HOLD · 54d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="inlineStr"/>
+      <c r="X4" s="4" t="n">
         <v>39.3</v>
       </c>
-      <c r="W4" s="4" t="inlineStr">
+      <c r="Y4" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X4" s="4" t="n">
+      <c r="Z4" s="4" t="n">
         <v>24.3</v>
       </c>
-      <c r="Y4" s="4" t="n">
+      <c r="AA4" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="Z4" s="4" t="n">
+      <c r="AB4" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="AA4" s="4" t="n">
+      <c r="AC4" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="AB4" s="4" t="inlineStr">
+      <c r="AD4" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="AC4" s="4" t="n">
+      <c r="AE4" s="4" t="n">
         <v>133.14</v>
       </c>
-      <c r="AD4" s="4" t="n">
+      <c r="AF4" s="4" t="n">
         <v>133.14</v>
       </c>
-      <c r="AE4" s="4" t="n">
+      <c r="AG4" s="4" t="n">
         <v>131.81</v>
       </c>
-      <c r="AF4" s="4" t="n">
+      <c r="AH4" s="4" t="n">
         <v>134.47</v>
       </c>
-      <c r="AG4" s="4" t="n">
+      <c r="AI4" s="4" t="n">
         <v>126.48</v>
       </c>
-      <c r="AH4" s="4" t="n">
+      <c r="AJ4" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI4" s="4" t="n">
+      <c r="AK4" s="4" t="n">
         <v>143.79</v>
       </c>
-      <c r="AJ4" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK4" s="4" t="n">
+      <c r="AL4" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM4" s="4" t="n">
         <v>153.11</v>
       </c>
-      <c r="AL4" s="4" t="n">
+      <c r="AN4" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AM4" s="4" t="n">
+      <c r="AO4" s="4" t="n">
         <v>1.33</v>
       </c>
-      <c r="AN4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO4" s="4" t="inlineStr"/>
-      <c r="AP4" s="4" t="inlineStr"/>
-      <c r="AQ4" s="4" t="inlineStr">
+      <c r="AP4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="4" t="inlineStr"/>
+      <c r="AR4" s="4" t="inlineStr"/>
+      <c r="AS4" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AR4" s="4" t="inlineStr">
+      <c r="AT4" s="4" t="inlineStr">
         <is>
           <t>Quality · Momentum · Ai Hybrid</t>
         </is>
       </c>
-      <c r="AS4" s="4" t="inlineStr"/>
-      <c r="AT4" s="4" t="inlineStr"/>
-      <c r="AU4" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV4" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AU4" s="4" t="inlineStr"/>
+      <c r="AV4" s="4" t="inlineStr"/>
+      <c r="AW4" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX4" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -1270,107 +1300,113 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N5" s="4" t="n">
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr"/>
+      <c r="P5" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="O5" s="4" t="n">
+      <c r="Q5" s="4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="P5" s="4" t="inlineStr">
+      <c r="R5" s="4" t="inlineStr">
         <is>
           <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
-      <c r="Q5" s="4" t="inlineStr"/>
-      <c r="R5" s="4" t="inlineStr"/>
       <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr">
+      <c r="T5" s="4" t="inlineStr"/>
+      <c r="U5" s="4" t="inlineStr"/>
+      <c r="V5" s="4" t="inlineStr">
         <is>
           <t>Rank → 4→4 · Conf 41% · band HOLD · 54d left · → HOLD</t>
         </is>
       </c>
-      <c r="U5" s="4" t="inlineStr"/>
-      <c r="V5" s="4" t="n">
+      <c r="W5" s="4" t="inlineStr"/>
+      <c r="X5" s="4" t="n">
         <v>40.7</v>
       </c>
-      <c r="W5" s="4" t="inlineStr">
+      <c r="Y5" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X5" s="4" t="n">
+      <c r="Z5" s="4" t="n">
         <v>23.8</v>
       </c>
-      <c r="Y5" s="4" t="n">
+      <c r="AA5" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="Z5" s="4" t="n">
+      <c r="AB5" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="AA5" s="4" t="n">
+      <c r="AC5" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="AB5" s="4" t="inlineStr">
+      <c r="AD5" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="AC5" s="4" t="n">
+      <c r="AE5" s="4" t="n">
         <v>5524</v>
       </c>
-      <c r="AD5" s="4" t="n">
+      <c r="AF5" s="4" t="n">
         <v>5524</v>
       </c>
-      <c r="AE5" s="4" t="n">
+      <c r="AG5" s="4" t="n">
         <v>5468.76</v>
       </c>
-      <c r="AF5" s="4" t="n">
+      <c r="AH5" s="4" t="n">
         <v>5579.24</v>
       </c>
-      <c r="AG5" s="4" t="n">
+      <c r="AI5" s="4" t="n">
         <v>5247.8</v>
       </c>
-      <c r="AH5" s="4" t="n">
+      <c r="AJ5" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI5" s="4" t="n">
+      <c r="AK5" s="4" t="n">
         <v>5965.92</v>
       </c>
-      <c r="AJ5" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK5" s="4" t="n">
+      <c r="AL5" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM5" s="4" t="n">
         <v>6352.6</v>
       </c>
-      <c r="AL5" s="4" t="n">
+      <c r="AN5" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AM5" s="4" t="n">
+      <c r="AO5" s="4" t="n">
         <v>0.26</v>
       </c>
-      <c r="AN5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO5" s="4" t="inlineStr"/>
-      <c r="AP5" s="4" t="inlineStr"/>
-      <c r="AQ5" s="4" t="inlineStr">
+      <c r="AP5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="4" t="inlineStr"/>
+      <c r="AR5" s="4" t="inlineStr"/>
+      <c r="AS5" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AR5" s="4" t="inlineStr">
+      <c r="AT5" s="4" t="inlineStr">
         <is>
           <t>Trend · Growth · Value</t>
         </is>
       </c>
-      <c r="AS5" s="4" t="inlineStr"/>
-      <c r="AT5" s="4" t="inlineStr"/>
-      <c r="AU5" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV5" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AU5" s="4" t="inlineStr"/>
+      <c r="AV5" s="4" t="inlineStr"/>
+      <c r="AW5" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX5" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -1424,107 +1460,113 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N6" s="4" t="n">
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr"/>
+      <c r="P6" s="4" t="n">
         <v>40.4</v>
       </c>
-      <c r="O6" s="4" t="n">
+      <c r="Q6" s="4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="P6" s="4" t="inlineStr">
+      <c r="R6" s="4" t="inlineStr">
         <is>
           <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
       <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr">
+      <c r="T6" s="4" t="inlineStr"/>
+      <c r="U6" s="4" t="inlineStr"/>
+      <c r="V6" s="4" t="inlineStr">
         <is>
           <t>Rank ↑ 8→5 · Conf 43% · band HOLD · 10d left · → HOLD</t>
         </is>
       </c>
-      <c r="U6" s="4" t="inlineStr"/>
-      <c r="V6" s="4" t="n">
+      <c r="W6" s="4" t="inlineStr"/>
+      <c r="X6" s="4" t="n">
         <v>43.1</v>
       </c>
-      <c r="W6" s="4" t="inlineStr">
+      <c r="Y6" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X6" s="4" t="n">
+      <c r="Z6" s="4" t="n">
         <v>23.8</v>
       </c>
-      <c r="Y6" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z6" s="4" t="n">
+      <c r="AA6" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB6" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="AA6" s="4" t="n">
+      <c r="AC6" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AB6" s="4" t="inlineStr">
+      <c r="AD6" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="AC6" s="4" t="n">
+      <c r="AE6" s="4" t="n">
         <v>1346.6</v>
       </c>
-      <c r="AD6" s="4" t="n">
+      <c r="AF6" s="4" t="n">
         <v>1346.6</v>
       </c>
-      <c r="AE6" s="4" t="n">
+      <c r="AG6" s="4" t="n">
         <v>1333.13</v>
       </c>
-      <c r="AF6" s="4" t="n">
+      <c r="AH6" s="4" t="n">
         <v>1360.07</v>
       </c>
-      <c r="AG6" s="4" t="n">
+      <c r="AI6" s="4" t="n">
         <v>1279.27</v>
       </c>
-      <c r="AH6" s="4" t="n">
+      <c r="AJ6" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI6" s="4" t="n">
+      <c r="AK6" s="4" t="n">
         <v>1454.33</v>
       </c>
-      <c r="AJ6" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK6" s="4" t="n">
+      <c r="AL6" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM6" s="4" t="n">
         <v>1548.59</v>
       </c>
-      <c r="AL6" s="4" t="n">
+      <c r="AN6" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AM6" s="4" t="n">
+      <c r="AO6" s="4" t="n">
         <v>0.46</v>
       </c>
-      <c r="AN6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO6" s="4" t="inlineStr"/>
-      <c r="AP6" s="4" t="inlineStr"/>
-      <c r="AQ6" s="4" t="inlineStr">
+      <c r="AP6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="4" t="inlineStr"/>
+      <c r="AR6" s="4" t="inlineStr"/>
+      <c r="AS6" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AR6" s="4" t="inlineStr">
+      <c r="AT6" s="4" t="inlineStr">
         <is>
           <t>Quality · Mean Reversion · Momentum</t>
         </is>
       </c>
-      <c r="AS6" s="4" t="inlineStr"/>
-      <c r="AT6" s="4" t="inlineStr"/>
-      <c r="AU6" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV6" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AU6" s="4" t="inlineStr"/>
+      <c r="AV6" s="4" t="inlineStr"/>
+      <c r="AW6" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX6" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -1574,107 +1616,113 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N7" s="4" t="n">
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr"/>
+      <c r="P7" s="4" t="n">
         <v>43.6</v>
       </c>
-      <c r="O7" s="4" t="n">
+      <c r="Q7" s="4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="P7" s="4" t="inlineStr">
+      <c r="R7" s="4" t="inlineStr">
         <is>
           <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
-      <c r="Q7" s="4" t="inlineStr"/>
-      <c r="R7" s="4" t="inlineStr"/>
       <c r="S7" s="4" t="inlineStr"/>
-      <c r="T7" s="4" t="inlineStr">
+      <c r="T7" s="4" t="inlineStr"/>
+      <c r="U7" s="4" t="inlineStr"/>
+      <c r="V7" s="4" t="inlineStr">
         <is>
           <t>Rank → 6→6 · Conf 46% · band HOLD · 11d left · → HOLD</t>
         </is>
       </c>
-      <c r="U7" s="4" t="inlineStr"/>
-      <c r="V7" s="4" t="n">
+      <c r="W7" s="4" t="inlineStr"/>
+      <c r="X7" s="4" t="n">
         <v>46.4</v>
       </c>
-      <c r="W7" s="4" t="inlineStr">
+      <c r="Y7" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X7" s="4" t="n">
+      <c r="Z7" s="4" t="n">
         <v>23.8</v>
       </c>
-      <c r="Y7" s="4" t="n">
+      <c r="AA7" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="Z7" s="4" t="n">
+      <c r="AB7" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="AA7" s="4" t="n">
+      <c r="AC7" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="AB7" s="4" t="inlineStr">
+      <c r="AD7" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="AC7" s="4" t="n">
+      <c r="AE7" s="4" t="n">
         <v>11602</v>
       </c>
-      <c r="AD7" s="4" t="n">
+      <c r="AF7" s="4" t="n">
         <v>11602</v>
       </c>
-      <c r="AE7" s="4" t="n">
+      <c r="AG7" s="4" t="n">
         <v>11485.98</v>
       </c>
-      <c r="AF7" s="4" t="n">
+      <c r="AH7" s="4" t="n">
         <v>11718.02</v>
       </c>
-      <c r="AG7" s="4" t="n">
+      <c r="AI7" s="4" t="n">
         <v>11021.9</v>
       </c>
-      <c r="AH7" s="4" t="n">
+      <c r="AJ7" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI7" s="4" t="n">
+      <c r="AK7" s="4" t="n">
         <v>12530.16</v>
       </c>
-      <c r="AJ7" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK7" s="4" t="n">
+      <c r="AL7" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM7" s="4" t="n">
         <v>13342.3</v>
       </c>
-      <c r="AL7" s="4" t="n">
+      <c r="AN7" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AM7" s="4" t="n">
+      <c r="AO7" s="4" t="n">
         <v>0.99</v>
       </c>
-      <c r="AN7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO7" s="4" t="inlineStr"/>
-      <c r="AP7" s="4" t="inlineStr"/>
-      <c r="AQ7" s="4" t="inlineStr">
+      <c r="AP7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="4" t="inlineStr"/>
+      <c r="AR7" s="4" t="inlineStr"/>
+      <c r="AS7" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AR7" s="4" t="inlineStr">
+      <c r="AT7" s="4" t="inlineStr">
         <is>
           <t>Quality · Growth · Momentum</t>
         </is>
       </c>
-      <c r="AS7" s="4" t="inlineStr"/>
-      <c r="AT7" s="4" t="inlineStr"/>
-      <c r="AU7" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV7" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AU7" s="4" t="inlineStr"/>
+      <c r="AV7" s="4" t="inlineStr"/>
+      <c r="AW7" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX7" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -1724,107 +1772,113 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N8" s="4" t="n">
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr"/>
+      <c r="P8" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="O8" s="4" t="n">
+      <c r="Q8" s="4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="P8" s="4" t="inlineStr">
+      <c r="R8" s="4" t="inlineStr">
         <is>
           <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
-      <c r="Q8" s="4" t="inlineStr"/>
-      <c r="R8" s="4" t="inlineStr"/>
       <c r="S8" s="4" t="inlineStr"/>
-      <c r="T8" s="4" t="inlineStr">
+      <c r="T8" s="4" t="inlineStr"/>
+      <c r="U8" s="4" t="inlineStr"/>
+      <c r="V8" s="4" t="inlineStr">
         <is>
           <t>Rank → 7→7 · Conf 41% · band HOLD · 54d left · → HOLD</t>
         </is>
       </c>
-      <c r="U8" s="4" t="inlineStr"/>
-      <c r="V8" s="4" t="n">
+      <c r="W8" s="4" t="inlineStr"/>
+      <c r="X8" s="4" t="n">
         <v>40.7</v>
       </c>
-      <c r="W8" s="4" t="inlineStr">
+      <c r="Y8" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X8" s="4" t="n">
+      <c r="Z8" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="Y8" s="4" t="n">
+      <c r="AA8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="Z8" s="4" t="n">
+      <c r="AB8" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="AA8" s="4" t="n">
+      <c r="AC8" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="AB8" s="4" t="inlineStr">
+      <c r="AD8" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="AC8" s="4" t="n">
+      <c r="AE8" s="4" t="n">
         <v>1158</v>
       </c>
-      <c r="AD8" s="4" t="n">
+      <c r="AF8" s="4" t="n">
         <v>1158</v>
       </c>
-      <c r="AE8" s="4" t="n">
+      <c r="AG8" s="4" t="n">
         <v>1146.42</v>
       </c>
-      <c r="AF8" s="4" t="n">
+      <c r="AH8" s="4" t="n">
         <v>1169.58</v>
       </c>
-      <c r="AG8" s="4" t="n">
+      <c r="AI8" s="4" t="n">
         <v>1100.1</v>
       </c>
-      <c r="AH8" s="4" t="n">
+      <c r="AJ8" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI8" s="4" t="n">
+      <c r="AK8" s="4" t="n">
         <v>1250.64</v>
       </c>
-      <c r="AJ8" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK8" s="4" t="n">
+      <c r="AL8" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM8" s="4" t="n">
         <v>1331.7</v>
       </c>
-      <c r="AL8" s="4" t="n">
+      <c r="AN8" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AM8" s="4" t="n">
+      <c r="AO8" s="4" t="n">
         <v>0.21</v>
       </c>
-      <c r="AN8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO8" s="4" t="inlineStr"/>
-      <c r="AP8" s="4" t="inlineStr"/>
-      <c r="AQ8" s="4" t="inlineStr">
+      <c r="AP8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="4" t="inlineStr"/>
+      <c r="AR8" s="4" t="inlineStr"/>
+      <c r="AS8" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AR8" s="4" t="inlineStr">
+      <c r="AT8" s="4" t="inlineStr">
         <is>
           <t>Mean Reversion · Quality · Momentum</t>
         </is>
       </c>
-      <c r="AS8" s="4" t="inlineStr"/>
-      <c r="AT8" s="4" t="inlineStr"/>
-      <c r="AU8" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV8" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AU8" s="4" t="inlineStr"/>
+      <c r="AV8" s="4" t="inlineStr"/>
+      <c r="AW8" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX8" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -1875,110 +1929,116 @@
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="N9" s="4" t="n">
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr"/>
+      <c r="P9" s="4" t="n">
         <v>35.6</v>
       </c>
-      <c r="O9" s="4" t="n">
+      <c r="Q9" s="4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="P9" s="4" t="inlineStr">
+      <c r="R9" s="4" t="inlineStr">
         <is>
           <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
-      <c r="Q9" s="4" t="inlineStr"/>
-      <c r="R9" s="4" t="inlineStr"/>
       <c r="S9" s="4" t="inlineStr"/>
-      <c r="T9" s="4" t="inlineStr">
-        <is>
-          <t>Rank ↓ 3→8 · Conf 38% · band WATCH · 53d left · → HOLD</t>
-        </is>
-      </c>
+      <c r="T9" s="4" t="inlineStr"/>
       <c r="U9" s="4" t="inlineStr"/>
-      <c r="V9" s="4" t="n">
+      <c r="V9" s="4" t="inlineStr">
+        <is>
+          <t>Rank ↓ 3→8 · Conf 38% · band WATCH→HOLD · 53d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="W9" s="4" t="inlineStr"/>
+      <c r="X9" s="4" t="n">
         <v>38.3</v>
       </c>
-      <c r="W9" s="4" t="inlineStr">
+      <c r="Y9" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X9" s="4" t="n">
+      <c r="Z9" s="4" t="n">
         <v>22.4</v>
       </c>
-      <c r="Y9" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z9" s="4" t="n">
+      <c r="AA9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB9" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="AA9" s="4" t="n">
+      <c r="AC9" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="AB9" s="4" t="inlineStr">
+      <c r="AD9" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="AC9" s="4" t="n">
+      <c r="AE9" s="4" t="n">
         <v>449.35</v>
       </c>
-      <c r="AD9" s="4" t="n">
+      <c r="AF9" s="4" t="n">
         <v>449.35</v>
       </c>
-      <c r="AE9" s="4" t="n">
+      <c r="AG9" s="4" t="n">
         <v>444.86</v>
       </c>
-      <c r="AF9" s="4" t="n">
+      <c r="AH9" s="4" t="n">
         <v>453.84</v>
       </c>
-      <c r="AG9" s="4" t="n">
+      <c r="AI9" s="4" t="n">
         <v>426.88</v>
       </c>
-      <c r="AH9" s="4" t="n">
+      <c r="AJ9" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI9" s="4" t="n">
+      <c r="AK9" s="4" t="n">
         <v>485.3</v>
       </c>
-      <c r="AJ9" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK9" s="4" t="n">
+      <c r="AL9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM9" s="4" t="n">
         <v>516.75</v>
       </c>
-      <c r="AL9" s="4" t="n">
+      <c r="AN9" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AM9" s="4" t="n">
+      <c r="AO9" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="AN9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO9" s="4" t="inlineStr"/>
-      <c r="AP9" s="4" t="inlineStr"/>
-      <c r="AQ9" s="4" t="inlineStr">
+      <c r="AP9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="4" t="inlineStr"/>
+      <c r="AR9" s="4" t="inlineStr"/>
+      <c r="AS9" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AR9" s="4" t="inlineStr">
+      <c r="AT9" s="4" t="inlineStr">
         <is>
           <t>Value · Mean Reversion · Growth</t>
         </is>
       </c>
-      <c r="AS9" s="4" t="inlineStr"/>
-      <c r="AT9" s="4" t="inlineStr"/>
-      <c r="AU9" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV9" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AU9" s="4" t="inlineStr"/>
+      <c r="AV9" s="4" t="inlineStr"/>
+      <c r="AW9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX9" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -2029,110 +2089,116 @@
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="N10" s="4" t="n">
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O10" s="4" t="inlineStr"/>
+      <c r="P10" s="4" t="n">
         <v>35.6</v>
       </c>
-      <c r="O10" s="4" t="n">
+      <c r="Q10" s="4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="P10" s="4" t="inlineStr">
+      <c r="R10" s="4" t="inlineStr">
         <is>
           <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
-      <c r="Q10" s="4" t="inlineStr"/>
-      <c r="R10" s="4" t="inlineStr"/>
       <c r="S10" s="4" t="inlineStr"/>
-      <c r="T10" s="4" t="inlineStr">
-        <is>
-          <t>Rank ↓ 7→9 · Conf 38% · band WATCH · 53d left · → HOLD</t>
-        </is>
-      </c>
+      <c r="T10" s="4" t="inlineStr"/>
       <c r="U10" s="4" t="inlineStr"/>
-      <c r="V10" s="4" t="n">
+      <c r="V10" s="4" t="inlineStr">
+        <is>
+          <t>Rank ↓ 7→9 · Conf 38% · band WATCH→HOLD · 53d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="W10" s="4" t="inlineStr"/>
+      <c r="X10" s="4" t="n">
         <v>38.3</v>
       </c>
-      <c r="W10" s="4" t="inlineStr">
+      <c r="Y10" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X10" s="4" t="n">
+      <c r="Z10" s="4" t="n">
         <v>21.6</v>
       </c>
-      <c r="Y10" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z10" s="4" t="n">
+      <c r="AA10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB10" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="AA10" s="4" t="n">
+      <c r="AC10" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="AB10" s="4" t="inlineStr">
+      <c r="AD10" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="AC10" s="4" t="n">
+      <c r="AE10" s="4" t="n">
         <v>287.2</v>
       </c>
-      <c r="AD10" s="4" t="n">
+      <c r="AF10" s="4" t="n">
         <v>287.2</v>
       </c>
-      <c r="AE10" s="4" t="n">
+      <c r="AG10" s="4" t="n">
         <v>284.33</v>
       </c>
-      <c r="AF10" s="4" t="n">
+      <c r="AH10" s="4" t="n">
         <v>290.07</v>
       </c>
-      <c r="AG10" s="4" t="n">
+      <c r="AI10" s="4" t="n">
         <v>272.84</v>
       </c>
-      <c r="AH10" s="4" t="n">
+      <c r="AJ10" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI10" s="4" t="n">
+      <c r="AK10" s="4" t="n">
         <v>310.18</v>
       </c>
-      <c r="AJ10" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK10" s="4" t="n">
+      <c r="AL10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM10" s="4" t="n">
         <v>330.28</v>
       </c>
-      <c r="AL10" s="4" t="n">
+      <c r="AN10" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AM10" s="4" t="n">
+      <c r="AO10" s="4" t="n">
         <v>1.46</v>
       </c>
-      <c r="AN10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO10" s="4" t="inlineStr"/>
-      <c r="AP10" s="4" t="inlineStr"/>
-      <c r="AQ10" s="4" t="inlineStr">
+      <c r="AP10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="4" t="inlineStr"/>
+      <c r="AR10" s="4" t="inlineStr"/>
+      <c r="AS10" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AR10" s="4" t="inlineStr">
+      <c r="AT10" s="4" t="inlineStr">
         <is>
           <t>Quality · Mean Reversion · Value</t>
         </is>
       </c>
-      <c r="AS10" s="4" t="inlineStr"/>
-      <c r="AT10" s="4" t="inlineStr"/>
-      <c r="AU10" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV10" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AU10" s="4" t="inlineStr"/>
+      <c r="AV10" s="4" t="inlineStr"/>
+      <c r="AW10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX10" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -2182,107 +2248,113 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N11" s="4" t="n">
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="inlineStr"/>
+      <c r="P11" s="4" t="n">
         <v>35.6</v>
       </c>
-      <c r="O11" s="4" t="n">
+      <c r="Q11" s="4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="P11" s="4" t="inlineStr">
+      <c r="R11" s="4" t="inlineStr">
         <is>
           <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
-      <c r="Q11" s="4" t="inlineStr"/>
-      <c r="R11" s="4" t="inlineStr"/>
       <c r="S11" s="4" t="inlineStr"/>
-      <c r="T11" s="4" t="inlineStr">
+      <c r="T11" s="4" t="inlineStr"/>
+      <c r="U11" s="4" t="inlineStr"/>
+      <c r="V11" s="4" t="inlineStr">
         <is>
           <t>Rank → 10→10 · Conf 38% · band HOLD · 10d left · → HOLD</t>
         </is>
       </c>
-      <c r="U11" s="4" t="inlineStr"/>
-      <c r="V11" s="4" t="n">
+      <c r="W11" s="4" t="inlineStr"/>
+      <c r="X11" s="4" t="n">
         <v>38.3</v>
       </c>
-      <c r="W11" s="4" t="inlineStr">
+      <c r="Y11" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X11" s="4" t="n">
+      <c r="Z11" s="4" t="n">
         <v>20.7</v>
       </c>
-      <c r="Y11" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z11" s="4" t="n">
+      <c r="AA11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB11" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="AA11" s="4" t="n">
+      <c r="AC11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AB11" s="4" t="inlineStr">
+      <c r="AD11" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="AC11" s="4" t="n">
+      <c r="AE11" s="4" t="n">
         <v>10880</v>
       </c>
-      <c r="AD11" s="4" t="n">
+      <c r="AF11" s="4" t="n">
         <v>10880</v>
       </c>
-      <c r="AE11" s="4" t="n">
+      <c r="AG11" s="4" t="n">
         <v>10771.2</v>
       </c>
-      <c r="AF11" s="4" t="n">
+      <c r="AH11" s="4" t="n">
         <v>10988.8</v>
       </c>
-      <c r="AG11" s="4" t="n">
+      <c r="AI11" s="4" t="n">
         <v>10336</v>
       </c>
-      <c r="AH11" s="4" t="n">
+      <c r="AJ11" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI11" s="4" t="n">
+      <c r="AK11" s="4" t="n">
         <v>11750.4</v>
       </c>
-      <c r="AJ11" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK11" s="4" t="n">
+      <c r="AL11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM11" s="4" t="n">
         <v>12512</v>
       </c>
-      <c r="AL11" s="4" t="n">
+      <c r="AN11" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AM11" s="4" t="n">
+      <c r="AO11" s="4" t="n">
         <v>-0.55</v>
       </c>
-      <c r="AN11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO11" s="4" t="inlineStr"/>
-      <c r="AP11" s="4" t="inlineStr"/>
-      <c r="AQ11" s="4" t="inlineStr">
+      <c r="AP11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="4" t="inlineStr"/>
+      <c r="AR11" s="4" t="inlineStr"/>
+      <c r="AS11" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AR11" s="4" t="inlineStr">
+      <c r="AT11" s="4" t="inlineStr">
         <is>
           <t>Value · Quality · Trend</t>
         </is>
       </c>
-      <c r="AS11" s="4" t="inlineStr"/>
-      <c r="AT11" s="4" t="inlineStr"/>
-      <c r="AU11" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV11" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AU11" s="4" t="inlineStr"/>
+      <c r="AV11" s="4" t="inlineStr"/>
+      <c r="AW11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX11" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -2333,110 +2405,116 @@
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="N12" s="4" t="n">
+          <t>WEAK</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>🟡</t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="inlineStr"/>
+      <c r="P12" s="4" t="n">
         <v>22.1</v>
       </c>
-      <c r="O12" s="4" t="n">
+      <c r="Q12" s="4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="P12" s="4" t="inlineStr">
+      <c r="R12" s="4" t="inlineStr">
         <is>
           <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
-      <c r="Q12" s="4" t="inlineStr"/>
-      <c r="R12" s="4" t="inlineStr"/>
       <c r="S12" s="4" t="inlineStr"/>
-      <c r="T12" s="4" t="inlineStr">
-        <is>
-          <t>Rank ↑ 12→11 · Conf 25% · band REVIEW · 10d left · → HOLD</t>
-        </is>
-      </c>
+      <c r="T12" s="4" t="inlineStr"/>
       <c r="U12" s="4" t="inlineStr"/>
-      <c r="V12" s="4" t="n">
+      <c r="V12" s="4" t="inlineStr">
+        <is>
+          <t>Rank ↑ 12→11 · Conf 25% · band REVIEW→WEAK · 10d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="W12" s="4" t="inlineStr"/>
+      <c r="X12" s="4" t="n">
         <v>24.8</v>
       </c>
-      <c r="W12" s="4" t="inlineStr">
+      <c r="Y12" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X12" s="4" t="n">
+      <c r="Z12" s="4" t="n">
         <v>-26.6</v>
       </c>
-      <c r="Y12" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z12" s="4" t="n">
+      <c r="AA12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB12" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="AA12" s="4" t="n">
+      <c r="AC12" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AB12" s="4" t="inlineStr">
+      <c r="AD12" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="AC12" s="4" t="n">
+      <c r="AE12" s="4" t="n">
         <v>952.55</v>
       </c>
-      <c r="AD12" s="4" t="n">
+      <c r="AF12" s="4" t="n">
         <v>952.55</v>
       </c>
-      <c r="AE12" s="4" t="n">
+      <c r="AG12" s="4" t="n">
         <v>943.02</v>
       </c>
-      <c r="AF12" s="4" t="n">
+      <c r="AH12" s="4" t="n">
         <v>962.08</v>
       </c>
-      <c r="AG12" s="4" t="n">
+      <c r="AI12" s="4" t="n">
         <v>904.92</v>
       </c>
-      <c r="AH12" s="4" t="n">
+      <c r="AJ12" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI12" s="4" t="n">
+      <c r="AK12" s="4" t="n">
         <v>1028.75</v>
       </c>
-      <c r="AJ12" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK12" s="4" t="n">
+      <c r="AL12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM12" s="4" t="n">
         <v>1095.43</v>
       </c>
-      <c r="AL12" s="4" t="n">
+      <c r="AN12" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AM12" s="4" t="n">
+      <c r="AO12" s="4" t="n">
         <v>-0.76</v>
       </c>
-      <c r="AN12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO12" s="4" t="inlineStr"/>
-      <c r="AP12" s="4" t="inlineStr"/>
-      <c r="AQ12" s="4" t="inlineStr">
+      <c r="AP12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="4" t="inlineStr"/>
+      <c r="AR12" s="4" t="inlineStr"/>
+      <c r="AS12" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AR12" s="4" t="inlineStr">
+      <c r="AT12" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
-      <c r="AS12" s="4" t="inlineStr"/>
-      <c r="AT12" s="4" t="inlineStr"/>
-      <c r="AU12" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV12" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AU12" s="4" t="inlineStr"/>
+      <c r="AV12" s="4" t="inlineStr"/>
+      <c r="AW12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX12" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -2487,110 +2565,116 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="N13" s="4" t="n">
+          <t>WEAK</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>🟡</t>
+        </is>
+      </c>
+      <c r="O13" s="4" t="inlineStr"/>
+      <c r="P13" s="4" t="n">
         <v>27.2</v>
       </c>
-      <c r="O13" s="4" t="n">
+      <c r="Q13" s="4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="P13" s="4" t="inlineStr">
+      <c r="R13" s="4" t="inlineStr">
         <is>
           <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
-      <c r="Q13" s="4" t="inlineStr"/>
-      <c r="R13" s="4" t="inlineStr"/>
       <c r="S13" s="4" t="inlineStr"/>
-      <c r="T13" s="4" t="inlineStr">
-        <is>
-          <t>Rank ↓ 11→12 · Conf 30% · band REVIEW · 10d left · → HOLD</t>
-        </is>
-      </c>
+      <c r="T13" s="4" t="inlineStr"/>
       <c r="U13" s="4" t="inlineStr"/>
-      <c r="V13" s="4" t="n">
+      <c r="V13" s="4" t="inlineStr">
+        <is>
+          <t>Rank ↓ 11→12 · Conf 30% · band REVIEW→WEAK · 10d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="W13" s="4" t="inlineStr"/>
+      <c r="X13" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="W13" s="4" t="inlineStr">
+      <c r="Y13" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X13" s="4" t="n">
+      <c r="Z13" s="4" t="n">
         <v>-28.1</v>
       </c>
-      <c r="Y13" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z13" s="4" t="n">
+      <c r="AA13" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB13" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="AA13" s="4" t="n">
+      <c r="AC13" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AB13" s="4" t="inlineStr">
+      <c r="AD13" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="AC13" s="4" t="n">
+      <c r="AE13" s="4" t="n">
         <v>431.4</v>
       </c>
-      <c r="AD13" s="4" t="n">
+      <c r="AF13" s="4" t="n">
         <v>431.4</v>
       </c>
-      <c r="AE13" s="4" t="n">
+      <c r="AG13" s="4" t="n">
         <v>427.09</v>
       </c>
-      <c r="AF13" s="4" t="n">
+      <c r="AH13" s="4" t="n">
         <v>435.71</v>
       </c>
-      <c r="AG13" s="4" t="n">
+      <c r="AI13" s="4" t="n">
         <v>409.83</v>
       </c>
-      <c r="AH13" s="4" t="n">
+      <c r="AJ13" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI13" s="4" t="n">
+      <c r="AK13" s="4" t="n">
         <v>465.91</v>
       </c>
-      <c r="AJ13" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK13" s="4" t="n">
+      <c r="AL13" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM13" s="4" t="n">
         <v>496.11</v>
       </c>
-      <c r="AL13" s="4" t="n">
+      <c r="AN13" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AM13" s="4" t="n">
+      <c r="AO13" s="4" t="n">
         <v>-0.72</v>
       </c>
-      <c r="AN13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO13" s="4" t="inlineStr"/>
-      <c r="AP13" s="4" t="inlineStr"/>
-      <c r="AQ13" s="4" t="inlineStr">
+      <c r="AP13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="4" t="inlineStr"/>
+      <c r="AR13" s="4" t="inlineStr"/>
+      <c r="AS13" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AR13" s="4" t="inlineStr">
+      <c r="AT13" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
-      <c r="AS13" s="4" t="inlineStr"/>
-      <c r="AT13" s="4" t="inlineStr"/>
-      <c r="AU13" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV13" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AU13" s="4" t="inlineStr"/>
+      <c r="AV13" s="4" t="inlineStr"/>
+      <c r="AW13" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX13" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -2637,110 +2721,116 @@
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="N14" s="4" t="n">
+          <t>WEAK</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>🟡</t>
+        </is>
+      </c>
+      <c r="O14" s="4" t="inlineStr"/>
+      <c r="P14" s="4" t="n">
         <v>27.2</v>
       </c>
-      <c r="O14" s="4" t="n">
+      <c r="Q14" s="4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="P14" s="4" t="inlineStr">
+      <c r="R14" s="4" t="inlineStr">
         <is>
           <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
-      <c r="Q14" s="4" t="inlineStr"/>
-      <c r="R14" s="4" t="inlineStr"/>
       <c r="S14" s="4" t="inlineStr"/>
-      <c r="T14" s="4" t="inlineStr">
-        <is>
-          <t>Rank → 13→13 · Conf 30% · band REVIEW · 54d left · → HOLD</t>
-        </is>
-      </c>
+      <c r="T14" s="4" t="inlineStr"/>
       <c r="U14" s="4" t="inlineStr"/>
-      <c r="V14" s="4" t="n">
+      <c r="V14" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 13→13 · Conf 30% · band REVIEW→WEAK · 54d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="W14" s="4" t="inlineStr"/>
+      <c r="X14" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="W14" s="4" t="inlineStr">
+      <c r="Y14" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X14" s="4" t="n">
+      <c r="Z14" s="4" t="n">
         <v>-28.4</v>
       </c>
-      <c r="Y14" s="4" t="n">
+      <c r="AA14" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="Z14" s="4" t="n">
+      <c r="AB14" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="AA14" s="4" t="n">
+      <c r="AC14" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="AB14" s="4" t="inlineStr">
+      <c r="AD14" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="AC14" s="4" t="n">
+      <c r="AE14" s="4" t="n">
         <v>2157.8</v>
       </c>
-      <c r="AD14" s="4" t="n">
+      <c r="AF14" s="4" t="n">
         <v>2157.8</v>
       </c>
-      <c r="AE14" s="4" t="n">
+      <c r="AG14" s="4" t="n">
         <v>2136.22</v>
       </c>
-      <c r="AF14" s="4" t="n">
+      <c r="AH14" s="4" t="n">
         <v>2179.38</v>
       </c>
-      <c r="AG14" s="4" t="n">
+      <c r="AI14" s="4" t="n">
         <v>2049.91</v>
       </c>
-      <c r="AH14" s="4" t="n">
+      <c r="AJ14" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI14" s="4" t="n">
+      <c r="AK14" s="4" t="n">
         <v>2330.42</v>
       </c>
-      <c r="AJ14" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK14" s="4" t="n">
+      <c r="AL14" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM14" s="4" t="n">
         <v>2481.47</v>
       </c>
-      <c r="AL14" s="4" t="n">
+      <c r="AN14" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AM14" s="4" t="n">
+      <c r="AO14" s="4" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AN14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO14" s="4" t="inlineStr"/>
-      <c r="AP14" s="4" t="inlineStr"/>
-      <c r="AQ14" s="4" t="inlineStr">
+      <c r="AP14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="4" t="inlineStr"/>
+      <c r="AR14" s="4" t="inlineStr"/>
+      <c r="AS14" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AR14" s="4" t="inlineStr">
+      <c r="AT14" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
-      <c r="AS14" s="4" t="inlineStr"/>
-      <c r="AT14" s="4" t="inlineStr"/>
-      <c r="AU14" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV14" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AU14" s="4" t="inlineStr"/>
+      <c r="AV14" s="4" t="inlineStr"/>
+      <c r="AW14" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX14" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -2791,110 +2881,116 @@
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="N15" s="4" t="n">
+          <t>WEAK</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>🟡</t>
+        </is>
+      </c>
+      <c r="O15" s="4" t="inlineStr"/>
+      <c r="P15" s="4" t="n">
         <v>22.1</v>
       </c>
-      <c r="O15" s="4" t="n">
+      <c r="Q15" s="4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="P15" s="4" t="inlineStr">
+      <c r="R15" s="4" t="inlineStr">
         <is>
           <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
-      <c r="Q15" s="4" t="inlineStr"/>
-      <c r="R15" s="4" t="inlineStr"/>
       <c r="S15" s="4" t="inlineStr"/>
-      <c r="T15" s="4" t="inlineStr">
-        <is>
-          <t>Rank ↓ 13→14 · Conf 25% · band REVIEW · 53d left · → HOLD</t>
-        </is>
-      </c>
+      <c r="T15" s="4" t="inlineStr"/>
       <c r="U15" s="4" t="inlineStr"/>
-      <c r="V15" s="4" t="n">
+      <c r="V15" s="4" t="inlineStr">
+        <is>
+          <t>Rank ↓ 13→14 · Conf 25% · band REVIEW→WEAK · 53d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="W15" s="4" t="inlineStr"/>
+      <c r="X15" s="4" t="n">
         <v>24.8</v>
       </c>
-      <c r="W15" s="4" t="inlineStr">
+      <c r="Y15" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X15" s="4" t="n">
+      <c r="Z15" s="4" t="n">
         <v>-29.9</v>
       </c>
-      <c r="Y15" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z15" s="4" t="n">
+      <c r="AA15" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB15" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="AA15" s="4" t="n">
+      <c r="AC15" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="AB15" s="4" t="inlineStr">
+      <c r="AD15" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="AC15" s="4" t="n">
+      <c r="AE15" s="4" t="n">
         <v>547.4</v>
       </c>
-      <c r="AD15" s="4" t="n">
+      <c r="AF15" s="4" t="n">
         <v>547.4</v>
       </c>
-      <c r="AE15" s="4" t="n">
+      <c r="AG15" s="4" t="n">
         <v>541.9299999999999</v>
       </c>
-      <c r="AF15" s="4" t="n">
+      <c r="AH15" s="4" t="n">
         <v>552.87</v>
       </c>
-      <c r="AG15" s="4" t="n">
+      <c r="AI15" s="4" t="n">
         <v>520.03</v>
       </c>
-      <c r="AH15" s="4" t="n">
+      <c r="AJ15" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI15" s="4" t="n">
+      <c r="AK15" s="4" t="n">
         <v>591.1900000000001</v>
       </c>
-      <c r="AJ15" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK15" s="4" t="n">
+      <c r="AL15" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM15" s="4" t="n">
         <v>629.51</v>
       </c>
-      <c r="AL15" s="4" t="n">
+      <c r="AN15" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AM15" s="4" t="n">
+      <c r="AO15" s="4" t="n">
         <v>0.12</v>
       </c>
-      <c r="AN15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO15" s="4" t="inlineStr"/>
-      <c r="AP15" s="4" t="inlineStr"/>
-      <c r="AQ15" s="4" t="inlineStr">
+      <c r="AP15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="4" t="inlineStr"/>
+      <c r="AR15" s="4" t="inlineStr"/>
+      <c r="AS15" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AR15" s="4" t="inlineStr">
+      <c r="AT15" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
-      <c r="AS15" s="4" t="inlineStr"/>
-      <c r="AT15" s="4" t="inlineStr"/>
-      <c r="AU15" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV15" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AU15" s="4" t="inlineStr"/>
+      <c r="AV15" s="4" t="inlineStr"/>
+      <c r="AW15" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX15" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -2941,110 +3037,116 @@
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="N16" s="4" t="n">
+          <t>WEAK</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>🟡</t>
+        </is>
+      </c>
+      <c r="O16" s="4" t="inlineStr"/>
+      <c r="P16" s="4" t="n">
         <v>25.6</v>
       </c>
-      <c r="O16" s="4" t="n">
+      <c r="Q16" s="4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="P16" s="4" t="inlineStr">
+      <c r="R16" s="4" t="inlineStr">
         <is>
           <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
-      <c r="Q16" s="4" t="inlineStr"/>
-      <c r="R16" s="4" t="inlineStr"/>
       <c r="S16" s="4" t="inlineStr"/>
-      <c r="T16" s="4" t="inlineStr">
-        <is>
-          <t>Rank → 15→15 · Conf 28% · band REVIEW · 54d left · → HOLD</t>
-        </is>
-      </c>
+      <c r="T16" s="4" t="inlineStr"/>
       <c r="U16" s="4" t="inlineStr"/>
-      <c r="V16" s="4" t="n">
+      <c r="V16" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 15→15 · Conf 28% · band REVIEW→WEAK · 54d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="W16" s="4" t="inlineStr"/>
+      <c r="X16" s="4" t="n">
         <v>28.4</v>
       </c>
-      <c r="W16" s="4" t="inlineStr">
+      <c r="Y16" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X16" s="4" t="n">
+      <c r="Z16" s="4" t="n">
         <v>-31.5</v>
       </c>
-      <c r="Y16" s="4" t="n">
+      <c r="AA16" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="Z16" s="4" t="n">
+      <c r="AB16" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="AA16" s="4" t="n">
+      <c r="AC16" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="AB16" s="4" t="inlineStr">
+      <c r="AD16" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="AC16" s="4" t="n">
+      <c r="AE16" s="4" t="n">
         <v>1363</v>
       </c>
-      <c r="AD16" s="4" t="n">
+      <c r="AF16" s="4" t="n">
         <v>1363</v>
       </c>
-      <c r="AE16" s="4" t="n">
+      <c r="AG16" s="4" t="n">
         <v>1349.37</v>
       </c>
-      <c r="AF16" s="4" t="n">
+      <c r="AH16" s="4" t="n">
         <v>1376.63</v>
       </c>
-      <c r="AG16" s="4" t="n">
+      <c r="AI16" s="4" t="n">
         <v>1294.85</v>
       </c>
-      <c r="AH16" s="4" t="n">
+      <c r="AJ16" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI16" s="4" t="n">
+      <c r="AK16" s="4" t="n">
         <v>1472.04</v>
       </c>
-      <c r="AJ16" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK16" s="4" t="n">
+      <c r="AL16" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM16" s="4" t="n">
         <v>1567.45</v>
       </c>
-      <c r="AL16" s="4" t="n">
+      <c r="AN16" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AM16" s="4" t="n">
+      <c r="AO16" s="4" t="n">
         <v>-1.52</v>
       </c>
-      <c r="AN16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO16" s="4" t="inlineStr"/>
-      <c r="AP16" s="4" t="inlineStr"/>
-      <c r="AQ16" s="4" t="inlineStr">
+      <c r="AP16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" s="4" t="inlineStr"/>
+      <c r="AR16" s="4" t="inlineStr"/>
+      <c r="AS16" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AR16" s="4" t="inlineStr">
+      <c r="AT16" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
-      <c r="AS16" s="4" t="inlineStr"/>
-      <c r="AT16" s="4" t="inlineStr"/>
-      <c r="AU16" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV16" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AU16" s="4" t="inlineStr"/>
+      <c r="AV16" s="4" t="inlineStr"/>
+      <c r="AW16" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX16" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -3093,98 +3195,102 @@
       <c r="L17" s="4" t="inlineStr"/>
       <c r="M17" s="4" t="inlineStr"/>
       <c r="N17" s="4" t="inlineStr"/>
-      <c r="O17" s="4" t="inlineStr"/>
+      <c r="O17" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="P17" s="4" t="inlineStr"/>
       <c r="Q17" s="4" t="inlineStr"/>
       <c r="R17" s="4" t="inlineStr"/>
       <c r="S17" s="4" t="inlineStr"/>
-      <c r="T17" s="4" t="inlineStr">
+      <c r="T17" s="4" t="inlineStr"/>
+      <c r="U17" s="4" t="inlineStr"/>
+      <c r="V17" s="4" t="inlineStr">
         <is>
           <t>Rank ↑ 2→1 · Conf 83% · momentum → · 61d left · → STRONG BUY</t>
         </is>
       </c>
-      <c r="U17" s="4" t="inlineStr"/>
-      <c r="V17" s="4" t="n">
+      <c r="W17" s="4" t="inlineStr"/>
+      <c r="X17" s="4" t="n">
         <v>83</v>
       </c>
-      <c r="W17" s="4" t="inlineStr">
+      <c r="Y17" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X17" s="4" t="n">
+      <c r="Z17" s="4" t="n">
         <v>78</v>
       </c>
-      <c r="Y17" s="4" t="inlineStr"/>
-      <c r="Z17" s="4" t="n">
+      <c r="AA17" s="4" t="inlineStr"/>
+      <c r="AB17" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="AA17" s="4" t="n">
+      <c r="AC17" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="AB17" s="4" t="inlineStr">
+      <c r="AD17" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="AC17" s="4" t="n">
+      <c r="AE17" s="4" t="n">
         <v>1454.6</v>
       </c>
-      <c r="AD17" s="4" t="n">
+      <c r="AF17" s="4" t="n">
         <v>1454.6</v>
       </c>
-      <c r="AE17" s="4" t="n">
+      <c r="AG17" s="4" t="n">
         <v>1415</v>
       </c>
-      <c r="AF17" s="4" t="n">
+      <c r="AH17" s="4" t="n">
         <v>1495</v>
       </c>
-      <c r="AG17" s="4" t="n">
+      <c r="AI17" s="4" t="n">
         <v>1381.87</v>
       </c>
-      <c r="AH17" s="4" t="n">
+      <c r="AJ17" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI17" s="4" t="n">
+      <c r="AK17" s="4" t="n">
         <v>1532</v>
       </c>
-      <c r="AJ17" s="4" t="n">
+      <c r="AL17" s="4" t="n">
         <v>5.32</v>
       </c>
-      <c r="AK17" s="4" t="n">
+      <c r="AM17" s="4" t="n">
         <v>1639.24</v>
       </c>
-      <c r="AL17" s="4" t="n">
+      <c r="AN17" s="4" t="n">
         <v>12.69</v>
       </c>
-      <c r="AM17" s="4" t="n">
+      <c r="AO17" s="4" t="n">
         <v>0.35</v>
       </c>
-      <c r="AN17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO17" s="4" t="inlineStr"/>
-      <c r="AP17" s="4" t="inlineStr"/>
-      <c r="AQ17" s="4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AP17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" s="4" t="inlineStr"/>
       <c r="AR17" s="4" t="inlineStr"/>
       <c r="AS17" s="4" t="inlineStr">
         <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT17" s="4" t="inlineStr"/>
+      <c r="AU17" s="4" t="inlineStr">
+        <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="AT17" s="4" t="n">
+      <c r="AV17" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AU17" s="4" t="n">
+      <c r="AW17" s="4" t="n">
         <v>5.32</v>
       </c>
-      <c r="AV17" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AX17" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -3233,98 +3339,102 @@
       <c r="L18" s="4" t="inlineStr"/>
       <c r="M18" s="4" t="inlineStr"/>
       <c r="N18" s="4" t="inlineStr"/>
-      <c r="O18" s="4" t="inlineStr"/>
+      <c r="O18" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="P18" s="4" t="inlineStr"/>
       <c r="Q18" s="4" t="inlineStr"/>
       <c r="R18" s="4" t="inlineStr"/>
       <c r="S18" s="4" t="inlineStr"/>
-      <c r="T18" s="4" t="inlineStr">
+      <c r="T18" s="4" t="inlineStr"/>
+      <c r="U18" s="4" t="inlineStr"/>
+      <c r="V18" s="4" t="inlineStr">
         <is>
           <t>Rank ↓ 1→2 · Conf 88% · momentum → · 61d left · → STRONG BUY</t>
         </is>
       </c>
-      <c r="U18" s="4" t="inlineStr"/>
-      <c r="V18" s="4" t="n">
+      <c r="W18" s="4" t="inlineStr"/>
+      <c r="X18" s="4" t="n">
         <v>88</v>
       </c>
-      <c r="W18" s="4" t="inlineStr">
+      <c r="Y18" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X18" s="4" t="n">
+      <c r="Z18" s="4" t="n">
         <v>74</v>
       </c>
-      <c r="Y18" s="4" t="inlineStr"/>
-      <c r="Z18" s="4" t="n">
+      <c r="AA18" s="4" t="inlineStr"/>
+      <c r="AB18" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="AA18" s="4" t="n">
+      <c r="AC18" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="AB18" s="4" t="inlineStr">
+      <c r="AD18" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="AC18" s="4" t="n">
+      <c r="AE18" s="4" t="n">
         <v>1964</v>
       </c>
-      <c r="AD18" s="4" t="n">
+      <c r="AF18" s="4" t="n">
         <v>1964</v>
       </c>
-      <c r="AE18" s="4" t="n">
+      <c r="AG18" s="4" t="n">
         <v>1911</v>
       </c>
-      <c r="AF18" s="4" t="n">
+      <c r="AH18" s="4" t="n">
         <v>2017</v>
       </c>
-      <c r="AG18" s="4" t="n">
+      <c r="AI18" s="4" t="n">
         <v>1865.8</v>
       </c>
-      <c r="AH18" s="4" t="n">
+      <c r="AJ18" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI18" s="4" t="n">
+      <c r="AK18" s="4" t="n">
         <v>2054</v>
       </c>
-      <c r="AJ18" s="4" t="n">
+      <c r="AL18" s="4" t="n">
         <v>4.58</v>
       </c>
-      <c r="AK18" s="4" t="n">
+      <c r="AM18" s="4" t="n">
         <v>2197.78</v>
       </c>
-      <c r="AL18" s="4" t="n">
+      <c r="AN18" s="4" t="n">
         <v>11.9</v>
       </c>
-      <c r="AM18" s="4" t="n">
+      <c r="AO18" s="4" t="n">
         <v>0.44</v>
       </c>
-      <c r="AN18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO18" s="4" t="inlineStr"/>
-      <c r="AP18" s="4" t="inlineStr"/>
-      <c r="AQ18" s="4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AP18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" s="4" t="inlineStr"/>
       <c r="AR18" s="4" t="inlineStr"/>
       <c r="AS18" s="4" t="inlineStr">
         <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT18" s="4" t="inlineStr"/>
+      <c r="AU18" s="4" t="inlineStr">
+        <is>
           <t>Pharma</t>
         </is>
       </c>
-      <c r="AT18" s="4" t="n">
+      <c r="AV18" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AU18" s="4" t="n">
+      <c r="AW18" s="4" t="n">
         <v>4.58</v>
       </c>
-      <c r="AV18" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AX18" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -3373,98 +3483,102 @@
       <c r="L19" s="4" t="inlineStr"/>
       <c r="M19" s="4" t="inlineStr"/>
       <c r="N19" s="4" t="inlineStr"/>
-      <c r="O19" s="4" t="inlineStr"/>
+      <c r="O19" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="P19" s="4" t="inlineStr"/>
       <c r="Q19" s="4" t="inlineStr"/>
       <c r="R19" s="4" t="inlineStr"/>
       <c r="S19" s="4" t="inlineStr"/>
-      <c r="T19" s="4" t="inlineStr">
+      <c r="T19" s="4" t="inlineStr"/>
+      <c r="U19" s="4" t="inlineStr"/>
+      <c r="V19" s="4" t="inlineStr">
         <is>
           <t>Rank → 3→3 · Conf 86% · momentum → · 61d left · → STRONG BUY</t>
         </is>
       </c>
-      <c r="U19" s="4" t="inlineStr"/>
-      <c r="V19" s="4" t="n">
+      <c r="W19" s="4" t="inlineStr"/>
+      <c r="X19" s="4" t="n">
         <v>86</v>
       </c>
-      <c r="W19" s="4" t="inlineStr">
+      <c r="Y19" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X19" s="4" t="n">
+      <c r="Z19" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="Y19" s="4" t="inlineStr"/>
-      <c r="Z19" s="4" t="n">
+      <c r="AA19" s="4" t="inlineStr"/>
+      <c r="AB19" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="AA19" s="4" t="n">
+      <c r="AC19" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="AB19" s="4" t="inlineStr">
+      <c r="AD19" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="AC19" s="4" t="n">
+      <c r="AE19" s="4" t="n">
         <v>1620</v>
       </c>
-      <c r="AD19" s="4" t="n">
+      <c r="AF19" s="4" t="n">
         <v>1620</v>
       </c>
-      <c r="AE19" s="4" t="n">
+      <c r="AG19" s="4" t="n">
         <v>1569</v>
       </c>
-      <c r="AF19" s="4" t="n">
+      <c r="AH19" s="4" t="n">
         <v>1671</v>
       </c>
-      <c r="AG19" s="4" t="n">
+      <c r="AI19" s="4" t="n">
         <v>1539</v>
       </c>
-      <c r="AH19" s="4" t="n">
+      <c r="AJ19" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI19" s="4" t="n">
+      <c r="AK19" s="4" t="n">
         <v>1642</v>
       </c>
-      <c r="AJ19" s="4" t="n">
+      <c r="AL19" s="4" t="n">
         <v>1.36</v>
       </c>
-      <c r="AK19" s="4" t="n">
+      <c r="AM19" s="4" t="n">
         <v>1756.94</v>
       </c>
-      <c r="AL19" s="4" t="n">
+      <c r="AN19" s="4" t="n">
         <v>8.449999999999999</v>
       </c>
-      <c r="AM19" s="4" t="n">
+      <c r="AO19" s="4" t="n">
         <v>-1.37</v>
       </c>
-      <c r="AN19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO19" s="4" t="inlineStr"/>
-      <c r="AP19" s="4" t="inlineStr"/>
-      <c r="AQ19" s="4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AP19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" s="4" t="inlineStr"/>
       <c r="AR19" s="4" t="inlineStr"/>
       <c r="AS19" s="4" t="inlineStr">
         <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT19" s="4" t="inlineStr"/>
+      <c r="AU19" s="4" t="inlineStr">
+        <is>
           <t>Chemicals</t>
         </is>
       </c>
-      <c r="AT19" s="4" t="n">
+      <c r="AV19" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AU19" s="4" t="n">
+      <c r="AW19" s="4" t="n">
         <v>1.36</v>
       </c>
-      <c r="AV19" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AX19" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -3513,98 +3627,102 @@
       <c r="L20" s="4" t="inlineStr"/>
       <c r="M20" s="4" t="inlineStr"/>
       <c r="N20" s="4" t="inlineStr"/>
-      <c r="O20" s="4" t="inlineStr"/>
+      <c r="O20" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="P20" s="4" t="inlineStr"/>
       <c r="Q20" s="4" t="inlineStr"/>
       <c r="R20" s="4" t="inlineStr"/>
       <c r="S20" s="4" t="inlineStr"/>
-      <c r="T20" s="4" t="inlineStr">
+      <c r="T20" s="4" t="inlineStr"/>
+      <c r="U20" s="4" t="inlineStr"/>
+      <c r="V20" s="4" t="inlineStr">
         <is>
           <t>Rank ↓ 3→4 · Conf 71% · momentum → · 61d left · → STRONG BUY</t>
         </is>
       </c>
-      <c r="U20" s="4" t="inlineStr"/>
-      <c r="V20" s="4" t="n">
+      <c r="W20" s="4" t="inlineStr"/>
+      <c r="X20" s="4" t="n">
         <v>71</v>
       </c>
-      <c r="W20" s="4" t="inlineStr">
+      <c r="Y20" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X20" s="4" t="n">
+      <c r="Z20" s="4" t="n">
         <v>68</v>
       </c>
-      <c r="Y20" s="4" t="inlineStr"/>
-      <c r="Z20" s="4" t="n">
+      <c r="AA20" s="4" t="inlineStr"/>
+      <c r="AB20" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="AA20" s="4" t="n">
+      <c r="AC20" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="AB20" s="4" t="inlineStr">
+      <c r="AD20" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="AC20" s="4" t="n">
+      <c r="AE20" s="4" t="n">
         <v>2410</v>
       </c>
-      <c r="AD20" s="4" t="n">
+      <c r="AF20" s="4" t="n">
         <v>2410</v>
       </c>
-      <c r="AE20" s="4" t="n">
+      <c r="AG20" s="4" t="n">
         <v>2349</v>
       </c>
-      <c r="AF20" s="4" t="n">
+      <c r="AH20" s="4" t="n">
         <v>2471</v>
       </c>
-      <c r="AG20" s="4" t="n">
+      <c r="AI20" s="4" t="n">
         <v>2289.5</v>
       </c>
-      <c r="AH20" s="4" t="n">
+      <c r="AJ20" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI20" s="4" t="n">
+      <c r="AK20" s="4" t="n">
         <v>2602.8</v>
       </c>
-      <c r="AJ20" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK20" s="4" t="n">
+      <c r="AL20" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM20" s="4" t="n">
         <v>2784.996000000001</v>
       </c>
-      <c r="AL20" s="4" t="n">
+      <c r="AN20" s="4" t="n">
         <v>15.56</v>
       </c>
-      <c r="AM20" s="4" t="n">
+      <c r="AO20" s="4" t="n">
         <v>1.09</v>
       </c>
-      <c r="AN20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO20" s="4" t="inlineStr"/>
-      <c r="AP20" s="4" t="inlineStr"/>
-      <c r="AQ20" s="4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AP20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" s="4" t="inlineStr"/>
       <c r="AR20" s="4" t="inlineStr"/>
       <c r="AS20" s="4" t="inlineStr">
         <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT20" s="4" t="inlineStr"/>
+      <c r="AU20" s="4" t="inlineStr">
+        <is>
           <t>Pharma</t>
         </is>
       </c>
-      <c r="AT20" s="4" t="n">
+      <c r="AV20" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AU20" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV20" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AW20" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX20" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -3653,98 +3771,102 @@
       <c r="L21" s="4" t="inlineStr"/>
       <c r="M21" s="4" t="inlineStr"/>
       <c r="N21" s="4" t="inlineStr"/>
-      <c r="O21" s="4" t="inlineStr"/>
+      <c r="O21" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="P21" s="4" t="inlineStr"/>
       <c r="Q21" s="4" t="inlineStr"/>
       <c r="R21" s="4" t="inlineStr"/>
       <c r="S21" s="4" t="inlineStr"/>
-      <c r="T21" s="4" t="inlineStr">
+      <c r="T21" s="4" t="inlineStr"/>
+      <c r="U21" s="4" t="inlineStr"/>
+      <c r="V21" s="4" t="inlineStr">
         <is>
           <t>Rank ↓ 4→5 · Conf 72% · momentum → · 61d left · → STRONG BUY</t>
         </is>
       </c>
-      <c r="U21" s="4" t="inlineStr"/>
-      <c r="V21" s="4" t="n">
+      <c r="W21" s="4" t="inlineStr"/>
+      <c r="X21" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="W21" s="4" t="inlineStr">
+      <c r="Y21" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X21" s="4" t="n">
+      <c r="Z21" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="Y21" s="4" t="inlineStr"/>
-      <c r="Z21" s="4" t="n">
+      <c r="AA21" s="4" t="inlineStr"/>
+      <c r="AB21" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="AA21" s="4" t="n">
+      <c r="AC21" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="AB21" s="4" t="inlineStr">
+      <c r="AD21" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="AC21" s="4" t="n">
+      <c r="AE21" s="4" t="n">
         <v>343.6</v>
       </c>
-      <c r="AD21" s="4" t="n">
+      <c r="AF21" s="4" t="n">
         <v>343.6</v>
       </c>
-      <c r="AE21" s="4" t="n">
+      <c r="AG21" s="4" t="n">
         <v>335</v>
       </c>
-      <c r="AF21" s="4" t="n">
+      <c r="AH21" s="4" t="n">
         <v>353</v>
       </c>
-      <c r="AG21" s="4" t="n">
+      <c r="AI21" s="4" t="n">
         <v>326.42</v>
       </c>
-      <c r="AH21" s="4" t="n">
+      <c r="AJ21" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI21" s="4" t="n">
+      <c r="AK21" s="4" t="n">
         <v>371.088</v>
       </c>
-      <c r="AJ21" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK21" s="4" t="n">
+      <c r="AL21" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM21" s="4" t="n">
         <v>397.0641600000001</v>
       </c>
-      <c r="AL21" s="4" t="n">
+      <c r="AN21" s="4" t="n">
         <v>15.56</v>
       </c>
-      <c r="AM21" s="4" t="n">
+      <c r="AO21" s="4" t="n">
         <v>-1.04</v>
       </c>
-      <c r="AN21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO21" s="4" t="inlineStr"/>
-      <c r="AP21" s="4" t="inlineStr"/>
-      <c r="AQ21" s="4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AP21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" s="4" t="inlineStr"/>
       <c r="AR21" s="4" t="inlineStr"/>
       <c r="AS21" s="4" t="inlineStr">
         <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT21" s="4" t="inlineStr"/>
+      <c r="AU21" s="4" t="inlineStr">
+        <is>
           <t>Power</t>
         </is>
       </c>
-      <c r="AT21" s="4" t="n">
+      <c r="AV21" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AU21" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV21" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AW21" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX21" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -3793,98 +3915,102 @@
       <c r="L22" s="4" t="inlineStr"/>
       <c r="M22" s="4" t="inlineStr"/>
       <c r="N22" s="4" t="inlineStr"/>
-      <c r="O22" s="4" t="inlineStr"/>
+      <c r="O22" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="P22" s="4" t="inlineStr"/>
       <c r="Q22" s="4" t="inlineStr"/>
       <c r="R22" s="4" t="inlineStr"/>
       <c r="S22" s="4" t="inlineStr"/>
-      <c r="T22" s="4" t="inlineStr">
+      <c r="T22" s="4" t="inlineStr"/>
+      <c r="U22" s="4" t="inlineStr"/>
+      <c r="V22" s="4" t="inlineStr">
         <is>
           <t>Rank ↓ 5→6 · Conf 72% · momentum → · 61d left · → BUY</t>
         </is>
       </c>
-      <c r="U22" s="4" t="inlineStr"/>
-      <c r="V22" s="4" t="n">
+      <c r="W22" s="4" t="inlineStr"/>
+      <c r="X22" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="W22" s="4" t="inlineStr">
+      <c r="Y22" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X22" s="4" t="n">
+      <c r="Z22" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="Y22" s="4" t="inlineStr"/>
-      <c r="Z22" s="4" t="n">
+      <c r="AA22" s="4" t="inlineStr"/>
+      <c r="AB22" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="AA22" s="4" t="n">
+      <c r="AC22" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="AB22" s="4" t="inlineStr">
+      <c r="AD22" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="AC22" s="4" t="n">
+      <c r="AE22" s="4" t="n">
         <v>398</v>
       </c>
-      <c r="AD22" s="4" t="n">
+      <c r="AF22" s="4" t="n">
         <v>398</v>
       </c>
-      <c r="AE22" s="4" t="n">
+      <c r="AG22" s="4" t="n">
         <v>386</v>
       </c>
-      <c r="AF22" s="4" t="n">
+      <c r="AH22" s="4" t="n">
         <v>410</v>
       </c>
-      <c r="AG22" s="4" t="n">
+      <c r="AI22" s="4" t="n">
         <v>378.1</v>
       </c>
-      <c r="AH22" s="4" t="n">
+      <c r="AJ22" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI22" s="4" t="n">
+      <c r="AK22" s="4" t="n">
         <v>429.84</v>
       </c>
-      <c r="AJ22" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK22" s="4" t="n">
+      <c r="AL22" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM22" s="4" t="n">
         <v>459.9288000000001</v>
       </c>
-      <c r="AL22" s="4" t="n">
+      <c r="AN22" s="4" t="n">
         <v>15.56</v>
       </c>
-      <c r="AM22" s="4" t="n">
+      <c r="AO22" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="AN22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO22" s="4" t="inlineStr"/>
-      <c r="AP22" s="4" t="inlineStr"/>
-      <c r="AQ22" s="4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AP22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" s="4" t="inlineStr"/>
       <c r="AR22" s="4" t="inlineStr"/>
       <c r="AS22" s="4" t="inlineStr">
         <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT22" s="4" t="inlineStr"/>
+      <c r="AU22" s="4" t="inlineStr">
+        <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="AT22" s="4" t="n">
+      <c r="AV22" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AU22" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV22" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AW22" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX22" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -3933,98 +4059,102 @@
       <c r="L23" s="4" t="inlineStr"/>
       <c r="M23" s="4" t="inlineStr"/>
       <c r="N23" s="4" t="inlineStr"/>
-      <c r="O23" s="4" t="inlineStr"/>
+      <c r="O23" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="P23" s="4" t="inlineStr"/>
       <c r="Q23" s="4" t="inlineStr"/>
       <c r="R23" s="4" t="inlineStr"/>
       <c r="S23" s="4" t="inlineStr"/>
-      <c r="T23" s="4" t="inlineStr">
+      <c r="T23" s="4" t="inlineStr"/>
+      <c r="U23" s="4" t="inlineStr"/>
+      <c r="V23" s="4" t="inlineStr">
         <is>
           <t>Rank → 7→7 · Conf 69% · momentum → · 61d left · → BUY</t>
         </is>
       </c>
-      <c r="U23" s="4" t="inlineStr"/>
-      <c r="V23" s="4" t="n">
+      <c r="W23" s="4" t="inlineStr"/>
+      <c r="X23" s="4" t="n">
         <v>69</v>
       </c>
-      <c r="W23" s="4" t="inlineStr">
+      <c r="Y23" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X23" s="4" t="n">
+      <c r="Z23" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="Y23" s="4" t="inlineStr"/>
-      <c r="Z23" s="4" t="n">
+      <c r="AA23" s="4" t="inlineStr"/>
+      <c r="AB23" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="AA23" s="4" t="n">
+      <c r="AC23" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="AB23" s="4" t="inlineStr">
+      <c r="AD23" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="AC23" s="4" t="n">
+      <c r="AE23" s="4" t="n">
         <v>283.4</v>
       </c>
-      <c r="AD23" s="4" t="n">
+      <c r="AF23" s="4" t="n">
         <v>283.4</v>
       </c>
-      <c r="AE23" s="4" t="n">
+      <c r="AG23" s="4" t="n">
         <v>276</v>
       </c>
-      <c r="AF23" s="4" t="n">
+      <c r="AH23" s="4" t="n">
         <v>290</v>
       </c>
-      <c r="AG23" s="4" t="n">
+      <c r="AI23" s="4" t="n">
         <v>269.23</v>
       </c>
-      <c r="AH23" s="4" t="n">
+      <c r="AJ23" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI23" s="4" t="n">
+      <c r="AK23" s="4" t="n">
         <v>306.072</v>
       </c>
-      <c r="AJ23" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK23" s="4" t="n">
+      <c r="AL23" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM23" s="4" t="n">
         <v>327.49704</v>
       </c>
-      <c r="AL23" s="4" t="n">
+      <c r="AN23" s="4" t="n">
         <v>15.56</v>
       </c>
-      <c r="AM23" s="4" t="n">
+      <c r="AO23" s="4" t="n">
         <v>-0.86</v>
       </c>
-      <c r="AN23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO23" s="4" t="inlineStr"/>
-      <c r="AP23" s="4" t="inlineStr"/>
-      <c r="AQ23" s="4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AP23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" s="4" t="inlineStr"/>
       <c r="AR23" s="4" t="inlineStr"/>
       <c r="AS23" s="4" t="inlineStr">
         <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT23" s="4" t="inlineStr"/>
+      <c r="AU23" s="4" t="inlineStr">
+        <is>
           <t>Power</t>
         </is>
       </c>
-      <c r="AT23" s="4" t="n">
+      <c r="AV23" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AU23" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV23" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AW23" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX23" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -4073,98 +4203,102 @@
       <c r="L24" s="4" t="inlineStr"/>
       <c r="M24" s="4" t="inlineStr"/>
       <c r="N24" s="4" t="inlineStr"/>
-      <c r="O24" s="4" t="inlineStr"/>
+      <c r="O24" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="P24" s="4" t="inlineStr"/>
       <c r="Q24" s="4" t="inlineStr"/>
       <c r="R24" s="4" t="inlineStr"/>
       <c r="S24" s="4" t="inlineStr"/>
-      <c r="T24" s="4" t="inlineStr">
+      <c r="T24" s="4" t="inlineStr"/>
+      <c r="U24" s="4" t="inlineStr"/>
+      <c r="V24" s="4" t="inlineStr">
         <is>
           <t>Rank ↓ 7→8 · Conf 67% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
-      <c r="U24" s="4" t="inlineStr"/>
-      <c r="V24" s="4" t="n">
+      <c r="W24" s="4" t="inlineStr"/>
+      <c r="X24" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="W24" s="4" t="inlineStr">
+      <c r="Y24" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X24" s="4" t="n">
+      <c r="Z24" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="Y24" s="4" t="inlineStr"/>
-      <c r="Z24" s="4" t="n">
+      <c r="AA24" s="4" t="inlineStr"/>
+      <c r="AB24" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="AA24" s="4" t="n">
+      <c r="AC24" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="AB24" s="4" t="inlineStr">
+      <c r="AD24" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="AC24" s="4" t="n">
+      <c r="AE24" s="4" t="n">
         <v>510.2</v>
       </c>
-      <c r="AD24" s="4" t="n">
+      <c r="AF24" s="4" t="n">
         <v>510.2</v>
       </c>
-      <c r="AE24" s="4" t="n">
+      <c r="AG24" s="4" t="n">
         <v>495</v>
       </c>
-      <c r="AF24" s="4" t="n">
+      <c r="AH24" s="4" t="n">
         <v>526</v>
       </c>
-      <c r="AG24" s="4" t="n">
+      <c r="AI24" s="4" t="n">
         <v>484.6899999999999</v>
       </c>
-      <c r="AH24" s="4" t="n">
+      <c r="AJ24" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI24" s="4" t="n">
+      <c r="AK24" s="4" t="n">
         <v>551.0160000000001</v>
       </c>
-      <c r="AJ24" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK24" s="4" t="n">
+      <c r="AL24" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM24" s="4" t="n">
         <v>589.5871200000001</v>
       </c>
-      <c r="AL24" s="4" t="n">
+      <c r="AN24" s="4" t="n">
         <v>15.56</v>
       </c>
-      <c r="AM24" s="4" t="n">
+      <c r="AO24" s="4" t="n">
         <v>0.46</v>
       </c>
-      <c r="AN24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO24" s="4" t="inlineStr"/>
-      <c r="AP24" s="4" t="inlineStr"/>
-      <c r="AQ24" s="4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AP24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" s="4" t="inlineStr"/>
       <c r="AR24" s="4" t="inlineStr"/>
       <c r="AS24" s="4" t="inlineStr">
         <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT24" s="4" t="inlineStr"/>
+      <c r="AU24" s="4" t="inlineStr">
+        <is>
           <t>Transport</t>
         </is>
       </c>
-      <c r="AT24" s="4" t="n">
+      <c r="AV24" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AU24" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV24" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AW24" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX24" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -4213,98 +4347,102 @@
       <c r="L25" s="4" t="inlineStr"/>
       <c r="M25" s="4" t="inlineStr"/>
       <c r="N25" s="4" t="inlineStr"/>
-      <c r="O25" s="4" t="inlineStr"/>
+      <c r="O25" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="P25" s="4" t="inlineStr"/>
       <c r="Q25" s="4" t="inlineStr"/>
       <c r="R25" s="4" t="inlineStr"/>
       <c r="S25" s="4" t="inlineStr"/>
-      <c r="T25" s="4" t="inlineStr">
+      <c r="T25" s="4" t="inlineStr"/>
+      <c r="U25" s="4" t="inlineStr"/>
+      <c r="V25" s="4" t="inlineStr">
         <is>
           <t>Rank ↓ 8→9 · Conf 64% · momentum → · 61d left · → BUY</t>
         </is>
       </c>
-      <c r="U25" s="4" t="inlineStr"/>
-      <c r="V25" s="4" t="n">
+      <c r="W25" s="4" t="inlineStr"/>
+      <c r="X25" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="W25" s="4" t="inlineStr">
+      <c r="Y25" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X25" s="4" t="n">
+      <c r="Z25" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="Y25" s="4" t="inlineStr"/>
-      <c r="Z25" s="4" t="n">
+      <c r="AA25" s="4" t="inlineStr"/>
+      <c r="AB25" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="AA25" s="4" t="n">
+      <c r="AC25" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="AB25" s="4" t="inlineStr">
+      <c r="AD25" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="AC25" s="4" t="n">
+      <c r="AE25" s="4" t="n">
         <v>391.5</v>
       </c>
-      <c r="AD25" s="4" t="n">
+      <c r="AF25" s="4" t="n">
         <v>391.5</v>
       </c>
-      <c r="AE25" s="4" t="n">
+      <c r="AG25" s="4" t="n">
         <v>379</v>
       </c>
-      <c r="AF25" s="4" t="n">
+      <c r="AH25" s="4" t="n">
         <v>404</v>
       </c>
-      <c r="AG25" s="4" t="n">
+      <c r="AI25" s="4" t="n">
         <v>371.925</v>
       </c>
-      <c r="AH25" s="4" t="n">
+      <c r="AJ25" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI25" s="4" t="n">
+      <c r="AK25" s="4" t="n">
         <v>422.8200000000001</v>
       </c>
-      <c r="AJ25" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK25" s="4" t="n">
+      <c r="AL25" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM25" s="4" t="n">
         <v>452.4174000000001</v>
       </c>
-      <c r="AL25" s="4" t="n">
+      <c r="AN25" s="4" t="n">
         <v>15.56</v>
       </c>
-      <c r="AM25" s="4" t="n">
+      <c r="AO25" s="4" t="n">
         <v>0.42</v>
       </c>
-      <c r="AN25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO25" s="4" t="inlineStr"/>
-      <c r="AP25" s="4" t="inlineStr"/>
-      <c r="AQ25" s="4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AP25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" s="4" t="inlineStr"/>
       <c r="AR25" s="4" t="inlineStr"/>
       <c r="AS25" s="4" t="inlineStr">
         <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT25" s="4" t="inlineStr"/>
+      <c r="AU25" s="4" t="inlineStr">
+        <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="AT25" s="4" t="n">
+      <c r="AV25" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AU25" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV25" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AW25" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX25" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -4349,98 +4487,102 @@
       <c r="L26" s="4" t="inlineStr"/>
       <c r="M26" s="4" t="inlineStr"/>
       <c r="N26" s="4" t="inlineStr"/>
-      <c r="O26" s="4" t="inlineStr"/>
+      <c r="O26" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="P26" s="4" t="inlineStr"/>
       <c r="Q26" s="4" t="inlineStr"/>
       <c r="R26" s="4" t="inlineStr"/>
       <c r="S26" s="4" t="inlineStr"/>
-      <c r="T26" s="4" t="inlineStr">
+      <c r="T26" s="4" t="inlineStr"/>
+      <c r="U26" s="4" t="inlineStr"/>
+      <c r="V26" s="4" t="inlineStr">
         <is>
           <t>Rank ↓ 9→10 · Conf 66% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
-      <c r="U26" s="4" t="inlineStr"/>
-      <c r="V26" s="4" t="n">
+      <c r="W26" s="4" t="inlineStr"/>
+      <c r="X26" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="W26" s="4" t="inlineStr">
+      <c r="Y26" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X26" s="4" t="n">
+      <c r="Z26" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="Y26" s="4" t="inlineStr"/>
-      <c r="Z26" s="4" t="n">
+      <c r="AA26" s="4" t="inlineStr"/>
+      <c r="AB26" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="AA26" s="4" t="n">
+      <c r="AC26" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="AB26" s="4" t="inlineStr">
+      <c r="AD26" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="AC26" s="4" t="n">
+      <c r="AE26" s="4" t="n">
         <v>5478</v>
       </c>
-      <c r="AD26" s="4" t="n">
+      <c r="AF26" s="4" t="n">
         <v>5478</v>
       </c>
-      <c r="AE26" s="4" t="n">
+      <c r="AG26" s="4" t="n">
         <v>5335</v>
       </c>
-      <c r="AF26" s="4" t="n">
+      <c r="AH26" s="4" t="n">
         <v>5621</v>
       </c>
-      <c r="AG26" s="4" t="n">
+      <c r="AI26" s="4" t="n">
         <v>5204.099999999999</v>
       </c>
-      <c r="AH26" s="4" t="n">
+      <c r="AJ26" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI26" s="4" t="n">
+      <c r="AK26" s="4" t="n">
         <v>5916.240000000001</v>
       </c>
-      <c r="AJ26" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK26" s="4" t="n">
+      <c r="AL26" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM26" s="4" t="n">
         <v>6330.376800000001</v>
       </c>
-      <c r="AL26" s="4" t="n">
+      <c r="AN26" s="4" t="n">
         <v>15.56</v>
       </c>
-      <c r="AM26" s="4" t="n">
+      <c r="AO26" s="4" t="n">
         <v>0.43</v>
       </c>
-      <c r="AN26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO26" s="4" t="inlineStr"/>
-      <c r="AP26" s="4" t="inlineStr"/>
-      <c r="AQ26" s="4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AP26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" s="4" t="inlineStr"/>
       <c r="AR26" s="4" t="inlineStr"/>
       <c r="AS26" s="4" t="inlineStr">
         <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT26" s="4" t="inlineStr"/>
+      <c r="AU26" s="4" t="inlineStr">
+        <is>
           <t>FMCG</t>
         </is>
       </c>
-      <c r="AT26" s="4" t="n">
+      <c r="AV26" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AU26" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV26" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AW26" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX26" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -4489,98 +4631,102 @@
       <c r="L27" s="4" t="inlineStr"/>
       <c r="M27" s="4" t="inlineStr"/>
       <c r="N27" s="4" t="inlineStr"/>
-      <c r="O27" s="4" t="inlineStr"/>
+      <c r="O27" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="P27" s="4" t="inlineStr"/>
       <c r="Q27" s="4" t="inlineStr"/>
       <c r="R27" s="4" t="inlineStr"/>
       <c r="S27" s="4" t="inlineStr"/>
-      <c r="T27" s="4" t="inlineStr">
+      <c r="T27" s="4" t="inlineStr"/>
+      <c r="U27" s="4" t="inlineStr"/>
+      <c r="V27" s="4" t="inlineStr">
         <is>
           <t>Rank ↓ 10→11 · Conf 66% · momentum → · 61d left · → BUY</t>
         </is>
       </c>
-      <c r="U27" s="4" t="inlineStr"/>
-      <c r="V27" s="4" t="n">
+      <c r="W27" s="4" t="inlineStr"/>
+      <c r="X27" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="W27" s="4" t="inlineStr">
+      <c r="Y27" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X27" s="4" t="n">
+      <c r="Z27" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="Y27" s="4" t="inlineStr"/>
-      <c r="Z27" s="4" t="n">
+      <c r="AA27" s="4" t="inlineStr"/>
+      <c r="AB27" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="AA27" s="4" t="n">
+      <c r="AC27" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="AB27" s="4" t="inlineStr">
+      <c r="AD27" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="AC27" s="4" t="n">
+      <c r="AE27" s="4" t="n">
         <v>417.6</v>
       </c>
-      <c r="AD27" s="4" t="n">
+      <c r="AF27" s="4" t="n">
         <v>417.6</v>
       </c>
-      <c r="AE27" s="4" t="n">
+      <c r="AG27" s="4" t="n">
         <v>405</v>
       </c>
-      <c r="AF27" s="4" t="n">
+      <c r="AH27" s="4" t="n">
         <v>430</v>
       </c>
-      <c r="AG27" s="4" t="n">
+      <c r="AI27" s="4" t="n">
         <v>396.72</v>
       </c>
-      <c r="AH27" s="4" t="n">
+      <c r="AJ27" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI27" s="4" t="n">
+      <c r="AK27" s="4" t="n">
         <v>451.008</v>
       </c>
-      <c r="AJ27" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK27" s="4" t="n">
+      <c r="AL27" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM27" s="4" t="n">
         <v>482.5785600000001</v>
       </c>
-      <c r="AL27" s="4" t="n">
+      <c r="AN27" s="4" t="n">
         <v>15.56</v>
       </c>
-      <c r="AM27" s="4" t="n">
+      <c r="AO27" s="4" t="n">
         <v>0.59</v>
       </c>
-      <c r="AN27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO27" s="4" t="inlineStr"/>
-      <c r="AP27" s="4" t="inlineStr"/>
-      <c r="AQ27" s="4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AP27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" s="4" t="inlineStr"/>
       <c r="AR27" s="4" t="inlineStr"/>
       <c r="AS27" s="4" t="inlineStr">
         <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT27" s="4" t="inlineStr"/>
+      <c r="AU27" s="4" t="inlineStr">
+        <is>
           <t>Metal</t>
         </is>
       </c>
-      <c r="AT27" s="4" t="n">
+      <c r="AV27" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AU27" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV27" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AW27" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX27" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -4634,113 +4780,119 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N28" s="4" t="n">
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O28" s="4" t="inlineStr"/>
+      <c r="P28" s="4" t="n">
         <v>56.1</v>
       </c>
-      <c r="O28" s="4" t="n">
+      <c r="Q28" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="P28" s="4" t="inlineStr">
+      <c r="R28" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 12 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="Q28" s="4" t="n">
+      <c r="S28" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="R28" s="4" t="inlineStr"/>
-      <c r="S28" s="4" t="inlineStr"/>
-      <c r="T28" s="4" t="inlineStr">
+      <c r="T28" s="4" t="inlineStr"/>
+      <c r="U28" s="4" t="inlineStr"/>
+      <c r="V28" s="4" t="inlineStr">
         <is>
           <t>Rank → 1→1 · Conf 57% · band HOLD · 14d left · → BUY</t>
         </is>
       </c>
-      <c r="U28" s="4" t="inlineStr"/>
-      <c r="V28" s="4" t="n">
+      <c r="W28" s="4" t="inlineStr"/>
+      <c r="X28" s="4" t="n">
         <v>56.8</v>
       </c>
-      <c r="W28" s="4" t="inlineStr">
+      <c r="Y28" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X28" s="4" t="n">
+      <c r="Z28" s="4" t="n">
         <v>29.2</v>
       </c>
-      <c r="Y28" s="4" t="n">
+      <c r="AA28" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="Z28" s="4" t="n">
+      <c r="AB28" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="AA28" s="4" t="n">
+      <c r="AC28" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="AB28" s="4" t="inlineStr">
+      <c r="AD28" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC28" s="4" t="n">
+      <c r="AE28" s="4" t="n">
         <v>368.98</v>
       </c>
-      <c r="AD28" s="4" t="n">
+      <c r="AF28" s="4" t="n">
         <v>368.98</v>
       </c>
-      <c r="AE28" s="4" t="n">
+      <c r="AG28" s="4" t="n">
         <v>365.29</v>
       </c>
-      <c r="AF28" s="4" t="n">
+      <c r="AH28" s="4" t="n">
         <v>372.67</v>
       </c>
-      <c r="AG28" s="4" t="n">
+      <c r="AI28" s="4" t="n">
         <v>346.84</v>
       </c>
-      <c r="AH28" s="4" t="n">
+      <c r="AJ28" s="4" t="n">
         <v>-6</v>
       </c>
-      <c r="AI28" s="4" t="n">
+      <c r="AK28" s="4" t="n">
         <v>413.26</v>
       </c>
-      <c r="AJ28" s="4" t="n">
+      <c r="AL28" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="AK28" s="4" t="n">
+      <c r="AM28" s="4" t="n">
         <v>457.54</v>
       </c>
-      <c r="AL28" s="4" t="n">
+      <c r="AN28" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="AM28" s="4" t="inlineStr"/>
-      <c r="AN28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO28" s="4" t="n">
+      <c r="AO28" s="4" t="inlineStr"/>
+      <c r="AP28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" s="4" t="n">
         <v>1.46</v>
       </c>
-      <c r="AP28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ28" s="4" t="inlineStr">
+      <c r="AR28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AR28" s="4" t="inlineStr">
+      <c r="AT28" s="4" t="inlineStr">
         <is>
           <t>Momentum · Value · Trend</t>
         </is>
       </c>
-      <c r="AS28" s="4" t="inlineStr"/>
-      <c r="AT28" s="4" t="n">
+      <c r="AU28" s="4" t="inlineStr"/>
+      <c r="AV28" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AU28" s="4" t="n">
+      <c r="AW28" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="AV28" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AX28" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -4791,116 +4943,122 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="N29" s="4" t="n">
+          <t>STRONG</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O29" s="4" t="inlineStr"/>
+      <c r="P29" s="4" t="n">
         <v>52.9</v>
       </c>
-      <c r="O29" s="4" t="n">
+      <c r="Q29" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="P29" s="4" t="inlineStr">
+      <c r="R29" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="Q29" s="4" t="n">
+      <c r="S29" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="R29" s="4" t="n">
+      <c r="T29" s="4" t="n">
         <v>0.184</v>
       </c>
-      <c r="S29" s="4" t="inlineStr"/>
-      <c r="T29" s="4" t="inlineStr">
-        <is>
-          <t>Rank → 2→2 · Conf 54% · band HOLD · 14d left · → HOLD</t>
-        </is>
-      </c>
       <c r="U29" s="4" t="inlineStr"/>
-      <c r="V29" s="4" t="n">
+      <c r="V29" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 2→2 · Conf 54% · band HOLD→STRONG · 14d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="W29" s="4" t="inlineStr"/>
+      <c r="X29" s="4" t="n">
         <v>53.6</v>
       </c>
-      <c r="W29" s="4" t="inlineStr">
+      <c r="Y29" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X29" s="4" t="n">
+      <c r="Z29" s="4" t="n">
         <v>27.8</v>
       </c>
-      <c r="Y29" s="4" t="n">
+      <c r="AA29" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="Z29" s="4" t="n">
+      <c r="AB29" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="AA29" s="4" t="n">
+      <c r="AC29" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="AB29" s="4" t="inlineStr">
+      <c r="AD29" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC29" s="4" t="n">
+      <c r="AE29" s="4" t="n">
         <v>358.56</v>
       </c>
-      <c r="AD29" s="4" t="n">
+      <c r="AF29" s="4" t="n">
         <v>358.56</v>
       </c>
-      <c r="AE29" s="4" t="n">
+      <c r="AG29" s="4" t="n">
         <v>354.97</v>
       </c>
-      <c r="AF29" s="4" t="n">
+      <c r="AH29" s="4" t="n">
         <v>362.15</v>
       </c>
-      <c r="AG29" s="4" t="n">
+      <c r="AI29" s="4" t="n">
         <v>340.63</v>
       </c>
-      <c r="AH29" s="4" t="n">
+      <c r="AJ29" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI29" s="4" t="n">
+      <c r="AK29" s="4" t="n">
         <v>387.24</v>
       </c>
-      <c r="AJ29" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK29" s="4" t="n">
+      <c r="AL29" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM29" s="4" t="n">
         <v>412.34</v>
       </c>
-      <c r="AL29" s="4" t="n">
+      <c r="AN29" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AM29" s="4" t="inlineStr"/>
-      <c r="AN29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO29" s="4" t="n">
+      <c r="AO29" s="4" t="inlineStr"/>
+      <c r="AP29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" s="4" t="n">
         <v>2.11</v>
       </c>
-      <c r="AP29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ29" s="4" t="inlineStr">
+      <c r="AR29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AR29" s="4" t="inlineStr">
+      <c r="AT29" s="4" t="inlineStr">
         <is>
           <t>Momentum · Trend · Quality</t>
         </is>
       </c>
-      <c r="AS29" s="4" t="inlineStr"/>
-      <c r="AT29" s="4" t="inlineStr"/>
-      <c r="AU29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV29" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AU29" s="4" t="inlineStr"/>
+      <c r="AV29" s="4" t="inlineStr"/>
+      <c r="AW29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX29" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -4937,7 +5095,7 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>Rotation → TRV (+12.2pp)</t>
+          <t>→ TRV · +12.2pp alpha</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
@@ -4957,114 +5115,120 @@
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="N30" s="4" t="n">
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O30" s="4" t="inlineStr"/>
+      <c r="P30" s="4" t="n">
         <v>46.6</v>
       </c>
-      <c r="O30" s="4" t="n">
+      <c r="Q30" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="P30" s="4" t="inlineStr">
+      <c r="R30" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 21 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="Q30" s="4" t="n">
+      <c r="S30" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="R30" s="4" t="inlineStr"/>
-      <c r="S30" s="4" t="inlineStr"/>
-      <c r="T30" s="4" t="inlineStr">
-        <is>
-          <t>Rank → 3→3 · Conf 47% · band WATCH · 6d left · → EXIT (rotate to TRV)</t>
-        </is>
-      </c>
+      <c r="T30" s="4" t="inlineStr"/>
       <c r="U30" s="4" t="inlineStr"/>
-      <c r="V30" s="4" t="n">
+      <c r="V30" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 3→3 · Conf 47% · band WATCH→HOLD · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="W30" s="4" t="inlineStr"/>
+      <c r="X30" s="4" t="n">
         <v>47.3</v>
       </c>
-      <c r="W30" s="4" t="inlineStr">
+      <c r="Y30" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X30" s="4" t="n">
+      <c r="Z30" s="4" t="n">
         <v>17.1</v>
       </c>
-      <c r="Y30" s="4" t="n">
+      <c r="AA30" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="Z30" s="4" t="n">
+      <c r="AB30" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="AA30" s="4" t="n">
+      <c r="AC30" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AB30" s="4" t="inlineStr">
+      <c r="AD30" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC30" s="4" t="n">
+      <c r="AE30" s="4" t="n">
         <v>202.81</v>
       </c>
-      <c r="AD30" s="4" t="n">
+      <c r="AF30" s="4" t="n">
         <v>202.81</v>
       </c>
-      <c r="AE30" s="4" t="n">
+      <c r="AG30" s="4" t="n">
         <v>200.78</v>
       </c>
-      <c r="AF30" s="4" t="n">
+      <c r="AH30" s="4" t="n">
         <v>204.84</v>
       </c>
-      <c r="AG30" s="4" t="n">
+      <c r="AI30" s="4" t="n">
         <v>192.67</v>
       </c>
-      <c r="AH30" s="4" t="n">
+      <c r="AJ30" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI30" s="4" t="n">
+      <c r="AK30" s="4" t="n">
         <v>219.03</v>
       </c>
-      <c r="AJ30" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK30" s="4" t="n">
+      <c r="AL30" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM30" s="4" t="n">
         <v>233.23</v>
       </c>
-      <c r="AL30" s="4" t="n">
+      <c r="AN30" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AM30" s="4" t="inlineStr"/>
-      <c r="AN30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO30" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AO30" s="4" t="inlineStr"/>
       <c r="AP30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" s="4" t="n">
         <v>-1.02</v>
       </c>
-      <c r="AQ30" s="4" t="inlineStr">
+      <c r="AS30" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AR30" s="4" t="inlineStr">
+      <c r="AT30" s="4" t="inlineStr">
         <is>
           <t>Quality · Growth · Mean Reversion</t>
         </is>
       </c>
-      <c r="AS30" s="4" t="inlineStr"/>
-      <c r="AT30" s="4" t="inlineStr"/>
-      <c r="AU30" s="4" t="n">
+      <c r="AU30" s="4" t="inlineStr"/>
+      <c r="AV30" s="4" t="inlineStr"/>
+      <c r="AW30" s="4" t="n">
         <v>12.15</v>
       </c>
-      <c r="AV30" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AX30" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -5101,7 +5265,7 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>Rotation → TRV (+13.0pp)</t>
+          <t>→ TRV · +13.0pp alpha</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
@@ -5124,111 +5288,117 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N31" s="4" t="n">
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O31" s="4" t="inlineStr"/>
+      <c r="P31" s="4" t="n">
         <v>48.9</v>
       </c>
-      <c r="O31" s="4" t="n">
+      <c r="Q31" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="P31" s="4" t="inlineStr">
+      <c r="R31" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 18 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="Q31" s="4" t="n">
+      <c r="S31" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="R31" s="4" t="inlineStr"/>
-      <c r="S31" s="4" t="inlineStr"/>
-      <c r="T31" s="4" t="inlineStr">
+      <c r="T31" s="4" t="inlineStr"/>
+      <c r="U31" s="4" t="inlineStr"/>
+      <c r="V31" s="4" t="inlineStr">
         <is>
           <t>Rank → 4→4 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
-      <c r="U31" s="4" t="inlineStr"/>
-      <c r="V31" s="4" t="n">
+      <c r="W31" s="4" t="inlineStr"/>
+      <c r="X31" s="4" t="n">
         <v>49.7</v>
       </c>
-      <c r="W31" s="4" t="inlineStr">
+      <c r="Y31" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X31" s="4" t="n">
+      <c r="Z31" s="4" t="n">
         <v>16.3</v>
       </c>
-      <c r="Y31" s="4" t="n">
+      <c r="AA31" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="Z31" s="4" t="n">
+      <c r="AB31" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="AA31" s="4" t="n">
+      <c r="AC31" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AB31" s="4" t="inlineStr">
+      <c r="AD31" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC31" s="4" t="n">
+      <c r="AE31" s="4" t="n">
         <v>341.1</v>
       </c>
-      <c r="AD31" s="4" t="n">
+      <c r="AF31" s="4" t="n">
         <v>341.1</v>
       </c>
-      <c r="AE31" s="4" t="n">
+      <c r="AG31" s="4" t="n">
         <v>337.69</v>
       </c>
-      <c r="AF31" s="4" t="n">
+      <c r="AH31" s="4" t="n">
         <v>344.51</v>
       </c>
-      <c r="AG31" s="4" t="n">
+      <c r="AI31" s="4" t="n">
         <v>324.05</v>
       </c>
-      <c r="AH31" s="4" t="n">
+      <c r="AJ31" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI31" s="4" t="n">
+      <c r="AK31" s="4" t="n">
         <v>368.39</v>
       </c>
-      <c r="AJ31" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK31" s="4" t="n">
+      <c r="AL31" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM31" s="4" t="n">
         <v>392.26</v>
       </c>
-      <c r="AL31" s="4" t="n">
+      <c r="AN31" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AM31" s="4" t="inlineStr"/>
-      <c r="AN31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO31" s="4" t="n">
+      <c r="AO31" s="4" t="inlineStr"/>
+      <c r="AP31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" s="4" t="n">
         <v>3.13</v>
       </c>
-      <c r="AP31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ31" s="4" t="inlineStr">
+      <c r="AR31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AR31" s="4" t="inlineStr">
+      <c r="AT31" s="4" t="inlineStr">
         <is>
           <t>Momentum · Value · Mean Reversion</t>
         </is>
       </c>
-      <c r="AS31" s="4" t="inlineStr"/>
-      <c r="AT31" s="4" t="inlineStr"/>
-      <c r="AU31" s="4" t="n">
+      <c r="AU31" s="4" t="inlineStr"/>
+      <c r="AV31" s="4" t="inlineStr"/>
+      <c r="AW31" s="4" t="n">
         <v>12.97</v>
       </c>
-      <c r="AV31" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AX31" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -5265,7 +5435,7 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>Rotation → TRV (+14.4pp)</t>
+          <t>→ TRV · +14.4pp alpha</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
@@ -5288,113 +5458,119 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N32" s="4" t="n">
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr"/>
+      <c r="P32" s="4" t="n">
         <v>49.7</v>
       </c>
-      <c r="O32" s="4" t="n">
+      <c r="Q32" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="P32" s="4" t="inlineStr">
+      <c r="R32" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 48 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="Q32" s="4" t="n">
+      <c r="S32" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="R32" s="4" t="n">
+      <c r="T32" s="4" t="n">
         <v>0.127</v>
       </c>
-      <c r="S32" s="4" t="inlineStr"/>
-      <c r="T32" s="4" t="inlineStr">
+      <c r="U32" s="4" t="inlineStr"/>
+      <c r="V32" s="4" t="inlineStr">
         <is>
           <t>Rank → 5→5 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
-      <c r="U32" s="4" t="inlineStr"/>
-      <c r="V32" s="4" t="n">
+      <c r="W32" s="4" t="inlineStr"/>
+      <c r="X32" s="4" t="n">
         <v>50.5</v>
       </c>
-      <c r="W32" s="4" t="inlineStr">
+      <c r="Y32" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X32" s="4" t="n">
+      <c r="Z32" s="4" t="n">
         <v>14.8</v>
       </c>
-      <c r="Y32" s="4" t="n">
+      <c r="AA32" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="Z32" s="4" t="n">
+      <c r="AB32" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="AA32" s="4" t="n">
+      <c r="AC32" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AB32" s="4" t="inlineStr">
+      <c r="AD32" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC32" s="4" t="n">
+      <c r="AE32" s="4" t="n">
         <v>225.02</v>
       </c>
-      <c r="AD32" s="4" t="n">
+      <c r="AF32" s="4" t="n">
         <v>225.02</v>
       </c>
-      <c r="AE32" s="4" t="n">
+      <c r="AG32" s="4" t="n">
         <v>222.77</v>
       </c>
-      <c r="AF32" s="4" t="n">
+      <c r="AH32" s="4" t="n">
         <v>227.27</v>
       </c>
-      <c r="AG32" s="4" t="n">
+      <c r="AI32" s="4" t="n">
         <v>213.77</v>
       </c>
-      <c r="AH32" s="4" t="n">
+      <c r="AJ32" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI32" s="4" t="n">
+      <c r="AK32" s="4" t="n">
         <v>243.02</v>
       </c>
-      <c r="AJ32" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK32" s="4" t="n">
+      <c r="AL32" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM32" s="4" t="n">
         <v>258.77</v>
       </c>
-      <c r="AL32" s="4" t="n">
+      <c r="AN32" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AM32" s="4" t="inlineStr"/>
-      <c r="AN32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO32" s="4" t="n">
+      <c r="AO32" s="4" t="inlineStr"/>
+      <c r="AP32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" s="4" t="n">
         <v>8.01</v>
       </c>
-      <c r="AP32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ32" s="4" t="inlineStr">
+      <c r="AR32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS32" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AR32" s="4" t="inlineStr">
+      <c r="AT32" s="4" t="inlineStr">
         <is>
           <t>Mean Reversion · Growth · Value</t>
         </is>
       </c>
-      <c r="AS32" s="4" t="inlineStr"/>
-      <c r="AT32" s="4" t="inlineStr"/>
-      <c r="AU32" s="4" t="n">
+      <c r="AU32" s="4" t="inlineStr"/>
+      <c r="AV32" s="4" t="inlineStr"/>
+      <c r="AW32" s="4" t="n">
         <v>14.45</v>
       </c>
-      <c r="AV32" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AX32" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -5431,7 +5607,7 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>Rotation → TRV (+14.8pp)</t>
+          <t>→ TRV · +14.8pp alpha</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
@@ -5451,114 +5627,120 @@
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="N33" s="4" t="n">
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O33" s="4" t="inlineStr"/>
+      <c r="P33" s="4" t="n">
         <v>50.2</v>
       </c>
-      <c r="O33" s="4" t="n">
+      <c r="Q33" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="P33" s="4" t="inlineStr">
+      <c r="R33" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 9 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="Q33" s="4" t="n">
+      <c r="S33" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="R33" s="4" t="inlineStr"/>
-      <c r="S33" s="4" t="inlineStr"/>
-      <c r="T33" s="4" t="inlineStr">
-        <is>
-          <t>Rank → 6→6 · Conf 51% · band WATCH · 6d left · → EXIT (rotate to TRV)</t>
-        </is>
-      </c>
+      <c r="T33" s="4" t="inlineStr"/>
       <c r="U33" s="4" t="inlineStr"/>
-      <c r="V33" s="4" t="n">
+      <c r="V33" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 6→6 · Conf 51% · band WATCH→HOLD · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="W33" s="4" t="inlineStr"/>
+      <c r="X33" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="W33" s="4" t="inlineStr">
+      <c r="Y33" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X33" s="4" t="n">
+      <c r="Z33" s="4" t="n">
         <v>14.5</v>
       </c>
-      <c r="Y33" s="4" t="n">
+      <c r="AA33" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="Z33" s="4" t="n">
+      <c r="AB33" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="AA33" s="4" t="n">
+      <c r="AC33" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AB33" s="4" t="inlineStr">
+      <c r="AD33" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC33" s="4" t="n">
+      <c r="AE33" s="4" t="n">
         <v>1065.22</v>
       </c>
-      <c r="AD33" s="4" t="n">
+      <c r="AF33" s="4" t="n">
         <v>1065.22</v>
       </c>
-      <c r="AE33" s="4" t="n">
+      <c r="AG33" s="4" t="n">
         <v>1054.57</v>
       </c>
-      <c r="AF33" s="4" t="n">
+      <c r="AH33" s="4" t="n">
         <v>1075.87</v>
       </c>
-      <c r="AG33" s="4" t="n">
+      <c r="AI33" s="4" t="n">
         <v>1011.96</v>
       </c>
-      <c r="AH33" s="4" t="n">
+      <c r="AJ33" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI33" s="4" t="n">
+      <c r="AK33" s="4" t="n">
         <v>1150.44</v>
       </c>
-      <c r="AJ33" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK33" s="4" t="n">
+      <c r="AL33" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM33" s="4" t="n">
         <v>1225</v>
       </c>
-      <c r="AL33" s="4" t="n">
+      <c r="AN33" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AM33" s="4" t="inlineStr"/>
-      <c r="AN33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO33" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AO33" s="4" t="inlineStr"/>
       <c r="AP33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" s="4" t="n">
         <v>-4.4</v>
       </c>
-      <c r="AQ33" s="4" t="inlineStr">
+      <c r="AS33" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AR33" s="4" t="inlineStr">
+      <c r="AT33" s="4" t="inlineStr">
         <is>
           <t>Value · News · Event Driven</t>
         </is>
       </c>
-      <c r="AS33" s="4" t="inlineStr"/>
-      <c r="AT33" s="4" t="inlineStr"/>
-      <c r="AU33" s="4" t="n">
+      <c r="AU33" s="4" t="inlineStr"/>
+      <c r="AV33" s="4" t="inlineStr"/>
+      <c r="AW33" s="4" t="n">
         <v>14.77</v>
       </c>
-      <c r="AV33" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AX33" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -5595,7 +5777,7 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>Rotation → TRV (+14.9pp)</t>
+          <t>→ TRV · +14.9pp alpha</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
@@ -5618,113 +5800,119 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N34" s="4" t="n">
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O34" s="4" t="inlineStr"/>
+      <c r="P34" s="4" t="n">
         <v>49.7</v>
       </c>
-      <c r="O34" s="4" t="n">
+      <c r="Q34" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="P34" s="4" t="inlineStr">
+      <c r="R34" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="Q34" s="4" t="n">
+      <c r="S34" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="R34" s="4" t="n">
+      <c r="T34" s="4" t="n">
         <v>0.109</v>
       </c>
-      <c r="S34" s="4" t="inlineStr"/>
-      <c r="T34" s="4" t="inlineStr">
+      <c r="U34" s="4" t="inlineStr"/>
+      <c r="V34" s="4" t="inlineStr">
         <is>
           <t>Rank → 7→7 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
-      <c r="U34" s="4" t="inlineStr"/>
-      <c r="V34" s="4" t="n">
+      <c r="W34" s="4" t="inlineStr"/>
+      <c r="X34" s="4" t="n">
         <v>50.5</v>
       </c>
-      <c r="W34" s="4" t="inlineStr">
+      <c r="Y34" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X34" s="4" t="n">
+      <c r="Z34" s="4" t="n">
         <v>14.4</v>
       </c>
-      <c r="Y34" s="4" t="n">
+      <c r="AA34" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="Z34" s="4" t="n">
+      <c r="AB34" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="AA34" s="4" t="n">
+      <c r="AC34" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AB34" s="4" t="inlineStr">
+      <c r="AD34" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC34" s="4" t="n">
+      <c r="AE34" s="4" t="n">
         <v>333.74</v>
       </c>
-      <c r="AD34" s="4" t="n">
+      <c r="AF34" s="4" t="n">
         <v>333.74</v>
       </c>
-      <c r="AE34" s="4" t="n">
+      <c r="AG34" s="4" t="n">
         <v>330.4</v>
       </c>
-      <c r="AF34" s="4" t="n">
+      <c r="AH34" s="4" t="n">
         <v>337.08</v>
       </c>
-      <c r="AG34" s="4" t="n">
+      <c r="AI34" s="4" t="n">
         <v>317.05</v>
       </c>
-      <c r="AH34" s="4" t="n">
+      <c r="AJ34" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI34" s="4" t="n">
+      <c r="AK34" s="4" t="n">
         <v>360.44</v>
       </c>
-      <c r="AJ34" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK34" s="4" t="n">
+      <c r="AL34" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM34" s="4" t="n">
         <v>383.8</v>
       </c>
-      <c r="AL34" s="4" t="n">
+      <c r="AN34" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AM34" s="4" t="inlineStr"/>
-      <c r="AN34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO34" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AO34" s="4" t="inlineStr"/>
       <c r="AP34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" s="4" t="n">
         <v>-7.44</v>
       </c>
-      <c r="AQ34" s="4" t="inlineStr">
+      <c r="AS34" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AR34" s="4" t="inlineStr">
+      <c r="AT34" s="4" t="inlineStr">
         <is>
           <t>Value · Trend · Momentum</t>
         </is>
       </c>
-      <c r="AS34" s="4" t="inlineStr"/>
-      <c r="AT34" s="4" t="inlineStr"/>
-      <c r="AU34" s="4" t="n">
+      <c r="AU34" s="4" t="inlineStr"/>
+      <c r="AV34" s="4" t="inlineStr"/>
+      <c r="AW34" s="4" t="n">
         <v>14.87</v>
       </c>
-      <c r="AV34" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AX34" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -5761,7 +5949,7 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>Rotation → TRV (+15.2pp)</t>
+          <t>→ TRV · +15.2pp alpha</t>
         </is>
       </c>
       <c r="H35" s="4" t="n">
@@ -5784,113 +5972,119 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N35" s="4" t="n">
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O35" s="4" t="inlineStr"/>
+      <c r="P35" s="4" t="n">
         <v>52.9</v>
       </c>
-      <c r="O35" s="4" t="n">
+      <c r="Q35" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="P35" s="4" t="inlineStr">
+      <c r="R35" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 33 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="Q35" s="4" t="n">
+      <c r="S35" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="R35" s="4" t="n">
+      <c r="T35" s="4" t="n">
         <v>0.15</v>
       </c>
-      <c r="S35" s="4" t="inlineStr"/>
-      <c r="T35" s="4" t="inlineStr">
+      <c r="U35" s="4" t="inlineStr"/>
+      <c r="V35" s="4" t="inlineStr">
         <is>
           <t>Rank → 8→8 · Conf 54% · band HOLD · 58d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
-      <c r="U35" s="4" t="inlineStr"/>
-      <c r="V35" s="4" t="n">
+      <c r="W35" s="4" t="inlineStr"/>
+      <c r="X35" s="4" t="n">
         <v>53.6</v>
       </c>
-      <c r="W35" s="4" t="inlineStr">
+      <c r="Y35" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X35" s="4" t="n">
+      <c r="Z35" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="Y35" s="4" t="n">
+      <c r="AA35" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="Z35" s="4" t="n">
+      <c r="AB35" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="AA35" s="4" t="n">
+      <c r="AC35" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="AB35" s="4" t="inlineStr">
+      <c r="AD35" s="4" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="AC35" s="4" t="n">
+      <c r="AE35" s="4" t="n">
         <v>393.82</v>
       </c>
-      <c r="AD35" s="4" t="n">
+      <c r="AF35" s="4" t="n">
         <v>393.82</v>
       </c>
-      <c r="AE35" s="4" t="n">
+      <c r="AG35" s="4" t="n">
         <v>389.88</v>
       </c>
-      <c r="AF35" s="4" t="n">
+      <c r="AH35" s="4" t="n">
         <v>397.76</v>
       </c>
-      <c r="AG35" s="4" t="n">
+      <c r="AI35" s="4" t="n">
         <v>374.13</v>
       </c>
-      <c r="AH35" s="4" t="n">
+      <c r="AJ35" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI35" s="4" t="n">
+      <c r="AK35" s="4" t="n">
         <v>425.33</v>
       </c>
-      <c r="AJ35" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK35" s="4" t="n">
+      <c r="AL35" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM35" s="4" t="n">
         <v>452.89</v>
       </c>
-      <c r="AL35" s="4" t="n">
+      <c r="AN35" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AM35" s="4" t="inlineStr"/>
-      <c r="AN35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO35" s="4" t="n">
+      <c r="AO35" s="4" t="inlineStr"/>
+      <c r="AP35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="AP35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ35" s="4" t="inlineStr">
+      <c r="AR35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AR35" s="4" t="inlineStr">
+      <c r="AT35" s="4" t="inlineStr">
         <is>
           <t>Quality · Mean Reversion · Trend</t>
         </is>
       </c>
-      <c r="AS35" s="4" t="inlineStr"/>
-      <c r="AT35" s="4" t="inlineStr"/>
-      <c r="AU35" s="4" t="n">
+      <c r="AU35" s="4" t="inlineStr"/>
+      <c r="AV35" s="4" t="inlineStr"/>
+      <c r="AW35" s="4" t="n">
         <v>15.21</v>
       </c>
-      <c r="AV35" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AX35" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -5927,7 +6121,7 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>Rotation → TRV (+15.5pp)</t>
+          <t>→ TRV · +15.5pp alpha</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
@@ -5950,113 +6144,119 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N36" s="4" t="n">
+      <c r="N36" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O36" s="4" t="inlineStr"/>
+      <c r="P36" s="4" t="n">
         <v>49.7</v>
       </c>
-      <c r="O36" s="4" t="n">
+      <c r="Q36" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="P36" s="4" t="inlineStr">
+      <c r="R36" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 11 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="Q36" s="4" t="n">
+      <c r="S36" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="R36" s="4" t="n">
+      <c r="T36" s="4" t="n">
         <v>0.08500000000000001</v>
       </c>
-      <c r="S36" s="4" t="inlineStr"/>
-      <c r="T36" s="4" t="inlineStr">
+      <c r="U36" s="4" t="inlineStr"/>
+      <c r="V36" s="4" t="inlineStr">
         <is>
           <t>Rank → 9→9 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
-      <c r="U36" s="4" t="inlineStr"/>
-      <c r="V36" s="4" t="n">
+      <c r="W36" s="4" t="inlineStr"/>
+      <c r="X36" s="4" t="n">
         <v>50.5</v>
       </c>
-      <c r="W36" s="4" t="inlineStr">
+      <c r="Y36" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X36" s="4" t="n">
+      <c r="Z36" s="4" t="n">
         <v>13.8</v>
       </c>
-      <c r="Y36" s="4" t="n">
+      <c r="AA36" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="Z36" s="4" t="n">
+      <c r="AB36" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="AA36" s="4" t="n">
+      <c r="AC36" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AB36" s="4" t="inlineStr">
+      <c r="AD36" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC36" s="4" t="n">
+      <c r="AE36" s="4" t="n">
         <v>81.56</v>
       </c>
-      <c r="AD36" s="4" t="n">
+      <c r="AF36" s="4" t="n">
         <v>81.56</v>
       </c>
-      <c r="AE36" s="4" t="n">
+      <c r="AG36" s="4" t="n">
         <v>80.73999999999999</v>
       </c>
-      <c r="AF36" s="4" t="n">
+      <c r="AH36" s="4" t="n">
         <v>82.38</v>
       </c>
-      <c r="AG36" s="4" t="n">
+      <c r="AI36" s="4" t="n">
         <v>77.48</v>
       </c>
-      <c r="AH36" s="4" t="n">
+      <c r="AJ36" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI36" s="4" t="n">
+      <c r="AK36" s="4" t="n">
         <v>88.08</v>
       </c>
-      <c r="AJ36" s="4" t="n">
+      <c r="AL36" s="4" t="n">
         <v>7.99</v>
       </c>
-      <c r="AK36" s="4" t="n">
+      <c r="AM36" s="4" t="n">
         <v>93.79000000000001</v>
       </c>
-      <c r="AL36" s="4" t="n">
+      <c r="AN36" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AM36" s="4" t="inlineStr"/>
-      <c r="AN36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO36" s="4" t="n">
+      <c r="AO36" s="4" t="inlineStr"/>
+      <c r="AP36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ36" s="4" t="n">
         <v>7.39</v>
       </c>
-      <c r="AP36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ36" s="4" t="inlineStr">
+      <c r="AR36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS36" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AR36" s="4" t="inlineStr">
+      <c r="AT36" s="4" t="inlineStr">
         <is>
           <t>Momentum · News · Quality</t>
         </is>
       </c>
-      <c r="AS36" s="4" t="inlineStr"/>
-      <c r="AT36" s="4" t="inlineStr"/>
-      <c r="AU36" s="4" t="n">
+      <c r="AU36" s="4" t="inlineStr"/>
+      <c r="AV36" s="4" t="inlineStr"/>
+      <c r="AW36" s="4" t="n">
         <v>15.5</v>
       </c>
-      <c r="AV36" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AX36" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -6093,7 +6293,7 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>Rotation → TRV (+16.4pp)</t>
+          <t>→ TRV · +16.4pp alpha</t>
         </is>
       </c>
       <c r="H37" s="4" t="n">
@@ -6116,111 +6316,117 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N37" s="4" t="n">
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O37" s="4" t="inlineStr"/>
+      <c r="P37" s="4" t="n">
         <v>52.9</v>
       </c>
-      <c r="O37" s="4" t="n">
+      <c r="Q37" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="P37" s="4" t="inlineStr">
+      <c r="R37" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 15 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="Q37" s="4" t="n">
+      <c r="S37" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="R37" s="4" t="inlineStr"/>
-      <c r="S37" s="4" t="inlineStr"/>
-      <c r="T37" s="4" t="inlineStr">
+      <c r="T37" s="4" t="inlineStr"/>
+      <c r="U37" s="4" t="inlineStr"/>
+      <c r="V37" s="4" t="inlineStr">
         <is>
           <t>Rank → 10→10 · Conf 54% · band HOLD · 58d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
-      <c r="U37" s="4" t="inlineStr"/>
-      <c r="V37" s="4" t="n">
+      <c r="W37" s="4" t="inlineStr"/>
+      <c r="X37" s="4" t="n">
         <v>53.6</v>
       </c>
-      <c r="W37" s="4" t="inlineStr">
+      <c r="Y37" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X37" s="4" t="n">
+      <c r="Z37" s="4" t="n">
         <v>12.8</v>
       </c>
-      <c r="Y37" s="4" t="n">
+      <c r="AA37" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="Z37" s="4" t="n">
+      <c r="AB37" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="AA37" s="4" t="n">
+      <c r="AC37" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="AB37" s="4" t="inlineStr">
+      <c r="AD37" s="4" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="AC37" s="4" t="n">
+      <c r="AE37" s="4" t="n">
         <v>159.84</v>
       </c>
-      <c r="AD37" s="4" t="n">
+      <c r="AF37" s="4" t="n">
         <v>159.84</v>
       </c>
-      <c r="AE37" s="4" t="n">
+      <c r="AG37" s="4" t="n">
         <v>158.24</v>
       </c>
-      <c r="AF37" s="4" t="n">
+      <c r="AH37" s="4" t="n">
         <v>161.44</v>
       </c>
-      <c r="AG37" s="4" t="n">
+      <c r="AI37" s="4" t="n">
         <v>151.85</v>
       </c>
-      <c r="AH37" s="4" t="n">
+      <c r="AJ37" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI37" s="4" t="n">
+      <c r="AK37" s="4" t="n">
         <v>172.63</v>
       </c>
-      <c r="AJ37" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK37" s="4" t="n">
+      <c r="AL37" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM37" s="4" t="n">
         <v>183.82</v>
       </c>
-      <c r="AL37" s="4" t="n">
+      <c r="AN37" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AM37" s="4" t="inlineStr"/>
-      <c r="AN37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO37" s="4" t="n">
+      <c r="AO37" s="4" t="inlineStr"/>
+      <c r="AP37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ37" s="4" t="n">
         <v>10.29</v>
       </c>
-      <c r="AP37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ37" s="4" t="inlineStr">
+      <c r="AR37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS37" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AR37" s="4" t="inlineStr">
+      <c r="AT37" s="4" t="inlineStr">
         <is>
           <t>Momentum · News · Value</t>
         </is>
       </c>
-      <c r="AS37" s="4" t="inlineStr"/>
-      <c r="AT37" s="4" t="inlineStr"/>
-      <c r="AU37" s="4" t="n">
+      <c r="AU37" s="4" t="inlineStr"/>
+      <c r="AV37" s="4" t="inlineStr"/>
+      <c r="AW37" s="4" t="n">
         <v>16.4</v>
       </c>
-      <c r="AV37" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AX37" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -6257,7 +6463,7 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>Rotation → TRV (+37.2pp)</t>
+          <t>→ TRV · +37.2pp alpha</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
@@ -6277,114 +6483,120 @@
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="N38" s="4" t="n">
+          <t>WEAK</t>
+        </is>
+      </c>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>🟡</t>
+        </is>
+      </c>
+      <c r="O38" s="4" t="inlineStr"/>
+      <c r="P38" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="O38" s="4" t="n">
+      <c r="Q38" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="P38" s="4" t="inlineStr">
+      <c r="R38" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 26 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="Q38" s="4" t="n">
+      <c r="S38" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="R38" s="4" t="inlineStr"/>
-      <c r="S38" s="4" t="inlineStr"/>
-      <c r="T38" s="4" t="inlineStr">
-        <is>
-          <t>Rank → 11→11 · Conf 29% · band REVIEW · 6d left · → EXIT (rotate to TRV)</t>
-        </is>
-      </c>
+      <c r="T38" s="4" t="inlineStr"/>
       <c r="U38" s="4" t="inlineStr"/>
-      <c r="V38" s="4" t="n">
+      <c r="V38" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 11→11 · Conf 29% · band REVIEW→WEAK · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="W38" s="4" t="inlineStr"/>
+      <c r="X38" s="4" t="n">
         <v>28.7</v>
       </c>
-      <c r="W38" s="4" t="inlineStr">
+      <c r="Y38" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X38" s="4" t="n">
+      <c r="Z38" s="4" t="n">
         <v>-7.9</v>
       </c>
-      <c r="Y38" s="4" t="n">
+      <c r="AA38" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="Z38" s="4" t="n">
+      <c r="AB38" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="AA38" s="4" t="n">
+      <c r="AC38" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AB38" s="4" t="inlineStr">
+      <c r="AD38" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC38" s="4" t="n">
+      <c r="AE38" s="4" t="n">
         <v>95.04000000000001</v>
       </c>
-      <c r="AD38" s="4" t="n">
+      <c r="AF38" s="4" t="n">
         <v>95.04000000000001</v>
       </c>
-      <c r="AE38" s="4" t="n">
+      <c r="AG38" s="4" t="n">
         <v>94.09</v>
       </c>
-      <c r="AF38" s="4" t="n">
+      <c r="AH38" s="4" t="n">
         <v>95.98999999999999</v>
       </c>
-      <c r="AG38" s="4" t="n">
+      <c r="AI38" s="4" t="n">
         <v>90.29000000000001</v>
       </c>
-      <c r="AH38" s="4" t="n">
+      <c r="AJ38" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI38" s="4" t="n">
+      <c r="AK38" s="4" t="n">
         <v>102.64</v>
       </c>
-      <c r="AJ38" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK38" s="4" t="n">
+      <c r="AL38" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM38" s="4" t="n">
         <v>109.3</v>
       </c>
-      <c r="AL38" s="4" t="n">
+      <c r="AN38" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AM38" s="4" t="inlineStr"/>
-      <c r="AN38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO38" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AO38" s="4" t="inlineStr"/>
       <c r="AP38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" s="4" t="n">
         <v>-5.09</v>
       </c>
-      <c r="AQ38" s="4" t="inlineStr">
+      <c r="AS38" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AR38" s="4" t="inlineStr">
+      <c r="AT38" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
-      <c r="AS38" s="4" t="inlineStr"/>
-      <c r="AT38" s="4" t="inlineStr"/>
-      <c r="AU38" s="4" t="n">
+      <c r="AU38" s="4" t="inlineStr"/>
+      <c r="AV38" s="4" t="inlineStr"/>
+      <c r="AW38" s="4" t="n">
         <v>37.17</v>
       </c>
-      <c r="AV38" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AX38" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -6421,7 +6633,7 @@
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>Rotation → TRV (+37.8pp)</t>
+          <t>→ TRV · +37.8pp alpha</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
@@ -6441,116 +6653,122 @@
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="N39" s="4" t="n">
+          <t>WEAK</t>
+        </is>
+      </c>
+      <c r="N39" s="4" t="inlineStr">
+        <is>
+          <t>🟡</t>
+        </is>
+      </c>
+      <c r="O39" s="4" t="inlineStr"/>
+      <c r="P39" s="4" t="n">
         <v>30.1</v>
       </c>
-      <c r="O39" s="4" t="n">
+      <c r="Q39" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="P39" s="4" t="inlineStr">
+      <c r="R39" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 12 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="Q39" s="4" t="n">
+      <c r="S39" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="R39" s="4" t="n">
+      <c r="T39" s="4" t="n">
         <v>0.122</v>
       </c>
-      <c r="S39" s="4" t="inlineStr"/>
-      <c r="T39" s="4" t="inlineStr">
-        <is>
-          <t>Rank → 12→12 · Conf 31% · band REVIEW · 58d left · → EXIT (rotate to TRV)</t>
-        </is>
-      </c>
       <c r="U39" s="4" t="inlineStr"/>
-      <c r="V39" s="4" t="n">
+      <c r="V39" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 12→12 · Conf 31% · band REVIEW→WEAK · 58d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="W39" s="4" t="inlineStr"/>
+      <c r="X39" s="4" t="n">
         <v>30.8</v>
       </c>
-      <c r="W39" s="4" t="inlineStr">
+      <c r="Y39" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X39" s="4" t="n">
+      <c r="Z39" s="4" t="n">
         <v>-8.5</v>
       </c>
-      <c r="Y39" s="4" t="n">
+      <c r="AA39" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="Z39" s="4" t="n">
+      <c r="AB39" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="AA39" s="4" t="n">
+      <c r="AC39" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="AB39" s="4" t="inlineStr">
+      <c r="AD39" s="4" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="AC39" s="4" t="n">
+      <c r="AE39" s="4" t="n">
         <v>214.03</v>
       </c>
-      <c r="AD39" s="4" t="n">
+      <c r="AF39" s="4" t="n">
         <v>214.03</v>
       </c>
-      <c r="AE39" s="4" t="n">
+      <c r="AG39" s="4" t="n">
         <v>211.89</v>
       </c>
-      <c r="AF39" s="4" t="n">
+      <c r="AH39" s="4" t="n">
         <v>216.17</v>
       </c>
-      <c r="AG39" s="4" t="n">
+      <c r="AI39" s="4" t="n">
         <v>203.33</v>
       </c>
-      <c r="AH39" s="4" t="n">
+      <c r="AJ39" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI39" s="4" t="n">
+      <c r="AK39" s="4" t="n">
         <v>231.15</v>
       </c>
-      <c r="AJ39" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK39" s="4" t="n">
+      <c r="AL39" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM39" s="4" t="n">
         <v>246.13</v>
       </c>
-      <c r="AL39" s="4" t="n">
+      <c r="AN39" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AM39" s="4" t="inlineStr"/>
-      <c r="AN39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO39" s="4" t="n">
+      <c r="AO39" s="4" t="inlineStr"/>
+      <c r="AP39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ39" s="4" t="n">
         <v>0.99</v>
       </c>
-      <c r="AP39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ39" s="4" t="inlineStr">
+      <c r="AR39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS39" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AR39" s="4" t="inlineStr">
+      <c r="AT39" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
-      <c r="AS39" s="4" t="inlineStr"/>
-      <c r="AT39" s="4" t="inlineStr"/>
-      <c r="AU39" s="4" t="n">
+      <c r="AU39" s="4" t="inlineStr"/>
+      <c r="AV39" s="4" t="inlineStr"/>
+      <c r="AW39" s="4" t="n">
         <v>37.79</v>
       </c>
-      <c r="AV39" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AX39" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6805,7 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>Rotation → TRV (+43.9pp)</t>
+          <t>→ TRV · +43.9pp alpha</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
@@ -6607,116 +6825,122 @@
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="N40" s="4" t="n">
+          <t>WEAK</t>
+        </is>
+      </c>
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t>🟡</t>
+        </is>
+      </c>
+      <c r="O40" s="4" t="inlineStr"/>
+      <c r="P40" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="O40" s="4" t="n">
+      <c r="Q40" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="P40" s="4" t="inlineStr">
+      <c r="R40" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 13 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="Q40" s="4" t="n">
+      <c r="S40" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="R40" s="4" t="n">
+      <c r="T40" s="4" t="n">
         <v>0.156</v>
       </c>
-      <c r="S40" s="4" t="inlineStr"/>
-      <c r="T40" s="4" t="inlineStr">
-        <is>
-          <t>Rank → 13→13 · Conf 35% · band REVIEW · 6d left · → EXIT (rotate to TRV)</t>
-        </is>
-      </c>
       <c r="U40" s="4" t="inlineStr"/>
-      <c r="V40" s="4" t="n">
+      <c r="V40" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 13→13 · Conf 35% · band REVIEW→WEAK · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="W40" s="4" t="inlineStr"/>
+      <c r="X40" s="4" t="n">
         <v>34.7</v>
       </c>
-      <c r="W40" s="4" t="inlineStr">
+      <c r="Y40" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X40" s="4" t="n">
+      <c r="Z40" s="4" t="n">
         <v>-14.6</v>
       </c>
-      <c r="Y40" s="4" t="n">
+      <c r="AA40" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="Z40" s="4" t="n">
+      <c r="AB40" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="AA40" s="4" t="n">
+      <c r="AC40" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AB40" s="4" t="inlineStr">
+      <c r="AD40" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC40" s="4" t="n">
+      <c r="AE40" s="4" t="n">
         <v>338.87</v>
       </c>
-      <c r="AD40" s="4" t="n">
+      <c r="AF40" s="4" t="n">
         <v>338.87</v>
       </c>
-      <c r="AE40" s="4" t="n">
+      <c r="AG40" s="4" t="n">
         <v>335.48</v>
       </c>
-      <c r="AF40" s="4" t="n">
+      <c r="AH40" s="4" t="n">
         <v>342.26</v>
       </c>
-      <c r="AG40" s="4" t="n">
+      <c r="AI40" s="4" t="n">
         <v>321.93</v>
       </c>
-      <c r="AH40" s="4" t="n">
+      <c r="AJ40" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI40" s="4" t="n">
+      <c r="AK40" s="4" t="n">
         <v>365.98</v>
       </c>
-      <c r="AJ40" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK40" s="4" t="n">
+      <c r="AL40" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM40" s="4" t="n">
         <v>389.7</v>
       </c>
-      <c r="AL40" s="4" t="n">
+      <c r="AN40" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AM40" s="4" t="inlineStr"/>
-      <c r="AN40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO40" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AO40" s="4" t="inlineStr"/>
       <c r="AP40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR40" s="4" t="n">
         <v>-2.04</v>
       </c>
-      <c r="AQ40" s="4" t="inlineStr">
+      <c r="AS40" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AR40" s="4" t="inlineStr">
+      <c r="AT40" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
-      <c r="AS40" s="4" t="inlineStr"/>
-      <c r="AT40" s="4" t="inlineStr"/>
-      <c r="AU40" s="4" t="n">
+      <c r="AU40" s="4" t="inlineStr"/>
+      <c r="AV40" s="4" t="inlineStr"/>
+      <c r="AW40" s="4" t="n">
         <v>43.85</v>
       </c>
-      <c r="AV40" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AX40" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -6753,7 +6977,7 @@
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>Rotation → TRV (+45.6pp)</t>
+          <t>→ TRV · +45.6pp alpha</t>
         </is>
       </c>
       <c r="H41" s="4" t="n">
@@ -6773,116 +6997,122 @@
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="N41" s="4" t="n">
+          <t>WEAK</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>🟡</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="inlineStr"/>
+      <c r="P41" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="O41" s="4" t="n">
+      <c r="Q41" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="P41" s="4" t="inlineStr">
+      <c r="R41" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 19 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="Q41" s="4" t="n">
+      <c r="S41" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="R41" s="4" t="n">
+      <c r="T41" s="4" t="n">
         <v>0.193</v>
       </c>
-      <c r="S41" s="4" t="inlineStr"/>
-      <c r="T41" s="4" t="inlineStr">
-        <is>
-          <t>Rank → 14→14 · Conf 35% · band REVIEW · 6d left · → EXIT (rotate to TRV)</t>
-        </is>
-      </c>
       <c r="U41" s="4" t="inlineStr"/>
-      <c r="V41" s="4" t="n">
+      <c r="V41" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 14→14 · Conf 35% · band REVIEW→WEAK · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="W41" s="4" t="inlineStr"/>
+      <c r="X41" s="4" t="n">
         <v>34.7</v>
       </c>
-      <c r="W41" s="4" t="inlineStr">
+      <c r="Y41" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X41" s="4" t="n">
+      <c r="Z41" s="4" t="n">
         <v>-16.4</v>
       </c>
-      <c r="Y41" s="4" t="n">
+      <c r="AA41" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="Z41" s="4" t="n">
+      <c r="AB41" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="AA41" s="4" t="n">
+      <c r="AC41" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AB41" s="4" t="inlineStr">
+      <c r="AD41" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC41" s="4" t="n">
+      <c r="AE41" s="4" t="n">
         <v>97.67</v>
       </c>
-      <c r="AD41" s="4" t="n">
+      <c r="AF41" s="4" t="n">
         <v>97.67</v>
       </c>
-      <c r="AE41" s="4" t="n">
+      <c r="AG41" s="4" t="n">
         <v>96.69</v>
       </c>
-      <c r="AF41" s="4" t="n">
+      <c r="AH41" s="4" t="n">
         <v>98.65000000000001</v>
       </c>
-      <c r="AG41" s="4" t="n">
+      <c r="AI41" s="4" t="n">
         <v>92.79000000000001</v>
       </c>
-      <c r="AH41" s="4" t="n">
+      <c r="AJ41" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI41" s="4" t="n">
+      <c r="AK41" s="4" t="n">
         <v>105.48</v>
       </c>
-      <c r="AJ41" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK41" s="4" t="n">
+      <c r="AL41" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM41" s="4" t="n">
         <v>112.32</v>
       </c>
-      <c r="AL41" s="4" t="n">
+      <c r="AN41" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AM41" s="4" t="inlineStr"/>
-      <c r="AN41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO41" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AO41" s="4" t="inlineStr"/>
       <c r="AP41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR41" s="4" t="n">
         <v>-1.52</v>
       </c>
-      <c r="AQ41" s="4" t="inlineStr">
+      <c r="AS41" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AR41" s="4" t="inlineStr">
+      <c r="AT41" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
-      <c r="AS41" s="4" t="inlineStr"/>
-      <c r="AT41" s="4" t="inlineStr"/>
-      <c r="AU41" s="4" t="n">
+      <c r="AU41" s="4" t="inlineStr"/>
+      <c r="AV41" s="4" t="inlineStr"/>
+      <c r="AW41" s="4" t="n">
         <v>45.62</v>
       </c>
-      <c r="AV41" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AX41" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -6919,7 +7149,7 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>Rotation → TRV (+45.9pp)</t>
+          <t>→ TRV · +45.9pp alpha</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
@@ -6939,116 +7169,122 @@
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="N42" s="4" t="n">
+          <t>WEAK</t>
+        </is>
+      </c>
+      <c r="N42" s="4" t="inlineStr">
+        <is>
+          <t>🟡</t>
+        </is>
+      </c>
+      <c r="O42" s="4" t="inlineStr"/>
+      <c r="P42" s="4" t="n">
         <v>27.6</v>
       </c>
-      <c r="O42" s="4" t="n">
+      <c r="Q42" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="P42" s="4" t="inlineStr">
+      <c r="R42" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 6 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="Q42" s="4" t="n">
+      <c r="S42" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="R42" s="4" t="n">
+      <c r="T42" s="4" t="n">
         <v>0.192</v>
       </c>
-      <c r="S42" s="4" t="inlineStr"/>
-      <c r="T42" s="4" t="inlineStr">
-        <is>
-          <t>Rank → 15→15 · Conf 28% · band REVIEW · 6d left · → EXIT (rotate to TRV)</t>
-        </is>
-      </c>
       <c r="U42" s="4" t="inlineStr"/>
-      <c r="V42" s="4" t="n">
+      <c r="V42" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 15→15 · Conf 28% · band REVIEW→WEAK · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="W42" s="4" t="inlineStr"/>
+      <c r="X42" s="4" t="n">
         <v>28.3</v>
       </c>
-      <c r="W42" s="4" t="inlineStr">
+      <c r="Y42" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X42" s="4" t="n">
+      <c r="Z42" s="4" t="n">
         <v>-16.7</v>
       </c>
-      <c r="Y42" s="4" t="n">
+      <c r="AA42" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="Z42" s="4" t="n">
+      <c r="AB42" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="AA42" s="4" t="n">
+      <c r="AC42" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AB42" s="4" t="inlineStr">
+      <c r="AD42" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC42" s="4" t="n">
+      <c r="AE42" s="4" t="n">
         <v>267.71</v>
       </c>
-      <c r="AD42" s="4" t="n">
+      <c r="AF42" s="4" t="n">
         <v>267.71</v>
       </c>
-      <c r="AE42" s="4" t="n">
+      <c r="AG42" s="4" t="n">
         <v>265.03</v>
       </c>
-      <c r="AF42" s="4" t="n">
+      <c r="AH42" s="4" t="n">
         <v>270.39</v>
       </c>
-      <c r="AG42" s="4" t="n">
+      <c r="AI42" s="4" t="n">
         <v>254.32</v>
       </c>
-      <c r="AH42" s="4" t="n">
+      <c r="AJ42" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI42" s="4" t="n">
+      <c r="AK42" s="4" t="n">
         <v>289.13</v>
       </c>
-      <c r="AJ42" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK42" s="4" t="n">
+      <c r="AL42" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM42" s="4" t="n">
         <v>307.87</v>
       </c>
-      <c r="AL42" s="4" t="n">
+      <c r="AN42" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AM42" s="4" t="inlineStr"/>
-      <c r="AN42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO42" s="4" t="n">
+      <c r="AO42" s="4" t="inlineStr"/>
+      <c r="AP42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ42" s="4" t="n">
         <v>1.09</v>
       </c>
-      <c r="AP42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ42" s="4" t="inlineStr">
+      <c r="AR42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS42" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AR42" s="4" t="inlineStr">
+      <c r="AT42" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
-      <c r="AS42" s="4" t="inlineStr"/>
-      <c r="AT42" s="4" t="inlineStr"/>
-      <c r="AU42" s="4" t="n">
+      <c r="AU42" s="4" t="inlineStr"/>
+      <c r="AV42" s="4" t="inlineStr"/>
+      <c r="AW42" s="4" t="n">
         <v>45.94</v>
       </c>
-      <c r="AV42" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AX42" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -7095,116 +7331,124 @@
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="N43" s="4" t="n">
+          <t>STRONG</t>
+        </is>
+      </c>
+      <c r="N43" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" s="4" t="n">
         <v>52.9</v>
       </c>
-      <c r="O43" s="4" t="n">
+      <c r="Q43" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="P43" s="4" t="inlineStr">
+      <c r="R43" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="Q43" s="4" t="n">
+      <c r="S43" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="R43" s="4" t="n">
+      <c r="T43" s="4" t="n">
         <v>0.184</v>
       </c>
-      <c r="S43" s="4" t="inlineStr"/>
-      <c r="T43" s="4" t="inlineStr">
-        <is>
-          <t>Rank #1 · Conf 54% · momentum → · band HOLD · 91d left · → BUY</t>
-        </is>
-      </c>
       <c r="U43" s="4" t="inlineStr"/>
-      <c r="V43" s="4" t="n">
+      <c r="V43" s="4" t="inlineStr">
+        <is>
+          <t>Rank #1 · Conf 54% · momentum → · band HOLD→STRONG · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="W43" s="4" t="inlineStr"/>
+      <c r="X43" s="4" t="n">
         <v>53.6</v>
       </c>
-      <c r="W43" s="4" t="inlineStr">
+      <c r="Y43" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X43" s="4" t="n">
+      <c r="Z43" s="4" t="n">
         <v>64.3</v>
       </c>
-      <c r="Y43" s="4" t="inlineStr"/>
-      <c r="Z43" s="4" t="n">
+      <c r="AA43" s="4" t="inlineStr"/>
+      <c r="AB43" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="AA43" s="4" t="n">
+      <c r="AC43" s="4" t="n">
         <v>91</v>
       </c>
-      <c r="AB43" s="4" t="inlineStr">
+      <c r="AD43" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC43" s="4" t="n">
+      <c r="AE43" s="4" t="n">
         <v>358.56</v>
       </c>
-      <c r="AD43" s="4" t="n">
+      <c r="AF43" s="4" t="n">
         <v>358.56</v>
       </c>
-      <c r="AE43" s="4" t="n">
+      <c r="AG43" s="4" t="n">
         <v>351.39</v>
       </c>
-      <c r="AF43" s="4" t="n">
+      <c r="AH43" s="4" t="n">
         <v>365.73</v>
       </c>
-      <c r="AG43" s="4" t="n">
+      <c r="AI43" s="4" t="n">
         <v>340.632</v>
       </c>
-      <c r="AH43" s="4" t="n">
+      <c r="AJ43" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI43" s="4" t="n">
+      <c r="AK43" s="4" t="n">
         <v>387.2448000000001</v>
       </c>
-      <c r="AJ43" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK43" s="4" t="n">
+      <c r="AL43" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM43" s="4" t="n">
         <v>414.3519360000001</v>
       </c>
-      <c r="AL43" s="4" t="n">
+      <c r="AN43" s="4" t="n">
         <v>15.56</v>
       </c>
-      <c r="AM43" s="4" t="inlineStr"/>
-      <c r="AN43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO43" s="4" t="n">
+      <c r="AO43" s="4" t="inlineStr"/>
+      <c r="AP43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ43" s="4" t="n">
         <v>2.11</v>
       </c>
-      <c r="AP43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ43" s="4" t="inlineStr">
+      <c r="AR43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS43" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AR43" s="4" t="inlineStr"/>
-      <c r="AS43" s="4" t="inlineStr">
+      <c r="AT43" s="4" t="inlineStr"/>
+      <c r="AU43" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AT43" s="4" t="n">
+      <c r="AV43" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AU43" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV43" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AW43" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX43" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -7254,111 +7498,119 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N44" s="4" t="n">
+      <c r="N44" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="4" t="n">
         <v>56.1</v>
       </c>
-      <c r="O44" s="4" t="n">
+      <c r="Q44" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="P44" s="4" t="inlineStr">
+      <c r="R44" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 12 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="Q44" s="4" t="n">
+      <c r="S44" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="R44" s="4" t="inlineStr"/>
-      <c r="S44" s="4" t="inlineStr"/>
-      <c r="T44" s="4" t="inlineStr">
+      <c r="T44" s="4" t="inlineStr"/>
+      <c r="U44" s="4" t="inlineStr"/>
+      <c r="V44" s="4" t="inlineStr">
         <is>
           <t>Rank #2 · Conf 57% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
-      <c r="U44" s="4" t="inlineStr"/>
-      <c r="V44" s="4" t="n">
+      <c r="W44" s="4" t="inlineStr"/>
+      <c r="X44" s="4" t="n">
         <v>56.8</v>
       </c>
-      <c r="W44" s="4" t="inlineStr">
+      <c r="Y44" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X44" s="4" t="n">
+      <c r="Z44" s="4" t="n">
         <v>58.8</v>
       </c>
-      <c r="Y44" s="4" t="inlineStr"/>
-      <c r="Z44" s="4" t="n">
+      <c r="AA44" s="4" t="inlineStr"/>
+      <c r="AB44" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="AA44" s="4" t="n">
+      <c r="AC44" s="4" t="n">
         <v>91</v>
       </c>
-      <c r="AB44" s="4" t="inlineStr">
+      <c r="AD44" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC44" s="4" t="n">
+      <c r="AE44" s="4" t="n">
         <v>368.98</v>
       </c>
-      <c r="AD44" s="4" t="n">
+      <c r="AF44" s="4" t="n">
         <v>368.98</v>
       </c>
-      <c r="AE44" s="4" t="n">
+      <c r="AG44" s="4" t="n">
         <v>365.29</v>
       </c>
-      <c r="AF44" s="4" t="n">
+      <c r="AH44" s="4" t="n">
         <v>372.67</v>
       </c>
-      <c r="AG44" s="4" t="n">
+      <c r="AI44" s="4" t="n">
         <v>350.531</v>
       </c>
-      <c r="AH44" s="4" t="n">
+      <c r="AJ44" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI44" s="4" t="n">
+      <c r="AK44" s="4" t="n">
         <v>413.26</v>
       </c>
-      <c r="AJ44" s="4" t="n">
+      <c r="AL44" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="AK44" s="4" t="n">
+      <c r="AM44" s="4" t="n">
         <v>442.1882</v>
       </c>
-      <c r="AL44" s="4" t="n">
+      <c r="AN44" s="4" t="n">
         <v>19.84</v>
       </c>
-      <c r="AM44" s="4" t="inlineStr"/>
-      <c r="AN44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO44" s="4" t="n">
+      <c r="AO44" s="4" t="inlineStr"/>
+      <c r="AP44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ44" s="4" t="n">
         <v>1.46</v>
       </c>
-      <c r="AP44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ44" s="4" t="inlineStr">
+      <c r="AR44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS44" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AR44" s="4" t="inlineStr"/>
-      <c r="AS44" s="4" t="inlineStr">
+      <c r="AT44" s="4" t="inlineStr"/>
+      <c r="AU44" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AT44" s="4" t="n">
+      <c r="AV44" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AU44" s="4" t="n">
+      <c r="AW44" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="AV44" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AX44" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -7405,114 +7657,122 @@
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="N45" s="4" t="n">
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N45" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" s="4" t="n">
         <v>46.6</v>
       </c>
-      <c r="O45" s="4" t="n">
+      <c r="Q45" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="P45" s="4" t="inlineStr">
+      <c r="R45" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 21 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="Q45" s="4" t="n">
+      <c r="S45" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="R45" s="4" t="inlineStr"/>
-      <c r="S45" s="4" t="inlineStr"/>
-      <c r="T45" s="4" t="inlineStr">
-        <is>
-          <t>Rank #3 · Conf 47% · momentum → · band WATCH · 91d left · → BUY</t>
-        </is>
-      </c>
+      <c r="T45" s="4" t="inlineStr"/>
       <c r="U45" s="4" t="inlineStr"/>
-      <c r="V45" s="4" t="n">
+      <c r="V45" s="4" t="inlineStr">
+        <is>
+          <t>Rank #3 · Conf 47% · momentum → · band WATCH→HOLD · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="W45" s="4" t="inlineStr"/>
+      <c r="X45" s="4" t="n">
         <v>47.3</v>
       </c>
-      <c r="W45" s="4" t="inlineStr">
+      <c r="Y45" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X45" s="4" t="n">
+      <c r="Z45" s="4" t="n">
         <v>55.7</v>
       </c>
-      <c r="Y45" s="4" t="inlineStr"/>
-      <c r="Z45" s="4" t="n">
+      <c r="AA45" s="4" t="inlineStr"/>
+      <c r="AB45" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="AA45" s="4" t="n">
+      <c r="AC45" s="4" t="n">
         <v>91</v>
       </c>
-      <c r="AB45" s="4" t="inlineStr">
+      <c r="AD45" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC45" s="4" t="n">
+      <c r="AE45" s="4" t="n">
         <v>202.81</v>
       </c>
-      <c r="AD45" s="4" t="n">
+      <c r="AF45" s="4" t="n">
         <v>202.81</v>
       </c>
-      <c r="AE45" s="4" t="n">
+      <c r="AG45" s="4" t="n">
         <v>198.75</v>
       </c>
-      <c r="AF45" s="4" t="n">
+      <c r="AH45" s="4" t="n">
         <v>206.87</v>
       </c>
-      <c r="AG45" s="4" t="n">
+      <c r="AI45" s="4" t="n">
         <v>192.6695</v>
       </c>
-      <c r="AH45" s="4" t="n">
+      <c r="AJ45" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI45" s="4" t="n">
+      <c r="AK45" s="4" t="n">
         <v>219.0348</v>
       </c>
-      <c r="AJ45" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK45" s="4" t="n">
+      <c r="AL45" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM45" s="4" t="n">
         <v>234.367236</v>
       </c>
-      <c r="AL45" s="4" t="n">
+      <c r="AN45" s="4" t="n">
         <v>15.56</v>
       </c>
-      <c r="AM45" s="4" t="inlineStr"/>
-      <c r="AN45" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO45" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AO45" s="4" t="inlineStr"/>
       <c r="AP45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR45" s="4" t="n">
         <v>-1.02</v>
       </c>
-      <c r="AQ45" s="4" t="inlineStr">
+      <c r="AS45" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AR45" s="4" t="inlineStr"/>
-      <c r="AS45" s="4" t="inlineStr">
+      <c r="AT45" s="4" t="inlineStr"/>
+      <c r="AU45" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AT45" s="4" t="n">
+      <c r="AV45" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AU45" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV45" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AW45" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX45" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -7562,113 +7822,121 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N46" s="4" t="n">
+      <c r="N46" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="4" t="n">
         <v>52.9</v>
       </c>
-      <c r="O46" s="4" t="n">
+      <c r="Q46" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="P46" s="4" t="inlineStr">
+      <c r="R46" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 33 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="Q46" s="4" t="n">
+      <c r="S46" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="R46" s="4" t="n">
+      <c r="T46" s="4" t="n">
         <v>0.15</v>
       </c>
-      <c r="S46" s="4" t="inlineStr"/>
-      <c r="T46" s="4" t="inlineStr">
+      <c r="U46" s="4" t="inlineStr"/>
+      <c r="V46" s="4" t="inlineStr">
         <is>
           <t>Rank #4 · Conf 54% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
-      <c r="U46" s="4" t="inlineStr"/>
-      <c r="V46" s="4" t="n">
+      <c r="W46" s="4" t="inlineStr"/>
+      <c r="X46" s="4" t="n">
         <v>53.6</v>
       </c>
-      <c r="W46" s="4" t="inlineStr">
+      <c r="Y46" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X46" s="4" t="n">
+      <c r="Z46" s="4" t="n">
         <v>51.8</v>
       </c>
-      <c r="Y46" s="4" t="inlineStr"/>
-      <c r="Z46" s="4" t="n">
+      <c r="AA46" s="4" t="inlineStr"/>
+      <c r="AB46" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="AA46" s="4" t="n">
+      <c r="AC46" s="4" t="n">
         <v>91</v>
       </c>
-      <c r="AB46" s="4" t="inlineStr">
+      <c r="AD46" s="4" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="AC46" s="4" t="n">
+      <c r="AE46" s="4" t="n">
         <v>393.82</v>
       </c>
-      <c r="AD46" s="4" t="n">
+      <c r="AF46" s="4" t="n">
         <v>393.82</v>
       </c>
-      <c r="AE46" s="4" t="n">
+      <c r="AG46" s="4" t="n">
         <v>385.94</v>
       </c>
-      <c r="AF46" s="4" t="n">
+      <c r="AH46" s="4" t="n">
         <v>401.7</v>
       </c>
-      <c r="AG46" s="4" t="n">
+      <c r="AI46" s="4" t="n">
         <v>374.129</v>
       </c>
-      <c r="AH46" s="4" t="n">
+      <c r="AJ46" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI46" s="4" t="n">
+      <c r="AK46" s="4" t="n">
         <v>425.3256</v>
       </c>
-      <c r="AJ46" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK46" s="4" t="n">
+      <c r="AL46" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM46" s="4" t="n">
         <v>455.098392</v>
       </c>
-      <c r="AL46" s="4" t="n">
+      <c r="AN46" s="4" t="n">
         <v>15.56</v>
       </c>
-      <c r="AM46" s="4" t="inlineStr"/>
-      <c r="AN46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO46" s="4" t="n">
+      <c r="AO46" s="4" t="inlineStr"/>
+      <c r="AP46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ46" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="AP46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ46" s="4" t="inlineStr">
+      <c r="AR46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS46" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AR46" s="4" t="inlineStr"/>
-      <c r="AS46" s="4" t="inlineStr">
+      <c r="AT46" s="4" t="inlineStr"/>
+      <c r="AU46" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AT46" s="4" t="n">
+      <c r="AV46" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AU46" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV46" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AW46" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX46" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -7718,113 +7986,121 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N47" s="4" t="n">
+      <c r="N47" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" s="4" t="n">
         <v>49.7</v>
       </c>
-      <c r="O47" s="4" t="n">
+      <c r="Q47" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="P47" s="4" t="inlineStr">
+      <c r="R47" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 11 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="Q47" s="4" t="n">
+      <c r="S47" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="R47" s="4" t="n">
+      <c r="T47" s="4" t="n">
         <v>0.08500000000000001</v>
       </c>
-      <c r="S47" s="4" t="inlineStr"/>
-      <c r="T47" s="4" t="inlineStr">
+      <c r="U47" s="4" t="inlineStr"/>
+      <c r="V47" s="4" t="inlineStr">
         <is>
           <t>Rank #5 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
-      <c r="U47" s="4" t="inlineStr"/>
-      <c r="V47" s="4" t="n">
+      <c r="W47" s="4" t="inlineStr"/>
+      <c r="X47" s="4" t="n">
         <v>50.5</v>
       </c>
-      <c r="W47" s="4" t="inlineStr">
+      <c r="Y47" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X47" s="4" t="n">
+      <c r="Z47" s="4" t="n">
         <v>46.7</v>
       </c>
-      <c r="Y47" s="4" t="inlineStr"/>
-      <c r="Z47" s="4" t="n">
+      <c r="AA47" s="4" t="inlineStr"/>
+      <c r="AB47" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="AA47" s="4" t="n">
+      <c r="AC47" s="4" t="n">
         <v>91</v>
       </c>
-      <c r="AB47" s="4" t="inlineStr">
+      <c r="AD47" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC47" s="4" t="n">
+      <c r="AE47" s="4" t="n">
         <v>81.56</v>
       </c>
-      <c r="AD47" s="4" t="n">
+      <c r="AF47" s="4" t="n">
         <v>81.56</v>
       </c>
-      <c r="AE47" s="4" t="n">
+      <c r="AG47" s="4" t="n">
         <v>79.93000000000001</v>
       </c>
-      <c r="AF47" s="4" t="n">
+      <c r="AH47" s="4" t="n">
         <v>83.19</v>
       </c>
-      <c r="AG47" s="4" t="n">
+      <c r="AI47" s="4" t="n">
         <v>77.482</v>
       </c>
-      <c r="AH47" s="4" t="n">
+      <c r="AJ47" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI47" s="4" t="n">
+      <c r="AK47" s="4" t="n">
         <v>88.0848</v>
       </c>
-      <c r="AJ47" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK47" s="4" t="n">
+      <c r="AL47" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM47" s="4" t="n">
         <v>94.250736</v>
       </c>
-      <c r="AL47" s="4" t="n">
+      <c r="AN47" s="4" t="n">
         <v>15.56</v>
       </c>
-      <c r="AM47" s="4" t="inlineStr"/>
-      <c r="AN47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO47" s="4" t="n">
+      <c r="AO47" s="4" t="inlineStr"/>
+      <c r="AP47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ47" s="4" t="n">
         <v>7.39</v>
       </c>
-      <c r="AP47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ47" s="4" t="inlineStr">
+      <c r="AR47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS47" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AR47" s="4" t="inlineStr"/>
-      <c r="AS47" s="4" t="inlineStr">
+      <c r="AT47" s="4" t="inlineStr"/>
+      <c r="AU47" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AT47" s="4" t="n">
+      <c r="AV47" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AU47" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV47" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AW47" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX47" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -7874,113 +8150,121 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N48" s="4" t="n">
+      <c r="N48" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="4" t="n">
         <v>49.7</v>
       </c>
-      <c r="O48" s="4" t="n">
+      <c r="Q48" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="P48" s="4" t="inlineStr">
+      <c r="R48" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 48 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="Q48" s="4" t="n">
+      <c r="S48" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="R48" s="4" t="n">
+      <c r="T48" s="4" t="n">
         <v>0.127</v>
       </c>
-      <c r="S48" s="4" t="inlineStr"/>
-      <c r="T48" s="4" t="inlineStr">
+      <c r="U48" s="4" t="inlineStr"/>
+      <c r="V48" s="4" t="inlineStr">
         <is>
           <t>Rank #6 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
-      <c r="U48" s="4" t="inlineStr"/>
-      <c r="V48" s="4" t="n">
+      <c r="W48" s="4" t="inlineStr"/>
+      <c r="X48" s="4" t="n">
         <v>50.5</v>
       </c>
-      <c r="W48" s="4" t="inlineStr">
+      <c r="Y48" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X48" s="4" t="n">
+      <c r="Z48" s="4" t="n">
         <v>46.5</v>
       </c>
-      <c r="Y48" s="4" t="inlineStr"/>
-      <c r="Z48" s="4" t="n">
+      <c r="AA48" s="4" t="inlineStr"/>
+      <c r="AB48" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="AA48" s="4" t="n">
+      <c r="AC48" s="4" t="n">
         <v>91</v>
       </c>
-      <c r="AB48" s="4" t="inlineStr">
+      <c r="AD48" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC48" s="4" t="n">
+      <c r="AE48" s="4" t="n">
         <v>225.02</v>
       </c>
-      <c r="AD48" s="4" t="n">
+      <c r="AF48" s="4" t="n">
         <v>225.02</v>
       </c>
-      <c r="AE48" s="4" t="n">
+      <c r="AG48" s="4" t="n">
         <v>220.52</v>
       </c>
-      <c r="AF48" s="4" t="n">
+      <c r="AH48" s="4" t="n">
         <v>229.52</v>
       </c>
-      <c r="AG48" s="4" t="n">
+      <c r="AI48" s="4" t="n">
         <v>213.769</v>
       </c>
-      <c r="AH48" s="4" t="n">
+      <c r="AJ48" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI48" s="4" t="n">
+      <c r="AK48" s="4" t="n">
         <v>243.0216</v>
       </c>
-      <c r="AJ48" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK48" s="4" t="n">
+      <c r="AL48" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM48" s="4" t="n">
         <v>260.0331120000001</v>
       </c>
-      <c r="AL48" s="4" t="n">
+      <c r="AN48" s="4" t="n">
         <v>15.56</v>
       </c>
-      <c r="AM48" s="4" t="inlineStr"/>
-      <c r="AN48" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO48" s="4" t="n">
+      <c r="AO48" s="4" t="inlineStr"/>
+      <c r="AP48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ48" s="4" t="n">
         <v>8.01</v>
       </c>
-      <c r="AP48" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ48" s="4" t="inlineStr">
+      <c r="AR48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS48" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AR48" s="4" t="inlineStr"/>
-      <c r="AS48" s="4" t="inlineStr">
+      <c r="AT48" s="4" t="inlineStr"/>
+      <c r="AU48" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AT48" s="4" t="n">
+      <c r="AV48" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AU48" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV48" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AW48" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX48" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -8030,113 +8314,121 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N49" s="4" t="n">
+      <c r="N49" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" s="4" t="n">
         <v>49.7</v>
       </c>
-      <c r="O49" s="4" t="n">
+      <c r="Q49" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="P49" s="4" t="inlineStr">
+      <c r="R49" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="Q49" s="4" t="n">
+      <c r="S49" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="R49" s="4" t="n">
+      <c r="T49" s="4" t="n">
         <v>0.109</v>
       </c>
-      <c r="S49" s="4" t="inlineStr"/>
-      <c r="T49" s="4" t="inlineStr">
+      <c r="U49" s="4" t="inlineStr"/>
+      <c r="V49" s="4" t="inlineStr">
         <is>
           <t>Rank #7 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
-      <c r="U49" s="4" t="inlineStr"/>
-      <c r="V49" s="4" t="n">
+      <c r="W49" s="4" t="inlineStr"/>
+      <c r="X49" s="4" t="n">
         <v>50.5</v>
       </c>
-      <c r="W49" s="4" t="inlineStr">
+      <c r="Y49" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X49" s="4" t="n">
+      <c r="Z49" s="4" t="n">
         <v>45.8</v>
       </c>
-      <c r="Y49" s="4" t="inlineStr"/>
-      <c r="Z49" s="4" t="n">
+      <c r="AA49" s="4" t="inlineStr"/>
+      <c r="AB49" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="AA49" s="4" t="n">
+      <c r="AC49" s="4" t="n">
         <v>91</v>
       </c>
-      <c r="AB49" s="4" t="inlineStr">
+      <c r="AD49" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC49" s="4" t="n">
+      <c r="AE49" s="4" t="n">
         <v>333.74</v>
       </c>
-      <c r="AD49" s="4" t="n">
+      <c r="AF49" s="4" t="n">
         <v>333.74</v>
       </c>
-      <c r="AE49" s="4" t="n">
+      <c r="AG49" s="4" t="n">
         <v>327.07</v>
       </c>
-      <c r="AF49" s="4" t="n">
+      <c r="AH49" s="4" t="n">
         <v>340.41</v>
       </c>
-      <c r="AG49" s="4" t="n">
+      <c r="AI49" s="4" t="n">
         <v>317.053</v>
       </c>
-      <c r="AH49" s="4" t="n">
+      <c r="AJ49" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI49" s="4" t="n">
+      <c r="AK49" s="4" t="n">
         <v>360.4392</v>
       </c>
-      <c r="AJ49" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK49" s="4" t="n">
+      <c r="AL49" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM49" s="4" t="n">
         <v>385.669944</v>
       </c>
-      <c r="AL49" s="4" t="n">
+      <c r="AN49" s="4" t="n">
         <v>15.56</v>
       </c>
-      <c r="AM49" s="4" t="inlineStr"/>
-      <c r="AN49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO49" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AO49" s="4" t="inlineStr"/>
       <c r="AP49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR49" s="4" t="n">
         <v>-7.44</v>
       </c>
-      <c r="AQ49" s="4" t="inlineStr">
+      <c r="AS49" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AR49" s="4" t="inlineStr"/>
-      <c r="AS49" s="4" t="inlineStr">
+      <c r="AT49" s="4" t="inlineStr"/>
+      <c r="AU49" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AT49" s="4" t="n">
+      <c r="AV49" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AU49" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV49" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AW49" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX49" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -8186,111 +8478,119 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N50" s="4" t="n">
+      <c r="N50" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="4" t="n">
         <v>48.9</v>
       </c>
-      <c r="O50" s="4" t="n">
+      <c r="Q50" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="P50" s="4" t="inlineStr">
+      <c r="R50" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 18 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="Q50" s="4" t="n">
+      <c r="S50" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="R50" s="4" t="inlineStr"/>
-      <c r="S50" s="4" t="inlineStr"/>
-      <c r="T50" s="4" t="inlineStr">
+      <c r="T50" s="4" t="inlineStr"/>
+      <c r="U50" s="4" t="inlineStr"/>
+      <c r="V50" s="4" t="inlineStr">
         <is>
           <t>Rank #8 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
-      <c r="U50" s="4" t="inlineStr"/>
-      <c r="V50" s="4" t="n">
+      <c r="W50" s="4" t="inlineStr"/>
+      <c r="X50" s="4" t="n">
         <v>49.7</v>
       </c>
-      <c r="W50" s="4" t="inlineStr">
+      <c r="Y50" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X50" s="4" t="n">
+      <c r="Z50" s="4" t="n">
         <v>37.6</v>
       </c>
-      <c r="Y50" s="4" t="inlineStr"/>
-      <c r="Z50" s="4" t="n">
+      <c r="AA50" s="4" t="inlineStr"/>
+      <c r="AB50" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="AA50" s="4" t="n">
+      <c r="AC50" s="4" t="n">
         <v>91</v>
       </c>
-      <c r="AB50" s="4" t="inlineStr">
+      <c r="AD50" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC50" s="4" t="n">
+      <c r="AE50" s="4" t="n">
         <v>341.1</v>
       </c>
-      <c r="AD50" s="4" t="n">
+      <c r="AF50" s="4" t="n">
         <v>341.1</v>
       </c>
-      <c r="AE50" s="4" t="n">
+      <c r="AG50" s="4" t="n">
         <v>334.28</v>
       </c>
-      <c r="AF50" s="4" t="n">
+      <c r="AH50" s="4" t="n">
         <v>347.92</v>
       </c>
-      <c r="AG50" s="4" t="n">
+      <c r="AI50" s="4" t="n">
         <v>324.045</v>
       </c>
-      <c r="AH50" s="4" t="n">
+      <c r="AJ50" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI50" s="4" t="n">
+      <c r="AK50" s="4" t="n">
         <v>368.388</v>
       </c>
-      <c r="AJ50" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK50" s="4" t="n">
+      <c r="AL50" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM50" s="4" t="n">
         <v>394.1751600000001</v>
       </c>
-      <c r="AL50" s="4" t="n">
+      <c r="AN50" s="4" t="n">
         <v>15.56</v>
       </c>
-      <c r="AM50" s="4" t="inlineStr"/>
-      <c r="AN50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO50" s="4" t="n">
+      <c r="AO50" s="4" t="inlineStr"/>
+      <c r="AP50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ50" s="4" t="n">
         <v>3.13</v>
       </c>
-      <c r="AP50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ50" s="4" t="inlineStr">
+      <c r="AR50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS50" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AR50" s="4" t="inlineStr"/>
-      <c r="AS50" s="4" t="inlineStr">
+      <c r="AT50" s="4" t="inlineStr"/>
+      <c r="AU50" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AT50" s="4" t="n">
+      <c r="AV50" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AU50" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV50" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AW50" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX50" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -8337,114 +8637,122 @@
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="N51" s="4" t="n">
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N51" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="4" t="n">
         <v>50.2</v>
       </c>
-      <c r="O51" s="4" t="n">
+      <c r="Q51" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="P51" s="4" t="inlineStr">
+      <c r="R51" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 9 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="Q51" s="4" t="n">
+      <c r="S51" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="R51" s="4" t="inlineStr"/>
-      <c r="S51" s="4" t="inlineStr"/>
-      <c r="T51" s="4" t="inlineStr">
-        <is>
-          <t>Rank #9 · Conf 51% · momentum → · band WATCH · 91d left · → HOLD</t>
-        </is>
-      </c>
+      <c r="T51" s="4" t="inlineStr"/>
       <c r="U51" s="4" t="inlineStr"/>
-      <c r="V51" s="4" t="n">
+      <c r="V51" s="4" t="inlineStr">
+        <is>
+          <t>Rank #9 · Conf 51% · momentum → · band WATCH→HOLD · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="W51" s="4" t="inlineStr"/>
+      <c r="X51" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="W51" s="4" t="inlineStr">
+      <c r="Y51" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X51" s="4" t="n">
+      <c r="Z51" s="4" t="n">
         <v>36.5</v>
       </c>
-      <c r="Y51" s="4" t="inlineStr"/>
-      <c r="Z51" s="4" t="n">
+      <c r="AA51" s="4" t="inlineStr"/>
+      <c r="AB51" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="AA51" s="4" t="n">
+      <c r="AC51" s="4" t="n">
         <v>91</v>
       </c>
-      <c r="AB51" s="4" t="inlineStr">
+      <c r="AD51" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC51" s="4" t="n">
+      <c r="AE51" s="4" t="n">
         <v>1065.22</v>
       </c>
-      <c r="AD51" s="4" t="n">
+      <c r="AF51" s="4" t="n">
         <v>1065.22</v>
       </c>
-      <c r="AE51" s="4" t="n">
+      <c r="AG51" s="4" t="n">
         <v>1043.92</v>
       </c>
-      <c r="AF51" s="4" t="n">
+      <c r="AH51" s="4" t="n">
         <v>1086.52</v>
       </c>
-      <c r="AG51" s="4" t="n">
+      <c r="AI51" s="4" t="n">
         <v>1011.959</v>
       </c>
-      <c r="AH51" s="4" t="n">
+      <c r="AJ51" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI51" s="4" t="n">
+      <c r="AK51" s="4" t="n">
         <v>1150.4376</v>
       </c>
-      <c r="AJ51" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK51" s="4" t="n">
+      <c r="AL51" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM51" s="4" t="n">
         <v>1230.968232</v>
       </c>
-      <c r="AL51" s="4" t="n">
+      <c r="AN51" s="4" t="n">
         <v>15.56</v>
       </c>
-      <c r="AM51" s="4" t="inlineStr"/>
-      <c r="AN51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO51" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AO51" s="4" t="inlineStr"/>
       <c r="AP51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR51" s="4" t="n">
         <v>-4.4</v>
       </c>
-      <c r="AQ51" s="4" t="inlineStr">
+      <c r="AS51" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AR51" s="4" t="inlineStr"/>
-      <c r="AS51" s="4" t="inlineStr">
+      <c r="AT51" s="4" t="inlineStr"/>
+      <c r="AU51" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AT51" s="4" t="n">
+      <c r="AV51" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AU51" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV51" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AW51" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX51" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
@@ -8494,116 +8802,124 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N52" s="4" t="n">
+      <c r="N52" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="4" t="n">
         <v>52.9</v>
       </c>
-      <c r="O52" s="4" t="n">
+      <c r="Q52" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="P52" s="4" t="inlineStr">
+      <c r="R52" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 15 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="Q52" s="4" t="n">
+      <c r="S52" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="R52" s="4" t="inlineStr"/>
-      <c r="S52" s="4" t="inlineStr"/>
-      <c r="T52" s="4" t="inlineStr">
+      <c r="T52" s="4" t="inlineStr"/>
+      <c r="U52" s="4" t="inlineStr"/>
+      <c r="V52" s="4" t="inlineStr">
         <is>
           <t>Rank #10 · Conf 54% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
-      <c r="U52" s="4" t="inlineStr"/>
-      <c r="V52" s="4" t="n">
+      <c r="W52" s="4" t="inlineStr"/>
+      <c r="X52" s="4" t="n">
         <v>53.6</v>
       </c>
-      <c r="W52" s="4" t="inlineStr">
+      <c r="Y52" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X52" s="4" t="n">
+      <c r="Z52" s="4" t="n">
         <v>32.3</v>
       </c>
-      <c r="Y52" s="4" t="inlineStr"/>
-      <c r="Z52" s="4" t="n">
+      <c r="AA52" s="4" t="inlineStr"/>
+      <c r="AB52" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="AA52" s="4" t="n">
+      <c r="AC52" s="4" t="n">
         <v>91</v>
       </c>
-      <c r="AB52" s="4" t="inlineStr">
+      <c r="AD52" s="4" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="AC52" s="4" t="n">
+      <c r="AE52" s="4" t="n">
         <v>159.84</v>
       </c>
-      <c r="AD52" s="4" t="n">
+      <c r="AF52" s="4" t="n">
         <v>159.84</v>
       </c>
-      <c r="AE52" s="4" t="n">
+      <c r="AG52" s="4" t="n">
         <v>156.64</v>
       </c>
-      <c r="AF52" s="4" t="n">
+      <c r="AH52" s="4" t="n">
         <v>163.04</v>
       </c>
-      <c r="AG52" s="4" t="n">
+      <c r="AI52" s="4" t="n">
         <v>151.848</v>
       </c>
-      <c r="AH52" s="4" t="n">
+      <c r="AJ52" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AI52" s="4" t="n">
+      <c r="AK52" s="4" t="n">
         <v>172.6272</v>
       </c>
-      <c r="AJ52" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK52" s="4" t="n">
+      <c r="AL52" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM52" s="4" t="n">
         <v>184.711104</v>
       </c>
-      <c r="AL52" s="4" t="n">
+      <c r="AN52" s="4" t="n">
         <v>15.56</v>
       </c>
-      <c r="AM52" s="4" t="inlineStr"/>
-      <c r="AN52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO52" s="4" t="n">
+      <c r="AO52" s="4" t="inlineStr"/>
+      <c r="AP52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ52" s="4" t="n">
         <v>10.29</v>
       </c>
-      <c r="AP52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ52" s="4" t="inlineStr">
+      <c r="AR52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS52" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AR52" s="4" t="inlineStr"/>
-      <c r="AS52" s="4" t="inlineStr">
+      <c r="AT52" s="4" t="inlineStr"/>
+      <c r="AU52" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AT52" s="4" t="n">
+      <c r="AV52" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AU52" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV52" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:20</t>
+      <c r="AW52" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX52" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:36</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AV52"/>
+  <autoFilter ref="A1:AX52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/telegram/aegis_daily_2026-08-06.xlsx
+++ b/reports/telegram/aegis_daily_2026-08-06.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AX$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AW$52</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX52"/>
+  <dimension ref="A1:AW52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -485,45 +485,44 @@
     <col width="6" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="50" customWidth="1" min="18" max="18"/>
+    <col width="50" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="60" customWidth="1" min="22" max="22"/>
-    <col width="34" customWidth="1" min="23" max="23"/>
-    <col width="13" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
-    <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="6" customWidth="1" min="27" max="27"/>
-    <col width="12" customWidth="1" min="28" max="28"/>
-    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="60" customWidth="1" min="21" max="21"/>
+    <col width="34" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="11" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="6" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
+    <col width="14" customWidth="1" min="29" max="29"/>
     <col width="14" customWidth="1" min="30" max="30"/>
-    <col width="14" customWidth="1" min="31" max="31"/>
-    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="13" customWidth="1" min="32" max="32"/>
     <col width="13" customWidth="1" min="33" max="33"/>
-    <col width="13" customWidth="1" min="34" max="34"/>
-    <col width="11" customWidth="1" min="35" max="35"/>
-    <col width="9" customWidth="1" min="36" max="36"/>
-    <col width="11" customWidth="1" min="37" max="37"/>
-    <col width="8" customWidth="1" min="38" max="38"/>
-    <col width="11" customWidth="1" min="39" max="39"/>
-    <col width="8" customWidth="1" min="40" max="40"/>
-    <col width="13" customWidth="1" min="41" max="41"/>
-    <col width="15" customWidth="1" min="42" max="42"/>
-    <col width="12" customWidth="1" min="43" max="43"/>
-    <col width="11" customWidth="1" min="44" max="44"/>
-    <col width="16" customWidth="1" min="45" max="45"/>
-    <col width="32" customWidth="1" min="46" max="46"/>
-    <col width="20" customWidth="1" min="47" max="47"/>
-    <col width="18" customWidth="1" min="48" max="48"/>
-    <col width="17" customWidth="1" min="49" max="49"/>
-    <col width="20" customWidth="1" min="50" max="50"/>
+    <col width="11" customWidth="1" min="34" max="34"/>
+    <col width="9" customWidth="1" min="35" max="35"/>
+    <col width="11" customWidth="1" min="36" max="36"/>
+    <col width="8" customWidth="1" min="37" max="37"/>
+    <col width="11" customWidth="1" min="38" max="38"/>
+    <col width="8" customWidth="1" min="39" max="39"/>
+    <col width="13" customWidth="1" min="40" max="40"/>
+    <col width="15" customWidth="1" min="41" max="41"/>
+    <col width="12" customWidth="1" min="42" max="42"/>
+    <col width="11" customWidth="1" min="43" max="43"/>
+    <col width="16" customWidth="1" min="44" max="44"/>
+    <col width="32" customWidth="1" min="45" max="45"/>
+    <col width="20" customWidth="1" min="46" max="46"/>
+    <col width="18" customWidth="1" min="47" max="47"/>
+    <col width="17" customWidth="1" min="48" max="48"/>
+    <col width="20" customWidth="1" min="49" max="49"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -584,12 +583,12 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Band</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Band</t>
+          <t>New Opp</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -599,180 +598,175 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Sector Exposure %</t>
+          <t>Adj Conf</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Adj Conf</t>
+          <t>Ctx Drag</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Ctx Drag</t>
+          <t>Ctx Reason</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Ctx Reason</t>
+          <t>Insider 90d</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Insider 90d</t>
+          <t>Corr to Uni</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Corr to Uni</t>
+          <t>Turnover σ</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Turnover σ</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Confidence %</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Confidence %</t>
+          <t>Conf Type</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>Conf Type</t>
+          <t>Model Score</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Model Score</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Horizon (d)</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Horizon (d)</t>
+          <t>Days Left</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Days Left</t>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Recommended</t>
+          <t>Current Price</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Current Price</t>
+          <t>Entry Price</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Entry Price</t>
+          <t>Buy Zone Low</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Buy Zone Low</t>
+          <t>Buy Zone High</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>Buy Zone High</t>
+          <t>Stop Loss</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Stop Loss</t>
+          <t>Risk %</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>Risk %</t>
+          <t>Target 1</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>Target 1</t>
+          <t>T1 %</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>T1 %</t>
+          <t>Target 2</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>Target 2</t>
+          <t>T2 %</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>T2 %</t>
+          <t>Today Move %</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>Today Move %</t>
+          <t>Current Perf %</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>Current Perf %</t>
+          <t>Max Gain %</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>Max Gain %</t>
+          <t>Max DD %</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>Max DD %</t>
+          <t>Lifecycle State</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>Lifecycle State</t>
+          <t>Top Drivers</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>Top Drivers</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Portfolio Weight %</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>Portfolio Weight %</t>
+          <t>Expected Alpha %</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>Expected Alpha %</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Last Updated (UTC)</t>
         </is>
@@ -820,12 +814,14 @@
       <c r="K2" s="4" t="n">
         <v>-8</v>
       </c>
-      <c r="L2" s="4" t="n">
-        <v>73.7</v>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
       </c>
       <c r="M2" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>🟢 NEW</t>
         </is>
       </c>
       <c r="N2" s="4" t="inlineStr">
@@ -833,108 +829,107 @@
           <t>🟢</t>
         </is>
       </c>
-      <c r="O2" s="4" t="inlineStr"/>
+      <c r="O2" s="4" t="n">
+        <v>36.6</v>
+      </c>
       <c r="P2" s="4" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="Q2" s="4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="R2" s="4" t="inlineStr">
+      <c r="Q2" s="4" t="inlineStr">
         <is>
           <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
+      <c r="R2" s="4" t="inlineStr"/>
       <c r="S2" s="4" t="inlineStr"/>
       <c r="T2" s="4" t="inlineStr"/>
-      <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="inlineStr">
-        <is>
-          <t>Rank ↑ 9→1 · Conf 39% · band WATCH→HOLD · 10d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="W2" s="4" t="inlineStr"/>
-      <c r="X2" s="4" t="n">
+      <c r="U2" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank ↑ 9→1 · Conf 39% · band HOLD · 10d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="V2" s="4" t="inlineStr"/>
+      <c r="W2" s="4" t="n">
         <v>39.3</v>
       </c>
-      <c r="Y2" s="4" t="inlineStr">
+      <c r="X2" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
+      <c r="Y2" s="4" t="n">
+        <v>26.3</v>
+      </c>
       <c r="Z2" s="4" t="n">
-        <v>26.3</v>
+        <v>8</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="AB2" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC2" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AD2" s="4" t="inlineStr">
+      <c r="AC2" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
+      </c>
+      <c r="AD2" s="4" t="n">
+        <v>2452.2</v>
       </c>
       <c r="AE2" s="4" t="n">
         <v>2452.2</v>
       </c>
       <c r="AF2" s="4" t="n">
-        <v>2452.2</v>
+        <v>2427.68</v>
       </c>
       <c r="AG2" s="4" t="n">
-        <v>2427.68</v>
+        <v>2476.72</v>
       </c>
       <c r="AH2" s="4" t="n">
-        <v>2476.72</v>
+        <v>2329.59</v>
       </c>
       <c r="AI2" s="4" t="n">
-        <v>2329.59</v>
+        <v>-5</v>
       </c>
       <c r="AJ2" s="4" t="n">
-        <v>-5</v>
+        <v>2648.38</v>
       </c>
       <c r="AK2" s="4" t="n">
-        <v>2648.38</v>
+        <v>8</v>
       </c>
       <c r="AL2" s="4" t="n">
-        <v>8</v>
+        <v>2820.03</v>
       </c>
       <c r="AM2" s="4" t="n">
-        <v>2820.03</v>
+        <v>15</v>
       </c>
       <c r="AN2" s="4" t="n">
-        <v>15</v>
+        <v>0.84</v>
       </c>
       <c r="AO2" s="4" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="AP2" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AP2" s="4" t="inlineStr"/>
       <c r="AQ2" s="4" t="inlineStr"/>
-      <c r="AR2" s="4" t="inlineStr"/>
+      <c r="AR2" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
       <c r="AS2" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT2" s="4" t="inlineStr">
-        <is>
           <t>Quality · Mean Reversion · Ai Hybrid</t>
         </is>
       </c>
+      <c r="AT2" s="4" t="inlineStr"/>
       <c r="AU2" s="4" t="inlineStr"/>
-      <c r="AV2" s="4" t="inlineStr"/>
-      <c r="AW2" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX2" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+      <c r="AV2" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW2" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -980,12 +975,14 @@
       <c r="K3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L3" s="4" t="n">
-        <v>75.7</v>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>🟢 NEW</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
@@ -993,108 +990,107 @@
           <t>🟢</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr"/>
+      <c r="O3" s="4" t="n">
+        <v>37.8</v>
+      </c>
       <c r="P3" s="4" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="Q3" s="4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
+      <c r="R3" s="4" t="inlineStr"/>
       <c r="S3" s="4" t="inlineStr"/>
       <c r="T3" s="4" t="inlineStr"/>
-      <c r="U3" s="4" t="inlineStr"/>
-      <c r="V3" s="4" t="inlineStr">
-        <is>
-          <t>Rank → 2→2 · Conf 41% · band HOLD · 10d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="W3" s="4" t="inlineStr"/>
-      <c r="X3" s="4" t="n">
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 2→2 · Conf 41% · band HOLD · 10d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr"/>
+      <c r="W3" s="4" t="n">
         <v>40.6</v>
       </c>
-      <c r="Y3" s="4" t="inlineStr">
+      <c r="X3" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
+      <c r="Y3" s="4" t="n">
+        <v>26.2</v>
+      </c>
       <c r="Z3" s="4" t="n">
-        <v>26.2</v>
+        <v>8</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC3" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AD3" s="4" t="inlineStr">
+      <c r="AC3" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
+      </c>
+      <c r="AD3" s="4" t="n">
+        <v>5196.6</v>
       </c>
       <c r="AE3" s="4" t="n">
         <v>5196.6</v>
       </c>
       <c r="AF3" s="4" t="n">
-        <v>5196.6</v>
+        <v>5144.63</v>
       </c>
       <c r="AG3" s="4" t="n">
-        <v>5144.63</v>
+        <v>5248.57</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>5248.57</v>
+        <v>4936.77</v>
       </c>
       <c r="AI3" s="4" t="n">
-        <v>4936.77</v>
+        <v>-5</v>
       </c>
       <c r="AJ3" s="4" t="n">
-        <v>-5</v>
+        <v>5612.33</v>
       </c>
       <c r="AK3" s="4" t="n">
-        <v>5612.33</v>
+        <v>8</v>
       </c>
       <c r="AL3" s="4" t="n">
-        <v>8</v>
+        <v>5976.09</v>
       </c>
       <c r="AM3" s="4" t="n">
-        <v>5976.09</v>
+        <v>15</v>
       </c>
       <c r="AN3" s="4" t="n">
-        <v>15</v>
+        <v>1.42</v>
       </c>
       <c r="AO3" s="4" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AP3" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AP3" s="4" t="inlineStr"/>
       <c r="AQ3" s="4" t="inlineStr"/>
-      <c r="AR3" s="4" t="inlineStr"/>
+      <c r="AR3" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
       <c r="AS3" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT3" s="4" t="inlineStr">
-        <is>
           <t>Quality · Growth · Ai Hybrid</t>
         </is>
       </c>
+      <c r="AT3" s="4" t="inlineStr"/>
       <c r="AU3" s="4" t="inlineStr"/>
-      <c r="AV3" s="4" t="inlineStr"/>
-      <c r="AW3" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX3" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+      <c r="AV3" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW3" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1132,14 @@
       <c r="K4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" s="4" t="n">
-        <v>74.2</v>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>🟢 NEW</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
@@ -1149,108 +1147,107 @@
           <t>🟢</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr"/>
+      <c r="O4" s="4" t="n">
+        <v>36.6</v>
+      </c>
       <c r="P4" s="4" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="Q4" s="4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="R4" s="4" t="inlineStr">
+      <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
+      <c r="R4" s="4" t="inlineStr"/>
       <c r="S4" s="4" t="inlineStr"/>
       <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
-      <c r="V4" s="4" t="inlineStr">
-        <is>
-          <t>Rank → 3→3 · Conf 39% · band WATCH→HOLD · 54d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="W4" s="4" t="inlineStr"/>
-      <c r="X4" s="4" t="n">
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 3→3 · Conf 39% · band HOLD · 54d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr"/>
+      <c r="W4" s="4" t="n">
         <v>39.3</v>
       </c>
-      <c r="Y4" s="4" t="inlineStr">
+      <c r="X4" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
+      <c r="Y4" s="4" t="n">
+        <v>24.3</v>
+      </c>
       <c r="Z4" s="4" t="n">
-        <v>24.3</v>
+        <v>7</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="AB4" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AC4" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="AD4" s="4" t="inlineStr">
+      <c r="AC4" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
+      </c>
+      <c r="AD4" s="4" t="n">
+        <v>133.14</v>
       </c>
       <c r="AE4" s="4" t="n">
         <v>133.14</v>
       </c>
       <c r="AF4" s="4" t="n">
-        <v>133.14</v>
+        <v>131.81</v>
       </c>
       <c r="AG4" s="4" t="n">
-        <v>131.81</v>
+        <v>134.47</v>
       </c>
       <c r="AH4" s="4" t="n">
-        <v>134.47</v>
+        <v>126.48</v>
       </c>
       <c r="AI4" s="4" t="n">
-        <v>126.48</v>
+        <v>-5</v>
       </c>
       <c r="AJ4" s="4" t="n">
-        <v>-5</v>
+        <v>143.79</v>
       </c>
       <c r="AK4" s="4" t="n">
-        <v>143.79</v>
+        <v>8</v>
       </c>
       <c r="AL4" s="4" t="n">
-        <v>8</v>
+        <v>153.11</v>
       </c>
       <c r="AM4" s="4" t="n">
-        <v>153.11</v>
+        <v>15</v>
       </c>
       <c r="AN4" s="4" t="n">
-        <v>15</v>
+        <v>1.33</v>
       </c>
       <c r="AO4" s="4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AP4" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AP4" s="4" t="inlineStr"/>
       <c r="AQ4" s="4" t="inlineStr"/>
-      <c r="AR4" s="4" t="inlineStr"/>
+      <c r="AR4" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
       <c r="AS4" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT4" s="4" t="inlineStr">
-        <is>
           <t>Quality · Momentum · Ai Hybrid</t>
         </is>
       </c>
+      <c r="AT4" s="4" t="inlineStr"/>
       <c r="AU4" s="4" t="inlineStr"/>
-      <c r="AV4" s="4" t="inlineStr"/>
-      <c r="AW4" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX4" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+      <c r="AV4" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW4" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1289,14 @@
       <c r="K5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="4" t="n">
-        <v>81.7</v>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>STRONG</t>
+        </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>🟢 NEW</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -1305,108 +1304,107 @@
           <t>🟢</t>
         </is>
       </c>
-      <c r="O5" s="4" t="inlineStr"/>
+      <c r="O5" s="4" t="n">
+        <v>38</v>
+      </c>
       <c r="P5" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="Q5" s="4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="R5" s="4" t="inlineStr">
+      <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
+      <c r="R5" s="4" t="inlineStr"/>
       <c r="S5" s="4" t="inlineStr"/>
       <c r="T5" s="4" t="inlineStr"/>
-      <c r="U5" s="4" t="inlineStr"/>
-      <c r="V5" s="4" t="inlineStr">
-        <is>
-          <t>Rank → 4→4 · Conf 41% · band HOLD · 54d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="W5" s="4" t="inlineStr"/>
-      <c r="X5" s="4" t="n">
+      <c r="U5" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 4→4 · Conf 41% · band STRONG · 54d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="V5" s="4" t="inlineStr"/>
+      <c r="W5" s="4" t="n">
         <v>40.7</v>
       </c>
-      <c r="Y5" s="4" t="inlineStr">
+      <c r="X5" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
+      <c r="Y5" s="4" t="n">
+        <v>23.8</v>
+      </c>
       <c r="Z5" s="4" t="n">
-        <v>23.8</v>
+        <v>7</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AC5" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="AD5" s="4" t="inlineStr">
+      <c r="AC5" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
+      </c>
+      <c r="AD5" s="4" t="n">
+        <v>5524</v>
       </c>
       <c r="AE5" s="4" t="n">
         <v>5524</v>
       </c>
       <c r="AF5" s="4" t="n">
-        <v>5524</v>
+        <v>5468.76</v>
       </c>
       <c r="AG5" s="4" t="n">
-        <v>5468.76</v>
+        <v>5579.24</v>
       </c>
       <c r="AH5" s="4" t="n">
-        <v>5579.24</v>
+        <v>5247.8</v>
       </c>
       <c r="AI5" s="4" t="n">
-        <v>5247.8</v>
+        <v>-5</v>
       </c>
       <c r="AJ5" s="4" t="n">
-        <v>-5</v>
+        <v>5965.92</v>
       </c>
       <c r="AK5" s="4" t="n">
-        <v>5965.92</v>
+        <v>8</v>
       </c>
       <c r="AL5" s="4" t="n">
-        <v>8</v>
+        <v>6352.6</v>
       </c>
       <c r="AM5" s="4" t="n">
-        <v>6352.6</v>
+        <v>15</v>
       </c>
       <c r="AN5" s="4" t="n">
-        <v>15</v>
+        <v>0.26</v>
       </c>
       <c r="AO5" s="4" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AP5" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AP5" s="4" t="inlineStr"/>
       <c r="AQ5" s="4" t="inlineStr"/>
-      <c r="AR5" s="4" t="inlineStr"/>
+      <c r="AR5" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
       <c r="AS5" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT5" s="4" t="inlineStr">
-        <is>
           <t>Trend · Growth · Value</t>
         </is>
       </c>
+      <c r="AT5" s="4" t="inlineStr"/>
       <c r="AU5" s="4" t="inlineStr"/>
-      <c r="AV5" s="4" t="inlineStr"/>
-      <c r="AW5" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX5" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+      <c r="AV5" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW5" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -1452,12 +1450,14 @@
       <c r="K6" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="L6" s="4" t="n">
-        <v>78.90000000000001</v>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>🟢 NEW</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -1465,108 +1465,107 @@
           <t>🟢</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr"/>
+      <c r="O6" s="4" t="n">
+        <v>40.4</v>
+      </c>
       <c r="P6" s="4" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="Q6" s="4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="R6" s="4" t="inlineStr">
+      <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
+      <c r="R6" s="4" t="inlineStr"/>
       <c r="S6" s="4" t="inlineStr"/>
       <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
-      <c r="V6" s="4" t="inlineStr">
-        <is>
-          <t>Rank ↑ 8→5 · Conf 43% · band HOLD · 10d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="W6" s="4" t="inlineStr"/>
-      <c r="X6" s="4" t="n">
+      <c r="U6" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank ↑ 8→5 · Conf 43% · band HOLD · 10d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="V6" s="4" t="inlineStr"/>
+      <c r="W6" s="4" t="n">
         <v>43.1</v>
       </c>
-      <c r="Y6" s="4" t="inlineStr">
+      <c r="X6" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
+      <c r="Y6" s="4" t="n">
+        <v>23.8</v>
+      </c>
       <c r="Z6" s="4" t="n">
-        <v>23.8</v>
+        <v>8</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="AB6" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC6" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AD6" s="4" t="inlineStr">
+      <c r="AC6" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
+      </c>
+      <c r="AD6" s="4" t="n">
+        <v>1346.6</v>
       </c>
       <c r="AE6" s="4" t="n">
         <v>1346.6</v>
       </c>
       <c r="AF6" s="4" t="n">
-        <v>1346.6</v>
+        <v>1333.13</v>
       </c>
       <c r="AG6" s="4" t="n">
-        <v>1333.13</v>
+        <v>1360.07</v>
       </c>
       <c r="AH6" s="4" t="n">
-        <v>1360.07</v>
+        <v>1279.27</v>
       </c>
       <c r="AI6" s="4" t="n">
-        <v>1279.27</v>
+        <v>-5</v>
       </c>
       <c r="AJ6" s="4" t="n">
-        <v>-5</v>
+        <v>1454.33</v>
       </c>
       <c r="AK6" s="4" t="n">
-        <v>1454.33</v>
+        <v>8</v>
       </c>
       <c r="AL6" s="4" t="n">
-        <v>8</v>
+        <v>1548.59</v>
       </c>
       <c r="AM6" s="4" t="n">
-        <v>1548.59</v>
+        <v>15</v>
       </c>
       <c r="AN6" s="4" t="n">
-        <v>15</v>
+        <v>0.46</v>
       </c>
       <c r="AO6" s="4" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="AP6" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AP6" s="4" t="inlineStr"/>
       <c r="AQ6" s="4" t="inlineStr"/>
-      <c r="AR6" s="4" t="inlineStr"/>
+      <c r="AR6" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
       <c r="AS6" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT6" s="4" t="inlineStr">
-        <is>
           <t>Quality · Mean Reversion · Momentum</t>
         </is>
       </c>
+      <c r="AT6" s="4" t="inlineStr"/>
       <c r="AU6" s="4" t="inlineStr"/>
-      <c r="AV6" s="4" t="inlineStr"/>
-      <c r="AW6" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX6" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+      <c r="AV6" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW6" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -1608,12 +1607,14 @@
       <c r="K7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="4" t="n">
-        <v>78.8</v>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>🟢 NEW</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -1621,108 +1622,107 @@
           <t>🟢</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr"/>
+      <c r="O7" s="4" t="n">
+        <v>43.6</v>
+      </c>
       <c r="P7" s="4" t="n">
-        <v>43.6</v>
-      </c>
-      <c r="Q7" s="4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="R7" s="4" t="inlineStr">
+      <c r="Q7" s="4" t="inlineStr">
         <is>
           <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
+      <c r="R7" s="4" t="inlineStr"/>
       <c r="S7" s="4" t="inlineStr"/>
       <c r="T7" s="4" t="inlineStr"/>
-      <c r="U7" s="4" t="inlineStr"/>
-      <c r="V7" s="4" t="inlineStr">
-        <is>
-          <t>Rank → 6→6 · Conf 46% · band HOLD · 11d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="W7" s="4" t="inlineStr"/>
-      <c r="X7" s="4" t="n">
+      <c r="U7" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 6→6 · Conf 46% · band HOLD · 11d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr"/>
+      <c r="W7" s="4" t="n">
         <v>46.4</v>
       </c>
-      <c r="Y7" s="4" t="inlineStr">
+      <c r="X7" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
+      <c r="Y7" s="4" t="n">
+        <v>23.8</v>
+      </c>
       <c r="Z7" s="4" t="n">
-        <v>23.8</v>
+        <v>7</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AB7" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC7" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="AD7" s="4" t="inlineStr">
+      <c r="AC7" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
+      </c>
+      <c r="AD7" s="4" t="n">
+        <v>11602</v>
       </c>
       <c r="AE7" s="4" t="n">
         <v>11602</v>
       </c>
       <c r="AF7" s="4" t="n">
-        <v>11602</v>
+        <v>11485.98</v>
       </c>
       <c r="AG7" s="4" t="n">
-        <v>11485.98</v>
+        <v>11718.02</v>
       </c>
       <c r="AH7" s="4" t="n">
-        <v>11718.02</v>
+        <v>11021.9</v>
       </c>
       <c r="AI7" s="4" t="n">
-        <v>11021.9</v>
+        <v>-5</v>
       </c>
       <c r="AJ7" s="4" t="n">
-        <v>-5</v>
+        <v>12530.16</v>
       </c>
       <c r="AK7" s="4" t="n">
-        <v>12530.16</v>
+        <v>8</v>
       </c>
       <c r="AL7" s="4" t="n">
-        <v>8</v>
+        <v>13342.3</v>
       </c>
       <c r="AM7" s="4" t="n">
-        <v>13342.3</v>
+        <v>15</v>
       </c>
       <c r="AN7" s="4" t="n">
-        <v>15</v>
+        <v>0.99</v>
       </c>
       <c r="AO7" s="4" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="AP7" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AP7" s="4" t="inlineStr"/>
       <c r="AQ7" s="4" t="inlineStr"/>
-      <c r="AR7" s="4" t="inlineStr"/>
+      <c r="AR7" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
       <c r="AS7" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT7" s="4" t="inlineStr">
-        <is>
           <t>Quality · Growth · Momentum</t>
         </is>
       </c>
+      <c r="AT7" s="4" t="inlineStr"/>
       <c r="AU7" s="4" t="inlineStr"/>
-      <c r="AV7" s="4" t="inlineStr"/>
-      <c r="AW7" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX7" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+      <c r="AV7" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW7" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -1764,12 +1764,14 @@
       <c r="K8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="4" t="n">
-        <v>76.8</v>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>🟢 NEW</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -1777,108 +1779,107 @@
           <t>🟢</t>
         </is>
       </c>
-      <c r="O8" s="4" t="inlineStr"/>
+      <c r="O8" s="4" t="n">
+        <v>38</v>
+      </c>
       <c r="P8" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="Q8" s="4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="R8" s="4" t="inlineStr">
+      <c r="Q8" s="4" t="inlineStr">
         <is>
           <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
+      <c r="R8" s="4" t="inlineStr"/>
       <c r="S8" s="4" t="inlineStr"/>
       <c r="T8" s="4" t="inlineStr"/>
-      <c r="U8" s="4" t="inlineStr"/>
-      <c r="V8" s="4" t="inlineStr">
-        <is>
-          <t>Rank → 7→7 · Conf 41% · band HOLD · 54d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="W8" s="4" t="inlineStr"/>
-      <c r="X8" s="4" t="n">
+      <c r="U8" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 7→7 · Conf 41% · band HOLD · 54d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr"/>
+      <c r="W8" s="4" t="n">
         <v>40.7</v>
       </c>
-      <c r="Y8" s="4" t="inlineStr">
+      <c r="X8" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
+      <c r="Y8" s="4" t="n">
+        <v>23</v>
+      </c>
       <c r="Z8" s="4" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="AB8" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AC8" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="AD8" s="4" t="inlineStr">
+      <c r="AC8" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
+      </c>
+      <c r="AD8" s="4" t="n">
+        <v>1158</v>
       </c>
       <c r="AE8" s="4" t="n">
         <v>1158</v>
       </c>
       <c r="AF8" s="4" t="n">
-        <v>1158</v>
+        <v>1146.42</v>
       </c>
       <c r="AG8" s="4" t="n">
-        <v>1146.42</v>
+        <v>1169.58</v>
       </c>
       <c r="AH8" s="4" t="n">
-        <v>1169.58</v>
+        <v>1100.1</v>
       </c>
       <c r="AI8" s="4" t="n">
-        <v>1100.1</v>
+        <v>-5</v>
       </c>
       <c r="AJ8" s="4" t="n">
-        <v>-5</v>
+        <v>1250.64</v>
       </c>
       <c r="AK8" s="4" t="n">
-        <v>1250.64</v>
+        <v>8</v>
       </c>
       <c r="AL8" s="4" t="n">
-        <v>8</v>
+        <v>1331.7</v>
       </c>
       <c r="AM8" s="4" t="n">
-        <v>1331.7</v>
+        <v>15</v>
       </c>
       <c r="AN8" s="4" t="n">
-        <v>15</v>
+        <v>0.21</v>
       </c>
       <c r="AO8" s="4" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="AP8" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AP8" s="4" t="inlineStr"/>
       <c r="AQ8" s="4" t="inlineStr"/>
-      <c r="AR8" s="4" t="inlineStr"/>
+      <c r="AR8" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
       <c r="AS8" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT8" s="4" t="inlineStr">
-        <is>
           <t>Mean Reversion · Quality · Momentum</t>
         </is>
       </c>
+      <c r="AT8" s="4" t="inlineStr"/>
       <c r="AU8" s="4" t="inlineStr"/>
-      <c r="AV8" s="4" t="inlineStr"/>
-      <c r="AW8" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX8" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+      <c r="AV8" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW8" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -1924,12 +1925,14 @@
       <c r="K9" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="L9" s="4" t="n">
-        <v>72.90000000000001</v>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>🟢 NEW</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -1937,108 +1940,107 @@
           <t>🟢</t>
         </is>
       </c>
-      <c r="O9" s="4" t="inlineStr"/>
+      <c r="O9" s="4" t="n">
+        <v>35.6</v>
+      </c>
       <c r="P9" s="4" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="Q9" s="4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="R9" s="4" t="inlineStr">
+      <c r="Q9" s="4" t="inlineStr">
         <is>
           <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
+      <c r="R9" s="4" t="inlineStr"/>
       <c r="S9" s="4" t="inlineStr"/>
       <c r="T9" s="4" t="inlineStr"/>
-      <c r="U9" s="4" t="inlineStr"/>
-      <c r="V9" s="4" t="inlineStr">
-        <is>
-          <t>Rank ↓ 3→8 · Conf 38% · band WATCH→HOLD · 53d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="W9" s="4" t="inlineStr"/>
-      <c r="X9" s="4" t="n">
+      <c r="U9" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank ↓ 3→8 · Conf 38% · band HOLD · 53d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="V9" s="4" t="inlineStr"/>
+      <c r="W9" s="4" t="n">
         <v>38.3</v>
       </c>
-      <c r="Y9" s="4" t="inlineStr">
+      <c r="X9" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
+      <c r="Y9" s="4" t="n">
+        <v>22.4</v>
+      </c>
       <c r="Z9" s="4" t="n">
-        <v>22.4</v>
+        <v>8</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="AB9" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AC9" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="AD9" s="4" t="inlineStr">
+      <c r="AC9" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
+      </c>
+      <c r="AD9" s="4" t="n">
+        <v>449.35</v>
       </c>
       <c r="AE9" s="4" t="n">
         <v>449.35</v>
       </c>
       <c r="AF9" s="4" t="n">
-        <v>449.35</v>
+        <v>444.86</v>
       </c>
       <c r="AG9" s="4" t="n">
-        <v>444.86</v>
+        <v>453.84</v>
       </c>
       <c r="AH9" s="4" t="n">
-        <v>453.84</v>
+        <v>426.88</v>
       </c>
       <c r="AI9" s="4" t="n">
-        <v>426.88</v>
+        <v>-5</v>
       </c>
       <c r="AJ9" s="4" t="n">
-        <v>-5</v>
+        <v>485.3</v>
       </c>
       <c r="AK9" s="4" t="n">
-        <v>485.3</v>
+        <v>8</v>
       </c>
       <c r="AL9" s="4" t="n">
-        <v>8</v>
+        <v>516.75</v>
       </c>
       <c r="AM9" s="4" t="n">
-        <v>516.75</v>
+        <v>15</v>
       </c>
       <c r="AN9" s="4" t="n">
-        <v>15</v>
+        <v>0.5</v>
       </c>
       <c r="AO9" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AP9" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AP9" s="4" t="inlineStr"/>
       <c r="AQ9" s="4" t="inlineStr"/>
-      <c r="AR9" s="4" t="inlineStr"/>
+      <c r="AR9" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
       <c r="AS9" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT9" s="4" t="inlineStr">
-        <is>
           <t>Value · Mean Reversion · Growth</t>
         </is>
       </c>
+      <c r="AT9" s="4" t="inlineStr"/>
       <c r="AU9" s="4" t="inlineStr"/>
-      <c r="AV9" s="4" t="inlineStr"/>
-      <c r="AW9" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX9" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+      <c r="AV9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW9" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -2084,121 +2086,118 @@
       <c r="K10" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L10" s="4" t="n">
-        <v>70.59999999999999</v>
-      </c>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
+      <c r="M10" s="4" t="inlineStr"/>
       <c r="N10" s="4" t="inlineStr">
         <is>
           <t>🟢</t>
         </is>
       </c>
-      <c r="O10" s="4" t="inlineStr"/>
+      <c r="O10" s="4" t="n">
+        <v>35.6</v>
+      </c>
       <c r="P10" s="4" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="Q10" s="4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="R10" s="4" t="inlineStr">
+      <c r="Q10" s="4" t="inlineStr">
         <is>
           <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
+      <c r="R10" s="4" t="inlineStr"/>
       <c r="S10" s="4" t="inlineStr"/>
       <c r="T10" s="4" t="inlineStr"/>
-      <c r="U10" s="4" t="inlineStr"/>
-      <c r="V10" s="4" t="inlineStr">
-        <is>
-          <t>Rank ↓ 7→9 · Conf 38% · band WATCH→HOLD · 53d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="W10" s="4" t="inlineStr"/>
-      <c r="X10" s="4" t="n">
+      <c r="U10" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank ↓ 7→9 · Conf 38% · band HOLD · 53d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="V10" s="4" t="inlineStr"/>
+      <c r="W10" s="4" t="n">
         <v>38.3</v>
       </c>
-      <c r="Y10" s="4" t="inlineStr">
+      <c r="X10" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
+      <c r="Y10" s="4" t="n">
+        <v>21.6</v>
+      </c>
       <c r="Z10" s="4" t="n">
-        <v>21.6</v>
+        <v>8</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="AB10" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AC10" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="AD10" s="4" t="inlineStr">
+      <c r="AC10" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
+      </c>
+      <c r="AD10" s="4" t="n">
+        <v>287.2</v>
       </c>
       <c r="AE10" s="4" t="n">
         <v>287.2</v>
       </c>
       <c r="AF10" s="4" t="n">
-        <v>287.2</v>
+        <v>284.33</v>
       </c>
       <c r="AG10" s="4" t="n">
-        <v>284.33</v>
+        <v>290.07</v>
       </c>
       <c r="AH10" s="4" t="n">
-        <v>290.07</v>
+        <v>272.84</v>
       </c>
       <c r="AI10" s="4" t="n">
-        <v>272.84</v>
+        <v>-5</v>
       </c>
       <c r="AJ10" s="4" t="n">
-        <v>-5</v>
+        <v>310.18</v>
       </c>
       <c r="AK10" s="4" t="n">
-        <v>310.18</v>
+        <v>8</v>
       </c>
       <c r="AL10" s="4" t="n">
-        <v>8</v>
+        <v>330.28</v>
       </c>
       <c r="AM10" s="4" t="n">
-        <v>330.28</v>
+        <v>15</v>
       </c>
       <c r="AN10" s="4" t="n">
-        <v>15</v>
+        <v>1.46</v>
       </c>
       <c r="AO10" s="4" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AP10" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AP10" s="4" t="inlineStr"/>
       <c r="AQ10" s="4" t="inlineStr"/>
-      <c r="AR10" s="4" t="inlineStr"/>
+      <c r="AR10" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
       <c r="AS10" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT10" s="4" t="inlineStr">
-        <is>
           <t>Quality · Mean Reversion · Value</t>
         </is>
       </c>
+      <c r="AT10" s="4" t="inlineStr"/>
       <c r="AU10" s="4" t="inlineStr"/>
-      <c r="AV10" s="4" t="inlineStr"/>
-      <c r="AW10" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX10" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+      <c r="AV10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW10" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -2240,121 +2239,118 @@
       <c r="K11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="4" t="n">
-        <v>77.90000000000001</v>
-      </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
+      <c r="M11" s="4" t="inlineStr"/>
       <c r="N11" s="4" t="inlineStr">
         <is>
           <t>🟢</t>
         </is>
       </c>
-      <c r="O11" s="4" t="inlineStr"/>
+      <c r="O11" s="4" t="n">
+        <v>35.6</v>
+      </c>
       <c r="P11" s="4" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="Q11" s="4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="R11" s="4" t="inlineStr">
+      <c r="Q11" s="4" t="inlineStr">
         <is>
           <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
+      <c r="R11" s="4" t="inlineStr"/>
       <c r="S11" s="4" t="inlineStr"/>
       <c r="T11" s="4" t="inlineStr"/>
-      <c r="U11" s="4" t="inlineStr"/>
-      <c r="V11" s="4" t="inlineStr">
-        <is>
-          <t>Rank → 10→10 · Conf 38% · band HOLD · 10d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="W11" s="4" t="inlineStr"/>
-      <c r="X11" s="4" t="n">
+      <c r="U11" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 10→10 · Conf 38% · band HOLD · 10d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="V11" s="4" t="inlineStr"/>
+      <c r="W11" s="4" t="n">
         <v>38.3</v>
       </c>
-      <c r="Y11" s="4" t="inlineStr">
+      <c r="X11" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
+      <c r="Y11" s="4" t="n">
+        <v>20.7</v>
+      </c>
       <c r="Z11" s="4" t="n">
-        <v>20.7</v>
+        <v>8</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="AB11" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AD11" s="4" t="inlineStr">
+      <c r="AC11" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
+      </c>
+      <c r="AD11" s="4" t="n">
+        <v>10880</v>
       </c>
       <c r="AE11" s="4" t="n">
         <v>10880</v>
       </c>
       <c r="AF11" s="4" t="n">
-        <v>10880</v>
+        <v>10771.2</v>
       </c>
       <c r="AG11" s="4" t="n">
-        <v>10771.2</v>
+        <v>10988.8</v>
       </c>
       <c r="AH11" s="4" t="n">
-        <v>10988.8</v>
+        <v>10336</v>
       </c>
       <c r="AI11" s="4" t="n">
-        <v>10336</v>
+        <v>-5</v>
       </c>
       <c r="AJ11" s="4" t="n">
-        <v>-5</v>
+        <v>11750.4</v>
       </c>
       <c r="AK11" s="4" t="n">
-        <v>11750.4</v>
+        <v>8</v>
       </c>
       <c r="AL11" s="4" t="n">
-        <v>8</v>
+        <v>12512</v>
       </c>
       <c r="AM11" s="4" t="n">
-        <v>12512</v>
+        <v>15</v>
       </c>
       <c r="AN11" s="4" t="n">
-        <v>15</v>
+        <v>-0.55</v>
       </c>
       <c r="AO11" s="4" t="n">
-        <v>-0.55</v>
-      </c>
-      <c r="AP11" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AP11" s="4" t="inlineStr"/>
       <c r="AQ11" s="4" t="inlineStr"/>
-      <c r="AR11" s="4" t="inlineStr"/>
+      <c r="AR11" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
       <c r="AS11" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT11" s="4" t="inlineStr">
-        <is>
           <t>Value · Quality · Trend</t>
         </is>
       </c>
+      <c r="AT11" s="4" t="inlineStr"/>
       <c r="AU11" s="4" t="inlineStr"/>
-      <c r="AV11" s="4" t="inlineStr"/>
-      <c r="AW11" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX11" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+      <c r="AV11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW11" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -2400,121 +2396,118 @@
       <c r="K12" s="4" t="n">
         <v>-1</v>
       </c>
-      <c r="L12" s="4" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="M12" s="4" t="inlineStr">
-        <is>
-          <t>WEAK</t>
-        </is>
-      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr"/>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>🟡</t>
-        </is>
-      </c>
-      <c r="O12" s="4" t="inlineStr"/>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="n">
+        <v>22.1</v>
+      </c>
       <c r="P12" s="4" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="Q12" s="4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="R12" s="4" t="inlineStr">
+      <c r="Q12" s="4" t="inlineStr">
         <is>
           <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
+      <c r="R12" s="4" t="inlineStr"/>
       <c r="S12" s="4" t="inlineStr"/>
       <c r="T12" s="4" t="inlineStr"/>
-      <c r="U12" s="4" t="inlineStr"/>
-      <c r="V12" s="4" t="inlineStr">
-        <is>
-          <t>Rank ↑ 12→11 · Conf 25% · band REVIEW→WEAK · 10d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="W12" s="4" t="inlineStr"/>
-      <c r="X12" s="4" t="n">
+      <c r="U12" s="4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank ↑ 12→11 · Conf 25% · band EXIT · 10d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="V12" s="4" t="inlineStr"/>
+      <c r="W12" s="4" t="n">
         <v>24.8</v>
       </c>
-      <c r="Y12" s="4" t="inlineStr">
+      <c r="X12" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
+      <c r="Y12" s="4" t="n">
+        <v>-26.6</v>
+      </c>
       <c r="Z12" s="4" t="n">
-        <v>-26.6</v>
+        <v>8</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="AB12" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC12" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AD12" s="4" t="inlineStr">
+      <c r="AC12" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
+      </c>
+      <c r="AD12" s="4" t="n">
+        <v>952.55</v>
       </c>
       <c r="AE12" s="4" t="n">
         <v>952.55</v>
       </c>
       <c r="AF12" s="4" t="n">
-        <v>952.55</v>
+        <v>943.02</v>
       </c>
       <c r="AG12" s="4" t="n">
-        <v>943.02</v>
+        <v>962.08</v>
       </c>
       <c r="AH12" s="4" t="n">
-        <v>962.08</v>
+        <v>904.92</v>
       </c>
       <c r="AI12" s="4" t="n">
-        <v>904.92</v>
+        <v>-5</v>
       </c>
       <c r="AJ12" s="4" t="n">
-        <v>-5</v>
+        <v>1028.75</v>
       </c>
       <c r="AK12" s="4" t="n">
-        <v>1028.75</v>
+        <v>8</v>
       </c>
       <c r="AL12" s="4" t="n">
-        <v>8</v>
+        <v>1095.43</v>
       </c>
       <c r="AM12" s="4" t="n">
-        <v>1095.43</v>
+        <v>15</v>
       </c>
       <c r="AN12" s="4" t="n">
-        <v>15</v>
+        <v>-0.76</v>
       </c>
       <c r="AO12" s="4" t="n">
-        <v>-0.76</v>
-      </c>
-      <c r="AP12" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AP12" s="4" t="inlineStr"/>
       <c r="AQ12" s="4" t="inlineStr"/>
-      <c r="AR12" s="4" t="inlineStr"/>
+      <c r="AR12" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
       <c r="AS12" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT12" s="4" t="inlineStr">
-        <is>
           <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
+      <c r="AT12" s="4" t="inlineStr"/>
       <c r="AU12" s="4" t="inlineStr"/>
-      <c r="AV12" s="4" t="inlineStr"/>
-      <c r="AW12" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX12" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+      <c r="AV12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW12" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -2560,121 +2553,118 @@
       <c r="K13" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L13" s="4" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="M13" s="4" t="inlineStr">
-        <is>
-          <t>WEAK</t>
-        </is>
-      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr"/>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>🟡</t>
-        </is>
-      </c>
-      <c r="O13" s="4" t="inlineStr"/>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="O13" s="4" t="n">
+        <v>27.2</v>
+      </c>
       <c r="P13" s="4" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="Q13" s="4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="R13" s="4" t="inlineStr">
+      <c r="Q13" s="4" t="inlineStr">
         <is>
           <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
+      <c r="R13" s="4" t="inlineStr"/>
       <c r="S13" s="4" t="inlineStr"/>
       <c r="T13" s="4" t="inlineStr"/>
-      <c r="U13" s="4" t="inlineStr"/>
-      <c r="V13" s="4" t="inlineStr">
-        <is>
-          <t>Rank ↓ 11→12 · Conf 30% · band REVIEW→WEAK · 10d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="W13" s="4" t="inlineStr"/>
-      <c r="X13" s="4" t="n">
+      <c r="U13" s="4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank ↓ 11→12 · Conf 30% · band EXIT · 10d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="V13" s="4" t="inlineStr"/>
+      <c r="W13" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="Y13" s="4" t="inlineStr">
+      <c r="X13" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
+      <c r="Y13" s="4" t="n">
+        <v>-28.1</v>
+      </c>
       <c r="Z13" s="4" t="n">
-        <v>-28.1</v>
+        <v>8</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="AB13" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC13" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AD13" s="4" t="inlineStr">
+      <c r="AC13" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
+      </c>
+      <c r="AD13" s="4" t="n">
+        <v>431.4</v>
       </c>
       <c r="AE13" s="4" t="n">
         <v>431.4</v>
       </c>
       <c r="AF13" s="4" t="n">
-        <v>431.4</v>
+        <v>427.09</v>
       </c>
       <c r="AG13" s="4" t="n">
-        <v>427.09</v>
+        <v>435.71</v>
       </c>
       <c r="AH13" s="4" t="n">
-        <v>435.71</v>
+        <v>409.83</v>
       </c>
       <c r="AI13" s="4" t="n">
-        <v>409.83</v>
+        <v>-5</v>
       </c>
       <c r="AJ13" s="4" t="n">
-        <v>-5</v>
+        <v>465.91</v>
       </c>
       <c r="AK13" s="4" t="n">
-        <v>465.91</v>
+        <v>8</v>
       </c>
       <c r="AL13" s="4" t="n">
-        <v>8</v>
+        <v>496.11</v>
       </c>
       <c r="AM13" s="4" t="n">
-        <v>496.11</v>
+        <v>15</v>
       </c>
       <c r="AN13" s="4" t="n">
-        <v>15</v>
+        <v>-0.72</v>
       </c>
       <c r="AO13" s="4" t="n">
-        <v>-0.72</v>
-      </c>
-      <c r="AP13" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AP13" s="4" t="inlineStr"/>
       <c r="AQ13" s="4" t="inlineStr"/>
-      <c r="AR13" s="4" t="inlineStr"/>
+      <c r="AR13" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
       <c r="AS13" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT13" s="4" t="inlineStr">
-        <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
+      <c r="AT13" s="4" t="inlineStr"/>
       <c r="AU13" s="4" t="inlineStr"/>
-      <c r="AV13" s="4" t="inlineStr"/>
-      <c r="AW13" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX13" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+      <c r="AV13" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW13" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -2716,121 +2706,118 @@
       <c r="K14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="4" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="M14" s="4" t="inlineStr">
-        <is>
-          <t>WEAK</t>
-        </is>
-      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr"/>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>🟡</t>
-        </is>
-      </c>
-      <c r="O14" s="4" t="inlineStr"/>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="O14" s="4" t="n">
+        <v>27.2</v>
+      </c>
       <c r="P14" s="4" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="Q14" s="4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="R14" s="4" t="inlineStr">
+      <c r="Q14" s="4" t="inlineStr">
         <is>
           <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
+      <c r="R14" s="4" t="inlineStr"/>
       <c r="S14" s="4" t="inlineStr"/>
       <c r="T14" s="4" t="inlineStr"/>
-      <c r="U14" s="4" t="inlineStr"/>
-      <c r="V14" s="4" t="inlineStr">
-        <is>
-          <t>Rank → 13→13 · Conf 30% · band REVIEW→WEAK · 54d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="W14" s="4" t="inlineStr"/>
-      <c r="X14" s="4" t="n">
+      <c r="U14" s="4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 13→13 · Conf 30% · band EXIT · 54d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="V14" s="4" t="inlineStr"/>
+      <c r="W14" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="Y14" s="4" t="inlineStr">
+      <c r="X14" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
+      <c r="Y14" s="4" t="n">
+        <v>-28.4</v>
+      </c>
       <c r="Z14" s="4" t="n">
-        <v>-28.4</v>
+        <v>7</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="AB14" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AC14" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="AD14" s="4" t="inlineStr">
+      <c r="AC14" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
+      </c>
+      <c r="AD14" s="4" t="n">
+        <v>2157.8</v>
       </c>
       <c r="AE14" s="4" t="n">
         <v>2157.8</v>
       </c>
       <c r="AF14" s="4" t="n">
-        <v>2157.8</v>
+        <v>2136.22</v>
       </c>
       <c r="AG14" s="4" t="n">
-        <v>2136.22</v>
+        <v>2179.38</v>
       </c>
       <c r="AH14" s="4" t="n">
-        <v>2179.38</v>
+        <v>2049.91</v>
       </c>
       <c r="AI14" s="4" t="n">
-        <v>2049.91</v>
+        <v>-5</v>
       </c>
       <c r="AJ14" s="4" t="n">
-        <v>-5</v>
+        <v>2330.42</v>
       </c>
       <c r="AK14" s="4" t="n">
-        <v>2330.42</v>
+        <v>8</v>
       </c>
       <c r="AL14" s="4" t="n">
-        <v>8</v>
+        <v>2481.47</v>
       </c>
       <c r="AM14" s="4" t="n">
-        <v>2481.47</v>
+        <v>15</v>
       </c>
       <c r="AN14" s="4" t="n">
-        <v>15</v>
+        <v>-0.25</v>
       </c>
       <c r="AO14" s="4" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AP14" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AP14" s="4" t="inlineStr"/>
       <c r="AQ14" s="4" t="inlineStr"/>
-      <c r="AR14" s="4" t="inlineStr"/>
+      <c r="AR14" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
       <c r="AS14" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT14" s="4" t="inlineStr">
-        <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
+      <c r="AT14" s="4" t="inlineStr"/>
       <c r="AU14" s="4" t="inlineStr"/>
-      <c r="AV14" s="4" t="inlineStr"/>
-      <c r="AW14" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX14" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+      <c r="AV14" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW14" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -2876,121 +2863,118 @@
       <c r="K15" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L15" s="4" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="M15" s="4" t="inlineStr">
-        <is>
-          <t>WEAK</t>
-        </is>
-      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr"/>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>🟡</t>
-        </is>
-      </c>
-      <c r="O15" s="4" t="inlineStr"/>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="O15" s="4" t="n">
+        <v>22.1</v>
+      </c>
       <c r="P15" s="4" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="Q15" s="4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="R15" s="4" t="inlineStr">
+      <c r="Q15" s="4" t="inlineStr">
         <is>
           <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
+      <c r="R15" s="4" t="inlineStr"/>
       <c r="S15" s="4" t="inlineStr"/>
       <c r="T15" s="4" t="inlineStr"/>
-      <c r="U15" s="4" t="inlineStr"/>
-      <c r="V15" s="4" t="inlineStr">
-        <is>
-          <t>Rank ↓ 13→14 · Conf 25% · band REVIEW→WEAK · 53d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="W15" s="4" t="inlineStr"/>
-      <c r="X15" s="4" t="n">
+      <c r="U15" s="4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank ↓ 13→14 · Conf 25% · band EXIT · 53d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="V15" s="4" t="inlineStr"/>
+      <c r="W15" s="4" t="n">
         <v>24.8</v>
       </c>
-      <c r="Y15" s="4" t="inlineStr">
+      <c r="X15" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
+      <c r="Y15" s="4" t="n">
+        <v>-29.9</v>
+      </c>
       <c r="Z15" s="4" t="n">
-        <v>-29.9</v>
+        <v>8</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="AB15" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AC15" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="AD15" s="4" t="inlineStr">
+      <c r="AC15" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
+      </c>
+      <c r="AD15" s="4" t="n">
+        <v>547.4</v>
       </c>
       <c r="AE15" s="4" t="n">
         <v>547.4</v>
       </c>
       <c r="AF15" s="4" t="n">
-        <v>547.4</v>
+        <v>541.9299999999999</v>
       </c>
       <c r="AG15" s="4" t="n">
-        <v>541.9299999999999</v>
+        <v>552.87</v>
       </c>
       <c r="AH15" s="4" t="n">
-        <v>552.87</v>
+        <v>520.03</v>
       </c>
       <c r="AI15" s="4" t="n">
-        <v>520.03</v>
+        <v>-5</v>
       </c>
       <c r="AJ15" s="4" t="n">
-        <v>-5</v>
+        <v>591.1900000000001</v>
       </c>
       <c r="AK15" s="4" t="n">
-        <v>591.1900000000001</v>
+        <v>8</v>
       </c>
       <c r="AL15" s="4" t="n">
-        <v>8</v>
+        <v>629.51</v>
       </c>
       <c r="AM15" s="4" t="n">
-        <v>629.51</v>
+        <v>15</v>
       </c>
       <c r="AN15" s="4" t="n">
-        <v>15</v>
+        <v>0.12</v>
       </c>
       <c r="AO15" s="4" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AP15" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AP15" s="4" t="inlineStr"/>
       <c r="AQ15" s="4" t="inlineStr"/>
-      <c r="AR15" s="4" t="inlineStr"/>
+      <c r="AR15" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
       <c r="AS15" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT15" s="4" t="inlineStr">
-        <is>
           <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
+      <c r="AT15" s="4" t="inlineStr"/>
       <c r="AU15" s="4" t="inlineStr"/>
-      <c r="AV15" s="4" t="inlineStr"/>
-      <c r="AW15" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX15" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+      <c r="AV15" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW15" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -3032,121 +3016,118 @@
       <c r="K16" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="4" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="M16" s="4" t="inlineStr">
-        <is>
-          <t>WEAK</t>
-        </is>
-      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr"/>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>🟡</t>
-        </is>
-      </c>
-      <c r="O16" s="4" t="inlineStr"/>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="O16" s="4" t="n">
+        <v>25.6</v>
+      </c>
       <c r="P16" s="4" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="Q16" s="4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="R16" s="4" t="inlineStr">
+      <c r="Q16" s="4" t="inlineStr">
         <is>
           <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
+      <c r="R16" s="4" t="inlineStr"/>
       <c r="S16" s="4" t="inlineStr"/>
       <c r="T16" s="4" t="inlineStr"/>
-      <c r="U16" s="4" t="inlineStr"/>
-      <c r="V16" s="4" t="inlineStr">
-        <is>
-          <t>Rank → 15→15 · Conf 28% · band REVIEW→WEAK · 54d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="W16" s="4" t="inlineStr"/>
-      <c r="X16" s="4" t="n">
+      <c r="U16" s="4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 15→15 · Conf 28% · band EXIT · 54d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="V16" s="4" t="inlineStr"/>
+      <c r="W16" s="4" t="n">
         <v>28.4</v>
       </c>
-      <c r="Y16" s="4" t="inlineStr">
+      <c r="X16" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
+      <c r="Y16" s="4" t="n">
+        <v>-31.5</v>
+      </c>
       <c r="Z16" s="4" t="n">
-        <v>-31.5</v>
+        <v>7</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="AB16" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AC16" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="AD16" s="4" t="inlineStr">
+      <c r="AC16" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
+      </c>
+      <c r="AD16" s="4" t="n">
+        <v>1363</v>
       </c>
       <c r="AE16" s="4" t="n">
         <v>1363</v>
       </c>
       <c r="AF16" s="4" t="n">
-        <v>1363</v>
+        <v>1349.37</v>
       </c>
       <c r="AG16" s="4" t="n">
-        <v>1349.37</v>
+        <v>1376.63</v>
       </c>
       <c r="AH16" s="4" t="n">
-        <v>1376.63</v>
+        <v>1294.85</v>
       </c>
       <c r="AI16" s="4" t="n">
-        <v>1294.85</v>
+        <v>-5</v>
       </c>
       <c r="AJ16" s="4" t="n">
-        <v>-5</v>
+        <v>1472.04</v>
       </c>
       <c r="AK16" s="4" t="n">
-        <v>1472.04</v>
+        <v>8</v>
       </c>
       <c r="AL16" s="4" t="n">
-        <v>8</v>
+        <v>1567.45</v>
       </c>
       <c r="AM16" s="4" t="n">
-        <v>1567.45</v>
+        <v>15</v>
       </c>
       <c r="AN16" s="4" t="n">
-        <v>15</v>
+        <v>-1.52</v>
       </c>
       <c r="AO16" s="4" t="n">
-        <v>-1.52</v>
-      </c>
-      <c r="AP16" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AP16" s="4" t="inlineStr"/>
       <c r="AQ16" s="4" t="inlineStr"/>
-      <c r="AR16" s="4" t="inlineStr"/>
+      <c r="AR16" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
       <c r="AS16" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT16" s="4" t="inlineStr">
-        <is>
           <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
+      <c r="AT16" s="4" t="inlineStr"/>
       <c r="AU16" s="4" t="inlineStr"/>
-      <c r="AV16" s="4" t="inlineStr"/>
-      <c r="AW16" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX16" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+      <c r="AV16" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW16" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -3195,102 +3176,99 @@
       <c r="L17" s="4" t="inlineStr"/>
       <c r="M17" s="4" t="inlineStr"/>
       <c r="N17" s="4" t="inlineStr"/>
-      <c r="O17" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="O17" s="4" t="inlineStr"/>
       <c r="P17" s="4" t="inlineStr"/>
       <c r="Q17" s="4" t="inlineStr"/>
       <c r="R17" s="4" t="inlineStr"/>
       <c r="S17" s="4" t="inlineStr"/>
       <c r="T17" s="4" t="inlineStr"/>
-      <c r="U17" s="4" t="inlineStr"/>
-      <c r="V17" s="4" t="inlineStr">
-        <is>
-          <t>Rank ↑ 2→1 · Conf 83% · momentum → · 61d left · → STRONG BUY</t>
-        </is>
-      </c>
-      <c r="W17" s="4" t="inlineStr"/>
-      <c r="X17" s="4" t="n">
+      <c r="U17" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.7%) · Rank ↑ 2→1 · Conf 83% · momentum → · 61d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="V17" s="4" t="inlineStr"/>
+      <c r="W17" s="4" t="n">
         <v>83</v>
       </c>
-      <c r="Y17" s="4" t="inlineStr">
+      <c r="X17" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Z17" s="4" t="n">
+      <c r="Y17" s="4" t="n">
         <v>78</v>
       </c>
-      <c r="AA17" s="4" t="inlineStr"/>
+      <c r="Z17" s="4" t="inlineStr"/>
+      <c r="AA17" s="4" t="n">
+        <v>60</v>
+      </c>
       <c r="AB17" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AC17" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="AD17" s="4" t="inlineStr">
+      <c r="AC17" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
+      </c>
+      <c r="AD17" s="4" t="n">
+        <v>1454.6</v>
       </c>
       <c r="AE17" s="4" t="n">
         <v>1454.6</v>
       </c>
       <c r="AF17" s="4" t="n">
-        <v>1454.6</v>
+        <v>1415</v>
       </c>
       <c r="AG17" s="4" t="n">
-        <v>1415</v>
+        <v>1495</v>
       </c>
       <c r="AH17" s="4" t="n">
-        <v>1495</v>
+        <v>1381.87</v>
       </c>
       <c r="AI17" s="4" t="n">
-        <v>1381.87</v>
+        <v>-5</v>
       </c>
       <c r="AJ17" s="4" t="n">
-        <v>-5</v>
+        <v>1532</v>
       </c>
       <c r="AK17" s="4" t="n">
-        <v>1532</v>
+        <v>5.32</v>
       </c>
       <c r="AL17" s="4" t="n">
+        <v>1639.24</v>
+      </c>
+      <c r="AM17" s="4" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="AN17" s="4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AO17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" s="4" t="inlineStr"/>
+      <c r="AQ17" s="4" t="inlineStr"/>
+      <c r="AR17" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AS17" s="4" t="inlineStr"/>
+      <c r="AT17" s="4" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="AU17" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV17" s="4" t="n">
         <v>5.32</v>
       </c>
-      <c r="AM17" s="4" t="n">
-        <v>1639.24</v>
-      </c>
-      <c r="AN17" s="4" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="AO17" s="4" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="AP17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" s="4" t="inlineStr"/>
-      <c r="AR17" s="4" t="inlineStr"/>
-      <c r="AS17" s="4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT17" s="4" t="inlineStr"/>
-      <c r="AU17" s="4" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="AV17" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW17" s="4" t="n">
-        <v>5.32</v>
-      </c>
-      <c r="AX17" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+      <c r="AW17" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -3339,102 +3317,99 @@
       <c r="L18" s="4" t="inlineStr"/>
       <c r="M18" s="4" t="inlineStr"/>
       <c r="N18" s="4" t="inlineStr"/>
-      <c r="O18" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="O18" s="4" t="inlineStr"/>
       <c r="P18" s="4" t="inlineStr"/>
       <c r="Q18" s="4" t="inlineStr"/>
       <c r="R18" s="4" t="inlineStr"/>
       <c r="S18" s="4" t="inlineStr"/>
       <c r="T18" s="4" t="inlineStr"/>
-      <c r="U18" s="4" t="inlineStr"/>
-      <c r="V18" s="4" t="inlineStr">
-        <is>
-          <t>Rank ↓ 1→2 · Conf 88% · momentum → · 61d left · → STRONG BUY</t>
-        </is>
-      </c>
-      <c r="W18" s="4" t="inlineStr"/>
-      <c r="X18" s="4" t="n">
+      <c r="U18" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.6%) · Rank ↓ 1→2 · Conf 88% · momentum → · 61d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="V18" s="4" t="inlineStr"/>
+      <c r="W18" s="4" t="n">
         <v>88</v>
       </c>
-      <c r="Y18" s="4" t="inlineStr">
+      <c r="X18" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Z18" s="4" t="n">
+      <c r="Y18" s="4" t="n">
         <v>74</v>
       </c>
-      <c r="AA18" s="4" t="inlineStr"/>
+      <c r="Z18" s="4" t="inlineStr"/>
+      <c r="AA18" s="4" t="n">
+        <v>60</v>
+      </c>
       <c r="AB18" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AC18" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="AD18" s="4" t="inlineStr">
+      <c r="AC18" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
+      </c>
+      <c r="AD18" s="4" t="n">
+        <v>1964</v>
       </c>
       <c r="AE18" s="4" t="n">
         <v>1964</v>
       </c>
       <c r="AF18" s="4" t="n">
-        <v>1964</v>
+        <v>1911</v>
       </c>
       <c r="AG18" s="4" t="n">
-        <v>1911</v>
+        <v>2017</v>
       </c>
       <c r="AH18" s="4" t="n">
-        <v>2017</v>
+        <v>1865.8</v>
       </c>
       <c r="AI18" s="4" t="n">
-        <v>1865.8</v>
+        <v>-5</v>
       </c>
       <c r="AJ18" s="4" t="n">
-        <v>-5</v>
+        <v>2054</v>
       </c>
       <c r="AK18" s="4" t="n">
-        <v>2054</v>
+        <v>4.58</v>
       </c>
       <c r="AL18" s="4" t="n">
+        <v>2197.78</v>
+      </c>
+      <c r="AM18" s="4" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="AN18" s="4" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AO18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" s="4" t="inlineStr"/>
+      <c r="AQ18" s="4" t="inlineStr"/>
+      <c r="AR18" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AS18" s="4" t="inlineStr"/>
+      <c r="AT18" s="4" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="AU18" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV18" s="4" t="n">
         <v>4.58</v>
       </c>
-      <c r="AM18" s="4" t="n">
-        <v>2197.78</v>
-      </c>
-      <c r="AN18" s="4" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="AO18" s="4" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="AP18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" s="4" t="inlineStr"/>
-      <c r="AR18" s="4" t="inlineStr"/>
-      <c r="AS18" s="4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT18" s="4" t="inlineStr"/>
-      <c r="AU18" s="4" t="inlineStr">
-        <is>
-          <t>Pharma</t>
-        </is>
-      </c>
-      <c r="AV18" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW18" s="4" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="AX18" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+      <c r="AW18" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -3483,102 +3458,99 @@
       <c r="L19" s="4" t="inlineStr"/>
       <c r="M19" s="4" t="inlineStr"/>
       <c r="N19" s="4" t="inlineStr"/>
-      <c r="O19" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="O19" s="4" t="inlineStr"/>
       <c r="P19" s="4" t="inlineStr"/>
       <c r="Q19" s="4" t="inlineStr"/>
       <c r="R19" s="4" t="inlineStr"/>
       <c r="S19" s="4" t="inlineStr"/>
       <c r="T19" s="4" t="inlineStr"/>
-      <c r="U19" s="4" t="inlineStr"/>
-      <c r="V19" s="4" t="inlineStr">
-        <is>
-          <t>Rank → 3→3 · Conf 86% · momentum → · 61d left · → STRONG BUY</t>
-        </is>
-      </c>
-      <c r="W19" s="4" t="inlineStr"/>
-      <c r="X19" s="4" t="n">
+      <c r="U19" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-3.0%) · Rank → 3→3 · Conf 86% · momentum → · 61d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="V19" s="4" t="inlineStr"/>
+      <c r="W19" s="4" t="n">
         <v>86</v>
       </c>
-      <c r="Y19" s="4" t="inlineStr">
+      <c r="X19" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Z19" s="4" t="n">
+      <c r="Y19" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="AA19" s="4" t="inlineStr"/>
+      <c r="Z19" s="4" t="inlineStr"/>
+      <c r="AA19" s="4" t="n">
+        <v>60</v>
+      </c>
       <c r="AB19" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AC19" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="AD19" s="4" t="inlineStr">
+      <c r="AC19" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
+      </c>
+      <c r="AD19" s="4" t="n">
+        <v>1620</v>
       </c>
       <c r="AE19" s="4" t="n">
         <v>1620</v>
       </c>
       <c r="AF19" s="4" t="n">
-        <v>1620</v>
+        <v>1569</v>
       </c>
       <c r="AG19" s="4" t="n">
-        <v>1569</v>
+        <v>1671</v>
       </c>
       <c r="AH19" s="4" t="n">
-        <v>1671</v>
+        <v>1539</v>
       </c>
       <c r="AI19" s="4" t="n">
-        <v>1539</v>
+        <v>-5</v>
       </c>
       <c r="AJ19" s="4" t="n">
-        <v>-5</v>
+        <v>1642</v>
       </c>
       <c r="AK19" s="4" t="n">
-        <v>1642</v>
+        <v>1.36</v>
       </c>
       <c r="AL19" s="4" t="n">
+        <v>1756.94</v>
+      </c>
+      <c r="AM19" s="4" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="AN19" s="4" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="AO19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" s="4" t="inlineStr"/>
+      <c r="AQ19" s="4" t="inlineStr"/>
+      <c r="AR19" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AS19" s="4" t="inlineStr"/>
+      <c r="AT19" s="4" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+      <c r="AU19" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV19" s="4" t="n">
         <v>1.36</v>
       </c>
-      <c r="AM19" s="4" t="n">
-        <v>1756.94</v>
-      </c>
-      <c r="AN19" s="4" t="n">
-        <v>8.449999999999999</v>
-      </c>
-      <c r="AO19" s="4" t="n">
-        <v>-1.37</v>
-      </c>
-      <c r="AP19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" s="4" t="inlineStr"/>
-      <c r="AR19" s="4" t="inlineStr"/>
-      <c r="AS19" s="4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT19" s="4" t="inlineStr"/>
-      <c r="AU19" s="4" t="inlineStr">
-        <is>
-          <t>Chemicals</t>
-        </is>
-      </c>
-      <c r="AV19" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW19" s="4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AX19" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+      <c r="AW19" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -3627,102 +3599,99 @@
       <c r="L20" s="4" t="inlineStr"/>
       <c r="M20" s="4" t="inlineStr"/>
       <c r="N20" s="4" t="inlineStr"/>
-      <c r="O20" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="O20" s="4" t="inlineStr"/>
       <c r="P20" s="4" t="inlineStr"/>
       <c r="Q20" s="4" t="inlineStr"/>
       <c r="R20" s="4" t="inlineStr"/>
       <c r="S20" s="4" t="inlineStr"/>
       <c r="T20" s="4" t="inlineStr"/>
-      <c r="U20" s="4" t="inlineStr"/>
-      <c r="V20" s="4" t="inlineStr">
-        <is>
-          <t>Rank ↓ 3→4 · Conf 71% · momentum → · 61d left · → STRONG BUY</t>
-        </is>
-      </c>
-      <c r="W20" s="4" t="inlineStr"/>
-      <c r="X20" s="4" t="n">
+      <c r="U20" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.5%) · Rank ↓ 3→4 · Conf 71% · momentum → · 61d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="V20" s="4" t="inlineStr"/>
+      <c r="W20" s="4" t="n">
         <v>71</v>
       </c>
-      <c r="Y20" s="4" t="inlineStr">
+      <c r="X20" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Z20" s="4" t="n">
+      <c r="Y20" s="4" t="n">
         <v>68</v>
       </c>
-      <c r="AA20" s="4" t="inlineStr"/>
+      <c r="Z20" s="4" t="inlineStr"/>
+      <c r="AA20" s="4" t="n">
+        <v>60</v>
+      </c>
       <c r="AB20" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AC20" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="AD20" s="4" t="inlineStr">
+      <c r="AC20" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
+      </c>
+      <c r="AD20" s="4" t="n">
+        <v>2410</v>
       </c>
       <c r="AE20" s="4" t="n">
         <v>2410</v>
       </c>
       <c r="AF20" s="4" t="n">
-        <v>2410</v>
+        <v>2349</v>
       </c>
       <c r="AG20" s="4" t="n">
-        <v>2349</v>
+        <v>2471</v>
       </c>
       <c r="AH20" s="4" t="n">
-        <v>2471</v>
+        <v>2289.5</v>
       </c>
       <c r="AI20" s="4" t="n">
-        <v>2289.5</v>
+        <v>-5</v>
       </c>
       <c r="AJ20" s="4" t="n">
-        <v>-5</v>
+        <v>2602.8</v>
       </c>
       <c r="AK20" s="4" t="n">
-        <v>2602.8</v>
+        <v>8</v>
       </c>
       <c r="AL20" s="4" t="n">
-        <v>8</v>
+        <v>2784.996000000001</v>
       </c>
       <c r="AM20" s="4" t="n">
-        <v>2784.996000000001</v>
+        <v>15.56</v>
       </c>
       <c r="AN20" s="4" t="n">
-        <v>15.56</v>
+        <v>1.09</v>
       </c>
       <c r="AO20" s="4" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AP20" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AP20" s="4" t="inlineStr"/>
       <c r="AQ20" s="4" t="inlineStr"/>
-      <c r="AR20" s="4" t="inlineStr"/>
-      <c r="AS20" s="4" t="inlineStr">
+      <c r="AR20" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AT20" s="4" t="inlineStr"/>
-      <c r="AU20" s="4" t="inlineStr">
+      <c r="AS20" s="4" t="inlineStr"/>
+      <c r="AT20" s="4" t="inlineStr">
         <is>
           <t>Pharma</t>
         </is>
       </c>
+      <c r="AU20" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AV20" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW20" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX20" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+        <v>8</v>
+      </c>
+      <c r="AW20" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -3771,102 +3740,99 @@
       <c r="L21" s="4" t="inlineStr"/>
       <c r="M21" s="4" t="inlineStr"/>
       <c r="N21" s="4" t="inlineStr"/>
-      <c r="O21" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="O21" s="4" t="inlineStr"/>
       <c r="P21" s="4" t="inlineStr"/>
       <c r="Q21" s="4" t="inlineStr"/>
       <c r="R21" s="4" t="inlineStr"/>
       <c r="S21" s="4" t="inlineStr"/>
       <c r="T21" s="4" t="inlineStr"/>
-      <c r="U21" s="4" t="inlineStr"/>
-      <c r="V21" s="4" t="inlineStr">
-        <is>
-          <t>Rank ↓ 4→5 · Conf 72% · momentum → · 61d left · → STRONG BUY</t>
-        </is>
-      </c>
-      <c r="W21" s="4" t="inlineStr"/>
-      <c r="X21" s="4" t="n">
+      <c r="U21" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.7%) · Rank ↓ 4→5 · Conf 72% · momentum → · 61d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="V21" s="4" t="inlineStr"/>
+      <c r="W21" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="Y21" s="4" t="inlineStr">
+      <c r="X21" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Z21" s="4" t="n">
+      <c r="Y21" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="AA21" s="4" t="inlineStr"/>
+      <c r="Z21" s="4" t="inlineStr"/>
+      <c r="AA21" s="4" t="n">
+        <v>60</v>
+      </c>
       <c r="AB21" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AC21" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="AD21" s="4" t="inlineStr">
+      <c r="AC21" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
+      </c>
+      <c r="AD21" s="4" t="n">
+        <v>343.6</v>
       </c>
       <c r="AE21" s="4" t="n">
         <v>343.6</v>
       </c>
       <c r="AF21" s="4" t="n">
-        <v>343.6</v>
+        <v>335</v>
       </c>
       <c r="AG21" s="4" t="n">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="AH21" s="4" t="n">
-        <v>353</v>
+        <v>326.42</v>
       </c>
       <c r="AI21" s="4" t="n">
-        <v>326.42</v>
+        <v>-5</v>
       </c>
       <c r="AJ21" s="4" t="n">
-        <v>-5</v>
+        <v>371.088</v>
       </c>
       <c r="AK21" s="4" t="n">
-        <v>371.088</v>
+        <v>8</v>
       </c>
       <c r="AL21" s="4" t="n">
-        <v>8</v>
+        <v>397.0641600000001</v>
       </c>
       <c r="AM21" s="4" t="n">
-        <v>397.0641600000001</v>
+        <v>15.56</v>
       </c>
       <c r="AN21" s="4" t="n">
-        <v>15.56</v>
+        <v>-1.04</v>
       </c>
       <c r="AO21" s="4" t="n">
-        <v>-1.04</v>
-      </c>
-      <c r="AP21" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AP21" s="4" t="inlineStr"/>
       <c r="AQ21" s="4" t="inlineStr"/>
-      <c r="AR21" s="4" t="inlineStr"/>
-      <c r="AS21" s="4" t="inlineStr">
+      <c r="AR21" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AT21" s="4" t="inlineStr"/>
-      <c r="AU21" s="4" t="inlineStr">
+      <c r="AS21" s="4" t="inlineStr"/>
+      <c r="AT21" s="4" t="inlineStr">
         <is>
           <t>Power</t>
         </is>
       </c>
+      <c r="AU21" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AV21" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW21" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX21" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+        <v>8</v>
+      </c>
+      <c r="AW21" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -3915,102 +3881,99 @@
       <c r="L22" s="4" t="inlineStr"/>
       <c r="M22" s="4" t="inlineStr"/>
       <c r="N22" s="4" t="inlineStr"/>
-      <c r="O22" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="O22" s="4" t="inlineStr"/>
       <c r="P22" s="4" t="inlineStr"/>
       <c r="Q22" s="4" t="inlineStr"/>
       <c r="R22" s="4" t="inlineStr"/>
       <c r="S22" s="4" t="inlineStr"/>
       <c r="T22" s="4" t="inlineStr"/>
-      <c r="U22" s="4" t="inlineStr"/>
-      <c r="V22" s="4" t="inlineStr">
-        <is>
-          <t>Rank ↓ 5→6 · Conf 72% · momentum → · 61d left · → BUY</t>
-        </is>
-      </c>
-      <c r="W22" s="4" t="inlineStr"/>
-      <c r="X22" s="4" t="n">
+      <c r="U22" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.9%) · Rank ↓ 5→6 · Conf 72% · momentum → · 61d left · → BUY</t>
+        </is>
+      </c>
+      <c r="V22" s="4" t="inlineStr"/>
+      <c r="W22" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="Y22" s="4" t="inlineStr">
+      <c r="X22" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Z22" s="4" t="n">
+      <c r="Y22" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="AA22" s="4" t="inlineStr"/>
+      <c r="Z22" s="4" t="inlineStr"/>
+      <c r="AA22" s="4" t="n">
+        <v>60</v>
+      </c>
       <c r="AB22" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AC22" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="AD22" s="4" t="inlineStr">
+      <c r="AC22" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
+      </c>
+      <c r="AD22" s="4" t="n">
+        <v>398</v>
       </c>
       <c r="AE22" s="4" t="n">
         <v>398</v>
       </c>
       <c r="AF22" s="4" t="n">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="AG22" s="4" t="n">
-        <v>386</v>
+        <v>410</v>
       </c>
       <c r="AH22" s="4" t="n">
-        <v>410</v>
+        <v>378.1</v>
       </c>
       <c r="AI22" s="4" t="n">
-        <v>378.1</v>
+        <v>-5</v>
       </c>
       <c r="AJ22" s="4" t="n">
-        <v>-5</v>
+        <v>429.84</v>
       </c>
       <c r="AK22" s="4" t="n">
-        <v>429.84</v>
+        <v>8</v>
       </c>
       <c r="AL22" s="4" t="n">
-        <v>8</v>
+        <v>459.9288000000001</v>
       </c>
       <c r="AM22" s="4" t="n">
-        <v>459.9288000000001</v>
+        <v>15.56</v>
       </c>
       <c r="AN22" s="4" t="n">
-        <v>15.56</v>
+        <v>0.25</v>
       </c>
       <c r="AO22" s="4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AP22" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AP22" s="4" t="inlineStr"/>
       <c r="AQ22" s="4" t="inlineStr"/>
-      <c r="AR22" s="4" t="inlineStr"/>
-      <c r="AS22" s="4" t="inlineStr">
+      <c r="AR22" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AT22" s="4" t="inlineStr"/>
-      <c r="AU22" s="4" t="inlineStr">
+      <c r="AS22" s="4" t="inlineStr"/>
+      <c r="AT22" s="4" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
+      <c r="AU22" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AV22" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW22" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX22" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+        <v>8</v>
+      </c>
+      <c r="AW22" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -4059,102 +4022,99 @@
       <c r="L23" s="4" t="inlineStr"/>
       <c r="M23" s="4" t="inlineStr"/>
       <c r="N23" s="4" t="inlineStr"/>
-      <c r="O23" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="O23" s="4" t="inlineStr"/>
       <c r="P23" s="4" t="inlineStr"/>
       <c r="Q23" s="4" t="inlineStr"/>
       <c r="R23" s="4" t="inlineStr"/>
       <c r="S23" s="4" t="inlineStr"/>
       <c r="T23" s="4" t="inlineStr"/>
-      <c r="U23" s="4" t="inlineStr"/>
-      <c r="V23" s="4" t="inlineStr">
-        <is>
-          <t>Rank → 7→7 · Conf 69% · momentum → · 61d left · → BUY</t>
-        </is>
-      </c>
-      <c r="W23" s="4" t="inlineStr"/>
-      <c r="X23" s="4" t="n">
+      <c r="U23" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.3%) · Rank → 7→7 · Conf 69% · momentum → · 61d left · → BUY</t>
+        </is>
+      </c>
+      <c r="V23" s="4" t="inlineStr"/>
+      <c r="W23" s="4" t="n">
         <v>69</v>
       </c>
-      <c r="Y23" s="4" t="inlineStr">
+      <c r="X23" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Z23" s="4" t="n">
+      <c r="Y23" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="AA23" s="4" t="inlineStr"/>
+      <c r="Z23" s="4" t="inlineStr"/>
+      <c r="AA23" s="4" t="n">
+        <v>60</v>
+      </c>
       <c r="AB23" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AC23" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="AD23" s="4" t="inlineStr">
+      <c r="AC23" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
+      </c>
+      <c r="AD23" s="4" t="n">
+        <v>283.4</v>
       </c>
       <c r="AE23" s="4" t="n">
         <v>283.4</v>
       </c>
       <c r="AF23" s="4" t="n">
-        <v>283.4</v>
+        <v>276</v>
       </c>
       <c r="AG23" s="4" t="n">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="AH23" s="4" t="n">
-        <v>290</v>
+        <v>269.23</v>
       </c>
       <c r="AI23" s="4" t="n">
-        <v>269.23</v>
+        <v>-5</v>
       </c>
       <c r="AJ23" s="4" t="n">
-        <v>-5</v>
+        <v>306.072</v>
       </c>
       <c r="AK23" s="4" t="n">
-        <v>306.072</v>
+        <v>8</v>
       </c>
       <c r="AL23" s="4" t="n">
-        <v>8</v>
+        <v>327.49704</v>
       </c>
       <c r="AM23" s="4" t="n">
-        <v>327.49704</v>
+        <v>15.56</v>
       </c>
       <c r="AN23" s="4" t="n">
-        <v>15.56</v>
+        <v>-0.86</v>
       </c>
       <c r="AO23" s="4" t="n">
-        <v>-0.86</v>
-      </c>
-      <c r="AP23" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AP23" s="4" t="inlineStr"/>
       <c r="AQ23" s="4" t="inlineStr"/>
-      <c r="AR23" s="4" t="inlineStr"/>
-      <c r="AS23" s="4" t="inlineStr">
+      <c r="AR23" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AT23" s="4" t="inlineStr"/>
-      <c r="AU23" s="4" t="inlineStr">
+      <c r="AS23" s="4" t="inlineStr"/>
+      <c r="AT23" s="4" t="inlineStr">
         <is>
           <t>Power</t>
         </is>
       </c>
+      <c r="AU23" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AV23" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW23" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX23" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+        <v>8</v>
+      </c>
+      <c r="AW23" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -4203,102 +4163,99 @@
       <c r="L24" s="4" t="inlineStr"/>
       <c r="M24" s="4" t="inlineStr"/>
       <c r="N24" s="4" t="inlineStr"/>
-      <c r="O24" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="O24" s="4" t="inlineStr"/>
       <c r="P24" s="4" t="inlineStr"/>
       <c r="Q24" s="4" t="inlineStr"/>
       <c r="R24" s="4" t="inlineStr"/>
       <c r="S24" s="4" t="inlineStr"/>
       <c r="T24" s="4" t="inlineStr"/>
-      <c r="U24" s="4" t="inlineStr"/>
-      <c r="V24" s="4" t="inlineStr">
-        <is>
-          <t>Rank ↓ 7→8 · Conf 67% · momentum → · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="W24" s="4" t="inlineStr"/>
-      <c r="X24" s="4" t="n">
+      <c r="U24" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-3.0%) · Rank ↓ 7→8 · Conf 67% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="V24" s="4" t="inlineStr"/>
+      <c r="W24" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="Y24" s="4" t="inlineStr">
+      <c r="X24" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Z24" s="4" t="n">
+      <c r="Y24" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="AA24" s="4" t="inlineStr"/>
+      <c r="Z24" s="4" t="inlineStr"/>
+      <c r="AA24" s="4" t="n">
+        <v>60</v>
+      </c>
       <c r="AB24" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AC24" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="AD24" s="4" t="inlineStr">
+      <c r="AC24" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
+      </c>
+      <c r="AD24" s="4" t="n">
+        <v>510.2</v>
       </c>
       <c r="AE24" s="4" t="n">
         <v>510.2</v>
       </c>
       <c r="AF24" s="4" t="n">
-        <v>510.2</v>
+        <v>495</v>
       </c>
       <c r="AG24" s="4" t="n">
-        <v>495</v>
+        <v>526</v>
       </c>
       <c r="AH24" s="4" t="n">
-        <v>526</v>
+        <v>484.6899999999999</v>
       </c>
       <c r="AI24" s="4" t="n">
-        <v>484.6899999999999</v>
+        <v>-5</v>
       </c>
       <c r="AJ24" s="4" t="n">
-        <v>-5</v>
+        <v>551.0160000000001</v>
       </c>
       <c r="AK24" s="4" t="n">
-        <v>551.0160000000001</v>
+        <v>8</v>
       </c>
       <c r="AL24" s="4" t="n">
-        <v>8</v>
+        <v>589.5871200000001</v>
       </c>
       <c r="AM24" s="4" t="n">
-        <v>589.5871200000001</v>
+        <v>15.56</v>
       </c>
       <c r="AN24" s="4" t="n">
-        <v>15.56</v>
+        <v>0.46</v>
       </c>
       <c r="AO24" s="4" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="AP24" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AP24" s="4" t="inlineStr"/>
       <c r="AQ24" s="4" t="inlineStr"/>
-      <c r="AR24" s="4" t="inlineStr"/>
-      <c r="AS24" s="4" t="inlineStr">
+      <c r="AR24" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AT24" s="4" t="inlineStr"/>
-      <c r="AU24" s="4" t="inlineStr">
+      <c r="AS24" s="4" t="inlineStr"/>
+      <c r="AT24" s="4" t="inlineStr">
         <is>
           <t>Transport</t>
         </is>
       </c>
+      <c r="AU24" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AV24" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW24" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX24" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+        <v>8</v>
+      </c>
+      <c r="AW24" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -4347,102 +4304,99 @@
       <c r="L25" s="4" t="inlineStr"/>
       <c r="M25" s="4" t="inlineStr"/>
       <c r="N25" s="4" t="inlineStr"/>
-      <c r="O25" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="O25" s="4" t="inlineStr"/>
       <c r="P25" s="4" t="inlineStr"/>
       <c r="Q25" s="4" t="inlineStr"/>
       <c r="R25" s="4" t="inlineStr"/>
       <c r="S25" s="4" t="inlineStr"/>
       <c r="T25" s="4" t="inlineStr"/>
-      <c r="U25" s="4" t="inlineStr"/>
-      <c r="V25" s="4" t="inlineStr">
-        <is>
-          <t>Rank ↓ 8→9 · Conf 64% · momentum → · 61d left · → BUY</t>
-        </is>
-      </c>
-      <c r="W25" s="4" t="inlineStr"/>
-      <c r="X25" s="4" t="n">
+      <c r="U25" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-3.1%) · Rank ↓ 8→9 · Conf 64% · momentum → · 61d left · → BUY</t>
+        </is>
+      </c>
+      <c r="V25" s="4" t="inlineStr"/>
+      <c r="W25" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="Y25" s="4" t="inlineStr">
+      <c r="X25" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Z25" s="4" t="n">
+      <c r="Y25" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="AA25" s="4" t="inlineStr"/>
+      <c r="Z25" s="4" t="inlineStr"/>
+      <c r="AA25" s="4" t="n">
+        <v>60</v>
+      </c>
       <c r="AB25" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AC25" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="AD25" s="4" t="inlineStr">
+      <c r="AC25" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
+      </c>
+      <c r="AD25" s="4" t="n">
+        <v>391.5</v>
       </c>
       <c r="AE25" s="4" t="n">
         <v>391.5</v>
       </c>
       <c r="AF25" s="4" t="n">
-        <v>391.5</v>
+        <v>379</v>
       </c>
       <c r="AG25" s="4" t="n">
-        <v>379</v>
+        <v>404</v>
       </c>
       <c r="AH25" s="4" t="n">
-        <v>404</v>
+        <v>371.925</v>
       </c>
       <c r="AI25" s="4" t="n">
-        <v>371.925</v>
+        <v>-5</v>
       </c>
       <c r="AJ25" s="4" t="n">
-        <v>-5</v>
+        <v>422.8200000000001</v>
       </c>
       <c r="AK25" s="4" t="n">
-        <v>422.8200000000001</v>
+        <v>8</v>
       </c>
       <c r="AL25" s="4" t="n">
-        <v>8</v>
+        <v>452.4174000000001</v>
       </c>
       <c r="AM25" s="4" t="n">
-        <v>452.4174000000001</v>
+        <v>15.56</v>
       </c>
       <c r="AN25" s="4" t="n">
-        <v>15.56</v>
+        <v>0.42</v>
       </c>
       <c r="AO25" s="4" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="AP25" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AP25" s="4" t="inlineStr"/>
       <c r="AQ25" s="4" t="inlineStr"/>
-      <c r="AR25" s="4" t="inlineStr"/>
-      <c r="AS25" s="4" t="inlineStr">
+      <c r="AR25" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AT25" s="4" t="inlineStr"/>
-      <c r="AU25" s="4" t="inlineStr">
+      <c r="AS25" s="4" t="inlineStr"/>
+      <c r="AT25" s="4" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
+      <c r="AU25" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AV25" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW25" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX25" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+        <v>8</v>
+      </c>
+      <c r="AW25" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -4487,102 +4441,99 @@
       <c r="L26" s="4" t="inlineStr"/>
       <c r="M26" s="4" t="inlineStr"/>
       <c r="N26" s="4" t="inlineStr"/>
-      <c r="O26" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="O26" s="4" t="inlineStr"/>
       <c r="P26" s="4" t="inlineStr"/>
       <c r="Q26" s="4" t="inlineStr"/>
       <c r="R26" s="4" t="inlineStr"/>
       <c r="S26" s="4" t="inlineStr"/>
       <c r="T26" s="4" t="inlineStr"/>
-      <c r="U26" s="4" t="inlineStr"/>
-      <c r="V26" s="4" t="inlineStr">
-        <is>
-          <t>Rank ↓ 9→10 · Conf 66% · momentum → · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="W26" s="4" t="inlineStr"/>
-      <c r="X26" s="4" t="n">
+      <c r="U26" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.5%) · Rank ↓ 9→10 · Conf 66% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="V26" s="4" t="inlineStr"/>
+      <c r="W26" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="Y26" s="4" t="inlineStr">
+      <c r="X26" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Z26" s="4" t="n">
+      <c r="Y26" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="AA26" s="4" t="inlineStr"/>
+      <c r="Z26" s="4" t="inlineStr"/>
+      <c r="AA26" s="4" t="n">
+        <v>60</v>
+      </c>
       <c r="AB26" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AC26" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="AD26" s="4" t="inlineStr">
+      <c r="AC26" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
+      </c>
+      <c r="AD26" s="4" t="n">
+        <v>5478</v>
       </c>
       <c r="AE26" s="4" t="n">
         <v>5478</v>
       </c>
       <c r="AF26" s="4" t="n">
-        <v>5478</v>
+        <v>5335</v>
       </c>
       <c r="AG26" s="4" t="n">
-        <v>5335</v>
+        <v>5621</v>
       </c>
       <c r="AH26" s="4" t="n">
-        <v>5621</v>
+        <v>5204.099999999999</v>
       </c>
       <c r="AI26" s="4" t="n">
-        <v>5204.099999999999</v>
+        <v>-5</v>
       </c>
       <c r="AJ26" s="4" t="n">
-        <v>-5</v>
+        <v>5916.240000000001</v>
       </c>
       <c r="AK26" s="4" t="n">
-        <v>5916.240000000001</v>
+        <v>8</v>
       </c>
       <c r="AL26" s="4" t="n">
-        <v>8</v>
+        <v>6330.376800000001</v>
       </c>
       <c r="AM26" s="4" t="n">
-        <v>6330.376800000001</v>
+        <v>15.56</v>
       </c>
       <c r="AN26" s="4" t="n">
-        <v>15.56</v>
+        <v>0.43</v>
       </c>
       <c r="AO26" s="4" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="AP26" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AP26" s="4" t="inlineStr"/>
       <c r="AQ26" s="4" t="inlineStr"/>
-      <c r="AR26" s="4" t="inlineStr"/>
-      <c r="AS26" s="4" t="inlineStr">
+      <c r="AR26" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AT26" s="4" t="inlineStr"/>
-      <c r="AU26" s="4" t="inlineStr">
+      <c r="AS26" s="4" t="inlineStr"/>
+      <c r="AT26" s="4" t="inlineStr">
         <is>
           <t>FMCG</t>
         </is>
       </c>
+      <c r="AU26" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AV26" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW26" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX26" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+        <v>8</v>
+      </c>
+      <c r="AW26" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -4631,102 +4582,99 @@
       <c r="L27" s="4" t="inlineStr"/>
       <c r="M27" s="4" t="inlineStr"/>
       <c r="N27" s="4" t="inlineStr"/>
-      <c r="O27" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="O27" s="4" t="inlineStr"/>
       <c r="P27" s="4" t="inlineStr"/>
       <c r="Q27" s="4" t="inlineStr"/>
       <c r="R27" s="4" t="inlineStr"/>
       <c r="S27" s="4" t="inlineStr"/>
       <c r="T27" s="4" t="inlineStr"/>
-      <c r="U27" s="4" t="inlineStr"/>
-      <c r="V27" s="4" t="inlineStr">
-        <is>
-          <t>Rank ↓ 10→11 · Conf 66% · momentum → · 61d left · → BUY</t>
-        </is>
-      </c>
-      <c r="W27" s="4" t="inlineStr"/>
-      <c r="X27" s="4" t="n">
+      <c r="U27" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.9%) · Rank ↓ 10→11 · Conf 66% · momentum → · 61d left · → BUY</t>
+        </is>
+      </c>
+      <c r="V27" s="4" t="inlineStr"/>
+      <c r="W27" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="Y27" s="4" t="inlineStr">
+      <c r="X27" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Z27" s="4" t="n">
+      <c r="Y27" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="AA27" s="4" t="inlineStr"/>
+      <c r="Z27" s="4" t="inlineStr"/>
+      <c r="AA27" s="4" t="n">
+        <v>60</v>
+      </c>
       <c r="AB27" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AC27" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="AD27" s="4" t="inlineStr">
+      <c r="AC27" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
+      </c>
+      <c r="AD27" s="4" t="n">
+        <v>417.6</v>
       </c>
       <c r="AE27" s="4" t="n">
         <v>417.6</v>
       </c>
       <c r="AF27" s="4" t="n">
-        <v>417.6</v>
+        <v>405</v>
       </c>
       <c r="AG27" s="4" t="n">
-        <v>405</v>
+        <v>430</v>
       </c>
       <c r="AH27" s="4" t="n">
-        <v>430</v>
+        <v>396.72</v>
       </c>
       <c r="AI27" s="4" t="n">
-        <v>396.72</v>
+        <v>-5</v>
       </c>
       <c r="AJ27" s="4" t="n">
-        <v>-5</v>
+        <v>451.008</v>
       </c>
       <c r="AK27" s="4" t="n">
-        <v>451.008</v>
+        <v>8</v>
       </c>
       <c r="AL27" s="4" t="n">
-        <v>8</v>
+        <v>482.5785600000001</v>
       </c>
       <c r="AM27" s="4" t="n">
-        <v>482.5785600000001</v>
+        <v>15.56</v>
       </c>
       <c r="AN27" s="4" t="n">
-        <v>15.56</v>
+        <v>0.59</v>
       </c>
       <c r="AO27" s="4" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="AP27" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AP27" s="4" t="inlineStr"/>
       <c r="AQ27" s="4" t="inlineStr"/>
-      <c r="AR27" s="4" t="inlineStr"/>
-      <c r="AS27" s="4" t="inlineStr">
+      <c r="AR27" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AT27" s="4" t="inlineStr"/>
-      <c r="AU27" s="4" t="inlineStr">
+      <c r="AS27" s="4" t="inlineStr"/>
+      <c r="AT27" s="4" t="inlineStr">
         <is>
           <t>Metal</t>
         </is>
       </c>
+      <c r="AU27" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AV27" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW27" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX27" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+        <v>8</v>
+      </c>
+      <c r="AW27" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -4772,12 +4720,14 @@
       <c r="K28" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L28" s="4" t="n">
-        <v>79.3</v>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>🟢 NEW</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
@@ -4785,114 +4735,113 @@
           <t>🟢</t>
         </is>
       </c>
-      <c r="O28" s="4" t="inlineStr"/>
+      <c r="O28" s="4" t="n">
+        <v>56.1</v>
+      </c>
       <c r="P28" s="4" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="Q28" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="R28" s="4" t="inlineStr">
+      <c r="Q28" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 12 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="S28" s="4" t="n">
+      <c r="R28" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="S28" s="4" t="inlineStr"/>
       <c r="T28" s="4" t="inlineStr"/>
-      <c r="U28" s="4" t="inlineStr"/>
-      <c r="V28" s="4" t="inlineStr">
-        <is>
-          <t>Rank → 1→1 · Conf 57% · band HOLD · 14d left · → BUY</t>
-        </is>
-      </c>
-      <c r="W28" s="4" t="inlineStr"/>
-      <c r="X28" s="4" t="n">
+      <c r="U28" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 1→1 · Conf 57% · band HOLD · 14d left · → BUY</t>
+        </is>
+      </c>
+      <c r="V28" s="4" t="inlineStr"/>
+      <c r="W28" s="4" t="n">
         <v>56.8</v>
       </c>
-      <c r="Y28" s="4" t="inlineStr">
+      <c r="X28" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
+      <c r="Y28" s="4" t="n">
+        <v>29.2</v>
+      </c>
       <c r="Z28" s="4" t="n">
-        <v>29.2</v>
+        <v>4</v>
       </c>
       <c r="AA28" s="4" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="AB28" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC28" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="AD28" s="4" t="inlineStr">
+      <c r="AC28" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
+      </c>
+      <c r="AD28" s="4" t="n">
+        <v>368.98</v>
       </c>
       <c r="AE28" s="4" t="n">
         <v>368.98</v>
       </c>
       <c r="AF28" s="4" t="n">
-        <v>368.98</v>
+        <v>365.29</v>
       </c>
       <c r="AG28" s="4" t="n">
-        <v>365.29</v>
+        <v>372.67</v>
       </c>
       <c r="AH28" s="4" t="n">
-        <v>372.67</v>
+        <v>346.84</v>
       </c>
       <c r="AI28" s="4" t="n">
-        <v>346.84</v>
+        <v>-6</v>
       </c>
       <c r="AJ28" s="4" t="n">
-        <v>-6</v>
+        <v>413.26</v>
       </c>
       <c r="AK28" s="4" t="n">
-        <v>413.26</v>
+        <v>12</v>
       </c>
       <c r="AL28" s="4" t="n">
+        <v>457.54</v>
+      </c>
+      <c r="AM28" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AN28" s="4" t="inlineStr"/>
+      <c r="AO28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" s="4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AS28" s="4" t="inlineStr">
+        <is>
+          <t>Momentum · Value · Trend</t>
+        </is>
+      </c>
+      <c r="AT28" s="4" t="inlineStr"/>
+      <c r="AU28" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV28" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="AM28" s="4" t="n">
-        <v>457.54</v>
-      </c>
-      <c r="AN28" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO28" s="4" t="inlineStr"/>
-      <c r="AP28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ28" s="4" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS28" s="4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT28" s="4" t="inlineStr">
-        <is>
-          <t>Momentum · Value · Trend</t>
-        </is>
-      </c>
-      <c r="AU28" s="4" t="inlineStr"/>
-      <c r="AV28" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW28" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX28" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+      <c r="AW28" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -4938,12 +4887,14 @@
       <c r="K29" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L29" s="4" t="n">
-        <v>86.5</v>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>STRONG</t>
+        </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>STRONG</t>
+          <t>🟢 NEW</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
@@ -4951,114 +4902,113 @@
           <t>🟢</t>
         </is>
       </c>
-      <c r="O29" s="4" t="inlineStr"/>
+      <c r="O29" s="4" t="n">
+        <v>52.9</v>
+      </c>
       <c r="P29" s="4" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="Q29" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="R29" s="4" t="inlineStr">
+      <c r="Q29" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
+      <c r="R29" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="S29" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="T29" s="4" t="n">
         <v>0.184</v>
       </c>
-      <c r="U29" s="4" t="inlineStr"/>
-      <c r="V29" s="4" t="inlineStr">
-        <is>
-          <t>Rank → 2→2 · Conf 54% · band HOLD→STRONG · 14d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="W29" s="4" t="inlineStr"/>
-      <c r="X29" s="4" t="n">
+      <c r="T29" s="4" t="inlineStr"/>
+      <c r="U29" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 2→2 · Conf 54% · band STRONG · 14d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="V29" s="4" t="inlineStr"/>
+      <c r="W29" s="4" t="n">
         <v>53.6</v>
       </c>
-      <c r="Y29" s="4" t="inlineStr">
+      <c r="X29" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
+      <c r="Y29" s="4" t="n">
+        <v>27.8</v>
+      </c>
       <c r="Z29" s="4" t="n">
-        <v>27.8</v>
+        <v>4</v>
       </c>
       <c r="AA29" s="4" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="AB29" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC29" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="AD29" s="4" t="inlineStr">
+      <c r="AC29" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
+      </c>
+      <c r="AD29" s="4" t="n">
+        <v>358.56</v>
       </c>
       <c r="AE29" s="4" t="n">
         <v>358.56</v>
       </c>
       <c r="AF29" s="4" t="n">
-        <v>358.56</v>
+        <v>354.97</v>
       </c>
       <c r="AG29" s="4" t="n">
-        <v>354.97</v>
+        <v>362.15</v>
       </c>
       <c r="AH29" s="4" t="n">
-        <v>362.15</v>
+        <v>340.63</v>
       </c>
       <c r="AI29" s="4" t="n">
-        <v>340.63</v>
+        <v>-5</v>
       </c>
       <c r="AJ29" s="4" t="n">
-        <v>-5</v>
+        <v>387.24</v>
       </c>
       <c r="AK29" s="4" t="n">
-        <v>387.24</v>
+        <v>8</v>
       </c>
       <c r="AL29" s="4" t="n">
-        <v>8</v>
+        <v>412.34</v>
       </c>
       <c r="AM29" s="4" t="n">
-        <v>412.34</v>
-      </c>
-      <c r="AN29" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AO29" s="4" t="inlineStr"/>
+      <c r="AN29" s="4" t="inlineStr"/>
+      <c r="AO29" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AP29" s="4" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AQ29" s="4" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AR29" s="4" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AR29" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
       </c>
       <c r="AS29" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT29" s="4" t="inlineStr">
-        <is>
           <t>Momentum · Trend · Quality</t>
         </is>
       </c>
+      <c r="AT29" s="4" t="inlineStr"/>
       <c r="AU29" s="4" t="inlineStr"/>
-      <c r="AV29" s="4" t="inlineStr"/>
-      <c r="AW29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX29" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+      <c r="AV29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -5110,12 +5060,14 @@
       <c r="K30" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L30" s="4" t="n">
-        <v>67.5</v>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>🟢 NEW</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
@@ -5123,112 +5075,111 @@
           <t>🟢</t>
         </is>
       </c>
-      <c r="O30" s="4" t="inlineStr"/>
+      <c r="O30" s="4" t="n">
+        <v>46.6</v>
+      </c>
       <c r="P30" s="4" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="Q30" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="R30" s="4" t="inlineStr">
+      <c r="Q30" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 21 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="S30" s="4" t="n">
+      <c r="R30" s="4" t="n">
         <v>21</v>
       </c>
+      <c r="S30" s="4" t="inlineStr"/>
       <c r="T30" s="4" t="inlineStr"/>
-      <c r="U30" s="4" t="inlineStr"/>
-      <c r="V30" s="4" t="inlineStr">
-        <is>
-          <t>Rank → 3→3 · Conf 47% · band WATCH→HOLD · 6d left · → EXIT (rotate to TRV)</t>
-        </is>
-      </c>
-      <c r="W30" s="4" t="inlineStr"/>
-      <c r="X30" s="4" t="n">
+      <c r="U30" s="4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 3→3 · Conf 47% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="V30" s="4" t="inlineStr"/>
+      <c r="W30" s="4" t="n">
         <v>47.3</v>
       </c>
-      <c r="Y30" s="4" t="inlineStr">
+      <c r="X30" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
+      <c r="Y30" s="4" t="n">
+        <v>17.1</v>
+      </c>
       <c r="Z30" s="4" t="n">
-        <v>17.1</v>
+        <v>4</v>
       </c>
       <c r="AA30" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AB30" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC30" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AD30" s="4" t="inlineStr">
+      <c r="AC30" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
+      </c>
+      <c r="AD30" s="4" t="n">
+        <v>202.81</v>
       </c>
       <c r="AE30" s="4" t="n">
         <v>202.81</v>
       </c>
       <c r="AF30" s="4" t="n">
-        <v>202.81</v>
+        <v>200.78</v>
       </c>
       <c r="AG30" s="4" t="n">
-        <v>200.78</v>
+        <v>204.84</v>
       </c>
       <c r="AH30" s="4" t="n">
-        <v>204.84</v>
+        <v>192.67</v>
       </c>
       <c r="AI30" s="4" t="n">
-        <v>192.67</v>
+        <v>-5</v>
       </c>
       <c r="AJ30" s="4" t="n">
-        <v>-5</v>
+        <v>219.03</v>
       </c>
       <c r="AK30" s="4" t="n">
-        <v>219.03</v>
+        <v>8</v>
       </c>
       <c r="AL30" s="4" t="n">
-        <v>8</v>
+        <v>233.23</v>
       </c>
       <c r="AM30" s="4" t="n">
-        <v>233.23</v>
-      </c>
-      <c r="AN30" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AO30" s="4" t="inlineStr"/>
+      <c r="AN30" s="4" t="inlineStr"/>
+      <c r="AO30" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AP30" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AQ30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR30" s="4" t="n">
         <v>-1.02</v>
       </c>
+      <c r="AR30" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
       <c r="AS30" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT30" s="4" t="inlineStr">
-        <is>
           <t>Quality · Growth · Mean Reversion</t>
         </is>
       </c>
+      <c r="AT30" s="4" t="inlineStr"/>
       <c r="AU30" s="4" t="inlineStr"/>
-      <c r="AV30" s="4" t="inlineStr"/>
-      <c r="AW30" s="4" t="n">
+      <c r="AV30" s="4" t="n">
         <v>12.15</v>
       </c>
-      <c r="AX30" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+      <c r="AW30" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -5280,12 +5231,14 @@
       <c r="K31" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L31" s="4" t="n">
-        <v>78.40000000000001</v>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>🟢 NEW</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -5293,112 +5246,111 @@
           <t>🟢</t>
         </is>
       </c>
-      <c r="O31" s="4" t="inlineStr"/>
+      <c r="O31" s="4" t="n">
+        <v>48.9</v>
+      </c>
       <c r="P31" s="4" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="Q31" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="R31" s="4" t="inlineStr">
+      <c r="Q31" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 18 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="S31" s="4" t="n">
+      <c r="R31" s="4" t="n">
         <v>18</v>
       </c>
+      <c r="S31" s="4" t="inlineStr"/>
       <c r="T31" s="4" t="inlineStr"/>
-      <c r="U31" s="4" t="inlineStr"/>
-      <c r="V31" s="4" t="inlineStr">
-        <is>
-          <t>Rank → 4→4 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
-        </is>
-      </c>
-      <c r="W31" s="4" t="inlineStr"/>
-      <c r="X31" s="4" t="n">
+      <c r="U31" s="4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 4→4 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="V31" s="4" t="inlineStr"/>
+      <c r="W31" s="4" t="n">
         <v>49.7</v>
       </c>
-      <c r="Y31" s="4" t="inlineStr">
+      <c r="X31" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
+      <c r="Y31" s="4" t="n">
+        <v>16.3</v>
+      </c>
       <c r="Z31" s="4" t="n">
-        <v>16.3</v>
+        <v>4</v>
       </c>
       <c r="AA31" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AB31" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC31" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AD31" s="4" t="inlineStr">
+      <c r="AC31" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
+      </c>
+      <c r="AD31" s="4" t="n">
+        <v>341.1</v>
       </c>
       <c r="AE31" s="4" t="n">
         <v>341.1</v>
       </c>
       <c r="AF31" s="4" t="n">
-        <v>341.1</v>
+        <v>337.69</v>
       </c>
       <c r="AG31" s="4" t="n">
-        <v>337.69</v>
+        <v>344.51</v>
       </c>
       <c r="AH31" s="4" t="n">
-        <v>344.51</v>
+        <v>324.05</v>
       </c>
       <c r="AI31" s="4" t="n">
-        <v>324.05</v>
+        <v>-5</v>
       </c>
       <c r="AJ31" s="4" t="n">
-        <v>-5</v>
+        <v>368.39</v>
       </c>
       <c r="AK31" s="4" t="n">
-        <v>368.39</v>
+        <v>8</v>
       </c>
       <c r="AL31" s="4" t="n">
-        <v>8</v>
+        <v>392.26</v>
       </c>
       <c r="AM31" s="4" t="n">
-        <v>392.26</v>
-      </c>
-      <c r="AN31" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AO31" s="4" t="inlineStr"/>
+      <c r="AN31" s="4" t="inlineStr"/>
+      <c r="AO31" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AP31" s="4" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AQ31" s="4" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="AR31" s="4" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AR31" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
       </c>
       <c r="AS31" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT31" s="4" t="inlineStr">
-        <is>
           <t>Momentum · Value · Mean Reversion</t>
         </is>
       </c>
+      <c r="AT31" s="4" t="inlineStr"/>
       <c r="AU31" s="4" t="inlineStr"/>
-      <c r="AV31" s="4" t="inlineStr"/>
-      <c r="AW31" s="4" t="n">
+      <c r="AV31" s="4" t="n">
         <v>12.97</v>
       </c>
-      <c r="AX31" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+      <c r="AW31" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -5450,12 +5402,14 @@
       <c r="K32" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L32" s="4" t="n">
-        <v>76</v>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>🟢 NEW</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -5463,114 +5417,113 @@
           <t>🟢</t>
         </is>
       </c>
-      <c r="O32" s="4" t="inlineStr"/>
+      <c r="O32" s="4" t="n">
+        <v>49.7</v>
+      </c>
       <c r="P32" s="4" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="Q32" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="R32" s="4" t="inlineStr">
+      <c r="Q32" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 48 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
+      <c r="R32" s="4" t="n">
+        <v>48</v>
+      </c>
       <c r="S32" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="T32" s="4" t="n">
         <v>0.127</v>
       </c>
-      <c r="U32" s="4" t="inlineStr"/>
-      <c r="V32" s="4" t="inlineStr">
-        <is>
-          <t>Rank → 5→5 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
-        </is>
-      </c>
-      <c r="W32" s="4" t="inlineStr"/>
-      <c r="X32" s="4" t="n">
+      <c r="T32" s="4" t="inlineStr"/>
+      <c r="U32" s="4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 5→5 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="V32" s="4" t="inlineStr"/>
+      <c r="W32" s="4" t="n">
         <v>50.5</v>
       </c>
-      <c r="Y32" s="4" t="inlineStr">
+      <c r="X32" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
+      <c r="Y32" s="4" t="n">
+        <v>14.8</v>
+      </c>
       <c r="Z32" s="4" t="n">
-        <v>14.8</v>
+        <v>4</v>
       </c>
       <c r="AA32" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AB32" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC32" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AD32" s="4" t="inlineStr">
+      <c r="AC32" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
+      </c>
+      <c r="AD32" s="4" t="n">
+        <v>225.02</v>
       </c>
       <c r="AE32" s="4" t="n">
         <v>225.02</v>
       </c>
       <c r="AF32" s="4" t="n">
-        <v>225.02</v>
+        <v>222.77</v>
       </c>
       <c r="AG32" s="4" t="n">
-        <v>222.77</v>
+        <v>227.27</v>
       </c>
       <c r="AH32" s="4" t="n">
-        <v>227.27</v>
+        <v>213.77</v>
       </c>
       <c r="AI32" s="4" t="n">
-        <v>213.77</v>
+        <v>-5</v>
       </c>
       <c r="AJ32" s="4" t="n">
-        <v>-5</v>
+        <v>243.02</v>
       </c>
       <c r="AK32" s="4" t="n">
-        <v>243.02</v>
+        <v>8</v>
       </c>
       <c r="AL32" s="4" t="n">
-        <v>8</v>
+        <v>258.77</v>
       </c>
       <c r="AM32" s="4" t="n">
-        <v>258.77</v>
-      </c>
-      <c r="AN32" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AO32" s="4" t="inlineStr"/>
+      <c r="AN32" s="4" t="inlineStr"/>
+      <c r="AO32" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AP32" s="4" t="n">
-        <v>0</v>
+        <v>8.01</v>
       </c>
       <c r="AQ32" s="4" t="n">
-        <v>8.01</v>
-      </c>
-      <c r="AR32" s="4" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AR32" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
       </c>
       <c r="AS32" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT32" s="4" t="inlineStr">
-        <is>
           <t>Mean Reversion · Growth · Value</t>
         </is>
       </c>
+      <c r="AT32" s="4" t="inlineStr"/>
       <c r="AU32" s="4" t="inlineStr"/>
-      <c r="AV32" s="4" t="inlineStr"/>
-      <c r="AW32" s="4" t="n">
+      <c r="AV32" s="4" t="n">
         <v>14.45</v>
       </c>
-      <c r="AX32" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+      <c r="AW32" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -5622,12 +5575,14 @@
       <c r="K33" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L33" s="4" t="n">
-        <v>66.3</v>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>🟢 NEW</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
@@ -5635,112 +5590,111 @@
           <t>🟢</t>
         </is>
       </c>
-      <c r="O33" s="4" t="inlineStr"/>
+      <c r="O33" s="4" t="n">
+        <v>50.2</v>
+      </c>
       <c r="P33" s="4" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="Q33" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="R33" s="4" t="inlineStr">
+      <c r="Q33" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 9 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="S33" s="4" t="n">
+      <c r="R33" s="4" t="n">
         <v>9</v>
       </c>
+      <c r="S33" s="4" t="inlineStr"/>
       <c r="T33" s="4" t="inlineStr"/>
-      <c r="U33" s="4" t="inlineStr"/>
-      <c r="V33" s="4" t="inlineStr">
-        <is>
-          <t>Rank → 6→6 · Conf 51% · band WATCH→HOLD · 6d left · → EXIT (rotate to TRV)</t>
-        </is>
-      </c>
-      <c r="W33" s="4" t="inlineStr"/>
-      <c r="X33" s="4" t="n">
+      <c r="U33" s="4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 6→6 · Conf 51% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="V33" s="4" t="inlineStr"/>
+      <c r="W33" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="Y33" s="4" t="inlineStr">
+      <c r="X33" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
+      <c r="Y33" s="4" t="n">
+        <v>14.5</v>
+      </c>
       <c r="Z33" s="4" t="n">
-        <v>14.5</v>
+        <v>4</v>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AB33" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC33" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AD33" s="4" t="inlineStr">
+      <c r="AC33" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
+      </c>
+      <c r="AD33" s="4" t="n">
+        <v>1065.22</v>
       </c>
       <c r="AE33" s="4" t="n">
         <v>1065.22</v>
       </c>
       <c r="AF33" s="4" t="n">
-        <v>1065.22</v>
+        <v>1054.57</v>
       </c>
       <c r="AG33" s="4" t="n">
-        <v>1054.57</v>
+        <v>1075.87</v>
       </c>
       <c r="AH33" s="4" t="n">
-        <v>1075.87</v>
+        <v>1011.96</v>
       </c>
       <c r="AI33" s="4" t="n">
-        <v>1011.96</v>
+        <v>-5</v>
       </c>
       <c r="AJ33" s="4" t="n">
-        <v>-5</v>
+        <v>1150.44</v>
       </c>
       <c r="AK33" s="4" t="n">
-        <v>1150.44</v>
+        <v>8</v>
       </c>
       <c r="AL33" s="4" t="n">
-        <v>8</v>
+        <v>1225</v>
       </c>
       <c r="AM33" s="4" t="n">
-        <v>1225</v>
-      </c>
-      <c r="AN33" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AO33" s="4" t="inlineStr"/>
+      <c r="AN33" s="4" t="inlineStr"/>
+      <c r="AO33" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AP33" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AQ33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR33" s="4" t="n">
         <v>-4.4</v>
       </c>
+      <c r="AR33" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
       <c r="AS33" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT33" s="4" t="inlineStr">
-        <is>
           <t>Value · News · Event Driven</t>
         </is>
       </c>
+      <c r="AT33" s="4" t="inlineStr"/>
       <c r="AU33" s="4" t="inlineStr"/>
-      <c r="AV33" s="4" t="inlineStr"/>
-      <c r="AW33" s="4" t="n">
+      <c r="AV33" s="4" t="n">
         <v>14.77</v>
       </c>
-      <c r="AX33" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+      <c r="AW33" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -5792,12 +5746,14 @@
       <c r="K34" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L34" s="4" t="n">
-        <v>83.5</v>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>STRONG</t>
+        </is>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>🟢 NEW</t>
         </is>
       </c>
       <c r="N34" s="4" t="inlineStr">
@@ -5805,114 +5761,113 @@
           <t>🟢</t>
         </is>
       </c>
-      <c r="O34" s="4" t="inlineStr"/>
+      <c r="O34" s="4" t="n">
+        <v>49.7</v>
+      </c>
       <c r="P34" s="4" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="Q34" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="R34" s="4" t="inlineStr">
+      <c r="Q34" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
+      <c r="R34" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="S34" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="T34" s="4" t="n">
         <v>0.109</v>
       </c>
-      <c r="U34" s="4" t="inlineStr"/>
-      <c r="V34" s="4" t="inlineStr">
-        <is>
-          <t>Rank → 7→7 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
-        </is>
-      </c>
-      <c r="W34" s="4" t="inlineStr"/>
-      <c r="X34" s="4" t="n">
+      <c r="T34" s="4" t="inlineStr"/>
+      <c r="U34" s="4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 7→7 · Conf 50% · band STRONG · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="V34" s="4" t="inlineStr"/>
+      <c r="W34" s="4" t="n">
         <v>50.5</v>
       </c>
-      <c r="Y34" s="4" t="inlineStr">
+      <c r="X34" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
+      <c r="Y34" s="4" t="n">
+        <v>14.4</v>
+      </c>
       <c r="Z34" s="4" t="n">
-        <v>14.4</v>
+        <v>4</v>
       </c>
       <c r="AA34" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AB34" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC34" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AD34" s="4" t="inlineStr">
+      <c r="AC34" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
+      </c>
+      <c r="AD34" s="4" t="n">
+        <v>333.74</v>
       </c>
       <c r="AE34" s="4" t="n">
         <v>333.74</v>
       </c>
       <c r="AF34" s="4" t="n">
-        <v>333.74</v>
+        <v>330.4</v>
       </c>
       <c r="AG34" s="4" t="n">
-        <v>330.4</v>
+        <v>337.08</v>
       </c>
       <c r="AH34" s="4" t="n">
-        <v>337.08</v>
+        <v>317.05</v>
       </c>
       <c r="AI34" s="4" t="n">
-        <v>317.05</v>
+        <v>-5</v>
       </c>
       <c r="AJ34" s="4" t="n">
-        <v>-5</v>
+        <v>360.44</v>
       </c>
       <c r="AK34" s="4" t="n">
-        <v>360.44</v>
+        <v>8</v>
       </c>
       <c r="AL34" s="4" t="n">
-        <v>8</v>
+        <v>383.8</v>
       </c>
       <c r="AM34" s="4" t="n">
-        <v>383.8</v>
-      </c>
-      <c r="AN34" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AO34" s="4" t="inlineStr"/>
+      <c r="AN34" s="4" t="inlineStr"/>
+      <c r="AO34" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AP34" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AQ34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR34" s="4" t="n">
         <v>-7.44</v>
       </c>
+      <c r="AR34" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
       <c r="AS34" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT34" s="4" t="inlineStr">
-        <is>
           <t>Value · Trend · Momentum</t>
         </is>
       </c>
+      <c r="AT34" s="4" t="inlineStr"/>
       <c r="AU34" s="4" t="inlineStr"/>
-      <c r="AV34" s="4" t="inlineStr"/>
-      <c r="AW34" s="4" t="n">
+      <c r="AV34" s="4" t="n">
         <v>14.87</v>
       </c>
-      <c r="AX34" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+      <c r="AW34" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5919,14 @@
       <c r="K35" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="4" t="n">
-        <v>79.5</v>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>🟢 NEW</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
@@ -5977,114 +5934,113 @@
           <t>🟢</t>
         </is>
       </c>
-      <c r="O35" s="4" t="inlineStr"/>
+      <c r="O35" s="4" t="n">
+        <v>52.9</v>
+      </c>
       <c r="P35" s="4" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="Q35" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="R35" s="4" t="inlineStr">
+      <c r="Q35" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 33 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
+      <c r="R35" s="4" t="n">
+        <v>33</v>
+      </c>
       <c r="S35" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="T35" s="4" t="n">
         <v>0.15</v>
       </c>
-      <c r="U35" s="4" t="inlineStr"/>
-      <c r="V35" s="4" t="inlineStr">
-        <is>
-          <t>Rank → 8→8 · Conf 54% · band HOLD · 58d left · → EXIT (rotate to TRV)</t>
-        </is>
-      </c>
-      <c r="W35" s="4" t="inlineStr"/>
-      <c r="X35" s="4" t="n">
+      <c r="T35" s="4" t="inlineStr"/>
+      <c r="U35" s="4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 8→8 · Conf 54% · band HOLD · 58d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="V35" s="4" t="inlineStr"/>
+      <c r="W35" s="4" t="n">
         <v>53.6</v>
       </c>
-      <c r="Y35" s="4" t="inlineStr">
+      <c r="X35" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
+      <c r="Y35" s="4" t="n">
+        <v>14</v>
+      </c>
       <c r="Z35" s="4" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="AA35" s="4" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="AB35" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AC35" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="AD35" s="4" t="inlineStr">
+      <c r="AC35" s="4" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
+      </c>
+      <c r="AD35" s="4" t="n">
+        <v>393.82</v>
       </c>
       <c r="AE35" s="4" t="n">
         <v>393.82</v>
       </c>
       <c r="AF35" s="4" t="n">
-        <v>393.82</v>
+        <v>389.88</v>
       </c>
       <c r="AG35" s="4" t="n">
-        <v>389.88</v>
+        <v>397.76</v>
       </c>
       <c r="AH35" s="4" t="n">
-        <v>397.76</v>
+        <v>374.13</v>
       </c>
       <c r="AI35" s="4" t="n">
-        <v>374.13</v>
+        <v>-5</v>
       </c>
       <c r="AJ35" s="4" t="n">
-        <v>-5</v>
+        <v>425.33</v>
       </c>
       <c r="AK35" s="4" t="n">
-        <v>425.33</v>
+        <v>8</v>
       </c>
       <c r="AL35" s="4" t="n">
-        <v>8</v>
+        <v>452.89</v>
       </c>
       <c r="AM35" s="4" t="n">
-        <v>452.89</v>
-      </c>
-      <c r="AN35" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AO35" s="4" t="inlineStr"/>
+      <c r="AN35" s="4" t="inlineStr"/>
+      <c r="AO35" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AP35" s="4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AQ35" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AR35" s="4" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AR35" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
       </c>
       <c r="AS35" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT35" s="4" t="inlineStr">
-        <is>
           <t>Quality · Mean Reversion · Trend</t>
         </is>
       </c>
+      <c r="AT35" s="4" t="inlineStr"/>
       <c r="AU35" s="4" t="inlineStr"/>
-      <c r="AV35" s="4" t="inlineStr"/>
-      <c r="AW35" s="4" t="n">
+      <c r="AV35" s="4" t="n">
         <v>15.21</v>
       </c>
-      <c r="AX35" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+      <c r="AW35" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -6136,127 +6092,124 @@
       <c r="K36" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="4" t="n">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="M36" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>STRONG</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="inlineStr"/>
       <c r="N36" s="4" t="inlineStr">
         <is>
           <t>🟢</t>
         </is>
       </c>
-      <c r="O36" s="4" t="inlineStr"/>
+      <c r="O36" s="4" t="n">
+        <v>49.7</v>
+      </c>
       <c r="P36" s="4" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="Q36" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="R36" s="4" t="inlineStr">
+      <c r="Q36" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 11 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
+      <c r="R36" s="4" t="n">
+        <v>11</v>
+      </c>
       <c r="S36" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="T36" s="4" t="n">
         <v>0.08500000000000001</v>
       </c>
-      <c r="U36" s="4" t="inlineStr"/>
-      <c r="V36" s="4" t="inlineStr">
-        <is>
-          <t>Rank → 9→9 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
-        </is>
-      </c>
-      <c r="W36" s="4" t="inlineStr"/>
-      <c r="X36" s="4" t="n">
+      <c r="T36" s="4" t="inlineStr"/>
+      <c r="U36" s="4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 9→9 · Conf 50% · band STRONG · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="V36" s="4" t="inlineStr"/>
+      <c r="W36" s="4" t="n">
         <v>50.5</v>
       </c>
-      <c r="Y36" s="4" t="inlineStr">
+      <c r="X36" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
+      <c r="Y36" s="4" t="n">
+        <v>13.8</v>
+      </c>
       <c r="Z36" s="4" t="n">
-        <v>13.8</v>
+        <v>4</v>
       </c>
       <c r="AA36" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AB36" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC36" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AD36" s="4" t="inlineStr">
+      <c r="AC36" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
+      </c>
+      <c r="AD36" s="4" t="n">
+        <v>81.56</v>
       </c>
       <c r="AE36" s="4" t="n">
         <v>81.56</v>
       </c>
       <c r="AF36" s="4" t="n">
-        <v>81.56</v>
+        <v>80.73999999999999</v>
       </c>
       <c r="AG36" s="4" t="n">
-        <v>80.73999999999999</v>
+        <v>82.38</v>
       </c>
       <c r="AH36" s="4" t="n">
-        <v>82.38</v>
+        <v>77.48</v>
       </c>
       <c r="AI36" s="4" t="n">
-        <v>77.48</v>
+        <v>-5</v>
       </c>
       <c r="AJ36" s="4" t="n">
-        <v>-5</v>
+        <v>88.08</v>
       </c>
       <c r="AK36" s="4" t="n">
-        <v>88.08</v>
+        <v>7.99</v>
       </c>
       <c r="AL36" s="4" t="n">
-        <v>7.99</v>
+        <v>93.79000000000001</v>
       </c>
       <c r="AM36" s="4" t="n">
-        <v>93.79000000000001</v>
-      </c>
-      <c r="AN36" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AO36" s="4" t="inlineStr"/>
+      <c r="AN36" s="4" t="inlineStr"/>
+      <c r="AO36" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AP36" s="4" t="n">
-        <v>0</v>
+        <v>7.39</v>
       </c>
       <c r="AQ36" s="4" t="n">
-        <v>7.39</v>
-      </c>
-      <c r="AR36" s="4" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AR36" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
       </c>
       <c r="AS36" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT36" s="4" t="inlineStr">
-        <is>
           <t>Momentum · News · Quality</t>
         </is>
       </c>
+      <c r="AT36" s="4" t="inlineStr"/>
       <c r="AU36" s="4" t="inlineStr"/>
-      <c r="AV36" s="4" t="inlineStr"/>
-      <c r="AW36" s="4" t="n">
+      <c r="AV36" s="4" t="n">
         <v>15.5</v>
       </c>
-      <c r="AX36" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+      <c r="AW36" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -6308,125 +6261,122 @@
       <c r="K37" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L37" s="4" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="M37" s="4" t="inlineStr">
+      <c r="L37" s="4" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
+      <c r="M37" s="4" t="inlineStr"/>
       <c r="N37" s="4" t="inlineStr">
         <is>
           <t>🟢</t>
         </is>
       </c>
-      <c r="O37" s="4" t="inlineStr"/>
+      <c r="O37" s="4" t="n">
+        <v>52.9</v>
+      </c>
       <c r="P37" s="4" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="Q37" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="R37" s="4" t="inlineStr">
+      <c r="Q37" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 15 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="S37" s="4" t="n">
+      <c r="R37" s="4" t="n">
         <v>15</v>
       </c>
+      <c r="S37" s="4" t="inlineStr"/>
       <c r="T37" s="4" t="inlineStr"/>
-      <c r="U37" s="4" t="inlineStr"/>
-      <c r="V37" s="4" t="inlineStr">
-        <is>
-          <t>Rank → 10→10 · Conf 54% · band HOLD · 58d left · → EXIT (rotate to TRV)</t>
-        </is>
-      </c>
-      <c r="W37" s="4" t="inlineStr"/>
-      <c r="X37" s="4" t="n">
+      <c r="U37" s="4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 10→10 · Conf 54% · band HOLD · 58d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="V37" s="4" t="inlineStr"/>
+      <c r="W37" s="4" t="n">
         <v>53.6</v>
       </c>
-      <c r="Y37" s="4" t="inlineStr">
+      <c r="X37" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
+      <c r="Y37" s="4" t="n">
+        <v>12.8</v>
+      </c>
       <c r="Z37" s="4" t="n">
-        <v>12.8</v>
+        <v>3</v>
       </c>
       <c r="AA37" s="4" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="AB37" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AC37" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="AD37" s="4" t="inlineStr">
+      <c r="AC37" s="4" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
+      </c>
+      <c r="AD37" s="4" t="n">
+        <v>159.84</v>
       </c>
       <c r="AE37" s="4" t="n">
         <v>159.84</v>
       </c>
       <c r="AF37" s="4" t="n">
-        <v>159.84</v>
+        <v>158.24</v>
       </c>
       <c r="AG37" s="4" t="n">
-        <v>158.24</v>
+        <v>161.44</v>
       </c>
       <c r="AH37" s="4" t="n">
-        <v>161.44</v>
+        <v>151.85</v>
       </c>
       <c r="AI37" s="4" t="n">
-        <v>151.85</v>
+        <v>-5</v>
       </c>
       <c r="AJ37" s="4" t="n">
-        <v>-5</v>
+        <v>172.63</v>
       </c>
       <c r="AK37" s="4" t="n">
-        <v>172.63</v>
+        <v>8</v>
       </c>
       <c r="AL37" s="4" t="n">
-        <v>8</v>
+        <v>183.82</v>
       </c>
       <c r="AM37" s="4" t="n">
-        <v>183.82</v>
-      </c>
-      <c r="AN37" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AO37" s="4" t="inlineStr"/>
+      <c r="AN37" s="4" t="inlineStr"/>
+      <c r="AO37" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AP37" s="4" t="n">
-        <v>0</v>
+        <v>10.29</v>
       </c>
       <c r="AQ37" s="4" t="n">
-        <v>10.29</v>
-      </c>
-      <c r="AR37" s="4" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AR37" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
       </c>
       <c r="AS37" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT37" s="4" t="inlineStr">
-        <is>
           <t>Momentum · News · Value</t>
         </is>
       </c>
+      <c r="AT37" s="4" t="inlineStr"/>
       <c r="AU37" s="4" t="inlineStr"/>
-      <c r="AV37" s="4" t="inlineStr"/>
-      <c r="AW37" s="4" t="n">
+      <c r="AV37" s="4" t="n">
         <v>16.4</v>
       </c>
-      <c r="AX37" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+      <c r="AW37" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -6478,125 +6428,122 @@
       <c r="K38" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L38" s="4" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="M38" s="4" t="inlineStr">
-        <is>
-          <t>WEAK</t>
-        </is>
-      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="M38" s="4" t="inlineStr"/>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>🟡</t>
-        </is>
-      </c>
-      <c r="O38" s="4" t="inlineStr"/>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="O38" s="4" t="n">
+        <v>28</v>
+      </c>
       <c r="P38" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q38" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="R38" s="4" t="inlineStr">
+      <c r="Q38" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 26 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="S38" s="4" t="n">
+      <c r="R38" s="4" t="n">
         <v>26</v>
       </c>
+      <c r="S38" s="4" t="inlineStr"/>
       <c r="T38" s="4" t="inlineStr"/>
-      <c r="U38" s="4" t="inlineStr"/>
-      <c r="V38" s="4" t="inlineStr">
-        <is>
-          <t>Rank → 11→11 · Conf 29% · band REVIEW→WEAK · 6d left · → EXIT (rotate to TRV)</t>
-        </is>
-      </c>
-      <c r="W38" s="4" t="inlineStr"/>
-      <c r="X38" s="4" t="n">
+      <c r="U38" s="4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 11→11 · Conf 29% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="V38" s="4" t="inlineStr"/>
+      <c r="W38" s="4" t="n">
         <v>28.7</v>
       </c>
-      <c r="Y38" s="4" t="inlineStr">
+      <c r="X38" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
+      <c r="Y38" s="4" t="n">
+        <v>-7.9</v>
+      </c>
       <c r="Z38" s="4" t="n">
-        <v>-7.9</v>
+        <v>4</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC38" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AD38" s="4" t="inlineStr">
+      <c r="AC38" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
+      </c>
+      <c r="AD38" s="4" t="n">
+        <v>95.04000000000001</v>
       </c>
       <c r="AE38" s="4" t="n">
         <v>95.04000000000001</v>
       </c>
       <c r="AF38" s="4" t="n">
-        <v>95.04000000000001</v>
+        <v>94.09</v>
       </c>
       <c r="AG38" s="4" t="n">
-        <v>94.09</v>
+        <v>95.98999999999999</v>
       </c>
       <c r="AH38" s="4" t="n">
-        <v>95.98999999999999</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="AI38" s="4" t="n">
-        <v>90.29000000000001</v>
+        <v>-5</v>
       </c>
       <c r="AJ38" s="4" t="n">
-        <v>-5</v>
+        <v>102.64</v>
       </c>
       <c r="AK38" s="4" t="n">
-        <v>102.64</v>
+        <v>8</v>
       </c>
       <c r="AL38" s="4" t="n">
-        <v>8</v>
+        <v>109.3</v>
       </c>
       <c r="AM38" s="4" t="n">
-        <v>109.3</v>
-      </c>
-      <c r="AN38" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AO38" s="4" t="inlineStr"/>
+      <c r="AN38" s="4" t="inlineStr"/>
+      <c r="AO38" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AP38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AQ38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR38" s="4" t="n">
         <v>-5.09</v>
       </c>
+      <c r="AR38" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
       <c r="AS38" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT38" s="4" t="inlineStr">
-        <is>
           <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
+      <c r="AT38" s="4" t="inlineStr"/>
       <c r="AU38" s="4" t="inlineStr"/>
-      <c r="AV38" s="4" t="inlineStr"/>
-      <c r="AW38" s="4" t="n">
+      <c r="AV38" s="4" t="n">
         <v>37.17</v>
       </c>
-      <c r="AX38" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+      <c r="AW38" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -6648,127 +6595,124 @@
       <c r="K39" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="4" t="n">
-        <v>52.6</v>
-      </c>
-      <c r="M39" s="4" t="inlineStr">
-        <is>
-          <t>WEAK</t>
-        </is>
-      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="M39" s="4" t="inlineStr"/>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>🟡</t>
-        </is>
-      </c>
-      <c r="O39" s="4" t="inlineStr"/>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="O39" s="4" t="n">
+        <v>30.1</v>
+      </c>
       <c r="P39" s="4" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="Q39" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="R39" s="4" t="inlineStr">
+      <c r="Q39" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 12 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
+      <c r="R39" s="4" t="n">
+        <v>12</v>
+      </c>
       <c r="S39" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="T39" s="4" t="n">
         <v>0.122</v>
       </c>
-      <c r="U39" s="4" t="inlineStr"/>
-      <c r="V39" s="4" t="inlineStr">
-        <is>
-          <t>Rank → 12→12 · Conf 31% · band REVIEW→WEAK · 58d left · → EXIT (rotate to TRV)</t>
-        </is>
-      </c>
-      <c r="W39" s="4" t="inlineStr"/>
-      <c r="X39" s="4" t="n">
+      <c r="T39" s="4" t="inlineStr"/>
+      <c r="U39" s="4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 12→12 · Conf 31% · band EXIT · 58d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="V39" s="4" t="inlineStr"/>
+      <c r="W39" s="4" t="n">
         <v>30.8</v>
       </c>
-      <c r="Y39" s="4" t="inlineStr">
+      <c r="X39" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
+      <c r="Y39" s="4" t="n">
+        <v>-8.5</v>
+      </c>
       <c r="Z39" s="4" t="n">
-        <v>-8.5</v>
+        <v>3</v>
       </c>
       <c r="AA39" s="4" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="AB39" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AC39" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="AD39" s="4" t="inlineStr">
+      <c r="AC39" s="4" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
+      </c>
+      <c r="AD39" s="4" t="n">
+        <v>214.03</v>
       </c>
       <c r="AE39" s="4" t="n">
         <v>214.03</v>
       </c>
       <c r="AF39" s="4" t="n">
-        <v>214.03</v>
+        <v>211.89</v>
       </c>
       <c r="AG39" s="4" t="n">
-        <v>211.89</v>
+        <v>216.17</v>
       </c>
       <c r="AH39" s="4" t="n">
-        <v>216.17</v>
+        <v>203.33</v>
       </c>
       <c r="AI39" s="4" t="n">
-        <v>203.33</v>
+        <v>-5</v>
       </c>
       <c r="AJ39" s="4" t="n">
-        <v>-5</v>
+        <v>231.15</v>
       </c>
       <c r="AK39" s="4" t="n">
-        <v>231.15</v>
+        <v>8</v>
       </c>
       <c r="AL39" s="4" t="n">
-        <v>8</v>
+        <v>246.13</v>
       </c>
       <c r="AM39" s="4" t="n">
-        <v>246.13</v>
-      </c>
-      <c r="AN39" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AO39" s="4" t="inlineStr"/>
+      <c r="AN39" s="4" t="inlineStr"/>
+      <c r="AO39" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AP39" s="4" t="n">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="AQ39" s="4" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="AR39" s="4" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AR39" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
       </c>
       <c r="AS39" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT39" s="4" t="inlineStr">
-        <is>
           <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
+      <c r="AT39" s="4" t="inlineStr"/>
       <c r="AU39" s="4" t="inlineStr"/>
-      <c r="AV39" s="4" t="inlineStr"/>
-      <c r="AW39" s="4" t="n">
+      <c r="AV39" s="4" t="n">
         <v>37.79</v>
       </c>
-      <c r="AX39" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+      <c r="AW39" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -6820,127 +6764,124 @@
       <c r="K40" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="4" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="M40" s="4" t="inlineStr">
-        <is>
-          <t>WEAK</t>
-        </is>
-      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="M40" s="4" t="inlineStr"/>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>🟡</t>
-        </is>
-      </c>
-      <c r="O40" s="4" t="inlineStr"/>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="O40" s="4" t="n">
+        <v>34</v>
+      </c>
       <c r="P40" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="Q40" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="R40" s="4" t="inlineStr">
+      <c r="Q40" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 13 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
+      <c r="R40" s="4" t="n">
+        <v>13</v>
+      </c>
       <c r="S40" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="T40" s="4" t="n">
         <v>0.156</v>
       </c>
-      <c r="U40" s="4" t="inlineStr"/>
-      <c r="V40" s="4" t="inlineStr">
-        <is>
-          <t>Rank → 13→13 · Conf 35% · band REVIEW→WEAK · 6d left · → EXIT (rotate to TRV)</t>
-        </is>
-      </c>
-      <c r="W40" s="4" t="inlineStr"/>
-      <c r="X40" s="4" t="n">
+      <c r="T40" s="4" t="inlineStr"/>
+      <c r="U40" s="4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 13→13 · Conf 35% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="V40" s="4" t="inlineStr"/>
+      <c r="W40" s="4" t="n">
         <v>34.7</v>
       </c>
-      <c r="Y40" s="4" t="inlineStr">
+      <c r="X40" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
+      <c r="Y40" s="4" t="n">
+        <v>-14.6</v>
+      </c>
       <c r="Z40" s="4" t="n">
-        <v>-14.6</v>
+        <v>4</v>
       </c>
       <c r="AA40" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AB40" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC40" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AD40" s="4" t="inlineStr">
+      <c r="AC40" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
+      </c>
+      <c r="AD40" s="4" t="n">
+        <v>338.87</v>
       </c>
       <c r="AE40" s="4" t="n">
         <v>338.87</v>
       </c>
       <c r="AF40" s="4" t="n">
-        <v>338.87</v>
+        <v>335.48</v>
       </c>
       <c r="AG40" s="4" t="n">
-        <v>335.48</v>
+        <v>342.26</v>
       </c>
       <c r="AH40" s="4" t="n">
-        <v>342.26</v>
+        <v>321.93</v>
       </c>
       <c r="AI40" s="4" t="n">
-        <v>321.93</v>
+        <v>-5</v>
       </c>
       <c r="AJ40" s="4" t="n">
-        <v>-5</v>
+        <v>365.98</v>
       </c>
       <c r="AK40" s="4" t="n">
-        <v>365.98</v>
+        <v>8</v>
       </c>
       <c r="AL40" s="4" t="n">
-        <v>8</v>
+        <v>389.7</v>
       </c>
       <c r="AM40" s="4" t="n">
-        <v>389.7</v>
-      </c>
-      <c r="AN40" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AO40" s="4" t="inlineStr"/>
+      <c r="AN40" s="4" t="inlineStr"/>
+      <c r="AO40" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AP40" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AQ40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR40" s="4" t="n">
         <v>-2.04</v>
       </c>
+      <c r="AR40" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
       <c r="AS40" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT40" s="4" t="inlineStr">
-        <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
+      <c r="AT40" s="4" t="inlineStr"/>
       <c r="AU40" s="4" t="inlineStr"/>
-      <c r="AV40" s="4" t="inlineStr"/>
-      <c r="AW40" s="4" t="n">
+      <c r="AV40" s="4" t="n">
         <v>43.85</v>
       </c>
-      <c r="AX40" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+      <c r="AW40" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -6992,127 +6933,124 @@
       <c r="K41" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="4" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="M41" s="4" t="inlineStr">
-        <is>
-          <t>WEAK</t>
-        </is>
-      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="M41" s="4" t="inlineStr"/>
       <c r="N41" s="4" t="inlineStr">
         <is>
-          <t>🟡</t>
-        </is>
-      </c>
-      <c r="O41" s="4" t="inlineStr"/>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="n">
+        <v>34</v>
+      </c>
       <c r="P41" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="Q41" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="R41" s="4" t="inlineStr">
+      <c r="Q41" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 19 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
+      <c r="R41" s="4" t="n">
+        <v>19</v>
+      </c>
       <c r="S41" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="T41" s="4" t="n">
         <v>0.193</v>
       </c>
-      <c r="U41" s="4" t="inlineStr"/>
-      <c r="V41" s="4" t="inlineStr">
-        <is>
-          <t>Rank → 14→14 · Conf 35% · band REVIEW→WEAK · 6d left · → EXIT (rotate to TRV)</t>
-        </is>
-      </c>
-      <c r="W41" s="4" t="inlineStr"/>
-      <c r="X41" s="4" t="n">
+      <c r="T41" s="4" t="inlineStr"/>
+      <c r="U41" s="4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 14→14 · Conf 35% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="V41" s="4" t="inlineStr"/>
+      <c r="W41" s="4" t="n">
         <v>34.7</v>
       </c>
-      <c r="Y41" s="4" t="inlineStr">
+      <c r="X41" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
+      <c r="Y41" s="4" t="n">
+        <v>-16.4</v>
+      </c>
       <c r="Z41" s="4" t="n">
-        <v>-16.4</v>
+        <v>4</v>
       </c>
       <c r="AA41" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AB41" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC41" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AD41" s="4" t="inlineStr">
+      <c r="AC41" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
+      </c>
+      <c r="AD41" s="4" t="n">
+        <v>97.67</v>
       </c>
       <c r="AE41" s="4" t="n">
         <v>97.67</v>
       </c>
       <c r="AF41" s="4" t="n">
-        <v>97.67</v>
+        <v>96.69</v>
       </c>
       <c r="AG41" s="4" t="n">
-        <v>96.69</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="AH41" s="4" t="n">
-        <v>98.65000000000001</v>
+        <v>92.79000000000001</v>
       </c>
       <c r="AI41" s="4" t="n">
-        <v>92.79000000000001</v>
+        <v>-5</v>
       </c>
       <c r="AJ41" s="4" t="n">
-        <v>-5</v>
+        <v>105.48</v>
       </c>
       <c r="AK41" s="4" t="n">
-        <v>105.48</v>
+        <v>8</v>
       </c>
       <c r="AL41" s="4" t="n">
-        <v>8</v>
+        <v>112.32</v>
       </c>
       <c r="AM41" s="4" t="n">
-        <v>112.32</v>
-      </c>
-      <c r="AN41" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AO41" s="4" t="inlineStr"/>
+      <c r="AN41" s="4" t="inlineStr"/>
+      <c r="AO41" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AP41" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AQ41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR41" s="4" t="n">
         <v>-1.52</v>
       </c>
+      <c r="AR41" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
       <c r="AS41" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT41" s="4" t="inlineStr">
-        <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
+      <c r="AT41" s="4" t="inlineStr"/>
       <c r="AU41" s="4" t="inlineStr"/>
-      <c r="AV41" s="4" t="inlineStr"/>
-      <c r="AW41" s="4" t="n">
+      <c r="AV41" s="4" t="n">
         <v>45.62</v>
       </c>
-      <c r="AX41" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+      <c r="AW41" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -7164,127 +7102,124 @@
       <c r="K42" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="4" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="M42" s="4" t="inlineStr">
-        <is>
-          <t>WEAK</t>
-        </is>
-      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="M42" s="4" t="inlineStr"/>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>🟡</t>
-        </is>
-      </c>
-      <c r="O42" s="4" t="inlineStr"/>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="O42" s="4" t="n">
+        <v>27.6</v>
+      </c>
       <c r="P42" s="4" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="Q42" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="R42" s="4" t="inlineStr">
+      <c r="Q42" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 6 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
+      <c r="R42" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="S42" s="4" t="n">
+        <v>0.192</v>
+      </c>
+      <c r="T42" s="4" t="inlineStr"/>
+      <c r="U42" s="4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 15→15 · Conf 28% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="V42" s="4" t="inlineStr"/>
+      <c r="W42" s="4" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="X42" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="Y42" s="4" t="n">
+        <v>-16.7</v>
+      </c>
+      <c r="Z42" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA42" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB42" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="T42" s="4" t="n">
-        <v>0.192</v>
-      </c>
-      <c r="U42" s="4" t="inlineStr"/>
-      <c r="V42" s="4" t="inlineStr">
-        <is>
-          <t>Rank → 15→15 · Conf 28% · band REVIEW→WEAK · 6d left · → EXIT (rotate to TRV)</t>
-        </is>
-      </c>
-      <c r="W42" s="4" t="inlineStr"/>
-      <c r="X42" s="4" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="Y42" s="4" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="Z42" s="4" t="n">
-        <v>-16.7</v>
-      </c>
-      <c r="AA42" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB42" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC42" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD42" s="4" t="inlineStr">
+      <c r="AC42" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
+      </c>
+      <c r="AD42" s="4" t="n">
+        <v>267.71</v>
       </c>
       <c r="AE42" s="4" t="n">
         <v>267.71</v>
       </c>
       <c r="AF42" s="4" t="n">
-        <v>267.71</v>
+        <v>265.03</v>
       </c>
       <c r="AG42" s="4" t="n">
-        <v>265.03</v>
+        <v>270.39</v>
       </c>
       <c r="AH42" s="4" t="n">
-        <v>270.39</v>
+        <v>254.32</v>
       </c>
       <c r="AI42" s="4" t="n">
-        <v>254.32</v>
+        <v>-5</v>
       </c>
       <c r="AJ42" s="4" t="n">
-        <v>-5</v>
+        <v>289.13</v>
       </c>
       <c r="AK42" s="4" t="n">
-        <v>289.13</v>
+        <v>8</v>
       </c>
       <c r="AL42" s="4" t="n">
-        <v>8</v>
+        <v>307.87</v>
       </c>
       <c r="AM42" s="4" t="n">
-        <v>307.87</v>
-      </c>
-      <c r="AN42" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AO42" s="4" t="inlineStr"/>
+      <c r="AN42" s="4" t="inlineStr"/>
+      <c r="AO42" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AP42" s="4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AQ42" s="4" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AR42" s="4" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AR42" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
       </c>
       <c r="AS42" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT42" s="4" t="inlineStr">
-        <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
+      <c r="AT42" s="4" t="inlineStr"/>
       <c r="AU42" s="4" t="inlineStr"/>
-      <c r="AV42" s="4" t="inlineStr"/>
-      <c r="AW42" s="4" t="n">
+      <c r="AV42" s="4" t="n">
         <v>45.94</v>
       </c>
-      <c r="AX42" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+      <c r="AW42" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -7326,12 +7261,14 @@
       </c>
       <c r="J43" s="4" t="inlineStr"/>
       <c r="K43" s="4" t="inlineStr"/>
-      <c r="L43" s="4" t="n">
-        <v>86.5</v>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>STRONG</t>
+        </is>
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>STRONG</t>
+          <t>🟢 NEW</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr">
@@ -7340,115 +7277,112 @@
         </is>
       </c>
       <c r="O43" s="4" t="n">
-        <v>0</v>
+        <v>52.9</v>
       </c>
       <c r="P43" s="4" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="Q43" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="R43" s="4" t="inlineStr">
+      <c r="Q43" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
+      <c r="R43" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="S43" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="T43" s="4" t="n">
         <v>0.184</v>
       </c>
-      <c r="U43" s="4" t="inlineStr"/>
-      <c r="V43" s="4" t="inlineStr">
-        <is>
-          <t>Rank #1 · Conf 54% · momentum → · band HOLD→STRONG · 91d left · → BUY</t>
-        </is>
-      </c>
-      <c r="W43" s="4" t="inlineStr"/>
-      <c r="X43" s="4" t="n">
+      <c r="T43" s="4" t="inlineStr"/>
+      <c r="U43" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #1 · Conf 54% · momentum → · band STRONG · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="V43" s="4" t="inlineStr"/>
+      <c r="W43" s="4" t="n">
         <v>53.6</v>
       </c>
-      <c r="Y43" s="4" t="inlineStr">
+      <c r="X43" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Z43" s="4" t="n">
+      <c r="Y43" s="4" t="n">
         <v>64.3</v>
       </c>
-      <c r="AA43" s="4" t="inlineStr"/>
+      <c r="Z43" s="4" t="inlineStr"/>
+      <c r="AA43" s="4" t="n">
+        <v>90</v>
+      </c>
       <c r="AB43" s="4" t="n">
-        <v>90</v>
-      </c>
-      <c r="AC43" s="4" t="n">
         <v>91</v>
       </c>
-      <c r="AD43" s="4" t="inlineStr">
+      <c r="AC43" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
+      </c>
+      <c r="AD43" s="4" t="n">
+        <v>358.56</v>
       </c>
       <c r="AE43" s="4" t="n">
         <v>358.56</v>
       </c>
       <c r="AF43" s="4" t="n">
-        <v>358.56</v>
+        <v>351.39</v>
       </c>
       <c r="AG43" s="4" t="n">
-        <v>351.39</v>
+        <v>365.73</v>
       </c>
       <c r="AH43" s="4" t="n">
-        <v>365.73</v>
+        <v>340.632</v>
       </c>
       <c r="AI43" s="4" t="n">
-        <v>340.632</v>
+        <v>-5</v>
       </c>
       <c r="AJ43" s="4" t="n">
-        <v>-5</v>
+        <v>387.2448000000001</v>
       </c>
       <c r="AK43" s="4" t="n">
-        <v>387.2448000000001</v>
+        <v>8</v>
       </c>
       <c r="AL43" s="4" t="n">
-        <v>8</v>
+        <v>414.3519360000001</v>
       </c>
       <c r="AM43" s="4" t="n">
-        <v>414.3519360000001</v>
-      </c>
-      <c r="AN43" s="4" t="n">
         <v>15.56</v>
       </c>
-      <c r="AO43" s="4" t="inlineStr"/>
+      <c r="AN43" s="4" t="inlineStr"/>
+      <c r="AO43" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AP43" s="4" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AQ43" s="4" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AR43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS43" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AR43" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AT43" s="4" t="inlineStr"/>
-      <c r="AU43" s="4" t="inlineStr">
+      <c r="AS43" s="4" t="inlineStr"/>
+      <c r="AT43" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="AU43" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AV43" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW43" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX43" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+        <v>8</v>
+      </c>
+      <c r="AW43" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7424,14 @@
       </c>
       <c r="J44" s="4" t="inlineStr"/>
       <c r="K44" s="4" t="inlineStr"/>
-      <c r="L44" s="4" t="n">
-        <v>79.3</v>
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>🟢 NEW</t>
         </is>
       </c>
       <c r="N44" s="4" t="inlineStr">
@@ -7504,113 +7440,110 @@
         </is>
       </c>
       <c r="O44" s="4" t="n">
-        <v>0</v>
+        <v>56.1</v>
       </c>
       <c r="P44" s="4" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="Q44" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="R44" s="4" t="inlineStr">
+      <c r="Q44" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 12 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="S44" s="4" t="n">
+      <c r="R44" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="S44" s="4" t="inlineStr"/>
       <c r="T44" s="4" t="inlineStr"/>
-      <c r="U44" s="4" t="inlineStr"/>
-      <c r="V44" s="4" t="inlineStr">
-        <is>
-          <t>Rank #2 · Conf 57% · momentum → · band HOLD · 91d left · → BUY</t>
-        </is>
-      </c>
-      <c r="W44" s="4" t="inlineStr"/>
-      <c r="X44" s="4" t="n">
+      <c r="U44" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank #2 · Conf 57% · momentum → · band HOLD · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="V44" s="4" t="inlineStr"/>
+      <c r="W44" s="4" t="n">
         <v>56.8</v>
       </c>
-      <c r="Y44" s="4" t="inlineStr">
+      <c r="X44" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Z44" s="4" t="n">
+      <c r="Y44" s="4" t="n">
         <v>58.8</v>
       </c>
-      <c r="AA44" s="4" t="inlineStr"/>
+      <c r="Z44" s="4" t="inlineStr"/>
+      <c r="AA44" s="4" t="n">
+        <v>90</v>
+      </c>
       <c r="AB44" s="4" t="n">
-        <v>90</v>
-      </c>
-      <c r="AC44" s="4" t="n">
         <v>91</v>
       </c>
-      <c r="AD44" s="4" t="inlineStr">
+      <c r="AC44" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
+      </c>
+      <c r="AD44" s="4" t="n">
+        <v>368.98</v>
       </c>
       <c r="AE44" s="4" t="n">
         <v>368.98</v>
       </c>
       <c r="AF44" s="4" t="n">
-        <v>368.98</v>
+        <v>365.29</v>
       </c>
       <c r="AG44" s="4" t="n">
-        <v>365.29</v>
+        <v>372.67</v>
       </c>
       <c r="AH44" s="4" t="n">
-        <v>372.67</v>
+        <v>350.531</v>
       </c>
       <c r="AI44" s="4" t="n">
-        <v>350.531</v>
+        <v>-5</v>
       </c>
       <c r="AJ44" s="4" t="n">
-        <v>-5</v>
+        <v>413.26</v>
       </c>
       <c r="AK44" s="4" t="n">
-        <v>413.26</v>
+        <v>12</v>
       </c>
       <c r="AL44" s="4" t="n">
+        <v>442.1882</v>
+      </c>
+      <c r="AM44" s="4" t="n">
+        <v>19.84</v>
+      </c>
+      <c r="AN44" s="4" t="inlineStr"/>
+      <c r="AO44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP44" s="4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR44" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AS44" s="4" t="inlineStr"/>
+      <c r="AT44" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU44" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV44" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="AM44" s="4" t="n">
-        <v>442.1882</v>
-      </c>
-      <c r="AN44" s="4" t="n">
-        <v>19.84</v>
-      </c>
-      <c r="AO44" s="4" t="inlineStr"/>
-      <c r="AP44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ44" s="4" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS44" s="4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT44" s="4" t="inlineStr"/>
-      <c r="AU44" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV44" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW44" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX44" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+      <c r="AW44" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -7652,12 +7585,14 @@
       </c>
       <c r="J45" s="4" t="inlineStr"/>
       <c r="K45" s="4" t="inlineStr"/>
-      <c r="L45" s="4" t="n">
-        <v>67.5</v>
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>🟢 NEW</t>
         </is>
       </c>
       <c r="N45" s="4" t="inlineStr">
@@ -7666,113 +7601,110 @@
         </is>
       </c>
       <c r="O45" s="4" t="n">
-        <v>0</v>
+        <v>46.6</v>
       </c>
       <c r="P45" s="4" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="Q45" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="R45" s="4" t="inlineStr">
+      <c r="Q45" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 21 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="S45" s="4" t="n">
+      <c r="R45" s="4" t="n">
         <v>21</v>
       </c>
+      <c r="S45" s="4" t="inlineStr"/>
       <c r="T45" s="4" t="inlineStr"/>
-      <c r="U45" s="4" t="inlineStr"/>
-      <c r="V45" s="4" t="inlineStr">
-        <is>
-          <t>Rank #3 · Conf 47% · momentum → · band WATCH→HOLD · 91d left · → BUY</t>
-        </is>
-      </c>
-      <c r="W45" s="4" t="inlineStr"/>
-      <c r="X45" s="4" t="n">
+      <c r="U45" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #3 · Conf 47% · momentum → · band HOLD · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="V45" s="4" t="inlineStr"/>
+      <c r="W45" s="4" t="n">
         <v>47.3</v>
       </c>
-      <c r="Y45" s="4" t="inlineStr">
+      <c r="X45" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Z45" s="4" t="n">
+      <c r="Y45" s="4" t="n">
         <v>55.7</v>
       </c>
-      <c r="AA45" s="4" t="inlineStr"/>
+      <c r="Z45" s="4" t="inlineStr"/>
+      <c r="AA45" s="4" t="n">
+        <v>90</v>
+      </c>
       <c r="AB45" s="4" t="n">
-        <v>90</v>
-      </c>
-      <c r="AC45" s="4" t="n">
         <v>91</v>
       </c>
-      <c r="AD45" s="4" t="inlineStr">
+      <c r="AC45" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
+      </c>
+      <c r="AD45" s="4" t="n">
+        <v>202.81</v>
       </c>
       <c r="AE45" s="4" t="n">
         <v>202.81</v>
       </c>
       <c r="AF45" s="4" t="n">
-        <v>202.81</v>
+        <v>198.75</v>
       </c>
       <c r="AG45" s="4" t="n">
-        <v>198.75</v>
+        <v>206.87</v>
       </c>
       <c r="AH45" s="4" t="n">
-        <v>206.87</v>
+        <v>192.6695</v>
       </c>
       <c r="AI45" s="4" t="n">
-        <v>192.6695</v>
+        <v>-5</v>
       </c>
       <c r="AJ45" s="4" t="n">
-        <v>-5</v>
+        <v>219.0348</v>
       </c>
       <c r="AK45" s="4" t="n">
-        <v>219.0348</v>
+        <v>8</v>
       </c>
       <c r="AL45" s="4" t="n">
-        <v>8</v>
+        <v>234.367236</v>
       </c>
       <c r="AM45" s="4" t="n">
-        <v>234.367236</v>
-      </c>
-      <c r="AN45" s="4" t="n">
         <v>15.56</v>
       </c>
-      <c r="AO45" s="4" t="inlineStr"/>
+      <c r="AN45" s="4" t="inlineStr"/>
+      <c r="AO45" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AP45" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AQ45" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR45" s="4" t="n">
         <v>-1.02</v>
       </c>
-      <c r="AS45" s="4" t="inlineStr">
+      <c r="AR45" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AT45" s="4" t="inlineStr"/>
-      <c r="AU45" s="4" t="inlineStr">
+      <c r="AS45" s="4" t="inlineStr"/>
+      <c r="AT45" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="AU45" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AV45" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW45" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX45" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+        <v>8</v>
+      </c>
+      <c r="AW45" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -7814,12 +7746,14 @@
       </c>
       <c r="J46" s="4" t="inlineStr"/>
       <c r="K46" s="4" t="inlineStr"/>
-      <c r="L46" s="4" t="n">
-        <v>79.5</v>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>🟢 NEW</t>
         </is>
       </c>
       <c r="N46" s="4" t="inlineStr">
@@ -7828,115 +7762,112 @@
         </is>
       </c>
       <c r="O46" s="4" t="n">
-        <v>0</v>
+        <v>52.9</v>
       </c>
       <c r="P46" s="4" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="Q46" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="R46" s="4" t="inlineStr">
+      <c r="Q46" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 33 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
+      <c r="R46" s="4" t="n">
+        <v>33</v>
+      </c>
       <c r="S46" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="T46" s="4" t="n">
         <v>0.15</v>
       </c>
-      <c r="U46" s="4" t="inlineStr"/>
-      <c r="V46" s="4" t="inlineStr">
-        <is>
-          <t>Rank #4 · Conf 54% · momentum → · band HOLD · 91d left · → BUY</t>
-        </is>
-      </c>
-      <c r="W46" s="4" t="inlineStr"/>
-      <c r="X46" s="4" t="n">
+      <c r="T46" s="4" t="inlineStr"/>
+      <c r="U46" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #4 · Conf 54% · momentum → · band HOLD · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="V46" s="4" t="inlineStr"/>
+      <c r="W46" s="4" t="n">
         <v>53.6</v>
       </c>
-      <c r="Y46" s="4" t="inlineStr">
+      <c r="X46" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Z46" s="4" t="n">
+      <c r="Y46" s="4" t="n">
         <v>51.8</v>
       </c>
-      <c r="AA46" s="4" t="inlineStr"/>
+      <c r="Z46" s="4" t="inlineStr"/>
+      <c r="AA46" s="4" t="n">
+        <v>90</v>
+      </c>
       <c r="AB46" s="4" t="n">
-        <v>90</v>
-      </c>
-      <c r="AC46" s="4" t="n">
         <v>91</v>
       </c>
-      <c r="AD46" s="4" t="inlineStr">
+      <c r="AC46" s="4" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
+      </c>
+      <c r="AD46" s="4" t="n">
+        <v>393.82</v>
       </c>
       <c r="AE46" s="4" t="n">
         <v>393.82</v>
       </c>
       <c r="AF46" s="4" t="n">
-        <v>393.82</v>
+        <v>385.94</v>
       </c>
       <c r="AG46" s="4" t="n">
-        <v>385.94</v>
+        <v>401.7</v>
       </c>
       <c r="AH46" s="4" t="n">
-        <v>401.7</v>
+        <v>374.129</v>
       </c>
       <c r="AI46" s="4" t="n">
-        <v>374.129</v>
+        <v>-5</v>
       </c>
       <c r="AJ46" s="4" t="n">
-        <v>-5</v>
+        <v>425.3256</v>
       </c>
       <c r="AK46" s="4" t="n">
-        <v>425.3256</v>
+        <v>8</v>
       </c>
       <c r="AL46" s="4" t="n">
-        <v>8</v>
+        <v>455.098392</v>
       </c>
       <c r="AM46" s="4" t="n">
-        <v>455.098392</v>
-      </c>
-      <c r="AN46" s="4" t="n">
         <v>15.56</v>
       </c>
-      <c r="AO46" s="4" t="inlineStr"/>
+      <c r="AN46" s="4" t="inlineStr"/>
+      <c r="AO46" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AP46" s="4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AQ46" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AR46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS46" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AR46" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AT46" s="4" t="inlineStr"/>
-      <c r="AU46" s="4" t="inlineStr">
+      <c r="AS46" s="4" t="inlineStr"/>
+      <c r="AT46" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="AU46" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AV46" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW46" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX46" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+        <v>8</v>
+      </c>
+      <c r="AW46" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -7978,129 +7909,124 @@
       </c>
       <c r="J47" s="4" t="inlineStr"/>
       <c r="K47" s="4" t="inlineStr"/>
-      <c r="L47" s="4" t="n">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="M47" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>STRONG</t>
+        </is>
+      </c>
+      <c r="M47" s="4" t="inlineStr"/>
       <c r="N47" s="4" t="inlineStr">
         <is>
           <t>🟢</t>
         </is>
       </c>
       <c r="O47" s="4" t="n">
-        <v>0</v>
+        <v>49.7</v>
       </c>
       <c r="P47" s="4" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="Q47" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="R47" s="4" t="inlineStr">
+      <c r="Q47" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 11 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
+      <c r="R47" s="4" t="n">
+        <v>11</v>
+      </c>
       <c r="S47" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="T47" s="4" t="n">
         <v>0.08500000000000001</v>
       </c>
-      <c r="U47" s="4" t="inlineStr"/>
-      <c r="V47" s="4" t="inlineStr">
-        <is>
-          <t>Rank #5 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="W47" s="4" t="inlineStr"/>
-      <c r="X47" s="4" t="n">
+      <c r="T47" s="4" t="inlineStr"/>
+      <c r="U47" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #5 · Conf 50% · momentum → · band STRONG · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="V47" s="4" t="inlineStr"/>
+      <c r="W47" s="4" t="n">
         <v>50.5</v>
       </c>
-      <c r="Y47" s="4" t="inlineStr">
+      <c r="X47" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Z47" s="4" t="n">
+      <c r="Y47" s="4" t="n">
         <v>46.7</v>
       </c>
-      <c r="AA47" s="4" t="inlineStr"/>
+      <c r="Z47" s="4" t="inlineStr"/>
+      <c r="AA47" s="4" t="n">
+        <v>90</v>
+      </c>
       <c r="AB47" s="4" t="n">
-        <v>90</v>
-      </c>
-      <c r="AC47" s="4" t="n">
         <v>91</v>
       </c>
-      <c r="AD47" s="4" t="inlineStr">
+      <c r="AC47" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
+      </c>
+      <c r="AD47" s="4" t="n">
+        <v>81.56</v>
       </c>
       <c r="AE47" s="4" t="n">
         <v>81.56</v>
       </c>
       <c r="AF47" s="4" t="n">
-        <v>81.56</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="AG47" s="4" t="n">
-        <v>79.93000000000001</v>
+        <v>83.19</v>
       </c>
       <c r="AH47" s="4" t="n">
-        <v>83.19</v>
+        <v>77.482</v>
       </c>
       <c r="AI47" s="4" t="n">
-        <v>77.482</v>
+        <v>-5</v>
       </c>
       <c r="AJ47" s="4" t="n">
-        <v>-5</v>
+        <v>88.0848</v>
       </c>
       <c r="AK47" s="4" t="n">
-        <v>88.0848</v>
+        <v>8</v>
       </c>
       <c r="AL47" s="4" t="n">
-        <v>8</v>
+        <v>94.250736</v>
       </c>
       <c r="AM47" s="4" t="n">
-        <v>94.250736</v>
-      </c>
-      <c r="AN47" s="4" t="n">
         <v>15.56</v>
       </c>
-      <c r="AO47" s="4" t="inlineStr"/>
+      <c r="AN47" s="4" t="inlineStr"/>
+      <c r="AO47" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AP47" s="4" t="n">
-        <v>0</v>
+        <v>7.39</v>
       </c>
       <c r="AQ47" s="4" t="n">
-        <v>7.39</v>
-      </c>
-      <c r="AR47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS47" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AR47" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AT47" s="4" t="inlineStr"/>
-      <c r="AU47" s="4" t="inlineStr">
+      <c r="AS47" s="4" t="inlineStr"/>
+      <c r="AT47" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="AU47" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AV47" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW47" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX47" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+        <v>8</v>
+      </c>
+      <c r="AW47" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -8142,12 +8068,14 @@
       </c>
       <c r="J48" s="4" t="inlineStr"/>
       <c r="K48" s="4" t="inlineStr"/>
-      <c r="L48" s="4" t="n">
-        <v>76</v>
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
       </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>🟢 NEW</t>
         </is>
       </c>
       <c r="N48" s="4" t="inlineStr">
@@ -8156,115 +8084,112 @@
         </is>
       </c>
       <c r="O48" s="4" t="n">
-        <v>0</v>
+        <v>49.7</v>
       </c>
       <c r="P48" s="4" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="Q48" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="R48" s="4" t="inlineStr">
+      <c r="Q48" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 48 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
+      <c r="R48" s="4" t="n">
+        <v>48</v>
+      </c>
       <c r="S48" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="T48" s="4" t="n">
         <v>0.127</v>
       </c>
-      <c r="U48" s="4" t="inlineStr"/>
-      <c r="V48" s="4" t="inlineStr">
-        <is>
-          <t>Rank #6 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="W48" s="4" t="inlineStr"/>
-      <c r="X48" s="4" t="n">
+      <c r="T48" s="4" t="inlineStr"/>
+      <c r="U48" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #6 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="V48" s="4" t="inlineStr"/>
+      <c r="W48" s="4" t="n">
         <v>50.5</v>
       </c>
-      <c r="Y48" s="4" t="inlineStr">
+      <c r="X48" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Z48" s="4" t="n">
+      <c r="Y48" s="4" t="n">
         <v>46.5</v>
       </c>
-      <c r="AA48" s="4" t="inlineStr"/>
+      <c r="Z48" s="4" t="inlineStr"/>
+      <c r="AA48" s="4" t="n">
+        <v>90</v>
+      </c>
       <c r="AB48" s="4" t="n">
-        <v>90</v>
-      </c>
-      <c r="AC48" s="4" t="n">
         <v>91</v>
       </c>
-      <c r="AD48" s="4" t="inlineStr">
+      <c r="AC48" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
+      </c>
+      <c r="AD48" s="4" t="n">
+        <v>225.02</v>
       </c>
       <c r="AE48" s="4" t="n">
         <v>225.02</v>
       </c>
       <c r="AF48" s="4" t="n">
-        <v>225.02</v>
+        <v>220.52</v>
       </c>
       <c r="AG48" s="4" t="n">
-        <v>220.52</v>
+        <v>229.52</v>
       </c>
       <c r="AH48" s="4" t="n">
-        <v>229.52</v>
+        <v>213.769</v>
       </c>
       <c r="AI48" s="4" t="n">
-        <v>213.769</v>
+        <v>-5</v>
       </c>
       <c r="AJ48" s="4" t="n">
-        <v>-5</v>
+        <v>243.0216</v>
       </c>
       <c r="AK48" s="4" t="n">
-        <v>243.0216</v>
+        <v>8</v>
       </c>
       <c r="AL48" s="4" t="n">
-        <v>8</v>
+        <v>260.0331120000001</v>
       </c>
       <c r="AM48" s="4" t="n">
-        <v>260.0331120000001</v>
-      </c>
-      <c r="AN48" s="4" t="n">
         <v>15.56</v>
       </c>
-      <c r="AO48" s="4" t="inlineStr"/>
+      <c r="AN48" s="4" t="inlineStr"/>
+      <c r="AO48" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AP48" s="4" t="n">
-        <v>0</v>
+        <v>8.01</v>
       </c>
       <c r="AQ48" s="4" t="n">
-        <v>8.01</v>
-      </c>
-      <c r="AR48" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS48" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AR48" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AT48" s="4" t="inlineStr"/>
-      <c r="AU48" s="4" t="inlineStr">
+      <c r="AS48" s="4" t="inlineStr"/>
+      <c r="AT48" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="AU48" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AV48" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW48" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX48" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+        <v>8</v>
+      </c>
+      <c r="AW48" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -8306,12 +8231,14 @@
       </c>
       <c r="J49" s="4" t="inlineStr"/>
       <c r="K49" s="4" t="inlineStr"/>
-      <c r="L49" s="4" t="n">
-        <v>83.5</v>
+      <c r="L49" s="4" t="inlineStr">
+        <is>
+          <t>STRONG</t>
+        </is>
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>🟢 NEW</t>
         </is>
       </c>
       <c r="N49" s="4" t="inlineStr">
@@ -8320,115 +8247,112 @@
         </is>
       </c>
       <c r="O49" s="4" t="n">
-        <v>0</v>
+        <v>49.7</v>
       </c>
       <c r="P49" s="4" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="Q49" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="R49" s="4" t="inlineStr">
+      <c r="Q49" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
+      <c r="R49" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="S49" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="T49" s="4" t="n">
         <v>0.109</v>
       </c>
-      <c r="U49" s="4" t="inlineStr"/>
-      <c r="V49" s="4" t="inlineStr">
-        <is>
-          <t>Rank #7 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="W49" s="4" t="inlineStr"/>
-      <c r="X49" s="4" t="n">
+      <c r="T49" s="4" t="inlineStr"/>
+      <c r="U49" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #7 · Conf 50% · momentum → · band STRONG · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="V49" s="4" t="inlineStr"/>
+      <c r="W49" s="4" t="n">
         <v>50.5</v>
       </c>
-      <c r="Y49" s="4" t="inlineStr">
+      <c r="X49" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Z49" s="4" t="n">
+      <c r="Y49" s="4" t="n">
         <v>45.8</v>
       </c>
-      <c r="AA49" s="4" t="inlineStr"/>
+      <c r="Z49" s="4" t="inlineStr"/>
+      <c r="AA49" s="4" t="n">
+        <v>90</v>
+      </c>
       <c r="AB49" s="4" t="n">
-        <v>90</v>
-      </c>
-      <c r="AC49" s="4" t="n">
         <v>91</v>
       </c>
-      <c r="AD49" s="4" t="inlineStr">
+      <c r="AC49" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
+      </c>
+      <c r="AD49" s="4" t="n">
+        <v>333.74</v>
       </c>
       <c r="AE49" s="4" t="n">
         <v>333.74</v>
       </c>
       <c r="AF49" s="4" t="n">
-        <v>333.74</v>
+        <v>327.07</v>
       </c>
       <c r="AG49" s="4" t="n">
-        <v>327.07</v>
+        <v>340.41</v>
       </c>
       <c r="AH49" s="4" t="n">
-        <v>340.41</v>
+        <v>317.053</v>
       </c>
       <c r="AI49" s="4" t="n">
-        <v>317.053</v>
+        <v>-5</v>
       </c>
       <c r="AJ49" s="4" t="n">
-        <v>-5</v>
+        <v>360.4392</v>
       </c>
       <c r="AK49" s="4" t="n">
-        <v>360.4392</v>
+        <v>8</v>
       </c>
       <c r="AL49" s="4" t="n">
-        <v>8</v>
+        <v>385.669944</v>
       </c>
       <c r="AM49" s="4" t="n">
-        <v>385.669944</v>
-      </c>
-      <c r="AN49" s="4" t="n">
         <v>15.56</v>
       </c>
-      <c r="AO49" s="4" t="inlineStr"/>
+      <c r="AN49" s="4" t="inlineStr"/>
+      <c r="AO49" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AP49" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AQ49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR49" s="4" t="n">
         <v>-7.44</v>
       </c>
-      <c r="AS49" s="4" t="inlineStr">
+      <c r="AR49" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AT49" s="4" t="inlineStr"/>
-      <c r="AU49" s="4" t="inlineStr">
+      <c r="AS49" s="4" t="inlineStr"/>
+      <c r="AT49" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="AU49" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AV49" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW49" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX49" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+        <v>8</v>
+      </c>
+      <c r="AW49" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -8470,12 +8394,14 @@
       </c>
       <c r="J50" s="4" t="inlineStr"/>
       <c r="K50" s="4" t="inlineStr"/>
-      <c r="L50" s="4" t="n">
-        <v>78.40000000000001</v>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
       </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>🟢 NEW</t>
         </is>
       </c>
       <c r="N50" s="4" t="inlineStr">
@@ -8484,113 +8410,110 @@
         </is>
       </c>
       <c r="O50" s="4" t="n">
-        <v>0</v>
+        <v>48.9</v>
       </c>
       <c r="P50" s="4" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="Q50" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="R50" s="4" t="inlineStr">
+      <c r="Q50" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 18 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="S50" s="4" t="n">
+      <c r="R50" s="4" t="n">
         <v>18</v>
       </c>
+      <c r="S50" s="4" t="inlineStr"/>
       <c r="T50" s="4" t="inlineStr"/>
-      <c r="U50" s="4" t="inlineStr"/>
-      <c r="V50" s="4" t="inlineStr">
-        <is>
-          <t>Rank #8 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="W50" s="4" t="inlineStr"/>
-      <c r="X50" s="4" t="n">
+      <c r="U50" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #8 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="V50" s="4" t="inlineStr"/>
+      <c r="W50" s="4" t="n">
         <v>49.7</v>
       </c>
-      <c r="Y50" s="4" t="inlineStr">
+      <c r="X50" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Z50" s="4" t="n">
+      <c r="Y50" s="4" t="n">
         <v>37.6</v>
       </c>
-      <c r="AA50" s="4" t="inlineStr"/>
+      <c r="Z50" s="4" t="inlineStr"/>
+      <c r="AA50" s="4" t="n">
+        <v>90</v>
+      </c>
       <c r="AB50" s="4" t="n">
-        <v>90</v>
-      </c>
-      <c r="AC50" s="4" t="n">
         <v>91</v>
       </c>
-      <c r="AD50" s="4" t="inlineStr">
+      <c r="AC50" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
+      </c>
+      <c r="AD50" s="4" t="n">
+        <v>341.1</v>
       </c>
       <c r="AE50" s="4" t="n">
         <v>341.1</v>
       </c>
       <c r="AF50" s="4" t="n">
-        <v>341.1</v>
+        <v>334.28</v>
       </c>
       <c r="AG50" s="4" t="n">
-        <v>334.28</v>
+        <v>347.92</v>
       </c>
       <c r="AH50" s="4" t="n">
-        <v>347.92</v>
+        <v>324.045</v>
       </c>
       <c r="AI50" s="4" t="n">
-        <v>324.045</v>
+        <v>-5</v>
       </c>
       <c r="AJ50" s="4" t="n">
-        <v>-5</v>
+        <v>368.388</v>
       </c>
       <c r="AK50" s="4" t="n">
-        <v>368.388</v>
+        <v>8</v>
       </c>
       <c r="AL50" s="4" t="n">
-        <v>8</v>
+        <v>394.1751600000001</v>
       </c>
       <c r="AM50" s="4" t="n">
-        <v>394.1751600000001</v>
-      </c>
-      <c r="AN50" s="4" t="n">
         <v>15.56</v>
       </c>
-      <c r="AO50" s="4" t="inlineStr"/>
+      <c r="AN50" s="4" t="inlineStr"/>
+      <c r="AO50" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AP50" s="4" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AQ50" s="4" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="AR50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS50" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AR50" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AT50" s="4" t="inlineStr"/>
-      <c r="AU50" s="4" t="inlineStr">
+      <c r="AS50" s="4" t="inlineStr"/>
+      <c r="AT50" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="AU50" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AV50" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW50" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX50" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+        <v>8</v>
+      </c>
+      <c r="AW50" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -8632,12 +8555,14 @@
       </c>
       <c r="J51" s="4" t="inlineStr"/>
       <c r="K51" s="4" t="inlineStr"/>
-      <c r="L51" s="4" t="n">
-        <v>66.3</v>
+      <c r="L51" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>🟢 NEW</t>
         </is>
       </c>
       <c r="N51" s="4" t="inlineStr">
@@ -8646,113 +8571,110 @@
         </is>
       </c>
       <c r="O51" s="4" t="n">
-        <v>0</v>
+        <v>50.2</v>
       </c>
       <c r="P51" s="4" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="Q51" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="R51" s="4" t="inlineStr">
+      <c r="Q51" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 9 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="S51" s="4" t="n">
+      <c r="R51" s="4" t="n">
         <v>9</v>
       </c>
+      <c r="S51" s="4" t="inlineStr"/>
       <c r="T51" s="4" t="inlineStr"/>
-      <c r="U51" s="4" t="inlineStr"/>
-      <c r="V51" s="4" t="inlineStr">
-        <is>
-          <t>Rank #9 · Conf 51% · momentum → · band WATCH→HOLD · 91d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="W51" s="4" t="inlineStr"/>
-      <c r="X51" s="4" t="n">
+      <c r="U51" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #9 · Conf 51% · momentum → · band HOLD · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="V51" s="4" t="inlineStr"/>
+      <c r="W51" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="Y51" s="4" t="inlineStr">
+      <c r="X51" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Z51" s="4" t="n">
+      <c r="Y51" s="4" t="n">
         <v>36.5</v>
       </c>
-      <c r="AA51" s="4" t="inlineStr"/>
+      <c r="Z51" s="4" t="inlineStr"/>
+      <c r="AA51" s="4" t="n">
+        <v>90</v>
+      </c>
       <c r="AB51" s="4" t="n">
-        <v>90</v>
-      </c>
-      <c r="AC51" s="4" t="n">
         <v>91</v>
       </c>
-      <c r="AD51" s="4" t="inlineStr">
+      <c r="AC51" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
+      </c>
+      <c r="AD51" s="4" t="n">
+        <v>1065.22</v>
       </c>
       <c r="AE51" s="4" t="n">
         <v>1065.22</v>
       </c>
       <c r="AF51" s="4" t="n">
-        <v>1065.22</v>
+        <v>1043.92</v>
       </c>
       <c r="AG51" s="4" t="n">
-        <v>1043.92</v>
+        <v>1086.52</v>
       </c>
       <c r="AH51" s="4" t="n">
-        <v>1086.52</v>
+        <v>1011.959</v>
       </c>
       <c r="AI51" s="4" t="n">
-        <v>1011.959</v>
+        <v>-5</v>
       </c>
       <c r="AJ51" s="4" t="n">
-        <v>-5</v>
+        <v>1150.4376</v>
       </c>
       <c r="AK51" s="4" t="n">
-        <v>1150.4376</v>
+        <v>8</v>
       </c>
       <c r="AL51" s="4" t="n">
-        <v>8</v>
+        <v>1230.968232</v>
       </c>
       <c r="AM51" s="4" t="n">
-        <v>1230.968232</v>
-      </c>
-      <c r="AN51" s="4" t="n">
         <v>15.56</v>
       </c>
-      <c r="AO51" s="4" t="inlineStr"/>
+      <c r="AN51" s="4" t="inlineStr"/>
+      <c r="AO51" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AP51" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AQ51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR51" s="4" t="n">
         <v>-4.4</v>
       </c>
-      <c r="AS51" s="4" t="inlineStr">
+      <c r="AR51" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AT51" s="4" t="inlineStr"/>
-      <c r="AU51" s="4" t="inlineStr">
+      <c r="AS51" s="4" t="inlineStr"/>
+      <c r="AT51" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="AU51" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AV51" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW51" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX51" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+        <v>8</v>
+      </c>
+      <c r="AW51" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
@@ -8794,132 +8716,127 @@
       </c>
       <c r="J52" s="4" t="inlineStr"/>
       <c r="K52" s="4" t="inlineStr"/>
-      <c r="L52" s="4" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="M52" s="4" t="inlineStr">
+      <c r="L52" s="4" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
+      <c r="M52" s="4" t="inlineStr"/>
       <c r="N52" s="4" t="inlineStr">
         <is>
           <t>🟢</t>
         </is>
       </c>
       <c r="O52" s="4" t="n">
-        <v>0</v>
+        <v>52.9</v>
       </c>
       <c r="P52" s="4" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="Q52" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="R52" s="4" t="inlineStr">
+      <c r="Q52" s="4" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 15 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="S52" s="4" t="n">
+      <c r="R52" s="4" t="n">
         <v>15</v>
       </c>
+      <c r="S52" s="4" t="inlineStr"/>
       <c r="T52" s="4" t="inlineStr"/>
-      <c r="U52" s="4" t="inlineStr"/>
-      <c r="V52" s="4" t="inlineStr">
-        <is>
-          <t>Rank #10 · Conf 54% · momentum → · band HOLD · 91d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="W52" s="4" t="inlineStr"/>
-      <c r="X52" s="4" t="n">
+      <c r="U52" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #10 · Conf 54% · momentum → · band HOLD · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="V52" s="4" t="inlineStr"/>
+      <c r="W52" s="4" t="n">
         <v>53.6</v>
       </c>
-      <c r="Y52" s="4" t="inlineStr">
+      <c r="X52" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Z52" s="4" t="n">
+      <c r="Y52" s="4" t="n">
         <v>32.3</v>
       </c>
-      <c r="AA52" s="4" t="inlineStr"/>
+      <c r="Z52" s="4" t="inlineStr"/>
+      <c r="AA52" s="4" t="n">
+        <v>90</v>
+      </c>
       <c r="AB52" s="4" t="n">
-        <v>90</v>
-      </c>
-      <c r="AC52" s="4" t="n">
         <v>91</v>
       </c>
-      <c r="AD52" s="4" t="inlineStr">
+      <c r="AC52" s="4" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
+      </c>
+      <c r="AD52" s="4" t="n">
+        <v>159.84</v>
       </c>
       <c r="AE52" s="4" t="n">
         <v>159.84</v>
       </c>
       <c r="AF52" s="4" t="n">
-        <v>159.84</v>
+        <v>156.64</v>
       </c>
       <c r="AG52" s="4" t="n">
-        <v>156.64</v>
+        <v>163.04</v>
       </c>
       <c r="AH52" s="4" t="n">
-        <v>163.04</v>
+        <v>151.848</v>
       </c>
       <c r="AI52" s="4" t="n">
-        <v>151.848</v>
+        <v>-5</v>
       </c>
       <c r="AJ52" s="4" t="n">
-        <v>-5</v>
+        <v>172.6272</v>
       </c>
       <c r="AK52" s="4" t="n">
-        <v>172.6272</v>
+        <v>8</v>
       </c>
       <c r="AL52" s="4" t="n">
-        <v>8</v>
+        <v>184.711104</v>
       </c>
       <c r="AM52" s="4" t="n">
-        <v>184.711104</v>
-      </c>
-      <c r="AN52" s="4" t="n">
         <v>15.56</v>
       </c>
-      <c r="AO52" s="4" t="inlineStr"/>
+      <c r="AN52" s="4" t="inlineStr"/>
+      <c r="AO52" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AP52" s="4" t="n">
-        <v>0</v>
+        <v>10.29</v>
       </c>
       <c r="AQ52" s="4" t="n">
-        <v>10.29</v>
-      </c>
-      <c r="AR52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS52" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AR52" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AT52" s="4" t="inlineStr"/>
-      <c r="AU52" s="4" t="inlineStr">
+      <c r="AS52" s="4" t="inlineStr"/>
+      <c r="AT52" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="AU52" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AV52" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW52" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX52" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06 02:36</t>
+        <v>8</v>
+      </c>
+      <c r="AW52" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:32</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AX52"/>
+  <autoFilter ref="A1:AW52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/telegram/aegis_daily_2026-08-06.xlsx
+++ b/reports/telegram/aegis_daily_2026-08-06.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$BB$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$BB$72</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB53"/>
+  <dimension ref="A1:BB72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -940,7 +940,7 @@
       </c>
       <c r="BB2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BB3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="BB4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="BB5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       <c r="W6" s="3" t="inlineStr"/>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank ↑ 8→5 · Conf 43% · band HOLD→STRONG · 16d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank ↑ 8→5 · Conf 43% · band STRONG · 16d left · → HOLD</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr"/>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="BB6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="BB7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="BB8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2062,7 @@
       <c r="W9" s="3" t="inlineStr"/>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank ↓ 2→8 · Conf 38% · band HOLD→STRONG · 16d left · → EXIT (rotate to TCS.NS)</t>
+          <t>🔴 AVOID · Rank ↓ 2→8 · Conf 38% · band STRONG · 16d left · → EXIT (rotate to TCS.NS)</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr"/>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="BB9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="BB10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="BB11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="BB12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="BB13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="BB14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="BB15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="BB16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="BB17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="BB18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="BB19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="BB20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BB21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="BB22" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="BB23" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BB24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="BB25" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -4990,7 +4990,7 @@
       </c>
       <c r="BB26" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -5150,7 +5150,7 @@
       </c>
       <c r="BB27" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -5306,14 +5306,14 @@
       </c>
       <c r="BB28" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>TRV_USA_20260729</t>
+          <t>LUPIN_IND_20260806</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -5323,32 +5323,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>INDIA</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R2_ARCH</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>TRV</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Lupin</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr"/>
@@ -5357,49 +5357,29 @@
         <v>1</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="3" t="n">
-        <v>79.3</v>
-      </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="P29" s="3" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="N29" s="3" t="inlineStr"/>
+      <c r="O29" s="3" t="inlineStr"/>
+      <c r="P29" s="3" t="inlineStr"/>
       <c r="Q29" s="3" t="inlineStr"/>
-      <c r="R29" s="3" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="S29" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="T29" s="3" t="inlineStr">
-        <is>
-          <t>crude +19.8% (rising) → +1.0pts · 12 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="U29" s="3" t="n">
-        <v>12</v>
-      </c>
+      <c r="R29" s="3" t="inlineStr"/>
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr"/>
       <c r="V29" s="3" t="inlineStr"/>
       <c r="W29" s="3" t="inlineStr"/>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 1→1 · Conf 57% · band HOLD · 14d left · → BUY</t>
+          <t>Rank ↑ 3→1 · Conf 52% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr"/>
       <c r="Z29" s="3" t="n">
-        <v>56.8</v>
+        <v>51.8</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -5407,93 +5387,57 @@
         </is>
       </c>
       <c r="AB29" s="3" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="AC29" s="3" t="n">
-        <v>4</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="AC29" s="3" t="inlineStr"/>
       <c r="AD29" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="n">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="AF29" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG29" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AH29" s="3" t="n">
-        <v>368.98</v>
-      </c>
-      <c r="AI29" s="3" t="n">
-        <v>368.98</v>
-      </c>
-      <c r="AJ29" s="3" t="n">
-        <v>365.29</v>
-      </c>
-      <c r="AK29" s="3" t="n">
-        <v>372.67</v>
-      </c>
-      <c r="AL29" s="3" t="n">
-        <v>346.84</v>
-      </c>
-      <c r="AM29" s="3" t="n">
-        <v>-6</v>
-      </c>
-      <c r="AN29" s="3" t="n">
-        <v>413.26</v>
-      </c>
-      <c r="AO29" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AP29" s="3" t="n">
-        <v>457.54</v>
-      </c>
-      <c r="AQ29" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AR29" s="3" t="inlineStr"/>
-      <c r="AS29" s="3" t="inlineStr"/>
-      <c r="AT29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU29" s="3" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AV29" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="AG29" s="3" t="inlineStr"/>
+      <c r="AH29" s="3" t="inlineStr"/>
+      <c r="AI29" s="3" t="inlineStr"/>
+      <c r="AJ29" s="3" t="inlineStr"/>
+      <c r="AK29" s="3" t="inlineStr"/>
+      <c r="AL29" s="3" t="inlineStr"/>
+      <c r="AM29" s="3" t="inlineStr"/>
+      <c r="AN29" s="3" t="inlineStr"/>
+      <c r="AO29" s="3" t="inlineStr"/>
+      <c r="AP29" s="3" t="inlineStr"/>
+      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AR29" s="3" t="n">
+        <v>2410</v>
+      </c>
+      <c r="AS29" s="3" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="AT29" s="3" t="inlineStr"/>
+      <c r="AU29" s="3" t="inlineStr"/>
+      <c r="AV29" s="3" t="inlineStr"/>
       <c r="AW29" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AX29" s="3" t="inlineStr">
-        <is>
-          <t>Momentum · Value · Trend</t>
-        </is>
-      </c>
+      <c r="AX29" s="3" t="inlineStr"/>
       <c r="AY29" s="3" t="inlineStr"/>
-      <c r="AZ29" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="BA29" s="3" t="n">
-        <v>12</v>
-      </c>
+      <c r="AZ29" s="3" t="inlineStr"/>
+      <c r="BA29" s="3" t="inlineStr"/>
       <c r="BB29" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>V_USA_20260729</t>
+          <t>PNB_IND_20260806</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -5503,22 +5447,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>INDIA</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R2_ARCH</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Punjab Natl. Bank</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -5528,60 +5472,34 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr"/>
       <c r="J30" s="3" t="inlineStr"/>
       <c r="K30" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L30" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="3" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>STRONG</t>
-        </is>
-      </c>
-      <c r="P30" s="3" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="L30" s="3" t="inlineStr"/>
+      <c r="M30" s="3" t="inlineStr"/>
+      <c r="N30" s="3" t="inlineStr"/>
+      <c r="O30" s="3" t="inlineStr"/>
+      <c r="P30" s="3" t="inlineStr"/>
       <c r="Q30" s="3" t="inlineStr"/>
-      <c r="R30" s="3" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="S30" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="T30" s="3" t="inlineStr">
-        <is>
-          <t>crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="U30" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="V30" s="3" t="n">
-        <v>0.184</v>
-      </c>
+      <c r="R30" s="3" t="inlineStr"/>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr"/>
+      <c r="V30" s="3" t="inlineStr"/>
       <c r="W30" s="3" t="inlineStr"/>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 2→2 · Conf 54% · band STRONG · 14d left · → HOLD</t>
+          <t>Rank #4 · Conf 32% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr"/>
       <c r="Z30" s="3" t="n">
-        <v>53.6</v>
+        <v>32.1</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -5589,91 +5507,57 @@
         </is>
       </c>
       <c r="AB30" s="3" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="AC30" s="3" t="n">
-        <v>4</v>
-      </c>
+        <v>22.2</v>
+      </c>
+      <c r="AC30" s="3" t="inlineStr"/>
       <c r="AD30" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE30" s="3" t="n">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="AF30" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG30" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AH30" s="3" t="n">
-        <v>358.56</v>
-      </c>
-      <c r="AI30" s="3" t="n">
-        <v>358.56</v>
-      </c>
-      <c r="AJ30" s="3" t="n">
-        <v>354.97</v>
-      </c>
-      <c r="AK30" s="3" t="n">
-        <v>362.15</v>
-      </c>
-      <c r="AL30" s="3" t="n">
-        <v>340.63</v>
-      </c>
-      <c r="AM30" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AN30" s="3" t="n">
-        <v>387.24</v>
-      </c>
-      <c r="AO30" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AP30" s="3" t="n">
-        <v>412.34</v>
-      </c>
-      <c r="AQ30" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR30" s="3" t="inlineStr"/>
-      <c r="AS30" s="3" t="inlineStr"/>
-      <c r="AT30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU30" s="3" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AV30" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="AG30" s="3" t="inlineStr"/>
+      <c r="AH30" s="3" t="inlineStr"/>
+      <c r="AI30" s="3" t="inlineStr"/>
+      <c r="AJ30" s="3" t="inlineStr"/>
+      <c r="AK30" s="3" t="inlineStr"/>
+      <c r="AL30" s="3" t="inlineStr"/>
+      <c r="AM30" s="3" t="inlineStr"/>
+      <c r="AN30" s="3" t="inlineStr"/>
+      <c r="AO30" s="3" t="inlineStr"/>
+      <c r="AP30" s="3" t="inlineStr"/>
+      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="n">
+        <v>113.99</v>
+      </c>
+      <c r="AS30" s="3" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="AT30" s="3" t="inlineStr"/>
+      <c r="AU30" s="3" t="inlineStr"/>
+      <c r="AV30" s="3" t="inlineStr"/>
       <c r="AW30" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AX30" s="3" t="inlineStr">
-        <is>
-          <t>Momentum · Trend · Quality</t>
-        </is>
-      </c>
+      <c r="AX30" s="3" t="inlineStr"/>
       <c r="AY30" s="3" t="inlineStr"/>
       <c r="AZ30" s="3" t="inlineStr"/>
-      <c r="BA30" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="BA30" s="3" t="inlineStr"/>
       <c r="BB30" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>NVDA_USA_20260729</t>
+          <t>COALINDIA_IND_20260806</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -5683,89 +5567,63 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>INDIA</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R2_ARCH</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Coal India</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>EXIT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>→ TRV · +12.2pp alpha</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="n">
-        <v>0</v>
-      </c>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr"/>
+      <c r="J31" s="3" t="inlineStr"/>
       <c r="K31" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="3" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="P31" s="3" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
+        <v>-5</v>
+      </c>
+      <c r="N31" s="3" t="inlineStr"/>
+      <c r="O31" s="3" t="inlineStr"/>
+      <c r="P31" s="3" t="inlineStr"/>
       <c r="Q31" s="3" t="inlineStr"/>
-      <c r="R31" s="3" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="S31" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="T31" s="3" t="inlineStr">
-        <is>
-          <t>crude +19.8% (rising) → +1.0pts · 21 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="U31" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="R31" s="3" t="inlineStr"/>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr"/>
       <c r="V31" s="3" t="inlineStr"/>
       <c r="W31" s="3" t="inlineStr"/>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank → 3→3 · Conf 47% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
+          <t>Rank ↑ 10→5 · Conf 36% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr"/>
       <c r="Z31" s="3" t="n">
-        <v>47.3</v>
+        <v>36.1</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -5773,91 +5631,57 @@
         </is>
       </c>
       <c r="AB31" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="AC31" s="3" t="n">
-        <v>4</v>
-      </c>
+        <v>22.2</v>
+      </c>
+      <c r="AC31" s="3" t="inlineStr"/>
       <c r="AD31" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE31" s="3" t="n">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="AF31" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG31" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AH31" s="3" t="n">
-        <v>202.81</v>
-      </c>
-      <c r="AI31" s="3" t="n">
-        <v>202.81</v>
-      </c>
-      <c r="AJ31" s="3" t="n">
-        <v>200.78</v>
-      </c>
-      <c r="AK31" s="3" t="n">
-        <v>204.84</v>
-      </c>
-      <c r="AL31" s="3" t="n">
-        <v>192.67</v>
-      </c>
-      <c r="AM31" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AN31" s="3" t="n">
-        <v>219.03</v>
-      </c>
-      <c r="AO31" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AP31" s="3" t="n">
-        <v>233.23</v>
-      </c>
-      <c r="AQ31" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR31" s="3" t="inlineStr"/>
-      <c r="AS31" s="3" t="inlineStr"/>
-      <c r="AT31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV31" s="3" t="n">
-        <v>-1.02</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="AG31" s="3" t="inlineStr"/>
+      <c r="AH31" s="3" t="inlineStr"/>
+      <c r="AI31" s="3" t="inlineStr"/>
+      <c r="AJ31" s="3" t="inlineStr"/>
+      <c r="AK31" s="3" t="inlineStr"/>
+      <c r="AL31" s="3" t="inlineStr"/>
+      <c r="AM31" s="3" t="inlineStr"/>
+      <c r="AN31" s="3" t="inlineStr"/>
+      <c r="AO31" s="3" t="inlineStr"/>
+      <c r="AP31" s="3" t="inlineStr"/>
+      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AR31" s="3" t="n">
+        <v>417.6</v>
+      </c>
+      <c r="AS31" s="3" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="AT31" s="3" t="inlineStr"/>
+      <c r="AU31" s="3" t="inlineStr"/>
+      <c r="AV31" s="3" t="inlineStr"/>
       <c r="AW31" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AX31" s="3" t="inlineStr">
-        <is>
-          <t>Quality · Growth · Mean Reversion</t>
-        </is>
-      </c>
+      <c r="AX31" s="3" t="inlineStr"/>
       <c r="AY31" s="3" t="inlineStr"/>
       <c r="AZ31" s="3" t="inlineStr"/>
-      <c r="BA31" s="3" t="n">
-        <v>12.15</v>
-      </c>
+      <c r="BA31" s="3" t="inlineStr"/>
       <c r="BB31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>JPM_USA_20260729</t>
+          <t>HINDZINC_IND_20260806</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -5867,89 +5691,59 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>INDIA</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R2_ARCH</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>JPMorgan Chase</t>
+          <t>Hindustan Zinc</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>EXIT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>→ TRV · +13.0pp alpha</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="n">
-        <v>0</v>
-      </c>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr"/>
+      <c r="J32" s="3" t="inlineStr"/>
       <c r="K32" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="L32" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="M32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3" t="n">
-        <v>78.40000000000001</v>
-      </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="L32" s="3" t="inlineStr"/>
+      <c r="M32" s="3" t="inlineStr"/>
+      <c r="N32" s="3" t="inlineStr"/>
+      <c r="O32" s="3" t="inlineStr"/>
+      <c r="P32" s="3" t="inlineStr"/>
       <c r="Q32" s="3" t="inlineStr"/>
-      <c r="R32" s="3" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="S32" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="T32" s="3" t="inlineStr">
-        <is>
-          <t>crude +19.8% (rising) → +1.0pts · 18 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="U32" s="3" t="n">
-        <v>18</v>
-      </c>
+      <c r="R32" s="3" t="inlineStr"/>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr"/>
       <c r="V32" s="3" t="inlineStr"/>
       <c r="W32" s="3" t="inlineStr"/>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank → 4→4 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
+          <t>Rank #10 · Conf 38% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr"/>
       <c r="Z32" s="3" t="n">
-        <v>49.7</v>
+        <v>38.3</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -5957,91 +5751,57 @@
         </is>
       </c>
       <c r="AB32" s="3" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="AC32" s="3" t="n">
-        <v>4</v>
-      </c>
+        <v>21.6</v>
+      </c>
+      <c r="AC32" s="3" t="inlineStr"/>
       <c r="AD32" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE32" s="3" t="n">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="AF32" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG32" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AH32" s="3" t="n">
-        <v>341.1</v>
-      </c>
-      <c r="AI32" s="3" t="n">
-        <v>341.1</v>
-      </c>
-      <c r="AJ32" s="3" t="n">
-        <v>337.69</v>
-      </c>
-      <c r="AK32" s="3" t="n">
-        <v>344.51</v>
-      </c>
-      <c r="AL32" s="3" t="n">
-        <v>324.05</v>
-      </c>
-      <c r="AM32" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AN32" s="3" t="n">
-        <v>368.39</v>
-      </c>
-      <c r="AO32" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AP32" s="3" t="n">
-        <v>392.26</v>
-      </c>
-      <c r="AQ32" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR32" s="3" t="inlineStr"/>
-      <c r="AS32" s="3" t="inlineStr"/>
-      <c r="AT32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU32" s="3" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="AV32" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="AG32" s="3" t="inlineStr"/>
+      <c r="AH32" s="3" t="inlineStr"/>
+      <c r="AI32" s="3" t="inlineStr"/>
+      <c r="AJ32" s="3" t="inlineStr"/>
+      <c r="AK32" s="3" t="inlineStr"/>
+      <c r="AL32" s="3" t="inlineStr"/>
+      <c r="AM32" s="3" t="inlineStr"/>
+      <c r="AN32" s="3" t="inlineStr"/>
+      <c r="AO32" s="3" t="inlineStr"/>
+      <c r="AP32" s="3" t="inlineStr"/>
+      <c r="AQ32" s="3" t="inlineStr"/>
+      <c r="AR32" s="3" t="n">
+        <v>562.9</v>
+      </c>
+      <c r="AS32" s="3" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="AT32" s="3" t="inlineStr"/>
+      <c r="AU32" s="3" t="inlineStr"/>
+      <c r="AV32" s="3" t="inlineStr"/>
       <c r="AW32" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AX32" s="3" t="inlineStr">
-        <is>
-          <t>Momentum · Value · Mean Reversion</t>
-        </is>
-      </c>
+      <c r="AX32" s="3" t="inlineStr"/>
       <c r="AY32" s="3" t="inlineStr"/>
       <c r="AZ32" s="3" t="inlineStr"/>
-      <c r="BA32" s="3" t="n">
-        <v>12.97</v>
-      </c>
+      <c r="BA32" s="3" t="inlineStr"/>
       <c r="BB32" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>HON_USA_20260729</t>
+          <t>BATAINDIA_IND_20260806</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -6051,91 +5811,59 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>INDIA</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R2_ARCH</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>BATAINDIA</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Bata India</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>EXIT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>→ TRV · +14.4pp alpha</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="n">
-        <v>0</v>
-      </c>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr"/>
+      <c r="J33" s="3" t="inlineStr"/>
       <c r="K33" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="L33" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="M33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="L33" s="3" t="inlineStr"/>
+      <c r="M33" s="3" t="inlineStr"/>
+      <c r="N33" s="3" t="inlineStr"/>
+      <c r="O33" s="3" t="inlineStr"/>
+      <c r="P33" s="3" t="inlineStr"/>
       <c r="Q33" s="3" t="inlineStr"/>
-      <c r="R33" s="3" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="S33" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="T33" s="3" t="inlineStr">
-        <is>
-          <t>crude +19.8% (rising) → +1.0pts · 48 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="U33" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="V33" s="3" t="n">
-        <v>0.127</v>
-      </c>
+      <c r="R33" s="3" t="inlineStr"/>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr"/>
+      <c r="V33" s="3" t="inlineStr"/>
       <c r="W33" s="3" t="inlineStr"/>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank → 5→5 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
+          <t>Rank #15 · Conf 24% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr"/>
       <c r="Z33" s="3" t="n">
-        <v>50.5</v>
+        <v>24</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -6143,91 +5871,57 @@
         </is>
       </c>
       <c r="AB33" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="AC33" s="3" t="n">
-        <v>4</v>
-      </c>
+        <v>-30.3</v>
+      </c>
+      <c r="AC33" s="3" t="inlineStr"/>
       <c r="AD33" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE33" s="3" t="n">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="AF33" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG33" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AH33" s="3" t="n">
-        <v>225.02</v>
-      </c>
-      <c r="AI33" s="3" t="n">
-        <v>225.02</v>
-      </c>
-      <c r="AJ33" s="3" t="n">
-        <v>222.77</v>
-      </c>
-      <c r="AK33" s="3" t="n">
-        <v>227.27</v>
-      </c>
-      <c r="AL33" s="3" t="n">
-        <v>213.77</v>
-      </c>
-      <c r="AM33" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AN33" s="3" t="n">
-        <v>243.02</v>
-      </c>
-      <c r="AO33" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AP33" s="3" t="n">
-        <v>258.77</v>
-      </c>
-      <c r="AQ33" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR33" s="3" t="inlineStr"/>
-      <c r="AS33" s="3" t="inlineStr"/>
-      <c r="AT33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU33" s="3" t="n">
-        <v>8.01</v>
-      </c>
-      <c r="AV33" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="AG33" s="3" t="inlineStr"/>
+      <c r="AH33" s="3" t="inlineStr"/>
+      <c r="AI33" s="3" t="inlineStr"/>
+      <c r="AJ33" s="3" t="inlineStr"/>
+      <c r="AK33" s="3" t="inlineStr"/>
+      <c r="AL33" s="3" t="inlineStr"/>
+      <c r="AM33" s="3" t="inlineStr"/>
+      <c r="AN33" s="3" t="inlineStr"/>
+      <c r="AO33" s="3" t="inlineStr"/>
+      <c r="AP33" s="3" t="inlineStr"/>
+      <c r="AQ33" s="3" t="inlineStr"/>
+      <c r="AR33" s="3" t="n">
+        <v>709.55</v>
+      </c>
+      <c r="AS33" s="3" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AT33" s="3" t="inlineStr"/>
+      <c r="AU33" s="3" t="inlineStr"/>
+      <c r="AV33" s="3" t="inlineStr"/>
       <c r="AW33" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AX33" s="3" t="inlineStr">
-        <is>
-          <t>Mean Reversion · Growth · Value</t>
-        </is>
-      </c>
+      <c r="AX33" s="3" t="inlineStr"/>
       <c r="AY33" s="3" t="inlineStr"/>
       <c r="AZ33" s="3" t="inlineStr"/>
-      <c r="BA33" s="3" t="n">
-        <v>14.45</v>
-      </c>
+      <c r="BA33" s="3" t="inlineStr"/>
       <c r="BB33" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GS_USA_20260729</t>
+          <t>LICI_IND_20260806</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -6237,89 +5931,55 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>INDIA</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R2_ARCH</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>GS</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
+          <t>LICI</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>EXIT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>→ TRV · +14.8pp alpha</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="n">
-        <v>0</v>
-      </c>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr"/>
+      <c r="J34" s="3" t="inlineStr"/>
       <c r="K34" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="L34" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="M34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" s="3" t="n">
-        <v>66.3</v>
-      </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="L34" s="3" t="inlineStr"/>
+      <c r="M34" s="3" t="inlineStr"/>
+      <c r="N34" s="3" t="inlineStr"/>
+      <c r="O34" s="3" t="inlineStr"/>
+      <c r="P34" s="3" t="inlineStr"/>
       <c r="Q34" s="3" t="inlineStr"/>
-      <c r="R34" s="3" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="S34" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="T34" s="3" t="inlineStr">
-        <is>
-          <t>crude +19.8% (rising) → +1.0pts · 9 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="U34" s="3" t="n">
-        <v>9</v>
-      </c>
+      <c r="R34" s="3" t="inlineStr"/>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr"/>
       <c r="V34" s="3" t="inlineStr"/>
       <c r="W34" s="3" t="inlineStr"/>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank → 6→6 · Conf 51% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
+          <t>Rank #9 · Conf 37% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr"/>
       <c r="Z34" s="3" t="n">
-        <v>51</v>
+        <v>37.2</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -6327,91 +5987,57 @@
         </is>
       </c>
       <c r="AB34" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC34" s="3" t="n">
-        <v>4</v>
-      </c>
+        <v>20.6</v>
+      </c>
+      <c r="AC34" s="3" t="inlineStr"/>
       <c r="AD34" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE34" s="3" t="n">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="AF34" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG34" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AH34" s="3" t="n">
-        <v>1065.22</v>
-      </c>
-      <c r="AI34" s="3" t="n">
-        <v>1065.22</v>
-      </c>
-      <c r="AJ34" s="3" t="n">
-        <v>1054.57</v>
-      </c>
-      <c r="AK34" s="3" t="n">
-        <v>1075.87</v>
-      </c>
-      <c r="AL34" s="3" t="n">
-        <v>1011.96</v>
-      </c>
-      <c r="AM34" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AN34" s="3" t="n">
-        <v>1150.44</v>
-      </c>
-      <c r="AO34" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AP34" s="3" t="n">
-        <v>1225</v>
-      </c>
-      <c r="AQ34" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR34" s="3" t="inlineStr"/>
-      <c r="AS34" s="3" t="inlineStr"/>
-      <c r="AT34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV34" s="3" t="n">
-        <v>-4.4</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="AG34" s="3" t="inlineStr"/>
+      <c r="AH34" s="3" t="inlineStr"/>
+      <c r="AI34" s="3" t="inlineStr"/>
+      <c r="AJ34" s="3" t="inlineStr"/>
+      <c r="AK34" s="3" t="inlineStr"/>
+      <c r="AL34" s="3" t="inlineStr"/>
+      <c r="AM34" s="3" t="inlineStr"/>
+      <c r="AN34" s="3" t="inlineStr"/>
+      <c r="AO34" s="3" t="inlineStr"/>
+      <c r="AP34" s="3" t="inlineStr"/>
+      <c r="AQ34" s="3" t="inlineStr"/>
+      <c r="AR34" s="3" t="n">
+        <v>391.3</v>
+      </c>
+      <c r="AS34" s="3" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="AT34" s="3" t="inlineStr"/>
+      <c r="AU34" s="3" t="inlineStr"/>
+      <c r="AV34" s="3" t="inlineStr"/>
       <c r="AW34" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AX34" s="3" t="inlineStr">
-        <is>
-          <t>Value · News · Event Driven</t>
-        </is>
-      </c>
+      <c r="AX34" s="3" t="inlineStr"/>
       <c r="AY34" s="3" t="inlineStr"/>
       <c r="AZ34" s="3" t="inlineStr"/>
-      <c r="BA34" s="3" t="n">
-        <v>14.77</v>
-      </c>
+      <c r="BA34" s="3" t="inlineStr"/>
       <c r="BB34" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>AAPL_USA_20260729</t>
+          <t>TIINDIA_IND_20260806</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -6421,91 +6047,55 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>INDIA</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R2_ARCH</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>AAPL</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Apple</t>
-        </is>
-      </c>
+          <t>TIINDIA</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>EXIT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>→ TRV · +14.9pp alpha</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="n">
-        <v>0</v>
-      </c>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr"/>
+      <c r="J35" s="3" t="inlineStr"/>
       <c r="K35" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="L35" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="M35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" s="3" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>STRONG</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="L35" s="3" t="inlineStr"/>
+      <c r="M35" s="3" t="inlineStr"/>
+      <c r="N35" s="3" t="inlineStr"/>
+      <c r="O35" s="3" t="inlineStr"/>
+      <c r="P35" s="3" t="inlineStr"/>
       <c r="Q35" s="3" t="inlineStr"/>
-      <c r="R35" s="3" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="S35" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="T35" s="3" t="inlineStr">
-        <is>
-          <t>crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="U35" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="V35" s="3" t="n">
-        <v>0.109</v>
-      </c>
+      <c r="R35" s="3" t="inlineStr"/>
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr"/>
+      <c r="V35" s="3" t="inlineStr"/>
       <c r="W35" s="3" t="inlineStr"/>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank → 7→7 · Conf 50% · band STRONG · 6d left · → EXIT (rotate to TRV)</t>
+          <t>Rank #12 · Conf 22% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr"/>
       <c r="Z35" s="3" t="n">
-        <v>50.5</v>
+        <v>21.5</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -6513,91 +6103,57 @@
         </is>
       </c>
       <c r="AB35" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="AC35" s="3" t="n">
-        <v>4</v>
-      </c>
+        <v>-25.9</v>
+      </c>
+      <c r="AC35" s="3" t="inlineStr"/>
       <c r="AD35" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE35" s="3" t="n">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="AF35" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG35" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AH35" s="3" t="n">
-        <v>333.74</v>
-      </c>
-      <c r="AI35" s="3" t="n">
-        <v>333.74</v>
-      </c>
-      <c r="AJ35" s="3" t="n">
-        <v>330.4</v>
-      </c>
-      <c r="AK35" s="3" t="n">
-        <v>337.08</v>
-      </c>
-      <c r="AL35" s="3" t="n">
-        <v>317.05</v>
-      </c>
-      <c r="AM35" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AN35" s="3" t="n">
-        <v>360.44</v>
-      </c>
-      <c r="AO35" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AP35" s="3" t="n">
-        <v>383.8</v>
-      </c>
-      <c r="AQ35" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR35" s="3" t="inlineStr"/>
-      <c r="AS35" s="3" t="inlineStr"/>
-      <c r="AT35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV35" s="3" t="n">
-        <v>-7.44</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="AG35" s="3" t="inlineStr"/>
+      <c r="AH35" s="3" t="inlineStr"/>
+      <c r="AI35" s="3" t="inlineStr"/>
+      <c r="AJ35" s="3" t="inlineStr"/>
+      <c r="AK35" s="3" t="inlineStr"/>
+      <c r="AL35" s="3" t="inlineStr"/>
+      <c r="AM35" s="3" t="inlineStr"/>
+      <c r="AN35" s="3" t="inlineStr"/>
+      <c r="AO35" s="3" t="inlineStr"/>
+      <c r="AP35" s="3" t="inlineStr"/>
+      <c r="AQ35" s="3" t="inlineStr"/>
+      <c r="AR35" s="3" t="n">
+        <v>2744.3</v>
+      </c>
+      <c r="AS35" s="3" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AT35" s="3" t="inlineStr"/>
+      <c r="AU35" s="3" t="inlineStr"/>
+      <c r="AV35" s="3" t="inlineStr"/>
       <c r="AW35" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AX35" s="3" t="inlineStr">
-        <is>
-          <t>Value · Trend · Momentum</t>
-        </is>
-      </c>
+      <c r="AX35" s="3" t="inlineStr"/>
       <c r="AY35" s="3" t="inlineStr"/>
       <c r="AZ35" s="3" t="inlineStr"/>
-      <c r="BA35" s="3" t="n">
-        <v>14.87</v>
-      </c>
+      <c r="BA35" s="3" t="inlineStr"/>
       <c r="BB35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>MSFT_USA_20260730</t>
+          <t>ICICIBANK_IND_20260806</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -6607,91 +6163,63 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>INDIA</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1_ARCH</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>ICICI Bank</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>EXIT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t>→ TRV · +15.2pp alpha</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="n">
-        <v>0</v>
-      </c>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr"/>
+      <c r="J36" s="3" t="inlineStr"/>
       <c r="K36" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N36" s="3" t="n">
-        <v>79.5</v>
-      </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="P36" s="3" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
+      <c r="N36" s="3" t="inlineStr"/>
+      <c r="O36" s="3" t="inlineStr"/>
+      <c r="P36" s="3" t="inlineStr"/>
       <c r="Q36" s="3" t="inlineStr"/>
-      <c r="R36" s="3" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="S36" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="T36" s="3" t="inlineStr">
-        <is>
-          <t>crude +19.8% (rising) → +1.0pts · 33 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="U36" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="V36" s="3" t="n">
-        <v>0.15</v>
-      </c>
+      <c r="R36" s="3" t="inlineStr"/>
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr"/>
+      <c r="V36" s="3" t="inlineStr"/>
       <c r="W36" s="3" t="inlineStr"/>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank → 8→8 · Conf 54% · band HOLD · 58d left · → EXIT (rotate to TRV)</t>
+          <t>Rank → 2→2 · Conf 83% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr"/>
       <c r="Z36" s="3" t="n">
-        <v>53.6</v>
+        <v>83</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -6699,91 +6227,57 @@
         </is>
       </c>
       <c r="AB36" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC36" s="3" t="n">
-        <v>3</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="AC36" s="3" t="inlineStr"/>
       <c r="AD36" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE36" s="3" t="n">
         <v>60</v>
       </c>
       <c r="AF36" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="AG36" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="AH36" s="3" t="n">
-        <v>393.82</v>
-      </c>
-      <c r="AI36" s="3" t="n">
-        <v>393.82</v>
-      </c>
-      <c r="AJ36" s="3" t="n">
-        <v>389.88</v>
-      </c>
-      <c r="AK36" s="3" t="n">
-        <v>397.76</v>
-      </c>
-      <c r="AL36" s="3" t="n">
-        <v>374.13</v>
-      </c>
-      <c r="AM36" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AN36" s="3" t="n">
-        <v>425.33</v>
-      </c>
-      <c r="AO36" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AP36" s="3" t="n">
-        <v>452.89</v>
-      </c>
-      <c r="AQ36" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR36" s="3" t="inlineStr"/>
-      <c r="AS36" s="3" t="inlineStr"/>
-      <c r="AT36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU36" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AV36" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="AG36" s="3" t="inlineStr"/>
+      <c r="AH36" s="3" t="inlineStr"/>
+      <c r="AI36" s="3" t="inlineStr"/>
+      <c r="AJ36" s="3" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr"/>
+      <c r="AL36" s="3" t="inlineStr"/>
+      <c r="AM36" s="3" t="inlineStr"/>
+      <c r="AN36" s="3" t="inlineStr"/>
+      <c r="AO36" s="3" t="inlineStr"/>
+      <c r="AP36" s="3" t="inlineStr"/>
+      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="n">
+        <v>1454.6</v>
+      </c>
+      <c r="AS36" s="3" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="AT36" s="3" t="inlineStr"/>
+      <c r="AU36" s="3" t="inlineStr"/>
+      <c r="AV36" s="3" t="inlineStr"/>
       <c r="AW36" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AX36" s="3" t="inlineStr">
-        <is>
-          <t>Quality · Mean Reversion · Trend</t>
-        </is>
-      </c>
+      <c r="AX36" s="3" t="inlineStr"/>
       <c r="AY36" s="3" t="inlineStr"/>
       <c r="AZ36" s="3" t="inlineStr"/>
-      <c r="BA36" s="3" t="n">
-        <v>15.21</v>
-      </c>
+      <c r="BA36" s="3" t="inlineStr"/>
       <c r="BB36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>KO_USA_20260729</t>
+          <t>SUNPHARMA_IND_20260806</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -6793,91 +6287,63 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>INDIA</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1_ARCH</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Sun Pharma</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>EXIT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>→ TRV · +15.5pp alpha</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="n">
-        <v>0</v>
-      </c>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr"/>
+      <c r="J37" s="3" t="inlineStr"/>
       <c r="K37" s="3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M37" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N37" s="3" t="n">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>STRONG</t>
-        </is>
-      </c>
-      <c r="P37" s="3" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
+      <c r="N37" s="3" t="inlineStr"/>
+      <c r="O37" s="3" t="inlineStr"/>
+      <c r="P37" s="3" t="inlineStr"/>
       <c r="Q37" s="3" t="inlineStr"/>
-      <c r="R37" s="3" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="S37" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="T37" s="3" t="inlineStr">
-        <is>
-          <t>crude +19.8% (rising) → +1.0pts · 11 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="U37" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="V37" s="3" t="n">
-        <v>0.08500000000000001</v>
-      </c>
+      <c r="R37" s="3" t="inlineStr"/>
+      <c r="S37" s="3" t="inlineStr"/>
+      <c r="T37" s="3" t="inlineStr"/>
+      <c r="U37" s="3" t="inlineStr"/>
+      <c r="V37" s="3" t="inlineStr"/>
       <c r="W37" s="3" t="inlineStr"/>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank → 9→9 · Conf 50% · band STRONG · 6d left · → EXIT (rotate to TRV)</t>
+          <t>Rank → 1→1 · Conf 90% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr"/>
       <c r="Z37" s="3" t="n">
-        <v>50.5</v>
+        <v>90</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -6885,91 +6351,57 @@
         </is>
       </c>
       <c r="AB37" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="AC37" s="3" t="n">
-        <v>4</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="AC37" s="3" t="inlineStr"/>
       <c r="AD37" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE37" s="3" t="n">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="AF37" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG37" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AH37" s="3" t="n">
-        <v>81.56</v>
-      </c>
-      <c r="AI37" s="3" t="n">
-        <v>81.56</v>
-      </c>
-      <c r="AJ37" s="3" t="n">
-        <v>80.73999999999999</v>
-      </c>
-      <c r="AK37" s="3" t="n">
-        <v>82.38</v>
-      </c>
-      <c r="AL37" s="3" t="n">
-        <v>77.48</v>
-      </c>
-      <c r="AM37" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AN37" s="3" t="n">
-        <v>88.08</v>
-      </c>
-      <c r="AO37" s="3" t="n">
-        <v>7.99</v>
-      </c>
-      <c r="AP37" s="3" t="n">
-        <v>93.79000000000001</v>
-      </c>
-      <c r="AQ37" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR37" s="3" t="inlineStr"/>
-      <c r="AS37" s="3" t="inlineStr"/>
-      <c r="AT37" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU37" s="3" t="n">
-        <v>7.39</v>
-      </c>
-      <c r="AV37" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="AG37" s="3" t="inlineStr"/>
+      <c r="AH37" s="3" t="inlineStr"/>
+      <c r="AI37" s="3" t="inlineStr"/>
+      <c r="AJ37" s="3" t="inlineStr"/>
+      <c r="AK37" s="3" t="inlineStr"/>
+      <c r="AL37" s="3" t="inlineStr"/>
+      <c r="AM37" s="3" t="inlineStr"/>
+      <c r="AN37" s="3" t="inlineStr"/>
+      <c r="AO37" s="3" t="inlineStr"/>
+      <c r="AP37" s="3" t="inlineStr"/>
+      <c r="AQ37" s="3" t="inlineStr"/>
+      <c r="AR37" s="3" t="n">
+        <v>1964</v>
+      </c>
+      <c r="AS37" s="3" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="AT37" s="3" t="inlineStr"/>
+      <c r="AU37" s="3" t="inlineStr"/>
+      <c r="AV37" s="3" t="inlineStr"/>
       <c r="AW37" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AX37" s="3" t="inlineStr">
-        <is>
-          <t>Momentum · News · Quality</t>
-        </is>
-      </c>
+      <c r="AX37" s="3" t="inlineStr"/>
       <c r="AY37" s="3" t="inlineStr"/>
       <c r="AZ37" s="3" t="inlineStr"/>
-      <c r="BA37" s="3" t="n">
-        <v>15.5</v>
-      </c>
+      <c r="BA37" s="3" t="inlineStr"/>
       <c r="BB37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>MMM_USA_20260730</t>
+          <t>LUPIN_IND_20260806</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -6979,89 +6411,63 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>INDIA</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1_ARCH</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3M</t>
+          <t>Lupin</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>EXIT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t>→ TRV · +16.4pp alpha</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="n">
-        <v>0</v>
-      </c>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr"/>
+      <c r="J38" s="3" t="inlineStr"/>
       <c r="K38" s="3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="M38" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N38" s="3" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="P38" s="3" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
+      <c r="N38" s="3" t="inlineStr"/>
+      <c r="O38" s="3" t="inlineStr"/>
+      <c r="P38" s="3" t="inlineStr"/>
       <c r="Q38" s="3" t="inlineStr"/>
-      <c r="R38" s="3" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="S38" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="T38" s="3" t="inlineStr">
-        <is>
-          <t>crude +19.8% (rising) → +1.0pts · 15 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="U38" s="3" t="n">
-        <v>15</v>
-      </c>
+      <c r="R38" s="3" t="inlineStr"/>
+      <c r="S38" s="3" t="inlineStr"/>
+      <c r="T38" s="3" t="inlineStr"/>
+      <c r="U38" s="3" t="inlineStr"/>
       <c r="V38" s="3" t="inlineStr"/>
       <c r="W38" s="3" t="inlineStr"/>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank → 10→10 · Conf 54% · band HOLD · 58d left · → EXIT (rotate to TRV)</t>
+          <t>Rank → 3→3 · Conf 72% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr"/>
       <c r="Z38" s="3" t="n">
-        <v>53.6</v>
+        <v>72</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -7069,91 +6475,57 @@
         </is>
       </c>
       <c r="AB38" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="AC38" s="3" t="n">
-        <v>3</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="AC38" s="3" t="inlineStr"/>
       <c r="AD38" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE38" s="3" t="n">
         <v>60</v>
       </c>
       <c r="AF38" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="AG38" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="AH38" s="3" t="n">
-        <v>159.84</v>
-      </c>
-      <c r="AI38" s="3" t="n">
-        <v>159.84</v>
-      </c>
-      <c r="AJ38" s="3" t="n">
-        <v>158.24</v>
-      </c>
-      <c r="AK38" s="3" t="n">
-        <v>161.44</v>
-      </c>
-      <c r="AL38" s="3" t="n">
-        <v>151.85</v>
-      </c>
-      <c r="AM38" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AN38" s="3" t="n">
-        <v>172.63</v>
-      </c>
-      <c r="AO38" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AP38" s="3" t="n">
-        <v>183.82</v>
-      </c>
-      <c r="AQ38" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR38" s="3" t="inlineStr"/>
-      <c r="AS38" s="3" t="inlineStr"/>
-      <c r="AT38" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU38" s="3" t="n">
-        <v>10.29</v>
-      </c>
-      <c r="AV38" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="AG38" s="3" t="inlineStr"/>
+      <c r="AH38" s="3" t="inlineStr"/>
+      <c r="AI38" s="3" t="inlineStr"/>
+      <c r="AJ38" s="3" t="inlineStr"/>
+      <c r="AK38" s="3" t="inlineStr"/>
+      <c r="AL38" s="3" t="inlineStr"/>
+      <c r="AM38" s="3" t="inlineStr"/>
+      <c r="AN38" s="3" t="inlineStr"/>
+      <c r="AO38" s="3" t="inlineStr"/>
+      <c r="AP38" s="3" t="inlineStr"/>
+      <c r="AQ38" s="3" t="inlineStr"/>
+      <c r="AR38" s="3" t="n">
+        <v>2410</v>
+      </c>
+      <c r="AS38" s="3" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="AT38" s="3" t="inlineStr"/>
+      <c r="AU38" s="3" t="inlineStr"/>
+      <c r="AV38" s="3" t="inlineStr"/>
       <c r="AW38" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AX38" s="3" t="inlineStr">
-        <is>
-          <t>Momentum · News · Value</t>
-        </is>
-      </c>
+      <c r="AX38" s="3" t="inlineStr"/>
       <c r="AY38" s="3" t="inlineStr"/>
       <c r="AZ38" s="3" t="inlineStr"/>
-      <c r="BA38" s="3" t="n">
-        <v>16.4</v>
-      </c>
+      <c r="BA38" s="3" t="inlineStr"/>
       <c r="BB38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>INTC_USA_20260729</t>
+          <t>PIDILITIND_IND_20260806</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -7163,89 +6535,63 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>INDIA</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1_ARCH</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Pidilite</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>EXIT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>→ TRV · +37.2pp alpha</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="n">
-        <v>0</v>
-      </c>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr"/>
+      <c r="J39" s="3" t="inlineStr"/>
       <c r="K39" s="3" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="M39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N39" s="3" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="inlineStr">
-        <is>
-          <t>🔴</t>
-        </is>
-      </c>
+      <c r="N39" s="3" t="inlineStr"/>
+      <c r="O39" s="3" t="inlineStr"/>
+      <c r="P39" s="3" t="inlineStr"/>
       <c r="Q39" s="3" t="inlineStr"/>
-      <c r="R39" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="S39" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="T39" s="3" t="inlineStr">
-        <is>
-          <t>crude +19.8% (rising) → +1.0pts · 26 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="U39" s="3" t="n">
-        <v>26</v>
-      </c>
+      <c r="R39" s="3" t="inlineStr"/>
+      <c r="S39" s="3" t="inlineStr"/>
+      <c r="T39" s="3" t="inlineStr"/>
+      <c r="U39" s="3" t="inlineStr"/>
       <c r="V39" s="3" t="inlineStr"/>
       <c r="W39" s="3" t="inlineStr"/>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank → 11→11 · Conf 29% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
+          <t>Rank → 3→3 · Conf 87% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr"/>
       <c r="Z39" s="3" t="n">
-        <v>28.7</v>
+        <v>87</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -7253,91 +6599,57 @@
         </is>
       </c>
       <c r="AB39" s="3" t="n">
-        <v>-7.9</v>
-      </c>
-      <c r="AC39" s="3" t="n">
-        <v>4</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="AC39" s="3" t="inlineStr"/>
       <c r="AD39" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE39" s="3" t="n">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="AF39" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG39" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AH39" s="3" t="n">
-        <v>95.04000000000001</v>
-      </c>
-      <c r="AI39" s="3" t="n">
-        <v>95.04000000000001</v>
-      </c>
-      <c r="AJ39" s="3" t="n">
-        <v>94.09</v>
-      </c>
-      <c r="AK39" s="3" t="n">
-        <v>95.98999999999999</v>
-      </c>
-      <c r="AL39" s="3" t="n">
-        <v>90.29000000000001</v>
-      </c>
-      <c r="AM39" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AN39" s="3" t="n">
-        <v>102.64</v>
-      </c>
-      <c r="AO39" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AP39" s="3" t="n">
-        <v>109.3</v>
-      </c>
-      <c r="AQ39" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR39" s="3" t="inlineStr"/>
-      <c r="AS39" s="3" t="inlineStr"/>
-      <c r="AT39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV39" s="3" t="n">
-        <v>-5.09</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="AG39" s="3" t="inlineStr"/>
+      <c r="AH39" s="3" t="inlineStr"/>
+      <c r="AI39" s="3" t="inlineStr"/>
+      <c r="AJ39" s="3" t="inlineStr"/>
+      <c r="AK39" s="3" t="inlineStr"/>
+      <c r="AL39" s="3" t="inlineStr"/>
+      <c r="AM39" s="3" t="inlineStr"/>
+      <c r="AN39" s="3" t="inlineStr"/>
+      <c r="AO39" s="3" t="inlineStr"/>
+      <c r="AP39" s="3" t="inlineStr"/>
+      <c r="AQ39" s="3" t="inlineStr"/>
+      <c r="AR39" s="3" t="n">
+        <v>1620</v>
+      </c>
+      <c r="AS39" s="3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT39" s="3" t="inlineStr"/>
+      <c r="AU39" s="3" t="inlineStr"/>
+      <c r="AV39" s="3" t="inlineStr"/>
       <c r="AW39" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AX39" s="3" t="inlineStr">
-        <is>
-          <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
-        </is>
-      </c>
+      <c r="AX39" s="3" t="inlineStr"/>
       <c r="AY39" s="3" t="inlineStr"/>
       <c r="AZ39" s="3" t="inlineStr"/>
-      <c r="BA39" s="3" t="n">
-        <v>37.17</v>
-      </c>
+      <c r="BA39" s="3" t="inlineStr"/>
       <c r="BB39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>BA_USA_20260730</t>
+          <t>NTPC_IND_20260806</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -7347,91 +6659,63 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>INDIA</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1_ARCH</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>EXIT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>→ TRV · +37.8pp alpha</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="n">
-        <v>0</v>
-      </c>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr"/>
+      <c r="J40" s="3" t="inlineStr"/>
       <c r="K40" s="3" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N40" s="3" t="n">
-        <v>52.6</v>
-      </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="inlineStr">
-        <is>
-          <t>🔴</t>
-        </is>
-      </c>
+      <c r="N40" s="3" t="inlineStr"/>
+      <c r="O40" s="3" t="inlineStr"/>
+      <c r="P40" s="3" t="inlineStr"/>
       <c r="Q40" s="3" t="inlineStr"/>
-      <c r="R40" s="3" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="S40" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="T40" s="3" t="inlineStr">
-        <is>
-          <t>crude +19.8% (rising) → +1.0pts · 12 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="U40" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="V40" s="3" t="n">
-        <v>0.122</v>
-      </c>
+      <c r="R40" s="3" t="inlineStr"/>
+      <c r="S40" s="3" t="inlineStr"/>
+      <c r="T40" s="3" t="inlineStr"/>
+      <c r="U40" s="3" t="inlineStr"/>
+      <c r="V40" s="3" t="inlineStr"/>
       <c r="W40" s="3" t="inlineStr"/>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank → 12→12 · Conf 31% · band EXIT · 58d left · → EXIT (rotate to TRV)</t>
+          <t>Rank → 4→4 · Conf 72% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr"/>
       <c r="Z40" s="3" t="n">
-        <v>30.8</v>
+        <v>72</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -7439,91 +6723,57 @@
         </is>
       </c>
       <c r="AB40" s="3" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="AC40" s="3" t="n">
-        <v>3</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="AC40" s="3" t="inlineStr"/>
       <c r="AD40" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE40" s="3" t="n">
         <v>60</v>
       </c>
       <c r="AF40" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="AG40" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="AH40" s="3" t="n">
-        <v>214.03</v>
-      </c>
-      <c r="AI40" s="3" t="n">
-        <v>214.03</v>
-      </c>
-      <c r="AJ40" s="3" t="n">
-        <v>211.89</v>
-      </c>
-      <c r="AK40" s="3" t="n">
-        <v>216.17</v>
-      </c>
-      <c r="AL40" s="3" t="n">
-        <v>203.33</v>
-      </c>
-      <c r="AM40" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AN40" s="3" t="n">
-        <v>231.15</v>
-      </c>
-      <c r="AO40" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AP40" s="3" t="n">
-        <v>246.13</v>
-      </c>
-      <c r="AQ40" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR40" s="3" t="inlineStr"/>
-      <c r="AS40" s="3" t="inlineStr"/>
-      <c r="AT40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU40" s="3" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="AV40" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="AG40" s="3" t="inlineStr"/>
+      <c r="AH40" s="3" t="inlineStr"/>
+      <c r="AI40" s="3" t="inlineStr"/>
+      <c r="AJ40" s="3" t="inlineStr"/>
+      <c r="AK40" s="3" t="inlineStr"/>
+      <c r="AL40" s="3" t="inlineStr"/>
+      <c r="AM40" s="3" t="inlineStr"/>
+      <c r="AN40" s="3" t="inlineStr"/>
+      <c r="AO40" s="3" t="inlineStr"/>
+      <c r="AP40" s="3" t="inlineStr"/>
+      <c r="AQ40" s="3" t="inlineStr"/>
+      <c r="AR40" s="3" t="n">
+        <v>343.65</v>
+      </c>
+      <c r="AS40" s="3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AT40" s="3" t="inlineStr"/>
+      <c r="AU40" s="3" t="inlineStr"/>
+      <c r="AV40" s="3" t="inlineStr"/>
       <c r="AW40" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AX40" s="3" t="inlineStr">
-        <is>
-          <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
-        </is>
-      </c>
+      <c r="AX40" s="3" t="inlineStr"/>
       <c r="AY40" s="3" t="inlineStr"/>
       <c r="AZ40" s="3" t="inlineStr"/>
-      <c r="BA40" s="3" t="n">
-        <v>37.79</v>
-      </c>
+      <c r="BA40" s="3" t="inlineStr"/>
       <c r="BB40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>HD_USA_20260729</t>
+          <t>KOTAKBANK_IND_20260806</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -7533,91 +6783,63 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>INDIA</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1_ARCH</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Home Depot</t>
+          <t>Kotak Bank</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>EXIT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>→ TRV · +43.9pp alpha</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="n">
-        <v>0</v>
-      </c>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr"/>
+      <c r="J41" s="3" t="inlineStr"/>
       <c r="K41" s="3" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N41" s="3" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="inlineStr">
-        <is>
-          <t>🔴</t>
-        </is>
-      </c>
+      <c r="N41" s="3" t="inlineStr"/>
+      <c r="O41" s="3" t="inlineStr"/>
+      <c r="P41" s="3" t="inlineStr"/>
       <c r="Q41" s="3" t="inlineStr"/>
-      <c r="R41" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="S41" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="T41" s="3" t="inlineStr">
-        <is>
-          <t>crude +19.8% (rising) → +1.0pts · 13 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="U41" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v>0.156</v>
-      </c>
+      <c r="R41" s="3" t="inlineStr"/>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="inlineStr"/>
+      <c r="U41" s="3" t="inlineStr"/>
+      <c r="V41" s="3" t="inlineStr"/>
       <c r="W41" s="3" t="inlineStr"/>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank → 13→13 · Conf 35% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
+          <t>Rank → 5→5 · Conf 71% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr"/>
       <c r="Z41" s="3" t="n">
-        <v>34.7</v>
+        <v>71</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -7625,91 +6847,57 @@
         </is>
       </c>
       <c r="AB41" s="3" t="n">
-        <v>-14.6</v>
-      </c>
-      <c r="AC41" s="3" t="n">
-        <v>4</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="AC41" s="3" t="inlineStr"/>
       <c r="AD41" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE41" s="3" t="n">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="AF41" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG41" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AH41" s="3" t="n">
-        <v>338.87</v>
-      </c>
-      <c r="AI41" s="3" t="n">
-        <v>338.87</v>
-      </c>
-      <c r="AJ41" s="3" t="n">
-        <v>335.48</v>
-      </c>
-      <c r="AK41" s="3" t="n">
-        <v>342.26</v>
-      </c>
-      <c r="AL41" s="3" t="n">
-        <v>321.93</v>
-      </c>
-      <c r="AM41" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AN41" s="3" t="n">
-        <v>365.98</v>
-      </c>
-      <c r="AO41" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AP41" s="3" t="n">
-        <v>389.7</v>
-      </c>
-      <c r="AQ41" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR41" s="3" t="inlineStr"/>
-      <c r="AS41" s="3" t="inlineStr"/>
-      <c r="AT41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV41" s="3" t="n">
-        <v>-2.04</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="AG41" s="3" t="inlineStr"/>
+      <c r="AH41" s="3" t="inlineStr"/>
+      <c r="AI41" s="3" t="inlineStr"/>
+      <c r="AJ41" s="3" t="inlineStr"/>
+      <c r="AK41" s="3" t="inlineStr"/>
+      <c r="AL41" s="3" t="inlineStr"/>
+      <c r="AM41" s="3" t="inlineStr"/>
+      <c r="AN41" s="3" t="inlineStr"/>
+      <c r="AO41" s="3" t="inlineStr"/>
+      <c r="AP41" s="3" t="inlineStr"/>
+      <c r="AQ41" s="3" t="inlineStr"/>
+      <c r="AR41" s="3" t="n">
+        <v>398</v>
+      </c>
+      <c r="AS41" s="3" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AT41" s="3" t="inlineStr"/>
+      <c r="AU41" s="3" t="inlineStr"/>
+      <c r="AV41" s="3" t="inlineStr"/>
       <c r="AW41" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AX41" s="3" t="inlineStr">
-        <is>
-          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
-        </is>
-      </c>
+      <c r="AX41" s="3" t="inlineStr"/>
       <c r="AY41" s="3" t="inlineStr"/>
       <c r="AZ41" s="3" t="inlineStr"/>
-      <c r="BA41" s="3" t="n">
-        <v>43.85</v>
-      </c>
+      <c r="BA41" s="3" t="inlineStr"/>
       <c r="BB41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>DIS_USA_20260729</t>
+          <t>POWERGRID_IND_20260806</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -7719,91 +6907,63 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>INDIA</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1_ARCH</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Walt Disney</t>
+          <t>Power Grid</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>EXIT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t>→ TRV · +45.6pp alpha</t>
-        </is>
-      </c>
-      <c r="J42" s="3" t="n">
-        <v>0</v>
-      </c>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr"/>
+      <c r="J42" s="3" t="inlineStr"/>
       <c r="K42" s="3" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="M42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N42" s="3" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="P42" s="3" t="inlineStr">
-        <is>
-          <t>🔴</t>
-        </is>
-      </c>
+      <c r="N42" s="3" t="inlineStr"/>
+      <c r="O42" s="3" t="inlineStr"/>
+      <c r="P42" s="3" t="inlineStr"/>
       <c r="Q42" s="3" t="inlineStr"/>
-      <c r="R42" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="S42" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="T42" s="3" t="inlineStr">
-        <is>
-          <t>crude +19.8% (rising) → +1.0pts · 19 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="U42" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="V42" s="3" t="n">
-        <v>0.193</v>
-      </c>
+      <c r="R42" s="3" t="inlineStr"/>
+      <c r="S42" s="3" t="inlineStr"/>
+      <c r="T42" s="3" t="inlineStr"/>
+      <c r="U42" s="3" t="inlineStr"/>
+      <c r="V42" s="3" t="inlineStr"/>
       <c r="W42" s="3" t="inlineStr"/>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank → 14→14 · Conf 35% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
+          <t>Rank → 7→7 · Conf 69% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr"/>
       <c r="Z42" s="3" t="n">
-        <v>34.7</v>
+        <v>69</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -7811,91 +6971,57 @@
         </is>
       </c>
       <c r="AB42" s="3" t="n">
-        <v>-16.4</v>
-      </c>
-      <c r="AC42" s="3" t="n">
-        <v>4</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="AC42" s="3" t="inlineStr"/>
       <c r="AD42" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE42" s="3" t="n">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="AF42" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG42" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AH42" s="3" t="n">
-        <v>97.67</v>
-      </c>
-      <c r="AI42" s="3" t="n">
-        <v>97.67</v>
-      </c>
-      <c r="AJ42" s="3" t="n">
-        <v>96.69</v>
-      </c>
-      <c r="AK42" s="3" t="n">
-        <v>98.65000000000001</v>
-      </c>
-      <c r="AL42" s="3" t="n">
-        <v>92.79000000000001</v>
-      </c>
-      <c r="AM42" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AN42" s="3" t="n">
-        <v>105.48</v>
-      </c>
-      <c r="AO42" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AP42" s="3" t="n">
-        <v>112.32</v>
-      </c>
-      <c r="AQ42" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR42" s="3" t="inlineStr"/>
-      <c r="AS42" s="3" t="inlineStr"/>
-      <c r="AT42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV42" s="3" t="n">
-        <v>-1.52</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="AG42" s="3" t="inlineStr"/>
+      <c r="AH42" s="3" t="inlineStr"/>
+      <c r="AI42" s="3" t="inlineStr"/>
+      <c r="AJ42" s="3" t="inlineStr"/>
+      <c r="AK42" s="3" t="inlineStr"/>
+      <c r="AL42" s="3" t="inlineStr"/>
+      <c r="AM42" s="3" t="inlineStr"/>
+      <c r="AN42" s="3" t="inlineStr"/>
+      <c r="AO42" s="3" t="inlineStr"/>
+      <c r="AP42" s="3" t="inlineStr"/>
+      <c r="AQ42" s="3" t="inlineStr"/>
+      <c r="AR42" s="3" t="n">
+        <v>283.4</v>
+      </c>
+      <c r="AS42" s="3" t="n">
+        <v>-2.33</v>
+      </c>
+      <c r="AT42" s="3" t="inlineStr"/>
+      <c r="AU42" s="3" t="inlineStr"/>
+      <c r="AV42" s="3" t="inlineStr"/>
       <c r="AW42" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AX42" s="3" t="inlineStr">
-        <is>
-          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
-        </is>
-      </c>
+      <c r="AX42" s="3" t="inlineStr"/>
       <c r="AY42" s="3" t="inlineStr"/>
       <c r="AZ42" s="3" t="inlineStr"/>
-      <c r="BA42" s="3" t="n">
-        <v>45.62</v>
-      </c>
+      <c r="BA42" s="3" t="inlineStr"/>
       <c r="BB42" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>MCD_USA_20260729</t>
+          <t>IRCTC_IND_20260806</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -7905,91 +7031,63 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>INDIA</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1_ARCH</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>EXIT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>→ TRV · +45.9pp alpha</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="n">
-        <v>0</v>
-      </c>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr"/>
+      <c r="J43" s="3" t="inlineStr"/>
       <c r="K43" s="3" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="M43" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N43" s="3" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="inlineStr">
-        <is>
-          <t>🔴</t>
-        </is>
-      </c>
+      <c r="N43" s="3" t="inlineStr"/>
+      <c r="O43" s="3" t="inlineStr"/>
+      <c r="P43" s="3" t="inlineStr"/>
       <c r="Q43" s="3" t="inlineStr"/>
-      <c r="R43" s="3" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="S43" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="T43" s="3" t="inlineStr">
-        <is>
-          <t>crude +19.8% (rising) → +1.0pts · 6 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="U43" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="V43" s="3" t="n">
-        <v>0.192</v>
-      </c>
+      <c r="R43" s="3" t="inlineStr"/>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr"/>
+      <c r="V43" s="3" t="inlineStr"/>
       <c r="W43" s="3" t="inlineStr"/>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank → 15→15 · Conf 28% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
+          <t>Rank → 7→7 · Conf 67% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr"/>
       <c r="Z43" s="3" t="n">
-        <v>28.3</v>
+        <v>67</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -7997,91 +7095,57 @@
         </is>
       </c>
       <c r="AB43" s="3" t="n">
-        <v>-16.7</v>
-      </c>
-      <c r="AC43" s="3" t="n">
-        <v>4</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="AC43" s="3" t="inlineStr"/>
       <c r="AD43" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE43" s="3" t="n">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="AF43" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG43" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AH43" s="3" t="n">
-        <v>267.71</v>
-      </c>
-      <c r="AI43" s="3" t="n">
-        <v>267.71</v>
-      </c>
-      <c r="AJ43" s="3" t="n">
-        <v>265.03</v>
-      </c>
-      <c r="AK43" s="3" t="n">
-        <v>270.39</v>
-      </c>
-      <c r="AL43" s="3" t="n">
-        <v>254.32</v>
-      </c>
-      <c r="AM43" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AN43" s="3" t="n">
-        <v>289.13</v>
-      </c>
-      <c r="AO43" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AP43" s="3" t="n">
-        <v>307.87</v>
-      </c>
-      <c r="AQ43" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR43" s="3" t="inlineStr"/>
-      <c r="AS43" s="3" t="inlineStr"/>
-      <c r="AT43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU43" s="3" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AV43" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="AG43" s="3" t="inlineStr"/>
+      <c r="AH43" s="3" t="inlineStr"/>
+      <c r="AI43" s="3" t="inlineStr"/>
+      <c r="AJ43" s="3" t="inlineStr"/>
+      <c r="AK43" s="3" t="inlineStr"/>
+      <c r="AL43" s="3" t="inlineStr"/>
+      <c r="AM43" s="3" t="inlineStr"/>
+      <c r="AN43" s="3" t="inlineStr"/>
+      <c r="AO43" s="3" t="inlineStr"/>
+      <c r="AP43" s="3" t="inlineStr"/>
+      <c r="AQ43" s="3" t="inlineStr"/>
+      <c r="AR43" s="3" t="n">
+        <v>510.25</v>
+      </c>
+      <c r="AS43" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AT43" s="3" t="inlineStr"/>
+      <c r="AU43" s="3" t="inlineStr"/>
+      <c r="AV43" s="3" t="inlineStr"/>
       <c r="AW43" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AX43" s="3" t="inlineStr">
-        <is>
-          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
-        </is>
-      </c>
+      <c r="AX43" s="3" t="inlineStr"/>
       <c r="AY43" s="3" t="inlineStr"/>
       <c r="AZ43" s="3" t="inlineStr"/>
-      <c r="BA43" s="3" t="n">
-        <v>45.94</v>
-      </c>
+      <c r="BA43" s="3" t="inlineStr"/>
       <c r="BB43" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>V_USA_20260729</t>
+          <t>BEL_IND_20260806</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -8091,27 +7155,27 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>INDIA</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>R1_NEW</t>
+          <t>R1_ARCH</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Bharat Electronics</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
@@ -8122,52 +7186,32 @@
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
       <c r="K44" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L44" s="3" t="inlineStr"/>
-      <c r="M44" s="3" t="inlineStr"/>
-      <c r="N44" s="3" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t>STRONG</t>
-        </is>
-      </c>
-      <c r="P44" s="3" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="Q44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" s="3" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="S44" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="T44" s="3" t="inlineStr">
-        <is>
-          <t>crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="U44" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="V44" s="3" t="n">
-        <v>0.184</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="M44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3" t="inlineStr"/>
+      <c r="O44" s="3" t="inlineStr"/>
+      <c r="P44" s="3" t="inlineStr"/>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr"/>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr"/>
+      <c r="V44" s="3" t="inlineStr"/>
       <c r="W44" s="3" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #1 · Conf 54% · momentum → · band STRONG · 91d left · → BUY</t>
+          <t>Rank → 8→8 · Conf 64% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="n">
-        <v>53.6</v>
+        <v>64</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -8175,91 +7219,57 @@
         </is>
       </c>
       <c r="AB44" s="3" t="n">
-        <v>64.3</v>
+        <v>53</v>
       </c>
       <c r="AC44" s="3" t="inlineStr"/>
       <c r="AD44" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE44" s="3" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AF44" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="AG44" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AH44" s="3" t="n">
-        <v>358.56</v>
-      </c>
-      <c r="AI44" s="3" t="n">
-        <v>358.56</v>
-      </c>
-      <c r="AJ44" s="3" t="n">
-        <v>351.39</v>
-      </c>
-      <c r="AK44" s="3" t="n">
-        <v>365.73</v>
-      </c>
-      <c r="AL44" s="3" t="n">
-        <v>340.632</v>
-      </c>
-      <c r="AM44" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AN44" s="3" t="n">
-        <v>387.2448000000001</v>
-      </c>
-      <c r="AO44" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AP44" s="3" t="n">
-        <v>414.3519360000001</v>
-      </c>
-      <c r="AQ44" s="3" t="n">
-        <v>15.56</v>
-      </c>
-      <c r="AR44" s="3" t="inlineStr"/>
-      <c r="AS44" s="3" t="inlineStr"/>
-      <c r="AT44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU44" s="3" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AV44" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="AG44" s="3" t="inlineStr"/>
+      <c r="AH44" s="3" t="inlineStr"/>
+      <c r="AI44" s="3" t="inlineStr"/>
+      <c r="AJ44" s="3" t="inlineStr"/>
+      <c r="AK44" s="3" t="inlineStr"/>
+      <c r="AL44" s="3" t="inlineStr"/>
+      <c r="AM44" s="3" t="inlineStr"/>
+      <c r="AN44" s="3" t="inlineStr"/>
+      <c r="AO44" s="3" t="inlineStr"/>
+      <c r="AP44" s="3" t="inlineStr"/>
+      <c r="AQ44" s="3" t="inlineStr"/>
+      <c r="AR44" s="3" t="n">
+        <v>391.5</v>
+      </c>
+      <c r="AS44" s="3" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="AT44" s="3" t="inlineStr"/>
+      <c r="AU44" s="3" t="inlineStr"/>
+      <c r="AV44" s="3" t="inlineStr"/>
       <c r="AW44" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
       <c r="AX44" s="3" t="inlineStr"/>
-      <c r="AY44" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AZ44" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA44" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="AY44" s="3" t="inlineStr"/>
+      <c r="AZ44" s="3" t="inlineStr"/>
+      <c r="BA44" s="3" t="inlineStr"/>
       <c r="BB44" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>TRV_USA_20260729</t>
+          <t>COALINDIA_IND_20260806</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -8269,27 +7279,27 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>INDIA</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>R1_NEW</t>
+          <t>R1_ARCH</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>TRV</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Coal India</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
@@ -8300,50 +7310,32 @@
       <c r="I45" s="3" t="inlineStr"/>
       <c r="J45" s="3" t="inlineStr"/>
       <c r="K45" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L45" s="3" t="inlineStr"/>
-      <c r="M45" s="3" t="inlineStr"/>
-      <c r="N45" s="3" t="n">
-        <v>79.3</v>
-      </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="P45" s="3" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="Q45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" s="3" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="S45" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="T45" s="3" t="inlineStr">
-        <is>
-          <t>crude +19.8% (rising) → +1.0pts · 12 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="U45" s="3" t="n">
-        <v>12</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="M45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3" t="inlineStr"/>
+      <c r="O45" s="3" t="inlineStr"/>
+      <c r="P45" s="3" t="inlineStr"/>
+      <c r="Q45" s="3" t="inlineStr"/>
+      <c r="R45" s="3" t="inlineStr"/>
+      <c r="S45" s="3" t="inlineStr"/>
+      <c r="T45" s="3" t="inlineStr"/>
+      <c r="U45" s="3" t="inlineStr"/>
       <c r="V45" s="3" t="inlineStr"/>
       <c r="W45" s="3" t="inlineStr"/>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #2 · Conf 57% · momentum → · band HOLD · 91d left · → BUY</t>
+          <t>Rank → 10→10 · Conf 66% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr"/>
       <c r="Z45" s="3" t="n">
-        <v>56.8</v>
+        <v>66</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -8351,91 +7343,57 @@
         </is>
       </c>
       <c r="AB45" s="3" t="n">
-        <v>58.8</v>
+        <v>50</v>
       </c>
       <c r="AC45" s="3" t="inlineStr"/>
       <c r="AD45" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE45" s="3" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AF45" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="AG45" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AH45" s="3" t="n">
-        <v>368.98</v>
-      </c>
-      <c r="AI45" s="3" t="n">
-        <v>368.98</v>
-      </c>
-      <c r="AJ45" s="3" t="n">
-        <v>365.29</v>
-      </c>
-      <c r="AK45" s="3" t="n">
-        <v>372.67</v>
-      </c>
-      <c r="AL45" s="3" t="n">
-        <v>350.531</v>
-      </c>
-      <c r="AM45" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AN45" s="3" t="n">
-        <v>413.26</v>
-      </c>
-      <c r="AO45" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AP45" s="3" t="n">
-        <v>442.1882</v>
-      </c>
-      <c r="AQ45" s="3" t="n">
-        <v>19.84</v>
-      </c>
-      <c r="AR45" s="3" t="inlineStr"/>
-      <c r="AS45" s="3" t="inlineStr"/>
-      <c r="AT45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU45" s="3" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AV45" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="AG45" s="3" t="inlineStr"/>
+      <c r="AH45" s="3" t="inlineStr"/>
+      <c r="AI45" s="3" t="inlineStr"/>
+      <c r="AJ45" s="3" t="inlineStr"/>
+      <c r="AK45" s="3" t="inlineStr"/>
+      <c r="AL45" s="3" t="inlineStr"/>
+      <c r="AM45" s="3" t="inlineStr"/>
+      <c r="AN45" s="3" t="inlineStr"/>
+      <c r="AO45" s="3" t="inlineStr"/>
+      <c r="AP45" s="3" t="inlineStr"/>
+      <c r="AQ45" s="3" t="inlineStr"/>
+      <c r="AR45" s="3" t="n">
+        <v>417.6</v>
+      </c>
+      <c r="AS45" s="3" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="AT45" s="3" t="inlineStr"/>
+      <c r="AU45" s="3" t="inlineStr"/>
+      <c r="AV45" s="3" t="inlineStr"/>
       <c r="AW45" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
       <c r="AX45" s="3" t="inlineStr"/>
-      <c r="AY45" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AZ45" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA45" s="3" t="n">
-        <v>12</v>
-      </c>
+      <c r="AY45" s="3" t="inlineStr"/>
+      <c r="AZ45" s="3" t="inlineStr"/>
+      <c r="BA45" s="3" t="inlineStr"/>
       <c r="BB45" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>NVDA_USA_20260729</t>
+          <t>BRITANNIA_IND_20260806</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -8445,27 +7403,23 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>INDIA</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>R1_NEW</t>
+          <t>R1_ARCH</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>NVIDIA</t>
-        </is>
-      </c>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -8476,50 +7430,32 @@
       <c r="I46" s="3" t="inlineStr"/>
       <c r="J46" s="3" t="inlineStr"/>
       <c r="K46" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L46" s="3" t="inlineStr"/>
-      <c r="M46" s="3" t="inlineStr"/>
-      <c r="N46" s="3" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="P46" s="3" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="Q46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" s="3" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="S46" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="T46" s="3" t="inlineStr">
-        <is>
-          <t>crude +19.8% (rising) → +1.0pts · 21 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="U46" s="3" t="n">
-        <v>21</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="3" t="inlineStr"/>
+      <c r="O46" s="3" t="inlineStr"/>
+      <c r="P46" s="3" t="inlineStr"/>
+      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="inlineStr"/>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr"/>
       <c r="V46" s="3" t="inlineStr"/>
       <c r="W46" s="3" t="inlineStr"/>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #3 · Conf 47% · momentum → · band HOLD · 91d left · → BUY</t>
+          <t>Rank → 9→9 · Conf 66% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr"/>
       <c r="Z46" s="3" t="n">
-        <v>47.3</v>
+        <v>66</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
@@ -8527,91 +7463,57 @@
         </is>
       </c>
       <c r="AB46" s="3" t="n">
-        <v>55.7</v>
+        <v>52</v>
       </c>
       <c r="AC46" s="3" t="inlineStr"/>
       <c r="AD46" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE46" s="3" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AF46" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="AG46" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AH46" s="3" t="n">
-        <v>202.81</v>
-      </c>
-      <c r="AI46" s="3" t="n">
-        <v>202.81</v>
-      </c>
-      <c r="AJ46" s="3" t="n">
-        <v>198.75</v>
-      </c>
-      <c r="AK46" s="3" t="n">
-        <v>206.87</v>
-      </c>
-      <c r="AL46" s="3" t="n">
-        <v>192.6695</v>
-      </c>
-      <c r="AM46" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AN46" s="3" t="n">
-        <v>219.0348</v>
-      </c>
-      <c r="AO46" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AP46" s="3" t="n">
-        <v>234.367236</v>
-      </c>
-      <c r="AQ46" s="3" t="n">
-        <v>15.56</v>
-      </c>
-      <c r="AR46" s="3" t="inlineStr"/>
-      <c r="AS46" s="3" t="inlineStr"/>
-      <c r="AT46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV46" s="3" t="n">
-        <v>-1.02</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="AG46" s="3" t="inlineStr"/>
+      <c r="AH46" s="3" t="inlineStr"/>
+      <c r="AI46" s="3" t="inlineStr"/>
+      <c r="AJ46" s="3" t="inlineStr"/>
+      <c r="AK46" s="3" t="inlineStr"/>
+      <c r="AL46" s="3" t="inlineStr"/>
+      <c r="AM46" s="3" t="inlineStr"/>
+      <c r="AN46" s="3" t="inlineStr"/>
+      <c r="AO46" s="3" t="inlineStr"/>
+      <c r="AP46" s="3" t="inlineStr"/>
+      <c r="AQ46" s="3" t="inlineStr"/>
+      <c r="AR46" s="3" t="n">
+        <v>5478</v>
+      </c>
+      <c r="AS46" s="3" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="AT46" s="3" t="inlineStr"/>
+      <c r="AU46" s="3" t="inlineStr"/>
+      <c r="AV46" s="3" t="inlineStr"/>
       <c r="AW46" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
       <c r="AX46" s="3" t="inlineStr"/>
-      <c r="AY46" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AZ46" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA46" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="AY46" s="3" t="inlineStr"/>
+      <c r="AZ46" s="3" t="inlineStr"/>
+      <c r="BA46" s="3" t="inlineStr"/>
       <c r="BB46" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>MSFT_USA_20260730</t>
+          <t>TATAPOWER_IND_20260806</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -8621,27 +7523,27 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>INDIA</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>R1_NEW</t>
+          <t>R1_ARCH</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Tata Power</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
@@ -8652,52 +7554,32 @@
       <c r="I47" s="3" t="inlineStr"/>
       <c r="J47" s="3" t="inlineStr"/>
       <c r="K47" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="L47" s="3" t="inlineStr"/>
-      <c r="M47" s="3" t="inlineStr"/>
-      <c r="N47" s="3" t="n">
-        <v>79.5</v>
-      </c>
-      <c r="O47" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="P47" s="3" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="Q47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" s="3" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="S47" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="T47" s="3" t="inlineStr">
-        <is>
-          <t>crude +19.8% (rising) → +1.0pts · 33 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="U47" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="V47" s="3" t="n">
-        <v>0.15</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="L47" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="M47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3" t="inlineStr"/>
+      <c r="O47" s="3" t="inlineStr"/>
+      <c r="P47" s="3" t="inlineStr"/>
+      <c r="Q47" s="3" t="inlineStr"/>
+      <c r="R47" s="3" t="inlineStr"/>
+      <c r="S47" s="3" t="inlineStr"/>
+      <c r="T47" s="3" t="inlineStr"/>
+      <c r="U47" s="3" t="inlineStr"/>
+      <c r="V47" s="3" t="inlineStr"/>
       <c r="W47" s="3" t="inlineStr"/>
       <c r="X47" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #4 · Conf 54% · momentum → · band HOLD · 91d left · → BUY</t>
+          <t>Rank → 6→6 · Conf 64% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y47" s="3" t="inlineStr"/>
       <c r="Z47" s="3" t="n">
-        <v>53.6</v>
+        <v>64</v>
       </c>
       <c r="AA47" s="3" t="inlineStr">
         <is>
@@ -8705,91 +7587,57 @@
         </is>
       </c>
       <c r="AB47" s="3" t="n">
-        <v>51.8</v>
+        <v>54</v>
       </c>
       <c r="AC47" s="3" t="inlineStr"/>
       <c r="AD47" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE47" s="3" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AF47" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="AG47" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="AH47" s="3" t="n">
-        <v>393.82</v>
-      </c>
-      <c r="AI47" s="3" t="n">
-        <v>393.82</v>
-      </c>
-      <c r="AJ47" s="3" t="n">
-        <v>385.94</v>
-      </c>
-      <c r="AK47" s="3" t="n">
-        <v>401.7</v>
-      </c>
-      <c r="AL47" s="3" t="n">
-        <v>374.129</v>
-      </c>
-      <c r="AM47" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AN47" s="3" t="n">
-        <v>425.3256</v>
-      </c>
-      <c r="AO47" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AP47" s="3" t="n">
-        <v>455.098392</v>
-      </c>
-      <c r="AQ47" s="3" t="n">
-        <v>15.56</v>
-      </c>
-      <c r="AR47" s="3" t="inlineStr"/>
-      <c r="AS47" s="3" t="inlineStr"/>
-      <c r="AT47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU47" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AV47" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="AG47" s="3" t="inlineStr"/>
+      <c r="AH47" s="3" t="inlineStr"/>
+      <c r="AI47" s="3" t="inlineStr"/>
+      <c r="AJ47" s="3" t="inlineStr"/>
+      <c r="AK47" s="3" t="inlineStr"/>
+      <c r="AL47" s="3" t="inlineStr"/>
+      <c r="AM47" s="3" t="inlineStr"/>
+      <c r="AN47" s="3" t="inlineStr"/>
+      <c r="AO47" s="3" t="inlineStr"/>
+      <c r="AP47" s="3" t="inlineStr"/>
+      <c r="AQ47" s="3" t="inlineStr"/>
+      <c r="AR47" s="3" t="n">
+        <v>380</v>
+      </c>
+      <c r="AS47" s="3" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="AT47" s="3" t="inlineStr"/>
+      <c r="AU47" s="3" t="inlineStr"/>
+      <c r="AV47" s="3" t="inlineStr"/>
       <c r="AW47" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
       <c r="AX47" s="3" t="inlineStr"/>
-      <c r="AY47" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AZ47" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA47" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="AY47" s="3" t="inlineStr"/>
+      <c r="AZ47" s="3" t="inlineStr"/>
+      <c r="BA47" s="3" t="inlineStr"/>
       <c r="BB47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>KO_USA_20260729</t>
+          <t>TRV_USA_20260729</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -8804,42 +7652,46 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>R1_NEW</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>TRV</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr"/>
       <c r="J48" s="3" t="inlineStr"/>
       <c r="K48" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="L48" s="3" t="inlineStr"/>
-      <c r="M48" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M48" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="N48" s="3" t="n">
-        <v>84.09999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>STRONG</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr">
@@ -8847,35 +7699,31 @@
           <t>🟢</t>
         </is>
       </c>
-      <c r="Q48" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q48" s="3" t="inlineStr"/>
       <c r="R48" s="3" t="n">
-        <v>49.7</v>
+        <v>56.1</v>
       </c>
       <c r="S48" s="3" t="n">
         <v>-0.8</v>
       </c>
       <c r="T48" s="3" t="inlineStr">
         <is>
-          <t>crude +19.8% (rising) → +1.0pts · 11 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+          <t>crude +19.8% (rising) → +1.0pts · 12 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
       <c r="U48" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="V48" s="3" t="n">
-        <v>0.08500000000000001</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="V48" s="3" t="inlineStr"/>
       <c r="W48" s="3" t="inlineStr"/>
       <c r="X48" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #5 · Conf 50% · momentum → · band STRONG · 91d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 1→1 · Conf 57% · band HOLD · 14d left · → BUY</t>
         </is>
       </c>
       <c r="Y48" s="3" t="inlineStr"/>
       <c r="Z48" s="3" t="n">
-        <v>50.5</v>
+        <v>56.8</v>
       </c>
       <c r="AA48" s="3" t="inlineStr">
         <is>
@@ -8883,17 +7731,19 @@
         </is>
       </c>
       <c r="AB48" s="3" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="AC48" s="3" t="inlineStr"/>
+        <v>29.2</v>
+      </c>
+      <c r="AC48" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="AD48" s="3" t="n">
         <v>6</v>
       </c>
       <c r="AE48" s="3" t="n">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="AF48" s="3" t="n">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="AG48" s="3" t="inlineStr">
         <is>
@@ -8901,34 +7751,34 @@
         </is>
       </c>
       <c r="AH48" s="3" t="n">
-        <v>81.56</v>
+        <v>368.98</v>
       </c>
       <c r="AI48" s="3" t="n">
-        <v>81.56</v>
+        <v>368.98</v>
       </c>
       <c r="AJ48" s="3" t="n">
-        <v>79.93000000000001</v>
+        <v>365.29</v>
       </c>
       <c r="AK48" s="3" t="n">
-        <v>83.19</v>
+        <v>372.67</v>
       </c>
       <c r="AL48" s="3" t="n">
-        <v>77.482</v>
+        <v>346.84</v>
       </c>
       <c r="AM48" s="3" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="AN48" s="3" t="n">
-        <v>88.0848</v>
+        <v>413.26</v>
       </c>
       <c r="AO48" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AP48" s="3" t="n">
-        <v>94.250736</v>
+        <v>457.54</v>
       </c>
       <c r="AQ48" s="3" t="n">
-        <v>15.56</v>
+        <v>24</v>
       </c>
       <c r="AR48" s="3" t="inlineStr"/>
       <c r="AS48" s="3" t="inlineStr"/>
@@ -8936,7 +7786,7 @@
         <v>0</v>
       </c>
       <c r="AU48" s="3" t="n">
-        <v>7.39</v>
+        <v>1.46</v>
       </c>
       <c r="AV48" s="3" t="n">
         <v>0</v>
@@ -8946,28 +7796,28 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AX48" s="3" t="inlineStr"/>
-      <c r="AY48" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="AX48" s="3" t="inlineStr">
+        <is>
+          <t>Momentum · Value · Trend</t>
+        </is>
+      </c>
+      <c r="AY48" s="3" t="inlineStr"/>
       <c r="AZ48" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BA48" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BB48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>HON_USA_20260729</t>
+          <t>V_USA_20260729</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -8982,17 +7832,17 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>R1_NEW</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>V</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -9002,22 +7852,26 @@
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr"/>
       <c r="J49" s="3" t="inlineStr"/>
       <c r="K49" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="L49" s="3" t="inlineStr"/>
-      <c r="M49" s="3" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L49" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M49" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="N49" s="3" t="n">
-        <v>76</v>
+        <v>86.5</v>
       </c>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>STRONG</t>
         </is>
       </c>
       <c r="P49" s="3" t="inlineStr">
@@ -9025,35 +7879,33 @@
           <t>🟢</t>
         </is>
       </c>
-      <c r="Q49" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q49" s="3" t="inlineStr"/>
       <c r="R49" s="3" t="n">
-        <v>49.7</v>
+        <v>52.9</v>
       </c>
       <c r="S49" s="3" t="n">
         <v>-0.8</v>
       </c>
       <c r="T49" s="3" t="inlineStr">
         <is>
-          <t>crude +19.8% (rising) → +1.0pts · 48 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+          <t>crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
       <c r="U49" s="3" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>0.127</v>
+        <v>0.184</v>
       </c>
       <c r="W49" s="3" t="inlineStr"/>
       <c r="X49" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #6 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 2→2 · Conf 54% · band STRONG · 14d left · → HOLD</t>
         </is>
       </c>
       <c r="Y49" s="3" t="inlineStr"/>
       <c r="Z49" s="3" t="n">
-        <v>50.5</v>
+        <v>53.6</v>
       </c>
       <c r="AA49" s="3" t="inlineStr">
         <is>
@@ -9061,17 +7913,19 @@
         </is>
       </c>
       <c r="AB49" s="3" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="AC49" s="3" t="inlineStr"/>
+        <v>27.8</v>
+      </c>
+      <c r="AC49" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="AD49" s="3" t="n">
         <v>6</v>
       </c>
       <c r="AE49" s="3" t="n">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="AF49" s="3" t="n">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="AG49" s="3" t="inlineStr">
         <is>
@@ -9079,34 +7933,34 @@
         </is>
       </c>
       <c r="AH49" s="3" t="n">
-        <v>225.02</v>
+        <v>358.56</v>
       </c>
       <c r="AI49" s="3" t="n">
-        <v>225.02</v>
+        <v>358.56</v>
       </c>
       <c r="AJ49" s="3" t="n">
-        <v>220.52</v>
+        <v>354.97</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>229.52</v>
+        <v>362.15</v>
       </c>
       <c r="AL49" s="3" t="n">
-        <v>213.769</v>
+        <v>340.63</v>
       </c>
       <c r="AM49" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AN49" s="3" t="n">
-        <v>243.0216</v>
+        <v>387.24</v>
       </c>
       <c r="AO49" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AP49" s="3" t="n">
-        <v>260.0331120000001</v>
+        <v>412.34</v>
       </c>
       <c r="AQ49" s="3" t="n">
-        <v>15.56</v>
+        <v>15</v>
       </c>
       <c r="AR49" s="3" t="inlineStr"/>
       <c r="AS49" s="3" t="inlineStr"/>
@@ -9114,7 +7968,7 @@
         <v>0</v>
       </c>
       <c r="AU49" s="3" t="n">
-        <v>8.01</v>
+        <v>2.11</v>
       </c>
       <c r="AV49" s="3" t="n">
         <v>0</v>
@@ -9124,28 +7978,26 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AX49" s="3" t="inlineStr"/>
-      <c r="AY49" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AZ49" s="3" t="n">
-        <v>5</v>
-      </c>
+      <c r="AX49" s="3" t="inlineStr">
+        <is>
+          <t>Momentum · Trend · Quality</t>
+        </is>
+      </c>
+      <c r="AY49" s="3" t="inlineStr"/>
+      <c r="AZ49" s="3" t="inlineStr"/>
       <c r="BA49" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BB49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>AAPL_USA_20260729</t>
+          <t>NVDA_USA_20260729</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -9160,78 +8012,84 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>R1_NEW</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>→ TRV · +12.2pp alpha</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="I50" s="3" t="inlineStr"/>
-      <c r="J50" s="3" t="inlineStr"/>
-      <c r="K50" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="L50" s="3" t="inlineStr"/>
-      <c r="M50" s="3" t="inlineStr"/>
-      <c r="N50" s="3" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="O50" s="3" t="inlineStr">
-        <is>
-          <t>STRONG</t>
-        </is>
-      </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
           <t>🟢</t>
         </is>
       </c>
-      <c r="Q50" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q50" s="3" t="inlineStr"/>
       <c r="R50" s="3" t="n">
-        <v>49.7</v>
+        <v>46.6</v>
       </c>
       <c r="S50" s="3" t="n">
         <v>-0.8</v>
       </c>
       <c r="T50" s="3" t="inlineStr">
         <is>
-          <t>crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+          <t>crude +19.8% (rising) → +1.0pts · 21 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
       <c r="U50" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="V50" s="3" t="n">
-        <v>0.109</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="V50" s="3" t="inlineStr"/>
       <c r="W50" s="3" t="inlineStr"/>
       <c r="X50" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #7 · Conf 50% · momentum → · band STRONG · 91d left · → HOLD</t>
+          <t>🔴 AVOID · Rank → 3→3 · Conf 47% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="Y50" s="3" t="inlineStr"/>
       <c r="Z50" s="3" t="n">
-        <v>50.5</v>
+        <v>47.3</v>
       </c>
       <c r="AA50" s="3" t="inlineStr">
         <is>
@@ -9239,17 +8097,19 @@
         </is>
       </c>
       <c r="AB50" s="3" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="AC50" s="3" t="inlineStr"/>
+        <v>17.1</v>
+      </c>
+      <c r="AC50" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="AD50" s="3" t="n">
         <v>6</v>
       </c>
       <c r="AE50" s="3" t="n">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="AF50" s="3" t="n">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="AG50" s="3" t="inlineStr">
         <is>
@@ -9257,34 +8117,34 @@
         </is>
       </c>
       <c r="AH50" s="3" t="n">
-        <v>333.74</v>
+        <v>202.81</v>
       </c>
       <c r="AI50" s="3" t="n">
-        <v>333.74</v>
+        <v>202.81</v>
       </c>
       <c r="AJ50" s="3" t="n">
-        <v>327.07</v>
+        <v>200.78</v>
       </c>
       <c r="AK50" s="3" t="n">
-        <v>340.41</v>
+        <v>204.84</v>
       </c>
       <c r="AL50" s="3" t="n">
-        <v>317.053</v>
+        <v>192.67</v>
       </c>
       <c r="AM50" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AN50" s="3" t="n">
-        <v>360.4392</v>
+        <v>219.03</v>
       </c>
       <c r="AO50" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AP50" s="3" t="n">
-        <v>385.669944</v>
+        <v>233.23</v>
       </c>
       <c r="AQ50" s="3" t="n">
-        <v>15.56</v>
+        <v>15</v>
       </c>
       <c r="AR50" s="3" t="inlineStr"/>
       <c r="AS50" s="3" t="inlineStr"/>
@@ -9295,28 +8155,26 @@
         <v>0</v>
       </c>
       <c r="AV50" s="3" t="n">
-        <v>-7.44</v>
+        <v>-1.02</v>
       </c>
       <c r="AW50" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AX50" s="3" t="inlineStr"/>
-      <c r="AY50" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AZ50" s="3" t="n">
-        <v>5</v>
-      </c>
+      <c r="AX50" s="3" t="inlineStr">
+        <is>
+          <t>Quality · Growth · Mean Reversion</t>
+        </is>
+      </c>
+      <c r="AY50" s="3" t="inlineStr"/>
+      <c r="AZ50" s="3" t="inlineStr"/>
       <c r="BA50" s="3" t="n">
-        <v>8</v>
+        <v>12.15</v>
       </c>
       <c r="BB50" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -9338,7 +8196,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>R1_NEW</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -9353,21 +8211,31 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>EXIT</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="I51" s="3" t="inlineStr"/>
-      <c r="J51" s="3" t="inlineStr"/>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>→ TRV · +13.0pp alpha</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="K51" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L51" s="3" t="inlineStr"/>
-      <c r="M51" s="3" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="L51" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="M51" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="N51" s="3" t="n">
         <v>78.40000000000001</v>
       </c>
@@ -9381,9 +8249,7 @@
           <t>🟢</t>
         </is>
       </c>
-      <c r="Q51" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q51" s="3" t="inlineStr"/>
       <c r="R51" s="3" t="n">
         <v>48.9</v>
       </c>
@@ -9402,7 +8268,7 @@
       <c r="W51" s="3" t="inlineStr"/>
       <c r="X51" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #8 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
+          <t>🔴 AVOID · Rank → 4→4 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="Y51" s="3" t="inlineStr"/>
@@ -9415,17 +8281,19 @@
         </is>
       </c>
       <c r="AB51" s="3" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="AC51" s="3" t="inlineStr"/>
+        <v>16.3</v>
+      </c>
+      <c r="AC51" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="AD51" s="3" t="n">
         <v>6</v>
       </c>
       <c r="AE51" s="3" t="n">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="AF51" s="3" t="n">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="AG51" s="3" t="inlineStr">
         <is>
@@ -9439,28 +8307,28 @@
         <v>341.1</v>
       </c>
       <c r="AJ51" s="3" t="n">
-        <v>334.28</v>
+        <v>337.69</v>
       </c>
       <c r="AK51" s="3" t="n">
-        <v>347.92</v>
+        <v>344.51</v>
       </c>
       <c r="AL51" s="3" t="n">
-        <v>324.045</v>
+        <v>324.05</v>
       </c>
       <c r="AM51" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AN51" s="3" t="n">
-        <v>368.388</v>
+        <v>368.39</v>
       </c>
       <c r="AO51" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AP51" s="3" t="n">
-        <v>394.1751600000001</v>
+        <v>392.26</v>
       </c>
       <c r="AQ51" s="3" t="n">
-        <v>15.56</v>
+        <v>15</v>
       </c>
       <c r="AR51" s="3" t="inlineStr"/>
       <c r="AS51" s="3" t="inlineStr"/>
@@ -9478,28 +8346,26 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AX51" s="3" t="inlineStr"/>
-      <c r="AY51" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AZ51" s="3" t="n">
-        <v>5</v>
-      </c>
+      <c r="AX51" s="3" t="inlineStr">
+        <is>
+          <t>Momentum · Value · Mean Reversion</t>
+        </is>
+      </c>
+      <c r="AY51" s="3" t="inlineStr"/>
+      <c r="AZ51" s="3" t="inlineStr"/>
       <c r="BA51" s="3" t="n">
-        <v>8</v>
+        <v>12.97</v>
       </c>
       <c r="BB51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GS_USA_20260729</t>
+          <t>HON_USA_20260729</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -9514,76 +8380,86 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>R1_NEW</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>→ TRV · +14.4pp alpha</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L52" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="I52" s="3" t="inlineStr"/>
-      <c r="J52" s="3" t="inlineStr"/>
-      <c r="K52" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="L52" s="3" t="inlineStr"/>
-      <c r="M52" s="3" t="inlineStr"/>
-      <c r="N52" s="3" t="n">
-        <v>66.3</v>
-      </c>
-      <c r="O52" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
           <t>🟢</t>
         </is>
       </c>
-      <c r="Q52" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q52" s="3" t="inlineStr"/>
       <c r="R52" s="3" t="n">
-        <v>50.2</v>
+        <v>49.7</v>
       </c>
       <c r="S52" s="3" t="n">
         <v>-0.8</v>
       </c>
       <c r="T52" s="3" t="inlineStr">
         <is>
-          <t>crude +19.8% (rising) → +1.0pts · 9 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+          <t>crude +19.8% (rising) → +1.0pts · 48 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
       <c r="U52" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="V52" s="3" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="V52" s="3" t="n">
+        <v>0.127</v>
+      </c>
       <c r="W52" s="3" t="inlineStr"/>
       <c r="X52" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #9 · Conf 51% · momentum → · band HOLD · 91d left · → HOLD</t>
+          <t>🔴 AVOID · Rank → 5→5 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="Y52" s="3" t="inlineStr"/>
       <c r="Z52" s="3" t="n">
-        <v>51</v>
+        <v>50.5</v>
       </c>
       <c r="AA52" s="3" t="inlineStr">
         <is>
@@ -9591,17 +8467,19 @@
         </is>
       </c>
       <c r="AB52" s="3" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="AC52" s="3" t="inlineStr"/>
+        <v>14.8</v>
+      </c>
+      <c r="AC52" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="AD52" s="3" t="n">
         <v>6</v>
       </c>
       <c r="AE52" s="3" t="n">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="AF52" s="3" t="n">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="AG52" s="3" t="inlineStr">
         <is>
@@ -9609,34 +8487,34 @@
         </is>
       </c>
       <c r="AH52" s="3" t="n">
-        <v>1065.22</v>
+        <v>225.02</v>
       </c>
       <c r="AI52" s="3" t="n">
-        <v>1065.22</v>
+        <v>225.02</v>
       </c>
       <c r="AJ52" s="3" t="n">
-        <v>1043.92</v>
+        <v>222.77</v>
       </c>
       <c r="AK52" s="3" t="n">
-        <v>1086.52</v>
+        <v>227.27</v>
       </c>
       <c r="AL52" s="3" t="n">
-        <v>1011.959</v>
+        <v>213.77</v>
       </c>
       <c r="AM52" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AN52" s="3" t="n">
-        <v>1150.4376</v>
+        <v>243.02</v>
       </c>
       <c r="AO52" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AP52" s="3" t="n">
-        <v>1230.968232</v>
+        <v>258.77</v>
       </c>
       <c r="AQ52" s="3" t="n">
-        <v>15.56</v>
+        <v>15</v>
       </c>
       <c r="AR52" s="3" t="inlineStr"/>
       <c r="AS52" s="3" t="inlineStr"/>
@@ -9644,38 +8522,36 @@
         <v>0</v>
       </c>
       <c r="AU52" s="3" t="n">
-        <v>0</v>
+        <v>8.01</v>
       </c>
       <c r="AV52" s="3" t="n">
-        <v>-4.4</v>
+        <v>0</v>
       </c>
       <c r="AW52" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AX52" s="3" t="inlineStr"/>
-      <c r="AY52" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AZ52" s="3" t="n">
-        <v>5</v>
-      </c>
+      <c r="AX52" s="3" t="inlineStr">
+        <is>
+          <t>Mean Reversion · Growth · Value</t>
+        </is>
+      </c>
+      <c r="AY52" s="3" t="inlineStr"/>
+      <c r="AZ52" s="3" t="inlineStr"/>
       <c r="BA52" s="3" t="n">
-        <v>8</v>
+        <v>14.45</v>
       </c>
       <c r="BB52" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>MMM_USA_20260730</t>
+          <t>GS_USA_20260729</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -9690,76 +8566,84 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>R1_NEW</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>3M</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>→ TRV · +14.8pp alpha</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L53" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="M53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="I53" s="3" t="inlineStr"/>
-      <c r="J53" s="3" t="inlineStr"/>
-      <c r="K53" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L53" s="3" t="inlineStr"/>
-      <c r="M53" s="3" t="inlineStr"/>
-      <c r="N53" s="3" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="O53" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
           <t>🟢</t>
         </is>
       </c>
-      <c r="Q53" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q53" s="3" t="inlineStr"/>
       <c r="R53" s="3" t="n">
-        <v>52.9</v>
+        <v>50.2</v>
       </c>
       <c r="S53" s="3" t="n">
         <v>-0.8</v>
       </c>
       <c r="T53" s="3" t="inlineStr">
         <is>
-          <t>crude +19.8% (rising) → +1.0pts · 15 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+          <t>crude +19.8% (rising) → +1.0pts · 9 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
       <c r="U53" s="3" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="V53" s="3" t="inlineStr"/>
       <c r="W53" s="3" t="inlineStr"/>
       <c r="X53" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #10 · Conf 54% · momentum → · band HOLD · 91d left · → HOLD</t>
+          <t>🔴 AVOID · Rank → 6→6 · Conf 51% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="Y53" s="3" t="inlineStr"/>
       <c r="Z53" s="3" t="n">
-        <v>53.6</v>
+        <v>51</v>
       </c>
       <c r="AA53" s="3" t="inlineStr">
         <is>
@@ -9767,52 +8651,54 @@
         </is>
       </c>
       <c r="AB53" s="3" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="AC53" s="3" t="inlineStr"/>
+        <v>14.5</v>
+      </c>
+      <c r="AC53" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="AD53" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE53" s="3" t="n">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="AF53" s="3" t="n">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="AG53" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH53" s="3" t="n">
-        <v>159.84</v>
+        <v>1065.22</v>
       </c>
       <c r="AI53" s="3" t="n">
-        <v>159.84</v>
+        <v>1065.22</v>
       </c>
       <c r="AJ53" s="3" t="n">
-        <v>156.64</v>
+        <v>1054.57</v>
       </c>
       <c r="AK53" s="3" t="n">
-        <v>163.04</v>
+        <v>1075.87</v>
       </c>
       <c r="AL53" s="3" t="n">
-        <v>151.848</v>
+        <v>1011.96</v>
       </c>
       <c r="AM53" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AN53" s="3" t="n">
-        <v>172.6272</v>
+        <v>1150.44</v>
       </c>
       <c r="AO53" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AP53" s="3" t="n">
-        <v>184.711104</v>
+        <v>1225</v>
       </c>
       <c r="AQ53" s="3" t="n">
-        <v>15.56</v>
+        <v>15</v>
       </c>
       <c r="AR53" s="3" t="inlineStr"/>
       <c r="AS53" s="3" t="inlineStr"/>
@@ -9820,36 +8706,3474 @@
         <v>0</v>
       </c>
       <c r="AU53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV53" s="3" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="AW53" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AX53" s="3" t="inlineStr">
+        <is>
+          <t>Value · News · Event Driven</t>
+        </is>
+      </c>
+      <c r="AY53" s="3" t="inlineStr"/>
+      <c r="AZ53" s="3" t="inlineStr"/>
+      <c r="BA53" s="3" t="n">
+        <v>14.77</v>
+      </c>
+      <c r="BB53" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>AAPL_USA_20260729</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>→ TRV · +14.9pp alpha</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="L54" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="M54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="3" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
+          <t>STRONG</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q54" s="3" t="inlineStr"/>
+      <c r="R54" s="3" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="S54" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="T54" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="U54" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="V54" s="3" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="W54" s="3" t="inlineStr"/>
+      <c r="X54" s="3" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 7→7 · Conf 50% · band STRONG · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="Y54" s="3" t="inlineStr"/>
+      <c r="Z54" s="3" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="AA54" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="AB54" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="AC54" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD54" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE54" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF54" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG54" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AH54" s="3" t="n">
+        <v>333.74</v>
+      </c>
+      <c r="AI54" s="3" t="n">
+        <v>333.74</v>
+      </c>
+      <c r="AJ54" s="3" t="n">
+        <v>330.4</v>
+      </c>
+      <c r="AK54" s="3" t="n">
+        <v>337.08</v>
+      </c>
+      <c r="AL54" s="3" t="n">
+        <v>317.05</v>
+      </c>
+      <c r="AM54" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AN54" s="3" t="n">
+        <v>360.44</v>
+      </c>
+      <c r="AO54" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP54" s="3" t="n">
+        <v>383.8</v>
+      </c>
+      <c r="AQ54" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR54" s="3" t="inlineStr"/>
+      <c r="AS54" s="3" t="inlineStr"/>
+      <c r="AT54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV54" s="3" t="n">
+        <v>-7.44</v>
+      </c>
+      <c r="AW54" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AX54" s="3" t="inlineStr">
+        <is>
+          <t>Value · Trend · Momentum</t>
+        </is>
+      </c>
+      <c r="AY54" s="3" t="inlineStr"/>
+      <c r="AZ54" s="3" t="inlineStr"/>
+      <c r="BA54" s="3" t="n">
+        <v>14.87</v>
+      </c>
+      <c r="BB54" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>MSFT_USA_20260730</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>→ TRV · +15.2pp alpha</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L55" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="M55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="3" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q55" s="3" t="inlineStr"/>
+      <c r="R55" s="3" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="S55" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="T55" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 33 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="U55" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="V55" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="W55" s="3" t="inlineStr"/>
+      <c r="X55" s="3" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 8→8 · Conf 54% · band HOLD · 58d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="Y55" s="3" t="inlineStr"/>
+      <c r="Z55" s="3" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="AA55" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="AB55" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC55" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD55" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE55" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF55" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="AG55" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AH55" s="3" t="n">
+        <v>393.82</v>
+      </c>
+      <c r="AI55" s="3" t="n">
+        <v>393.82</v>
+      </c>
+      <c r="AJ55" s="3" t="n">
+        <v>389.88</v>
+      </c>
+      <c r="AK55" s="3" t="n">
+        <v>397.76</v>
+      </c>
+      <c r="AL55" s="3" t="n">
+        <v>374.13</v>
+      </c>
+      <c r="AM55" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AN55" s="3" t="n">
+        <v>425.33</v>
+      </c>
+      <c r="AO55" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP55" s="3" t="n">
+        <v>452.89</v>
+      </c>
+      <c r="AQ55" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR55" s="3" t="inlineStr"/>
+      <c r="AS55" s="3" t="inlineStr"/>
+      <c r="AT55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU55" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AV55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW55" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AX55" s="3" t="inlineStr">
+        <is>
+          <t>Quality · Mean Reversion · Trend</t>
+        </is>
+      </c>
+      <c r="AY55" s="3" t="inlineStr"/>
+      <c r="AZ55" s="3" t="inlineStr"/>
+      <c r="BA55" s="3" t="n">
+        <v>15.21</v>
+      </c>
+      <c r="BB55" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>KO_USA_20260729</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Coca-Cola</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>→ TRV · +15.5pp alpha</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L56" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="M56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="3" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="O56" s="3" t="inlineStr">
+        <is>
+          <t>STRONG</t>
+        </is>
+      </c>
+      <c r="P56" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q56" s="3" t="inlineStr"/>
+      <c r="R56" s="3" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="S56" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="T56" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 11 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="U56" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="V56" s="3" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="W56" s="3" t="inlineStr"/>
+      <c r="X56" s="3" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 9→9 · Conf 50% · band STRONG · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="Y56" s="3" t="inlineStr"/>
+      <c r="Z56" s="3" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="AA56" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="AB56" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="AC56" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD56" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE56" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF56" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG56" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AH56" s="3" t="n">
+        <v>81.56</v>
+      </c>
+      <c r="AI56" s="3" t="n">
+        <v>81.56</v>
+      </c>
+      <c r="AJ56" s="3" t="n">
+        <v>80.73999999999999</v>
+      </c>
+      <c r="AK56" s="3" t="n">
+        <v>82.38</v>
+      </c>
+      <c r="AL56" s="3" t="n">
+        <v>77.48</v>
+      </c>
+      <c r="AM56" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AN56" s="3" t="n">
+        <v>88.08</v>
+      </c>
+      <c r="AO56" s="3" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="AP56" s="3" t="n">
+        <v>93.79000000000001</v>
+      </c>
+      <c r="AQ56" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR56" s="3" t="inlineStr"/>
+      <c r="AS56" s="3" t="inlineStr"/>
+      <c r="AT56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU56" s="3" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="AV56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW56" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AX56" s="3" t="inlineStr">
+        <is>
+          <t>Momentum · News · Quality</t>
+        </is>
+      </c>
+      <c r="AY56" s="3" t="inlineStr"/>
+      <c r="AZ56" s="3" t="inlineStr"/>
+      <c r="BA56" s="3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BB56" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>MMM_USA_20260730</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>MMM</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>→ TRV · +16.4pp alpha</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L57" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="M57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="3" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="O57" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="P57" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q57" s="3" t="inlineStr"/>
+      <c r="R57" s="3" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="S57" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="T57" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 15 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="U57" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="V57" s="3" t="inlineStr"/>
+      <c r="W57" s="3" t="inlineStr"/>
+      <c r="X57" s="3" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 10→10 · Conf 54% · band HOLD · 58d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="Y57" s="3" t="inlineStr"/>
+      <c r="Z57" s="3" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="AA57" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="AB57" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="AC57" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD57" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE57" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF57" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="AG57" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AH57" s="3" t="n">
+        <v>159.84</v>
+      </c>
+      <c r="AI57" s="3" t="n">
+        <v>159.84</v>
+      </c>
+      <c r="AJ57" s="3" t="n">
+        <v>158.24</v>
+      </c>
+      <c r="AK57" s="3" t="n">
+        <v>161.44</v>
+      </c>
+      <c r="AL57" s="3" t="n">
+        <v>151.85</v>
+      </c>
+      <c r="AM57" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AN57" s="3" t="n">
+        <v>172.63</v>
+      </c>
+      <c r="AO57" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP57" s="3" t="n">
+        <v>183.82</v>
+      </c>
+      <c r="AQ57" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR57" s="3" t="inlineStr"/>
+      <c r="AS57" s="3" t="inlineStr"/>
+      <c r="AT57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU57" s="3" t="n">
         <v>10.29</v>
       </c>
-      <c r="AV53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW53" s="3" t="inlineStr">
+      <c r="AV57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW57" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AX53" s="3" t="inlineStr"/>
-      <c r="AY53" s="3" t="inlineStr">
+      <c r="AX57" s="3" t="inlineStr">
+        <is>
+          <t>Momentum · News · Value</t>
+        </is>
+      </c>
+      <c r="AY57" s="3" t="inlineStr"/>
+      <c r="AZ57" s="3" t="inlineStr"/>
+      <c r="BA57" s="3" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="BB57" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>INTC_USA_20260729</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>→ TRV · +37.2pp alpha</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="L58" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="M58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="O58" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="Q58" s="3" t="inlineStr"/>
+      <c r="R58" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="S58" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="T58" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 26 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="U58" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="V58" s="3" t="inlineStr"/>
+      <c r="W58" s="3" t="inlineStr"/>
+      <c r="X58" s="3" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 11→11 · Conf 29% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="Y58" s="3" t="inlineStr"/>
+      <c r="Z58" s="3" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="AA58" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="AB58" s="3" t="n">
+        <v>-7.9</v>
+      </c>
+      <c r="AC58" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD58" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE58" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF58" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG58" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AH58" s="3" t="n">
+        <v>95.04000000000001</v>
+      </c>
+      <c r="AI58" s="3" t="n">
+        <v>95.04000000000001</v>
+      </c>
+      <c r="AJ58" s="3" t="n">
+        <v>94.09</v>
+      </c>
+      <c r="AK58" s="3" t="n">
+        <v>95.98999999999999</v>
+      </c>
+      <c r="AL58" s="3" t="n">
+        <v>90.29000000000001</v>
+      </c>
+      <c r="AM58" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AN58" s="3" t="n">
+        <v>102.64</v>
+      </c>
+      <c r="AO58" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP58" s="3" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="AQ58" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR58" s="3" t="inlineStr"/>
+      <c r="AS58" s="3" t="inlineStr"/>
+      <c r="AT58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV58" s="3" t="n">
+        <v>-5.09</v>
+      </c>
+      <c r="AW58" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AX58" s="3" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
+        </is>
+      </c>
+      <c r="AY58" s="3" t="inlineStr"/>
+      <c r="AZ58" s="3" t="inlineStr"/>
+      <c r="BA58" s="3" t="n">
+        <v>37.17</v>
+      </c>
+      <c r="BB58" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>BA_USA_20260730</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Boeing</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>→ TRV · +37.8pp alpha</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="L59" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="M59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" s="3" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="O59" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="Q59" s="3" t="inlineStr"/>
+      <c r="R59" s="3" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="S59" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="T59" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 12 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="U59" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="V59" s="3" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="W59" s="3" t="inlineStr"/>
+      <c r="X59" s="3" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 12→12 · Conf 31% · band EXIT · 58d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="Y59" s="3" t="inlineStr"/>
+      <c r="Z59" s="3" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="AA59" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="AB59" s="3" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="AC59" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD59" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE59" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF59" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="AG59" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AH59" s="3" t="n">
+        <v>214.03</v>
+      </c>
+      <c r="AI59" s="3" t="n">
+        <v>214.03</v>
+      </c>
+      <c r="AJ59" s="3" t="n">
+        <v>211.89</v>
+      </c>
+      <c r="AK59" s="3" t="n">
+        <v>216.17</v>
+      </c>
+      <c r="AL59" s="3" t="n">
+        <v>203.33</v>
+      </c>
+      <c r="AM59" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AN59" s="3" t="n">
+        <v>231.15</v>
+      </c>
+      <c r="AO59" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP59" s="3" t="n">
+        <v>246.13</v>
+      </c>
+      <c r="AQ59" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR59" s="3" t="inlineStr"/>
+      <c r="AS59" s="3" t="inlineStr"/>
+      <c r="AT59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU59" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AV59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW59" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AX59" s="3" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
+        </is>
+      </c>
+      <c r="AY59" s="3" t="inlineStr"/>
+      <c r="AZ59" s="3" t="inlineStr"/>
+      <c r="BA59" s="3" t="n">
+        <v>37.79</v>
+      </c>
+      <c r="BB59" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>HD_USA_20260729</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Home Depot</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>→ TRV · +43.9pp alpha</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="L60" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="M60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="3" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="O60" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="P60" s="3" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="Q60" s="3" t="inlineStr"/>
+      <c r="R60" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="S60" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="T60" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 13 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="U60" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="V60" s="3" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="W60" s="3" t="inlineStr"/>
+      <c r="X60" s="3" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 13→13 · Conf 35% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="Y60" s="3" t="inlineStr"/>
+      <c r="Z60" s="3" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="AA60" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="AB60" s="3" t="n">
+        <v>-14.6</v>
+      </c>
+      <c r="AC60" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD60" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE60" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF60" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG60" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AH60" s="3" t="n">
+        <v>338.87</v>
+      </c>
+      <c r="AI60" s="3" t="n">
+        <v>338.87</v>
+      </c>
+      <c r="AJ60" s="3" t="n">
+        <v>335.48</v>
+      </c>
+      <c r="AK60" s="3" t="n">
+        <v>342.26</v>
+      </c>
+      <c r="AL60" s="3" t="n">
+        <v>321.93</v>
+      </c>
+      <c r="AM60" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AN60" s="3" t="n">
+        <v>365.98</v>
+      </c>
+      <c r="AO60" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP60" s="3" t="n">
+        <v>389.7</v>
+      </c>
+      <c r="AQ60" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR60" s="3" t="inlineStr"/>
+      <c r="AS60" s="3" t="inlineStr"/>
+      <c r="AT60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV60" s="3" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="AW60" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AX60" s="3" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
+        </is>
+      </c>
+      <c r="AY60" s="3" t="inlineStr"/>
+      <c r="AZ60" s="3" t="inlineStr"/>
+      <c r="BA60" s="3" t="n">
+        <v>43.85</v>
+      </c>
+      <c r="BB60" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>DIS_USA_20260729</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Walt Disney</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>→ TRV · +45.6pp alpha</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="L61" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="M61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="O61" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="P61" s="3" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="Q61" s="3" t="inlineStr"/>
+      <c r="R61" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="S61" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="T61" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 19 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="U61" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="V61" s="3" t="n">
+        <v>0.193</v>
+      </c>
+      <c r="W61" s="3" t="inlineStr"/>
+      <c r="X61" s="3" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 14→14 · Conf 35% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="Y61" s="3" t="inlineStr"/>
+      <c r="Z61" s="3" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="AA61" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="AB61" s="3" t="n">
+        <v>-16.4</v>
+      </c>
+      <c r="AC61" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD61" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE61" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF61" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG61" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AH61" s="3" t="n">
+        <v>97.67</v>
+      </c>
+      <c r="AI61" s="3" t="n">
+        <v>97.67</v>
+      </c>
+      <c r="AJ61" s="3" t="n">
+        <v>96.69</v>
+      </c>
+      <c r="AK61" s="3" t="n">
+        <v>98.65000000000001</v>
+      </c>
+      <c r="AL61" s="3" t="n">
+        <v>92.79000000000001</v>
+      </c>
+      <c r="AM61" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AN61" s="3" t="n">
+        <v>105.48</v>
+      </c>
+      <c r="AO61" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP61" s="3" t="n">
+        <v>112.32</v>
+      </c>
+      <c r="AQ61" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR61" s="3" t="inlineStr"/>
+      <c r="AS61" s="3" t="inlineStr"/>
+      <c r="AT61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV61" s="3" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="AW61" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AX61" s="3" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
+        </is>
+      </c>
+      <c r="AY61" s="3" t="inlineStr"/>
+      <c r="AZ61" s="3" t="inlineStr"/>
+      <c r="BA61" s="3" t="n">
+        <v>45.62</v>
+      </c>
+      <c r="BB61" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>MCD_USA_20260729</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>MCD</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>McDonald's</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>→ TRV · +45.9pp alpha</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="L62" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="M62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" s="3" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="O62" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="P62" s="3" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="Q62" s="3" t="inlineStr"/>
+      <c r="R62" s="3" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="S62" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="T62" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 6 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="U62" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="V62" s="3" t="n">
+        <v>0.192</v>
+      </c>
+      <c r="W62" s="3" t="inlineStr"/>
+      <c r="X62" s="3" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 15→15 · Conf 28% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="Y62" s="3" t="inlineStr"/>
+      <c r="Z62" s="3" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="AA62" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="AB62" s="3" t="n">
+        <v>-16.7</v>
+      </c>
+      <c r="AC62" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD62" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE62" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF62" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG62" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AH62" s="3" t="n">
+        <v>267.71</v>
+      </c>
+      <c r="AI62" s="3" t="n">
+        <v>267.71</v>
+      </c>
+      <c r="AJ62" s="3" t="n">
+        <v>265.03</v>
+      </c>
+      <c r="AK62" s="3" t="n">
+        <v>270.39</v>
+      </c>
+      <c r="AL62" s="3" t="n">
+        <v>254.32</v>
+      </c>
+      <c r="AM62" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AN62" s="3" t="n">
+        <v>289.13</v>
+      </c>
+      <c r="AO62" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP62" s="3" t="n">
+        <v>307.87</v>
+      </c>
+      <c r="AQ62" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR62" s="3" t="inlineStr"/>
+      <c r="AS62" s="3" t="inlineStr"/>
+      <c r="AT62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU62" s="3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AV62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW62" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AX62" s="3" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
+        </is>
+      </c>
+      <c r="AY62" s="3" t="inlineStr"/>
+      <c r="AZ62" s="3" t="inlineStr"/>
+      <c r="BA62" s="3" t="n">
+        <v>45.94</v>
+      </c>
+      <c r="BB62" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>V_USA_20260729</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>R1_NEW</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr"/>
+      <c r="J63" s="3" t="inlineStr"/>
+      <c r="K63" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L63" s="3" t="inlineStr"/>
+      <c r="M63" s="3" t="inlineStr"/>
+      <c r="N63" s="3" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="O63" s="3" t="inlineStr">
+        <is>
+          <t>STRONG</t>
+        </is>
+      </c>
+      <c r="P63" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="S63" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="T63" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="U63" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="V63" s="3" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="W63" s="3" t="inlineStr"/>
+      <c r="X63" s="3" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #1 · Conf 54% · momentum → · band STRONG · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="Y63" s="3" t="inlineStr"/>
+      <c r="Z63" s="3" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="AA63" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="AB63" s="3" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="AC63" s="3" t="inlineStr"/>
+      <c r="AD63" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE63" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF63" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="AG63" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AH63" s="3" t="n">
+        <v>358.56</v>
+      </c>
+      <c r="AI63" s="3" t="n">
+        <v>358.56</v>
+      </c>
+      <c r="AJ63" s="3" t="n">
+        <v>351.39</v>
+      </c>
+      <c r="AK63" s="3" t="n">
+        <v>365.73</v>
+      </c>
+      <c r="AL63" s="3" t="n">
+        <v>340.632</v>
+      </c>
+      <c r="AM63" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AN63" s="3" t="n">
+        <v>387.2448000000001</v>
+      </c>
+      <c r="AO63" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP63" s="3" t="n">
+        <v>414.3519360000001</v>
+      </c>
+      <c r="AQ63" s="3" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AR63" s="3" t="inlineStr"/>
+      <c r="AS63" s="3" t="inlineStr"/>
+      <c r="AT63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU63" s="3" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AV63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW63" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AX63" s="3" t="inlineStr"/>
+      <c r="AY63" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AZ53" s="3" t="n">
+      <c r="AZ63" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="BA53" s="3" t="n">
+      <c r="BA63" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="BB53" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 10:36</t>
+      <c r="BB63" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>TRV_USA_20260729</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>R1_NEW</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>TRV</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr"/>
+      <c r="J64" s="3" t="inlineStr"/>
+      <c r="K64" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L64" s="3" t="inlineStr"/>
+      <c r="M64" s="3" t="inlineStr"/>
+      <c r="N64" s="3" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="O64" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="P64" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="S64" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="T64" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 12 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="U64" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="V64" s="3" t="inlineStr"/>
+      <c r="W64" s="3" t="inlineStr"/>
+      <c r="X64" s="3" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank #2 · Conf 57% · momentum → · band HOLD · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="Y64" s="3" t="inlineStr"/>
+      <c r="Z64" s="3" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="AA64" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="AB64" s="3" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="AC64" s="3" t="inlineStr"/>
+      <c r="AD64" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE64" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF64" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="AG64" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AH64" s="3" t="n">
+        <v>368.98</v>
+      </c>
+      <c r="AI64" s="3" t="n">
+        <v>368.98</v>
+      </c>
+      <c r="AJ64" s="3" t="n">
+        <v>365.29</v>
+      </c>
+      <c r="AK64" s="3" t="n">
+        <v>372.67</v>
+      </c>
+      <c r="AL64" s="3" t="n">
+        <v>350.531</v>
+      </c>
+      <c r="AM64" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AN64" s="3" t="n">
+        <v>413.26</v>
+      </c>
+      <c r="AO64" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP64" s="3" t="n">
+        <v>442.1882</v>
+      </c>
+      <c r="AQ64" s="3" t="n">
+        <v>19.84</v>
+      </c>
+      <c r="AR64" s="3" t="inlineStr"/>
+      <c r="AS64" s="3" t="inlineStr"/>
+      <c r="AT64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU64" s="3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AV64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW64" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AX64" s="3" t="inlineStr"/>
+      <c r="AY64" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AZ64" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA64" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB64" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>NVDA_USA_20260729</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>R1_NEW</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr"/>
+      <c r="J65" s="3" t="inlineStr"/>
+      <c r="K65" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L65" s="3" t="inlineStr"/>
+      <c r="M65" s="3" t="inlineStr"/>
+      <c r="N65" s="3" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="O65" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="P65" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="S65" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="T65" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 21 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="U65" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="V65" s="3" t="inlineStr"/>
+      <c r="W65" s="3" t="inlineStr"/>
+      <c r="X65" s="3" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #3 · Conf 47% · momentum → · band HOLD · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="Y65" s="3" t="inlineStr"/>
+      <c r="Z65" s="3" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="AA65" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="AB65" s="3" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="AC65" s="3" t="inlineStr"/>
+      <c r="AD65" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE65" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF65" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="AG65" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AH65" s="3" t="n">
+        <v>202.81</v>
+      </c>
+      <c r="AI65" s="3" t="n">
+        <v>202.81</v>
+      </c>
+      <c r="AJ65" s="3" t="n">
+        <v>198.75</v>
+      </c>
+      <c r="AK65" s="3" t="n">
+        <v>206.87</v>
+      </c>
+      <c r="AL65" s="3" t="n">
+        <v>192.6695</v>
+      </c>
+      <c r="AM65" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AN65" s="3" t="n">
+        <v>219.0348</v>
+      </c>
+      <c r="AO65" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP65" s="3" t="n">
+        <v>234.367236</v>
+      </c>
+      <c r="AQ65" s="3" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AR65" s="3" t="inlineStr"/>
+      <c r="AS65" s="3" t="inlineStr"/>
+      <c r="AT65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV65" s="3" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="AW65" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AX65" s="3" t="inlineStr"/>
+      <c r="AY65" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AZ65" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA65" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB65" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>MSFT_USA_20260730</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>R1_NEW</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr"/>
+      <c r="J66" s="3" t="inlineStr"/>
+      <c r="K66" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L66" s="3" t="inlineStr"/>
+      <c r="M66" s="3" t="inlineStr"/>
+      <c r="N66" s="3" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="O66" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="P66" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="S66" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="T66" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 33 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="U66" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="V66" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="W66" s="3" t="inlineStr"/>
+      <c r="X66" s="3" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #4 · Conf 54% · momentum → · band HOLD · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="Y66" s="3" t="inlineStr"/>
+      <c r="Z66" s="3" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="AA66" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="AB66" s="3" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="AC66" s="3" t="inlineStr"/>
+      <c r="AD66" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE66" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF66" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="AG66" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AH66" s="3" t="n">
+        <v>393.82</v>
+      </c>
+      <c r="AI66" s="3" t="n">
+        <v>393.82</v>
+      </c>
+      <c r="AJ66" s="3" t="n">
+        <v>385.94</v>
+      </c>
+      <c r="AK66" s="3" t="n">
+        <v>401.7</v>
+      </c>
+      <c r="AL66" s="3" t="n">
+        <v>374.129</v>
+      </c>
+      <c r="AM66" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AN66" s="3" t="n">
+        <v>425.3256</v>
+      </c>
+      <c r="AO66" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP66" s="3" t="n">
+        <v>455.098392</v>
+      </c>
+      <c r="AQ66" s="3" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AR66" s="3" t="inlineStr"/>
+      <c r="AS66" s="3" t="inlineStr"/>
+      <c r="AT66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU66" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AV66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW66" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AX66" s="3" t="inlineStr"/>
+      <c r="AY66" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AZ66" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA66" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB66" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>KO_USA_20260729</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>R1_NEW</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Coca-Cola</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr"/>
+      <c r="J67" s="3" t="inlineStr"/>
+      <c r="K67" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L67" s="3" t="inlineStr"/>
+      <c r="M67" s="3" t="inlineStr"/>
+      <c r="N67" s="3" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="O67" s="3" t="inlineStr">
+        <is>
+          <t>STRONG</t>
+        </is>
+      </c>
+      <c r="P67" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="S67" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="T67" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 11 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="U67" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="V67" s="3" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="W67" s="3" t="inlineStr"/>
+      <c r="X67" s="3" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #5 · Conf 50% · momentum → · band STRONG · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="Y67" s="3" t="inlineStr"/>
+      <c r="Z67" s="3" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="AA67" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="AB67" s="3" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="AC67" s="3" t="inlineStr"/>
+      <c r="AD67" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE67" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF67" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="AG67" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AH67" s="3" t="n">
+        <v>81.56</v>
+      </c>
+      <c r="AI67" s="3" t="n">
+        <v>81.56</v>
+      </c>
+      <c r="AJ67" s="3" t="n">
+        <v>79.93000000000001</v>
+      </c>
+      <c r="AK67" s="3" t="n">
+        <v>83.19</v>
+      </c>
+      <c r="AL67" s="3" t="n">
+        <v>77.482</v>
+      </c>
+      <c r="AM67" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AN67" s="3" t="n">
+        <v>88.0848</v>
+      </c>
+      <c r="AO67" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP67" s="3" t="n">
+        <v>94.250736</v>
+      </c>
+      <c r="AQ67" s="3" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AR67" s="3" t="inlineStr"/>
+      <c r="AS67" s="3" t="inlineStr"/>
+      <c r="AT67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU67" s="3" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="AV67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW67" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AX67" s="3" t="inlineStr"/>
+      <c r="AY67" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AZ67" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA67" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB67" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>HON_USA_20260729</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>R1_NEW</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Honeywell</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr"/>
+      <c r="J68" s="3" t="inlineStr"/>
+      <c r="K68" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L68" s="3" t="inlineStr"/>
+      <c r="M68" s="3" t="inlineStr"/>
+      <c r="N68" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="O68" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="P68" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="S68" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="T68" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 48 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="U68" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="V68" s="3" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="W68" s="3" t="inlineStr"/>
+      <c r="X68" s="3" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #6 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="Y68" s="3" t="inlineStr"/>
+      <c r="Z68" s="3" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="AA68" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="AB68" s="3" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="AC68" s="3" t="inlineStr"/>
+      <c r="AD68" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE68" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF68" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="AG68" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AH68" s="3" t="n">
+        <v>225.02</v>
+      </c>
+      <c r="AI68" s="3" t="n">
+        <v>225.02</v>
+      </c>
+      <c r="AJ68" s="3" t="n">
+        <v>220.52</v>
+      </c>
+      <c r="AK68" s="3" t="n">
+        <v>229.52</v>
+      </c>
+      <c r="AL68" s="3" t="n">
+        <v>213.769</v>
+      </c>
+      <c r="AM68" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AN68" s="3" t="n">
+        <v>243.0216</v>
+      </c>
+      <c r="AO68" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP68" s="3" t="n">
+        <v>260.0331120000001</v>
+      </c>
+      <c r="AQ68" s="3" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AR68" s="3" t="inlineStr"/>
+      <c r="AS68" s="3" t="inlineStr"/>
+      <c r="AT68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU68" s="3" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="AV68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW68" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AX68" s="3" t="inlineStr"/>
+      <c r="AY68" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AZ68" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA68" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB68" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>AAPL_USA_20260729</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>R1_NEW</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr"/>
+      <c r="J69" s="3" t="inlineStr"/>
+      <c r="K69" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="L69" s="3" t="inlineStr"/>
+      <c r="M69" s="3" t="inlineStr"/>
+      <c r="N69" s="3" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="O69" s="3" t="inlineStr">
+        <is>
+          <t>STRONG</t>
+        </is>
+      </c>
+      <c r="P69" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="S69" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="T69" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="U69" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="V69" s="3" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="W69" s="3" t="inlineStr"/>
+      <c r="X69" s="3" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #7 · Conf 50% · momentum → · band STRONG · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="Y69" s="3" t="inlineStr"/>
+      <c r="Z69" s="3" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="AA69" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="AB69" s="3" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="AC69" s="3" t="inlineStr"/>
+      <c r="AD69" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE69" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF69" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="AG69" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AH69" s="3" t="n">
+        <v>333.74</v>
+      </c>
+      <c r="AI69" s="3" t="n">
+        <v>333.74</v>
+      </c>
+      <c r="AJ69" s="3" t="n">
+        <v>327.07</v>
+      </c>
+      <c r="AK69" s="3" t="n">
+        <v>340.41</v>
+      </c>
+      <c r="AL69" s="3" t="n">
+        <v>317.053</v>
+      </c>
+      <c r="AM69" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AN69" s="3" t="n">
+        <v>360.4392</v>
+      </c>
+      <c r="AO69" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP69" s="3" t="n">
+        <v>385.669944</v>
+      </c>
+      <c r="AQ69" s="3" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AR69" s="3" t="inlineStr"/>
+      <c r="AS69" s="3" t="inlineStr"/>
+      <c r="AT69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV69" s="3" t="n">
+        <v>-7.44</v>
+      </c>
+      <c r="AW69" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AX69" s="3" t="inlineStr"/>
+      <c r="AY69" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AZ69" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA69" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB69" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>JPM_USA_20260729</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>R1_NEW</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr"/>
+      <c r="J70" s="3" t="inlineStr"/>
+      <c r="K70" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L70" s="3" t="inlineStr"/>
+      <c r="M70" s="3" t="inlineStr"/>
+      <c r="N70" s="3" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="O70" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="P70" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="S70" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="T70" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 18 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="U70" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="V70" s="3" t="inlineStr"/>
+      <c r="W70" s="3" t="inlineStr"/>
+      <c r="X70" s="3" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #8 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="Y70" s="3" t="inlineStr"/>
+      <c r="Z70" s="3" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="AA70" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="AB70" s="3" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="AC70" s="3" t="inlineStr"/>
+      <c r="AD70" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE70" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF70" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="AG70" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AH70" s="3" t="n">
+        <v>341.1</v>
+      </c>
+      <c r="AI70" s="3" t="n">
+        <v>341.1</v>
+      </c>
+      <c r="AJ70" s="3" t="n">
+        <v>334.28</v>
+      </c>
+      <c r="AK70" s="3" t="n">
+        <v>347.92</v>
+      </c>
+      <c r="AL70" s="3" t="n">
+        <v>324.045</v>
+      </c>
+      <c r="AM70" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AN70" s="3" t="n">
+        <v>368.388</v>
+      </c>
+      <c r="AO70" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP70" s="3" t="n">
+        <v>394.1751600000001</v>
+      </c>
+      <c r="AQ70" s="3" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AR70" s="3" t="inlineStr"/>
+      <c r="AS70" s="3" t="inlineStr"/>
+      <c r="AT70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU70" s="3" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AV70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW70" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AX70" s="3" t="inlineStr"/>
+      <c r="AY70" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AZ70" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA70" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB70" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>GS_USA_20260729</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>R1_NEW</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr"/>
+      <c r="J71" s="3" t="inlineStr"/>
+      <c r="K71" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L71" s="3" t="inlineStr"/>
+      <c r="M71" s="3" t="inlineStr"/>
+      <c r="N71" s="3" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="O71" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="P71" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="S71" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="T71" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 9 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="U71" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="V71" s="3" t="inlineStr"/>
+      <c r="W71" s="3" t="inlineStr"/>
+      <c r="X71" s="3" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #9 · Conf 51% · momentum → · band HOLD · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="Y71" s="3" t="inlineStr"/>
+      <c r="Z71" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA71" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="AB71" s="3" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="AC71" s="3" t="inlineStr"/>
+      <c r="AD71" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE71" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF71" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="AG71" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AH71" s="3" t="n">
+        <v>1065.22</v>
+      </c>
+      <c r="AI71" s="3" t="n">
+        <v>1065.22</v>
+      </c>
+      <c r="AJ71" s="3" t="n">
+        <v>1043.92</v>
+      </c>
+      <c r="AK71" s="3" t="n">
+        <v>1086.52</v>
+      </c>
+      <c r="AL71" s="3" t="n">
+        <v>1011.959</v>
+      </c>
+      <c r="AM71" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AN71" s="3" t="n">
+        <v>1150.4376</v>
+      </c>
+      <c r="AO71" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP71" s="3" t="n">
+        <v>1230.968232</v>
+      </c>
+      <c r="AQ71" s="3" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AR71" s="3" t="inlineStr"/>
+      <c r="AS71" s="3" t="inlineStr"/>
+      <c r="AT71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV71" s="3" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="AW71" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AX71" s="3" t="inlineStr"/>
+      <c r="AY71" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AZ71" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA71" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB71" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>MMM_USA_20260730</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>R1_NEW</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>MMM</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr"/>
+      <c r="J72" s="3" t="inlineStr"/>
+      <c r="K72" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L72" s="3" t="inlineStr"/>
+      <c r="M72" s="3" t="inlineStr"/>
+      <c r="N72" s="3" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="O72" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="P72" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="S72" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="T72" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 15 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="U72" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="V72" s="3" t="inlineStr"/>
+      <c r="W72" s="3" t="inlineStr"/>
+      <c r="X72" s="3" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #10 · Conf 54% · momentum → · band HOLD · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="Y72" s="3" t="inlineStr"/>
+      <c r="Z72" s="3" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="AA72" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="AB72" s="3" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="AC72" s="3" t="inlineStr"/>
+      <c r="AD72" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE72" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF72" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="AG72" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AH72" s="3" t="n">
+        <v>159.84</v>
+      </c>
+      <c r="AI72" s="3" t="n">
+        <v>159.84</v>
+      </c>
+      <c r="AJ72" s="3" t="n">
+        <v>156.64</v>
+      </c>
+      <c r="AK72" s="3" t="n">
+        <v>163.04</v>
+      </c>
+      <c r="AL72" s="3" t="n">
+        <v>151.848</v>
+      </c>
+      <c r="AM72" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AN72" s="3" t="n">
+        <v>172.6272</v>
+      </c>
+      <c r="AO72" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP72" s="3" t="n">
+        <v>184.711104</v>
+      </c>
+      <c r="AQ72" s="3" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AR72" s="3" t="inlineStr"/>
+      <c r="AS72" s="3" t="inlineStr"/>
+      <c r="AT72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU72" s="3" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="AV72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW72" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AX72" s="3" t="inlineStr"/>
+      <c r="AY72" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AZ72" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA72" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB72" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BB53"/>
+  <autoFilter ref="A1:BB72"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/telegram/aegis_daily_2026-08-06.xlsx
+++ b/reports/telegram/aegis_daily_2026-08-06.xlsx
@@ -940,7 +940,7 @@
       </c>
       <c r="BB2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BB3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="BB4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="BB5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="BB6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="BB7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="BB8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="BB9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="BB10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="BB11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="BB12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="BB13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="BB14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="BB15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="BB16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="BB17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="BB18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="BB19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="BB20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BB21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="BB22" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="BB23" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BB24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="BB25" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -4990,7 +4990,7 @@
       </c>
       <c r="BB26" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -5150,7 +5150,7 @@
       </c>
       <c r="BB27" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="BB28" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       <c r="BA29" s="3" t="inlineStr"/>
       <c r="BB29" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       <c r="BA30" s="3" t="inlineStr"/>
       <c r="BB30" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -5674,7 +5674,7 @@
       <c r="BA31" s="3" t="inlineStr"/>
       <c r="BB31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -5794,7 +5794,7 @@
       <c r="BA32" s="3" t="inlineStr"/>
       <c r="BB32" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       <c r="BA33" s="3" t="inlineStr"/>
       <c r="BB33" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -6030,7 +6030,7 @@
       <c r="BA34" s="3" t="inlineStr"/>
       <c r="BB34" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       <c r="BA35" s="3" t="inlineStr"/>
       <c r="BB35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
       <c r="BA36" s="3" t="inlineStr"/>
       <c r="BB36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -6394,7 +6394,7 @@
       <c r="BA37" s="3" t="inlineStr"/>
       <c r="BB37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -6518,7 +6518,7 @@
       <c r="BA38" s="3" t="inlineStr"/>
       <c r="BB38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       <c r="BA39" s="3" t="inlineStr"/>
       <c r="BB39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -6766,7 +6766,7 @@
       <c r="BA40" s="3" t="inlineStr"/>
       <c r="BB40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -6890,7 +6890,7 @@
       <c r="BA41" s="3" t="inlineStr"/>
       <c r="BB41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -7014,7 +7014,7 @@
       <c r="BA42" s="3" t="inlineStr"/>
       <c r="BB42" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -7138,7 +7138,7 @@
       <c r="BA43" s="3" t="inlineStr"/>
       <c r="BB43" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -7262,7 +7262,7 @@
       <c r="BA44" s="3" t="inlineStr"/>
       <c r="BB44" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -7386,7 +7386,7 @@
       <c r="BA45" s="3" t="inlineStr"/>
       <c r="BB45" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -7506,7 +7506,7 @@
       <c r="BA46" s="3" t="inlineStr"/>
       <c r="BB46" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -7630,7 +7630,7 @@
       <c r="BA47" s="3" t="inlineStr"/>
       <c r="BB47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -7810,7 +7810,7 @@
       </c>
       <c r="BB48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -7990,7 +7990,7 @@
       </c>
       <c r="BB49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -8174,7 +8174,7 @@
       </c>
       <c r="BB50" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="BB51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -8544,7 +8544,7 @@
       </c>
       <c r="BB52" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -8728,7 +8728,7 @@
       </c>
       <c r="BB53" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -8914,7 +8914,7 @@
       </c>
       <c r="BB54" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -9100,7 +9100,7 @@
       </c>
       <c r="BB55" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="BB56" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="BB57" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -9654,7 +9654,7 @@
       </c>
       <c r="BB58" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -9840,7 +9840,7 @@
       </c>
       <c r="BB59" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="BB60" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -10212,7 +10212,7 @@
       </c>
       <c r="BB61" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -10398,7 +10398,7 @@
       </c>
       <c r="BB62" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -10576,7 +10576,7 @@
       </c>
       <c r="BB63" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -10752,7 +10752,7 @@
       </c>
       <c r="BB64" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -10928,7 +10928,7 @@
       </c>
       <c r="BB65" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="BB66" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -11284,7 +11284,7 @@
       </c>
       <c r="BB67" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="BB68" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -11640,7 +11640,7 @@
       </c>
       <c r="BB69" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -11816,7 +11816,7 @@
       </c>
       <c r="BB70" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -11992,7 +11992,7 @@
       </c>
       <c r="BB71" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="BB72" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_daily_2026-08-06.xlsx
+++ b/reports/telegram/aegis_daily_2026-08-06.xlsx
@@ -769,7 +769,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TCS_IND_20260806</t>
+          <t>TCS_IND_20260729</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -867,7 +867,7 @@
         <v>2</v>
       </c>
       <c r="AD2" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE2" s="3" t="n">
         <v>17</v>
@@ -877,14 +877,14 @@
       </c>
       <c r="AG2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH2" s="3" t="n">
         <v>2421.9</v>
       </c>
       <c r="AI2" s="3" t="n">
-        <v>2421.9</v>
+        <v>2258.5</v>
       </c>
       <c r="AJ2" s="3" t="n">
         <v>2397.68</v>
@@ -896,19 +896,19 @@
         <v>2276.59</v>
       </c>
       <c r="AM2" s="3" t="n">
-        <v>-6</v>
+        <v>0.8</v>
       </c>
       <c r="AN2" s="3" t="n">
         <v>2712.53</v>
       </c>
       <c r="AO2" s="3" t="n">
-        <v>12</v>
+        <v>20.1</v>
       </c>
       <c r="AP2" s="3" t="n">
         <v>3003.16</v>
       </c>
       <c r="AQ2" s="3" t="n">
-        <v>24</v>
+        <v>32.97</v>
       </c>
       <c r="AR2" s="3" t="n">
         <v>2460</v>
@@ -917,10 +917,14 @@
         <v>-1.55</v>
       </c>
       <c r="AT2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" s="3" t="inlineStr"/>
-      <c r="AV2" s="3" t="inlineStr"/>
+        <v>7.23</v>
+      </c>
+      <c r="AU2" s="3" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="AV2" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AW2" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -940,14 +944,14 @@
       </c>
       <c r="BB2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>OFSS_IND_20260806</t>
+          <t>OFSS_IND_20260730</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -1041,7 +1045,7 @@
         <v>2</v>
       </c>
       <c r="AD3" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE3" s="3" t="n">
         <v>17</v>
@@ -1051,14 +1055,14 @@
       </c>
       <c r="AG3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AH3" s="3" t="n">
         <v>11727</v>
       </c>
       <c r="AI3" s="3" t="n">
-        <v>11727</v>
+        <v>11602</v>
       </c>
       <c r="AJ3" s="3" t="n">
         <v>11609.73</v>
@@ -1070,19 +1074,19 @@
         <v>11023.38</v>
       </c>
       <c r="AM3" s="3" t="n">
-        <v>-6</v>
+        <v>-4.99</v>
       </c>
       <c r="AN3" s="3" t="n">
         <v>13134.24</v>
       </c>
       <c r="AO3" s="3" t="n">
-        <v>12</v>
+        <v>13.21</v>
       </c>
       <c r="AP3" s="3" t="n">
         <v>14541.48</v>
       </c>
       <c r="AQ3" s="3" t="n">
-        <v>24</v>
+        <v>25.34</v>
       </c>
       <c r="AR3" s="3" t="n">
         <v>11600</v>
@@ -1091,10 +1095,14 @@
         <v>1.09</v>
       </c>
       <c r="AT3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" s="3" t="inlineStr"/>
-      <c r="AV3" s="3" t="inlineStr"/>
+        <v>1.08</v>
+      </c>
+      <c r="AU3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" s="3" t="n">
+        <v>-4.54</v>
+      </c>
       <c r="AW3" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -1114,7 +1122,7 @@
       </c>
       <c r="BB3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1236,7 @@
         <v>853.4</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>853.4</v>
+        <v>853.4000244140625</v>
       </c>
       <c r="AJ4" s="3" t="n">
         <v>844.87</v>
@@ -1261,7 +1269,7 @@
         <v>0.99</v>
       </c>
       <c r="AT4" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU4" s="3" t="inlineStr"/>
       <c r="AV4" s="3" t="inlineStr"/>
@@ -1284,7 +1292,7 @@
       </c>
       <c r="BB4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -1452,14 +1460,14 @@
       </c>
       <c r="BB5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>HCLTECH_IND_20260806</t>
+          <t>HCLTECH_IND_20260729</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -1538,7 +1546,7 @@
       <c r="W6" s="3" t="inlineStr"/>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank ↑ 8→5 · Conf 43% · band STRONG · 16d left · → HOLD</t>
+          <t>🟡 WAIT (Δ+5.9%) · Rank ↑ 8→5 · Conf 43% · band STRONG · 16d left · → HOLD</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr"/>
@@ -1557,7 +1565,7 @@
         <v>2</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE6" s="3" t="n">
         <v>17</v>
@@ -1567,35 +1575,35 @@
       </c>
       <c r="AG6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH6" s="3" t="n">
         <v>1351.3</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>1351.3</v>
+        <v>1263.5</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>1337.79</v>
+        <v>1250.87</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>1364.81</v>
+        <v>1276.13</v>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>1283.73</v>
+        <v>1200.33</v>
       </c>
       <c r="AM6" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>1459.4</v>
+        <v>1364.58</v>
       </c>
       <c r="AO6" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AP6" s="3" t="n">
-        <v>1553.99</v>
+        <v>1453.02</v>
       </c>
       <c r="AQ6" s="3" t="n">
         <v>15</v>
@@ -1607,10 +1615,14 @@
         <v>-1.36</v>
       </c>
       <c r="AT6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" s="3" t="inlineStr"/>
-      <c r="AV6" s="3" t="inlineStr"/>
+        <v>6.95</v>
+      </c>
+      <c r="AU6" s="3" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="AV6" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AW6" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -1628,7 +1640,7 @@
       </c>
       <c r="BB6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1754,7 @@
         <v>553.3</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>553.3</v>
+        <v>553.2999877929688</v>
       </c>
       <c r="AJ7" s="3" t="n">
         <v>547.77</v>
@@ -1796,14 +1808,14 @@
       </c>
       <c r="BB7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>OIL_IND_20260806</t>
+          <t>OIL_IND_20260729</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1843,7 +1855,7 @@
         </is>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0</v>
+        <v>-3.34</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>7</v>
@@ -1899,7 +1911,7 @@
         <v>1</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE8" s="3" t="n">
         <v>17</v>
@@ -1909,35 +1921,35 @@
       </c>
       <c r="AG8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH8" s="3" t="n">
         <v>443.9</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>443.9</v>
+        <v>459.25</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>439.46</v>
+        <v>454.66</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>448.34</v>
+        <v>463.84</v>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>421.7</v>
+        <v>436.29</v>
       </c>
       <c r="AM8" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AN8" s="3" t="n">
-        <v>479.41</v>
+        <v>495.99</v>
       </c>
       <c r="AO8" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AP8" s="3" t="n">
-        <v>510.48</v>
+        <v>528.14</v>
       </c>
       <c r="AQ8" s="3" t="n">
         <v>15</v>
@@ -1949,10 +1961,14 @@
         <v>-1.36</v>
       </c>
       <c r="AT8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" s="3" t="inlineStr"/>
-      <c r="AV8" s="3" t="inlineStr"/>
+        <v>-3.34</v>
+      </c>
+      <c r="AU8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AW8" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -1970,14 +1986,14 @@
       </c>
       <c r="BB8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>HEROMOTOCO_IND_20260806</t>
+          <t>HEROMOTOCO_IND_20260729</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -2021,7 +2037,7 @@
         </is>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0</v>
+        <v>11.75</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>8</v>
@@ -2081,7 +2097,7 @@
         <v>2</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE9" s="3" t="n">
         <v>17</v>
@@ -2091,35 +2107,35 @@
       </c>
       <c r="AG9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH9" s="3" t="n">
         <v>5651.5</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>5651.5</v>
+        <v>5057.4</v>
       </c>
       <c r="AJ9" s="3" t="n">
-        <v>5594.98</v>
+        <v>5006.83</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>5708.02</v>
+        <v>5107.97</v>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>5368.93</v>
+        <v>4804.53</v>
       </c>
       <c r="AM9" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AN9" s="3" t="n">
-        <v>6103.62</v>
+        <v>5461.99</v>
       </c>
       <c r="AO9" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AP9" s="3" t="n">
-        <v>6499.22</v>
+        <v>5816.01</v>
       </c>
       <c r="AQ9" s="3" t="n">
         <v>15</v>
@@ -2131,10 +2147,14 @@
         <v>1.87</v>
       </c>
       <c r="AT9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" s="3" t="inlineStr"/>
-      <c r="AV9" s="3" t="inlineStr"/>
+        <v>11.75</v>
+      </c>
+      <c r="AU9" s="3" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="AV9" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AW9" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -2152,14 +2172,14 @@
       </c>
       <c r="BB9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>VEDL_IND_20260806</t>
+          <t>VEDL_IND_20260729</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -2203,7 +2223,7 @@
         </is>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>6.82</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>9</v>
@@ -2263,7 +2283,7 @@
         <v>1</v>
       </c>
       <c r="AD10" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE10" s="3" t="n">
         <v>60</v>
@@ -2273,35 +2293,35 @@
       </c>
       <c r="AG10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH10" s="3" t="n">
         <v>278.8</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>278.8</v>
+        <v>261</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>276.01</v>
+        <v>258.39</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>281.59</v>
+        <v>263.61</v>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>264.86</v>
+        <v>247.95</v>
       </c>
       <c r="AM10" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AN10" s="3" t="n">
-        <v>301.1</v>
+        <v>281.88</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AP10" s="3" t="n">
-        <v>320.62</v>
+        <v>300.15</v>
       </c>
       <c r="AQ10" s="3" t="n">
         <v>15</v>
@@ -2313,10 +2333,14 @@
         <v>3.64</v>
       </c>
       <c r="AT10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" s="3" t="inlineStr"/>
-      <c r="AV10" s="3" t="inlineStr"/>
+        <v>6.82</v>
+      </c>
+      <c r="AU10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AW10" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -2334,7 +2358,7 @@
       </c>
       <c r="BB10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2405,7 @@
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>10</v>
@@ -2454,7 +2478,7 @@
         <v>380.35</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>380.35</v>
+        <v>380.3500061035156</v>
       </c>
       <c r="AJ11" s="3" t="n">
         <v>376.55</v>
@@ -2487,7 +2511,7 @@
         <v>0.89</v>
       </c>
       <c r="AT11" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU11" s="3" t="inlineStr"/>
       <c r="AV11" s="3" t="inlineStr"/>
@@ -2508,14 +2532,14 @@
       </c>
       <c r="BB11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>AMBER_IND_20260806</t>
+          <t>AMBER_IND_20260729</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -2559,7 +2583,7 @@
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>11</v>
@@ -2619,7 +2643,7 @@
         <v>1</v>
       </c>
       <c r="AD12" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE12" s="3" t="n">
         <v>60</v>
@@ -2629,35 +2653,35 @@
       </c>
       <c r="AG12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH12" s="3" t="n">
         <v>7531.5</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>7531.5</v>
+        <v>7338.5</v>
       </c>
       <c r="AJ12" s="3" t="n">
-        <v>7456.18</v>
+        <v>7265.11</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>7606.82</v>
+        <v>7411.89</v>
       </c>
       <c r="AL12" s="3" t="n">
-        <v>7154.92</v>
+        <v>6971.57</v>
       </c>
       <c r="AM12" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AN12" s="3" t="n">
-        <v>8134.02</v>
+        <v>7925.58</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AP12" s="3" t="n">
-        <v>8661.219999999999</v>
+        <v>8439.27</v>
       </c>
       <c r="AQ12" s="3" t="n">
         <v>15</v>
@@ -2669,10 +2693,14 @@
         <v>1.85</v>
       </c>
       <c r="AT12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" s="3" t="inlineStr"/>
-      <c r="AV12" s="3" t="inlineStr"/>
+        <v>2.63</v>
+      </c>
+      <c r="AU12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AW12" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -2690,14 +2718,14 @@
       </c>
       <c r="BB12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>BIOCON_IND_20260806</t>
+          <t>BIOCON_IND_20260729</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -2741,7 +2769,7 @@
         </is>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0</v>
+        <v>-0.28</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>12</v>
@@ -2801,7 +2829,7 @@
         <v>2</v>
       </c>
       <c r="AD13" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE13" s="3" t="n">
         <v>17</v>
@@ -2811,35 +2839,35 @@
       </c>
       <c r="AG13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH13" s="3" t="n">
         <v>428.2</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>428.2</v>
+        <v>429.4</v>
       </c>
       <c r="AJ13" s="3" t="n">
-        <v>423.92</v>
+        <v>425.11</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>432.48</v>
+        <v>433.69</v>
       </c>
       <c r="AL13" s="3" t="n">
-        <v>406.79</v>
+        <v>407.93</v>
       </c>
       <c r="AM13" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AN13" s="3" t="n">
-        <v>462.46</v>
+        <v>463.75</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AP13" s="3" t="n">
-        <v>492.43</v>
+        <v>493.81</v>
       </c>
       <c r="AQ13" s="3" t="n">
         <v>15</v>
@@ -2851,10 +2879,14 @@
         <v>1.47</v>
       </c>
       <c r="AT13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" s="3" t="inlineStr"/>
-      <c r="AV13" s="3" t="inlineStr"/>
+        <v>-0.28</v>
+      </c>
+      <c r="AU13" s="3" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AV13" s="3" t="n">
+        <v>-0.91</v>
+      </c>
       <c r="AW13" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -2872,7 +2904,7 @@
       </c>
       <c r="BB13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -2919,7 +2951,7 @@
         </is>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>13</v>
@@ -2992,7 +3024,7 @@
         <v>471.2</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>471.2</v>
+        <v>471.2000122070312</v>
       </c>
       <c r="AJ14" s="3" t="n">
         <v>466.49</v>
@@ -3025,7 +3057,7 @@
         <v>-2.24</v>
       </c>
       <c r="AT14" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU14" s="3" t="inlineStr"/>
       <c r="AV14" s="3" t="inlineStr"/>
@@ -3046,7 +3078,7 @@
       </c>
       <c r="BB14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -3220,14 +3252,14 @@
       </c>
       <c r="BB15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>VOLTAS_IND_20260806</t>
+          <t>VOLTAS_IND_20260729</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -3267,7 +3299,7 @@
         </is>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0</v>
+        <v>-0.16</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>15</v>
@@ -3323,7 +3355,7 @@
         <v>1</v>
       </c>
       <c r="AD16" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE16" s="3" t="n">
         <v>17</v>
@@ -3333,35 +3365,35 @@
       </c>
       <c r="AG16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH16" s="3" t="n">
         <v>1296.8</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>1296.8</v>
+        <v>1298.9</v>
       </c>
       <c r="AJ16" s="3" t="n">
-        <v>1283.83</v>
+        <v>1285.91</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>1309.77</v>
+        <v>1311.89</v>
       </c>
       <c r="AL16" s="3" t="n">
-        <v>1231.96</v>
+        <v>1233.95</v>
       </c>
       <c r="AM16" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AN16" s="3" t="n">
-        <v>1400.54</v>
+        <v>1402.81</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AP16" s="3" t="n">
-        <v>1491.32</v>
+        <v>1493.73</v>
       </c>
       <c r="AQ16" s="3" t="n">
         <v>15</v>
@@ -3373,10 +3405,14 @@
         <v>-2.33</v>
       </c>
       <c r="AT16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" s="3" t="inlineStr"/>
-      <c r="AV16" s="3" t="inlineStr"/>
+        <v>-0.16</v>
+      </c>
+      <c r="AU16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AW16" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -3394,7 +3430,7 @@
       </c>
       <c r="BB16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -3498,7 +3534,7 @@
         <v>1449.6</v>
       </c>
       <c r="AI17" s="3" t="n">
-        <v>1449.6</v>
+        <v>1449.599975585938</v>
       </c>
       <c r="AJ17" s="3" t="n">
         <v>1410</v>
@@ -3554,7 +3590,7 @@
       </c>
       <c r="BB17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -3714,14 +3750,14 @@
       </c>
       <c r="BB18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>LUPIN_IND_20260806</t>
+          <t>LUPIN_IND_20260729</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -3801,7 +3837,7 @@
       </c>
       <c r="AC19" s="3" t="inlineStr"/>
       <c r="AD19" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE19" s="3" t="n">
         <v>60</v>
@@ -3811,14 +3847,14 @@
       </c>
       <c r="AG19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH19" s="3" t="n">
         <v>2390.4</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>2390.4</v>
+        <v>2376.2</v>
       </c>
       <c r="AJ19" s="3" t="n">
         <v>2329</v>
@@ -3830,19 +3866,19 @@
         <v>2270.88</v>
       </c>
       <c r="AM19" s="3" t="n">
-        <v>-5</v>
+        <v>-4.43</v>
       </c>
       <c r="AN19" s="3" t="n">
         <v>2581.632</v>
       </c>
       <c r="AO19" s="3" t="n">
-        <v>8</v>
+        <v>8.65</v>
       </c>
       <c r="AP19" s="3" t="n">
         <v>2762.34624</v>
       </c>
       <c r="AQ19" s="3" t="n">
-        <v>15.56</v>
+        <v>16.25</v>
       </c>
       <c r="AR19" s="3" t="n">
         <v>2410</v>
@@ -3851,10 +3887,14 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="AT19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" s="3" t="inlineStr"/>
-      <c r="AV19" s="3" t="inlineStr"/>
+        <v>0.6</v>
+      </c>
+      <c r="AU19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AW19" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -3870,11 +3910,11 @@
         <v>5</v>
       </c>
       <c r="BA19" s="3" t="n">
-        <v>8</v>
+        <v>8.65</v>
       </c>
       <c r="BB19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -4034,7 +4074,7 @@
       </c>
       <c r="BB20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4178,7 @@
         <v>397.2</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>397.2</v>
+        <v>397.2000122070312</v>
       </c>
       <c r="AJ21" s="3" t="n">
         <v>386</v>
@@ -4171,7 +4211,7 @@
         <v>-0.2</v>
       </c>
       <c r="AT21" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU21" s="3" t="inlineStr"/>
       <c r="AV21" s="3" t="inlineStr"/>
@@ -4194,7 +4234,7 @@
       </c>
       <c r="BB21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -4298,7 +4338,7 @@
         <v>346.9</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>346.9</v>
+        <v>346.8999938964844</v>
       </c>
       <c r="AJ22" s="3" t="n">
         <v>338</v>
@@ -4354,7 +4394,7 @@
       </c>
       <c r="BB22" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -4458,7 +4498,7 @@
         <v>276.8</v>
       </c>
       <c r="AI23" s="3" t="n">
-        <v>276.8</v>
+        <v>276.7999877929688</v>
       </c>
       <c r="AJ23" s="3" t="n">
         <v>270</v>
@@ -4514,14 +4554,14 @@
       </c>
       <c r="BB23" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>ITC_IND_20260806</t>
+          <t>ITC_IND_20260729</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -4597,7 +4637,7 @@
       </c>
       <c r="AC24" s="3" t="inlineStr"/>
       <c r="AD24" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE24" s="3" t="n">
         <v>60</v>
@@ -4607,14 +4647,14 @@
       </c>
       <c r="AG24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH24" s="3" t="n">
         <v>285.8</v>
       </c>
       <c r="AI24" s="3" t="n">
-        <v>285.8</v>
+        <v>280.95</v>
       </c>
       <c r="AJ24" s="3" t="n">
         <v>279</v>
@@ -4626,19 +4666,19 @@
         <v>271.51</v>
       </c>
       <c r="AM24" s="3" t="n">
-        <v>-5</v>
+        <v>-3.36</v>
       </c>
       <c r="AN24" s="3" t="n">
         <v>287</v>
       </c>
       <c r="AO24" s="3" t="n">
-        <v>0.42</v>
+        <v>2.15</v>
       </c>
       <c r="AP24" s="3" t="n">
         <v>307.09</v>
       </c>
       <c r="AQ24" s="3" t="n">
-        <v>7.45</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AR24" s="3" t="n">
         <v>289</v>
@@ -4647,10 +4687,14 @@
         <v>-1.11</v>
       </c>
       <c r="AT24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU24" s="3" t="inlineStr"/>
-      <c r="AV24" s="3" t="inlineStr"/>
+        <v>1.73</v>
+      </c>
+      <c r="AU24" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AV24" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AW24" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -4666,11 +4710,11 @@
         <v>5</v>
       </c>
       <c r="BA24" s="3" t="n">
-        <v>0.42</v>
+        <v>2.15</v>
       </c>
       <c r="BB24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -4774,7 +4818,7 @@
         <v>510.9</v>
       </c>
       <c r="AI25" s="3" t="n">
-        <v>510.9</v>
+        <v>510.8500061035156</v>
       </c>
       <c r="AJ25" s="3" t="n">
         <v>495</v>
@@ -4786,19 +4830,19 @@
         <v>485.355</v>
       </c>
       <c r="AM25" s="3" t="n">
-        <v>-5</v>
+        <v>-4.99</v>
       </c>
       <c r="AN25" s="3" t="n">
         <v>551.772</v>
       </c>
       <c r="AO25" s="3" t="n">
-        <v>8</v>
+        <v>8.01</v>
       </c>
       <c r="AP25" s="3" t="n">
         <v>590.3960400000001</v>
       </c>
       <c r="AQ25" s="3" t="n">
-        <v>15.56</v>
+        <v>15.57</v>
       </c>
       <c r="AR25" s="3" t="n">
         <v>510.25</v>
@@ -4807,7 +4851,7 @@
         <v>0.12</v>
       </c>
       <c r="AT25" s="3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AU25" s="3" t="inlineStr"/>
       <c r="AV25" s="3" t="inlineStr"/>
@@ -4826,11 +4870,11 @@
         <v>5</v>
       </c>
       <c r="BA25" s="3" t="n">
-        <v>8</v>
+        <v>8.01</v>
       </c>
       <c r="BB25" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4978,7 @@
         <v>390</v>
       </c>
       <c r="AI26" s="3" t="n">
-        <v>390</v>
+        <v>390.0499877929688</v>
       </c>
       <c r="AJ26" s="3" t="n">
         <v>378</v>
@@ -4946,19 +4990,19 @@
         <v>370.5</v>
       </c>
       <c r="AM26" s="3" t="n">
-        <v>-5</v>
+        <v>-5.01</v>
       </c>
       <c r="AN26" s="3" t="n">
         <v>421.2</v>
       </c>
       <c r="AO26" s="3" t="n">
-        <v>8</v>
+        <v>7.99</v>
       </c>
       <c r="AP26" s="3" t="n">
         <v>450.6840000000001</v>
       </c>
       <c r="AQ26" s="3" t="n">
-        <v>15.56</v>
+        <v>15.55</v>
       </c>
       <c r="AR26" s="3" t="n">
         <v>391.5</v>
@@ -4967,7 +5011,7 @@
         <v>-0.37</v>
       </c>
       <c r="AT26" s="3" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AU26" s="3" t="inlineStr"/>
       <c r="AV26" s="3" t="inlineStr"/>
@@ -4986,18 +5030,18 @@
         <v>5</v>
       </c>
       <c r="BA26" s="3" t="n">
-        <v>8</v>
+        <v>7.99</v>
       </c>
       <c r="BB26" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA_IND_20260806</t>
+          <t>COALINDIA_IND_20260729</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -5077,7 +5121,7 @@
       </c>
       <c r="AC27" s="3" t="inlineStr"/>
       <c r="AD27" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE27" s="3" t="n">
         <v>60</v>
@@ -5087,14 +5131,14 @@
       </c>
       <c r="AG27" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH27" s="3" t="n">
         <v>414</v>
       </c>
       <c r="AI27" s="3" t="n">
-        <v>414</v>
+        <v>426.65</v>
       </c>
       <c r="AJ27" s="3" t="n">
         <v>401</v>
@@ -5106,19 +5150,19 @@
         <v>393.3</v>
       </c>
       <c r="AM27" s="3" t="n">
-        <v>-5</v>
+        <v>-7.82</v>
       </c>
       <c r="AN27" s="3" t="n">
         <v>447.12</v>
       </c>
       <c r="AO27" s="3" t="n">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="AP27" s="3" t="n">
         <v>478.4184</v>
       </c>
       <c r="AQ27" s="3" t="n">
-        <v>15.56</v>
+        <v>12.13</v>
       </c>
       <c r="AR27" s="3" t="n">
         <v>417.6</v>
@@ -5127,10 +5171,14 @@
         <v>-0.85</v>
       </c>
       <c r="AT27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU27" s="3" t="inlineStr"/>
-      <c r="AV27" s="3" t="inlineStr"/>
+        <v>-2.96</v>
+      </c>
+      <c r="AU27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AW27" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -5146,11 +5194,11 @@
         <v>5</v>
       </c>
       <c r="BA27" s="3" t="n">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="BB27" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -5306,14 +5354,14 @@
       </c>
       <c r="BB28" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>LUPIN_IND_20260806</t>
+          <t>LUPIN_IND_20260729</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -5374,7 +5422,7 @@
       <c r="W29" s="3" t="inlineStr"/>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>Rank ↑ 3→1 · Conf 52% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank ↑ 3→1 · Conf 52% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr"/>
@@ -5391,7 +5439,7 @@
       </c>
       <c r="AC29" s="3" t="inlineStr"/>
       <c r="AD29" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE29" s="3" t="n">
         <v>60</v>
@@ -5399,26 +5447,56 @@
       <c r="AF29" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="AG29" s="3" t="inlineStr"/>
-      <c r="AH29" s="3" t="inlineStr"/>
-      <c r="AI29" s="3" t="inlineStr"/>
-      <c r="AJ29" s="3" t="inlineStr"/>
-      <c r="AK29" s="3" t="inlineStr"/>
-      <c r="AL29" s="3" t="inlineStr"/>
-      <c r="AM29" s="3" t="inlineStr"/>
-      <c r="AN29" s="3" t="inlineStr"/>
-      <c r="AO29" s="3" t="inlineStr"/>
-      <c r="AP29" s="3" t="inlineStr"/>
-      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AG29" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AH29" s="3" t="n">
+        <v>2376.2</v>
+      </c>
+      <c r="AI29" s="3" t="n">
+        <v>2376.2</v>
+      </c>
+      <c r="AJ29" s="3" t="n">
+        <v>2352.44</v>
+      </c>
+      <c r="AK29" s="3" t="n">
+        <v>2399.96</v>
+      </c>
+      <c r="AL29" s="3" t="n">
+        <v>2257.39</v>
+      </c>
+      <c r="AM29" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AN29" s="3" t="n">
+        <v>2566.296</v>
+      </c>
+      <c r="AO29" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP29" s="3" t="n">
+        <v>2732.63</v>
+      </c>
+      <c r="AQ29" s="3" t="n">
+        <v>15</v>
+      </c>
       <c r="AR29" s="3" t="n">
         <v>2410</v>
       </c>
       <c r="AS29" s="3" t="n">
         <v>-0.8100000000000001</v>
       </c>
-      <c r="AT29" s="3" t="inlineStr"/>
-      <c r="AU29" s="3" t="inlineStr"/>
-      <c r="AV29" s="3" t="inlineStr"/>
+      <c r="AT29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AW29" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -5427,17 +5505,19 @@
       <c r="AX29" s="3" t="inlineStr"/>
       <c r="AY29" s="3" t="inlineStr"/>
       <c r="AZ29" s="3" t="inlineStr"/>
-      <c r="BA29" s="3" t="inlineStr"/>
+      <c r="BA29" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="BB29" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>PNB_IND_20260806</t>
+          <t>PNB_IND_20260729</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -5494,7 +5574,7 @@
       <c r="W30" s="3" t="inlineStr"/>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>Rank #4 · Conf 32% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #4 · Conf 32% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr"/>
@@ -5511,7 +5591,7 @@
       </c>
       <c r="AC30" s="3" t="inlineStr"/>
       <c r="AD30" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE30" s="3" t="n">
         <v>60</v>
@@ -5519,26 +5599,56 @@
       <c r="AF30" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="AG30" s="3" t="inlineStr"/>
-      <c r="AH30" s="3" t="inlineStr"/>
-      <c r="AI30" s="3" t="inlineStr"/>
-      <c r="AJ30" s="3" t="inlineStr"/>
-      <c r="AK30" s="3" t="inlineStr"/>
-      <c r="AL30" s="3" t="inlineStr"/>
-      <c r="AM30" s="3" t="inlineStr"/>
-      <c r="AN30" s="3" t="inlineStr"/>
-      <c r="AO30" s="3" t="inlineStr"/>
-      <c r="AP30" s="3" t="inlineStr"/>
-      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AG30" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AH30" s="3" t="n">
+        <v>109.29</v>
+      </c>
+      <c r="AI30" s="3" t="n">
+        <v>109.29</v>
+      </c>
+      <c r="AJ30" s="3" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="AK30" s="3" t="n">
+        <v>110.38</v>
+      </c>
+      <c r="AL30" s="3" t="n">
+        <v>103.8255</v>
+      </c>
+      <c r="AM30" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AN30" s="3" t="n">
+        <v>118.0332</v>
+      </c>
+      <c r="AO30" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP30" s="3" t="n">
+        <v>125.6835</v>
+      </c>
+      <c r="AQ30" s="3" t="n">
+        <v>15</v>
+      </c>
       <c r="AR30" s="3" t="n">
         <v>113.99</v>
       </c>
       <c r="AS30" s="3" t="n">
         <v>-0.39</v>
       </c>
-      <c r="AT30" s="3" t="inlineStr"/>
-      <c r="AU30" s="3" t="inlineStr"/>
-      <c r="AV30" s="3" t="inlineStr"/>
+      <c r="AT30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AW30" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -5547,17 +5657,19 @@
       <c r="AX30" s="3" t="inlineStr"/>
       <c r="AY30" s="3" t="inlineStr"/>
       <c r="AZ30" s="3" t="inlineStr"/>
-      <c r="BA30" s="3" t="inlineStr"/>
+      <c r="BA30" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="BB30" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA_IND_20260806</t>
+          <t>COALINDIA_IND_20260729</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -5618,7 +5730,7 @@
       <c r="W31" s="3" t="inlineStr"/>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>Rank ↑ 10→5 · Conf 36% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank ↑ 10→5 · Conf 36% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr"/>
@@ -5635,7 +5747,7 @@
       </c>
       <c r="AC31" s="3" t="inlineStr"/>
       <c r="AD31" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE31" s="3" t="n">
         <v>60</v>
@@ -5643,26 +5755,56 @@
       <c r="AF31" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="AG31" s="3" t="inlineStr"/>
-      <c r="AH31" s="3" t="inlineStr"/>
-      <c r="AI31" s="3" t="inlineStr"/>
-      <c r="AJ31" s="3" t="inlineStr"/>
-      <c r="AK31" s="3" t="inlineStr"/>
-      <c r="AL31" s="3" t="inlineStr"/>
-      <c r="AM31" s="3" t="inlineStr"/>
-      <c r="AN31" s="3" t="inlineStr"/>
-      <c r="AO31" s="3" t="inlineStr"/>
-      <c r="AP31" s="3" t="inlineStr"/>
-      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AG31" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AH31" s="3" t="n">
+        <v>426.65</v>
+      </c>
+      <c r="AI31" s="3" t="n">
+        <v>426.65</v>
+      </c>
+      <c r="AJ31" s="3" t="n">
+        <v>422.38</v>
+      </c>
+      <c r="AK31" s="3" t="n">
+        <v>430.92</v>
+      </c>
+      <c r="AL31" s="3" t="n">
+        <v>405.3174999999999</v>
+      </c>
+      <c r="AM31" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AN31" s="3" t="n">
+        <v>460.782</v>
+      </c>
+      <c r="AO31" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP31" s="3" t="n">
+        <v>490.6474999999999</v>
+      </c>
+      <c r="AQ31" s="3" t="n">
+        <v>15</v>
+      </c>
       <c r="AR31" s="3" t="n">
         <v>417.6</v>
       </c>
       <c r="AS31" s="3" t="n">
         <v>-0.85</v>
       </c>
-      <c r="AT31" s="3" t="inlineStr"/>
-      <c r="AU31" s="3" t="inlineStr"/>
-      <c r="AV31" s="3" t="inlineStr"/>
+      <c r="AT31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AW31" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -5671,17 +5813,19 @@
       <c r="AX31" s="3" t="inlineStr"/>
       <c r="AY31" s="3" t="inlineStr"/>
       <c r="AZ31" s="3" t="inlineStr"/>
-      <c r="BA31" s="3" t="inlineStr"/>
+      <c r="BA31" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="BB31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>HINDZINC_IND_20260806</t>
+          <t>HINDZINC_IND_20260729</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -5738,7 +5882,7 @@
       <c r="W32" s="3" t="inlineStr"/>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>Rank #10 · Conf 38% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #10 · Conf 38% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr"/>
@@ -5755,7 +5899,7 @@
       </c>
       <c r="AC32" s="3" t="inlineStr"/>
       <c r="AD32" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE32" s="3" t="n">
         <v>60</v>
@@ -5763,26 +5907,56 @@
       <c r="AF32" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="AG32" s="3" t="inlineStr"/>
-      <c r="AH32" s="3" t="inlineStr"/>
-      <c r="AI32" s="3" t="inlineStr"/>
-      <c r="AJ32" s="3" t="inlineStr"/>
-      <c r="AK32" s="3" t="inlineStr"/>
-      <c r="AL32" s="3" t="inlineStr"/>
-      <c r="AM32" s="3" t="inlineStr"/>
-      <c r="AN32" s="3" t="inlineStr"/>
-      <c r="AO32" s="3" t="inlineStr"/>
-      <c r="AP32" s="3" t="inlineStr"/>
-      <c r="AQ32" s="3" t="inlineStr"/>
+      <c r="AG32" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AH32" s="3" t="n">
+        <v>526.45</v>
+      </c>
+      <c r="AI32" s="3" t="n">
+        <v>526.45</v>
+      </c>
+      <c r="AJ32" s="3" t="n">
+        <v>521.1900000000001</v>
+      </c>
+      <c r="AK32" s="3" t="n">
+        <v>531.71</v>
+      </c>
+      <c r="AL32" s="3" t="n">
+        <v>500.1275</v>
+      </c>
+      <c r="AM32" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AN32" s="3" t="n">
+        <v>568.566</v>
+      </c>
+      <c r="AO32" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP32" s="3" t="n">
+        <v>605.4175</v>
+      </c>
+      <c r="AQ32" s="3" t="n">
+        <v>15</v>
+      </c>
       <c r="AR32" s="3" t="n">
         <v>562.9</v>
       </c>
       <c r="AS32" s="3" t="n">
         <v>6.16</v>
       </c>
-      <c r="AT32" s="3" t="inlineStr"/>
-      <c r="AU32" s="3" t="inlineStr"/>
-      <c r="AV32" s="3" t="inlineStr"/>
+      <c r="AT32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AW32" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -5791,17 +5965,19 @@
       <c r="AX32" s="3" t="inlineStr"/>
       <c r="AY32" s="3" t="inlineStr"/>
       <c r="AZ32" s="3" t="inlineStr"/>
-      <c r="BA32" s="3" t="inlineStr"/>
+      <c r="BA32" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="BB32" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>BATAINDIA_IND_20260806</t>
+          <t>BATAINDIA_IND_20260729</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -5858,7 +6034,7 @@
       <c r="W33" s="3" t="inlineStr"/>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>Rank #15 · Conf 24% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #15 · Conf 24% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr"/>
@@ -5875,7 +6051,7 @@
       </c>
       <c r="AC33" s="3" t="inlineStr"/>
       <c r="AD33" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE33" s="3" t="n">
         <v>60</v>
@@ -5883,26 +6059,56 @@
       <c r="AF33" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="AG33" s="3" t="inlineStr"/>
-      <c r="AH33" s="3" t="inlineStr"/>
-      <c r="AI33" s="3" t="inlineStr"/>
-      <c r="AJ33" s="3" t="inlineStr"/>
-      <c r="AK33" s="3" t="inlineStr"/>
-      <c r="AL33" s="3" t="inlineStr"/>
-      <c r="AM33" s="3" t="inlineStr"/>
-      <c r="AN33" s="3" t="inlineStr"/>
-      <c r="AO33" s="3" t="inlineStr"/>
-      <c r="AP33" s="3" t="inlineStr"/>
-      <c r="AQ33" s="3" t="inlineStr"/>
+      <c r="AG33" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AH33" s="3" t="n">
+        <v>673.7</v>
+      </c>
+      <c r="AI33" s="3" t="n">
+        <v>673.7</v>
+      </c>
+      <c r="AJ33" s="3" t="n">
+        <v>666.96</v>
+      </c>
+      <c r="AK33" s="3" t="n">
+        <v>680.4400000000001</v>
+      </c>
+      <c r="AL33" s="3" t="n">
+        <v>640.015</v>
+      </c>
+      <c r="AM33" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AN33" s="3" t="n">
+        <v>727.5960000000001</v>
+      </c>
+      <c r="AO33" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP33" s="3" t="n">
+        <v>774.755</v>
+      </c>
+      <c r="AQ33" s="3" t="n">
+        <v>15</v>
+      </c>
       <c r="AR33" s="3" t="n">
         <v>709.55</v>
       </c>
       <c r="AS33" s="3" t="n">
         <v>3.02</v>
       </c>
-      <c r="AT33" s="3" t="inlineStr"/>
-      <c r="AU33" s="3" t="inlineStr"/>
-      <c r="AV33" s="3" t="inlineStr"/>
+      <c r="AT33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AW33" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -5911,10 +6117,12 @@
       <c r="AX33" s="3" t="inlineStr"/>
       <c r="AY33" s="3" t="inlineStr"/>
       <c r="AZ33" s="3" t="inlineStr"/>
-      <c r="BA33" s="3" t="inlineStr"/>
+      <c r="BA33" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="BB33" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -6030,7 +6238,7 @@
       <c r="BA34" s="3" t="inlineStr"/>
       <c r="BB34" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6354,7 @@
       <c r="BA35" s="3" t="inlineStr"/>
       <c r="BB35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6478,7 @@
       <c r="BA36" s="3" t="inlineStr"/>
       <c r="BB36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -6394,14 +6602,14 @@
       <c r="BA37" s="3" t="inlineStr"/>
       <c r="BB37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>LUPIN_IND_20260806</t>
+          <t>LUPIN_IND_20260729</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -6462,7 +6670,7 @@
       <c r="W38" s="3" t="inlineStr"/>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>Rank → 3→3 · Conf 72% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 3→3 · Conf 72% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr"/>
@@ -6479,7 +6687,7 @@
       </c>
       <c r="AC38" s="3" t="inlineStr"/>
       <c r="AD38" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE38" s="3" t="n">
         <v>60</v>
@@ -6487,26 +6695,56 @@
       <c r="AF38" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="AG38" s="3" t="inlineStr"/>
-      <c r="AH38" s="3" t="inlineStr"/>
-      <c r="AI38" s="3" t="inlineStr"/>
-      <c r="AJ38" s="3" t="inlineStr"/>
-      <c r="AK38" s="3" t="inlineStr"/>
-      <c r="AL38" s="3" t="inlineStr"/>
-      <c r="AM38" s="3" t="inlineStr"/>
-      <c r="AN38" s="3" t="inlineStr"/>
-      <c r="AO38" s="3" t="inlineStr"/>
-      <c r="AP38" s="3" t="inlineStr"/>
-      <c r="AQ38" s="3" t="inlineStr"/>
+      <c r="AG38" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AH38" s="3" t="n">
+        <v>2376.2</v>
+      </c>
+      <c r="AI38" s="3" t="n">
+        <v>2376.2</v>
+      </c>
+      <c r="AJ38" s="3" t="n">
+        <v>2352.44</v>
+      </c>
+      <c r="AK38" s="3" t="n">
+        <v>2399.96</v>
+      </c>
+      <c r="AL38" s="3" t="n">
+        <v>2257.39</v>
+      </c>
+      <c r="AM38" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AN38" s="3" t="n">
+        <v>2566.296</v>
+      </c>
+      <c r="AO38" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP38" s="3" t="n">
+        <v>2732.63</v>
+      </c>
+      <c r="AQ38" s="3" t="n">
+        <v>15</v>
+      </c>
       <c r="AR38" s="3" t="n">
         <v>2410</v>
       </c>
       <c r="AS38" s="3" t="n">
         <v>-0.8100000000000001</v>
       </c>
-      <c r="AT38" s="3" t="inlineStr"/>
-      <c r="AU38" s="3" t="inlineStr"/>
-      <c r="AV38" s="3" t="inlineStr"/>
+      <c r="AT38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AW38" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -6515,10 +6753,12 @@
       <c r="AX38" s="3" t="inlineStr"/>
       <c r="AY38" s="3" t="inlineStr"/>
       <c r="AZ38" s="3" t="inlineStr"/>
-      <c r="BA38" s="3" t="inlineStr"/>
+      <c r="BA38" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="BB38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6882,7 @@
       <c r="BA39" s="3" t="inlineStr"/>
       <c r="BB39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -6766,7 +7006,7 @@
       <c r="BA40" s="3" t="inlineStr"/>
       <c r="BB40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -6890,7 +7130,7 @@
       <c r="BA41" s="3" t="inlineStr"/>
       <c r="BB41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -7014,7 +7254,7 @@
       <c r="BA42" s="3" t="inlineStr"/>
       <c r="BB42" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -7138,7 +7378,7 @@
       <c r="BA43" s="3" t="inlineStr"/>
       <c r="BB43" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -7262,14 +7502,14 @@
       <c r="BA44" s="3" t="inlineStr"/>
       <c r="BB44" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA_IND_20260806</t>
+          <t>COALINDIA_IND_20260729</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -7330,7 +7570,7 @@
       <c r="W45" s="3" t="inlineStr"/>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>Rank → 10→10 · Conf 66% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 10→10 · Conf 66% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr"/>
@@ -7347,7 +7587,7 @@
       </c>
       <c r="AC45" s="3" t="inlineStr"/>
       <c r="AD45" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE45" s="3" t="n">
         <v>60</v>
@@ -7355,26 +7595,56 @@
       <c r="AF45" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="AG45" s="3" t="inlineStr"/>
-      <c r="AH45" s="3" t="inlineStr"/>
-      <c r="AI45" s="3" t="inlineStr"/>
-      <c r="AJ45" s="3" t="inlineStr"/>
-      <c r="AK45" s="3" t="inlineStr"/>
-      <c r="AL45" s="3" t="inlineStr"/>
-      <c r="AM45" s="3" t="inlineStr"/>
-      <c r="AN45" s="3" t="inlineStr"/>
-      <c r="AO45" s="3" t="inlineStr"/>
-      <c r="AP45" s="3" t="inlineStr"/>
-      <c r="AQ45" s="3" t="inlineStr"/>
+      <c r="AG45" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AH45" s="3" t="n">
+        <v>426.65</v>
+      </c>
+      <c r="AI45" s="3" t="n">
+        <v>426.65</v>
+      </c>
+      <c r="AJ45" s="3" t="n">
+        <v>422.38</v>
+      </c>
+      <c r="AK45" s="3" t="n">
+        <v>430.92</v>
+      </c>
+      <c r="AL45" s="3" t="n">
+        <v>405.3174999999999</v>
+      </c>
+      <c r="AM45" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AN45" s="3" t="n">
+        <v>460.782</v>
+      </c>
+      <c r="AO45" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP45" s="3" t="n">
+        <v>490.6474999999999</v>
+      </c>
+      <c r="AQ45" s="3" t="n">
+        <v>15</v>
+      </c>
       <c r="AR45" s="3" t="n">
         <v>417.6</v>
       </c>
       <c r="AS45" s="3" t="n">
         <v>-0.85</v>
       </c>
-      <c r="AT45" s="3" t="inlineStr"/>
-      <c r="AU45" s="3" t="inlineStr"/>
-      <c r="AV45" s="3" t="inlineStr"/>
+      <c r="AT45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV45" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AW45" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -7383,10 +7653,12 @@
       <c r="AX45" s="3" t="inlineStr"/>
       <c r="AY45" s="3" t="inlineStr"/>
       <c r="AZ45" s="3" t="inlineStr"/>
-      <c r="BA45" s="3" t="inlineStr"/>
+      <c r="BA45" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="BB45" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -7506,7 +7778,7 @@
       <c r="BA46" s="3" t="inlineStr"/>
       <c r="BB46" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -7630,7 +7902,7 @@
       <c r="BA47" s="3" t="inlineStr"/>
       <c r="BB47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -7810,7 +8082,7 @@
       </c>
       <c r="BB48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -7990,7 +8262,7 @@
       </c>
       <c r="BB49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -8174,7 +8446,7 @@
       </c>
       <c r="BB50" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -8358,7 +8630,7 @@
       </c>
       <c r="BB51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -8544,7 +8816,7 @@
       </c>
       <c r="BB52" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -8728,7 +9000,7 @@
       </c>
       <c r="BB53" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -8914,7 +9186,7 @@
       </c>
       <c r="BB54" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -9100,7 +9372,7 @@
       </c>
       <c r="BB55" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -9286,7 +9558,7 @@
       </c>
       <c r="BB56" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9742,7 @@
       </c>
       <c r="BB57" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -9654,7 +9926,7 @@
       </c>
       <c r="BB58" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -9840,7 +10112,7 @@
       </c>
       <c r="BB59" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -10026,7 +10298,7 @@
       </c>
       <c r="BB60" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -10212,7 +10484,7 @@
       </c>
       <c r="BB61" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -10398,7 +10670,7 @@
       </c>
       <c r="BB62" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -10576,7 +10848,7 @@
       </c>
       <c r="BB63" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -10752,7 +11024,7 @@
       </c>
       <c r="BB64" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -10928,7 +11200,7 @@
       </c>
       <c r="BB65" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11378,7 @@
       </c>
       <c r="BB66" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -11284,7 +11556,7 @@
       </c>
       <c r="BB67" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -11462,7 +11734,7 @@
       </c>
       <c r="BB68" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -11640,7 +11912,7 @@
       </c>
       <c r="BB69" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -11816,7 +12088,7 @@
       </c>
       <c r="BB70" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -11992,7 +12264,7 @@
       </c>
       <c r="BB71" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -12168,7 +12440,7 @@
       </c>
       <c r="BB72" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_daily_2026-08-06.xlsx
+++ b/reports/telegram/aegis_daily_2026-08-06.xlsx
@@ -944,7 +944,7 @@
       </c>
       <c r="BB2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="BB3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="BB4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="BB5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BB6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="BB7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="BB8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="BB9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="BB10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="BB11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="BB12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="BB13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="BB14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="BB15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="BB16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="BB17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BB18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="BB19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="BB20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="BB21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="BB22" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="BB23" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="BB24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -4874,7 +4874,7 @@
       </c>
       <c r="BB25" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="BB26" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="BB27" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="BB28" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="BB29" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -5662,7 +5662,7 @@
       </c>
       <c r="BB30" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="BB31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="BB32" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="BB33" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       <c r="BA34" s="3" t="inlineStr"/>
       <c r="BB34" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -6354,7 +6354,7 @@
       <c r="BA35" s="3" t="inlineStr"/>
       <c r="BB35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -6478,7 +6478,7 @@
       <c r="BA36" s="3" t="inlineStr"/>
       <c r="BB36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -6602,7 +6602,7 @@
       <c r="BA37" s="3" t="inlineStr"/>
       <c r="BB37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="BB38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -6882,7 +6882,7 @@
       <c r="BA39" s="3" t="inlineStr"/>
       <c r="BB39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -7006,7 +7006,7 @@
       <c r="BA40" s="3" t="inlineStr"/>
       <c r="BB40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       <c r="BA41" s="3" t="inlineStr"/>
       <c r="BB41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -7254,7 +7254,7 @@
       <c r="BA42" s="3" t="inlineStr"/>
       <c r="BB42" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -7378,7 +7378,7 @@
       <c r="BA43" s="3" t="inlineStr"/>
       <c r="BB43" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -7502,7 +7502,7 @@
       <c r="BA44" s="3" t="inlineStr"/>
       <c r="BB44" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="BB45" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -7778,7 +7778,7 @@
       <c r="BA46" s="3" t="inlineStr"/>
       <c r="BB46" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       <c r="BA47" s="3" t="inlineStr"/>
       <c r="BB47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="BB48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -8262,7 +8262,7 @@
       </c>
       <c r="BB49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="BB50" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="BB51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -8816,7 +8816,7 @@
       </c>
       <c r="BB52" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -9000,7 +9000,7 @@
       </c>
       <c r="BB53" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -9186,7 +9186,7 @@
       </c>
       <c r="BB54" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="BB55" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="BB56" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -9742,7 +9742,7 @@
       </c>
       <c r="BB57" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -9926,7 +9926,7 @@
       </c>
       <c r="BB58" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="BB59" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -10298,7 +10298,7 @@
       </c>
       <c r="BB60" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -10484,7 +10484,7 @@
       </c>
       <c r="BB61" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -10670,7 +10670,7 @@
       </c>
       <c r="BB62" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -10848,7 +10848,7 @@
       </c>
       <c r="BB63" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -11024,7 +11024,7 @@
       </c>
       <c r="BB64" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -11200,7 +11200,7 @@
       </c>
       <c r="BB65" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -11378,7 +11378,7 @@
       </c>
       <c r="BB66" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -11556,7 +11556,7 @@
       </c>
       <c r="BB67" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="BB68" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -11912,7 +11912,7 @@
       </c>
       <c r="BB69" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -12088,7 +12088,7 @@
       </c>
       <c r="BB70" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -12264,7 +12264,7 @@
       </c>
       <c r="BB71" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -12440,7 +12440,7 @@
       </c>
       <c r="BB72" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_daily_2026-08-06.xlsx
+++ b/reports/telegram/aegis_daily_2026-08-06.xlsx
@@ -833,14 +833,14 @@
       </c>
       <c r="Q2" s="3" t="inlineStr"/>
       <c r="R2" s="3" t="n">
-        <v>36.6</v>
+        <v>38.6</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr"/>
@@ -884,7 +884,7 @@
         <v>2421.9</v>
       </c>
       <c r="AI2" s="3" t="n">
-        <v>2258.5</v>
+        <v>2452.2</v>
       </c>
       <c r="AJ2" s="3" t="n">
         <v>2397.68</v>
@@ -896,19 +896,19 @@
         <v>2276.59</v>
       </c>
       <c r="AM2" s="3" t="n">
-        <v>0.8</v>
+        <v>-7.16</v>
       </c>
       <c r="AN2" s="3" t="n">
         <v>2712.53</v>
       </c>
       <c r="AO2" s="3" t="n">
-        <v>20.1</v>
+        <v>10.62</v>
       </c>
       <c r="AP2" s="3" t="n">
         <v>3003.16</v>
       </c>
       <c r="AQ2" s="3" t="n">
-        <v>32.97</v>
+        <v>22.47</v>
       </c>
       <c r="AR2" s="3" t="n">
         <v>2460</v>
@@ -917,13 +917,13 @@
         <v>-1.55</v>
       </c>
       <c r="AT2" s="3" t="n">
-        <v>7.23</v>
+        <v>-1.24</v>
       </c>
       <c r="AU2" s="3" t="n">
-        <v>8.58</v>
+        <v>0.32</v>
       </c>
       <c r="AV2" s="3" t="n">
-        <v>0</v>
+        <v>-4.11</v>
       </c>
       <c r="AW2" s="3" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="BB2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -1011,14 +1011,14 @@
       </c>
       <c r="Q3" s="3" t="inlineStr"/>
       <c r="R3" s="3" t="n">
-        <v>43.6</v>
+        <v>45.6</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr"/>
@@ -1062,7 +1062,7 @@
         <v>11727</v>
       </c>
       <c r="AI3" s="3" t="n">
-        <v>11602</v>
+        <v>11427</v>
       </c>
       <c r="AJ3" s="3" t="n">
         <v>11609.73</v>
@@ -1074,19 +1074,19 @@
         <v>11023.38</v>
       </c>
       <c r="AM3" s="3" t="n">
-        <v>-4.99</v>
+        <v>-3.53</v>
       </c>
       <c r="AN3" s="3" t="n">
         <v>13134.24</v>
       </c>
       <c r="AO3" s="3" t="n">
-        <v>13.21</v>
+        <v>14.94</v>
       </c>
       <c r="AP3" s="3" t="n">
         <v>14541.48</v>
       </c>
       <c r="AQ3" s="3" t="n">
-        <v>25.34</v>
+        <v>27.26</v>
       </c>
       <c r="AR3" s="3" t="n">
         <v>11600</v>
@@ -1095,13 +1095,13 @@
         <v>1.09</v>
       </c>
       <c r="AT3" s="3" t="n">
-        <v>1.08</v>
+        <v>2.63</v>
       </c>
       <c r="AU3" s="3" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AV3" s="3" t="n">
-        <v>-4.54</v>
+        <v>-3.08</v>
       </c>
       <c r="AW3" s="3" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="BB3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -1185,14 +1185,14 @@
       </c>
       <c r="Q4" s="3" t="inlineStr"/>
       <c r="R4" s="3" t="n">
-        <v>32.2</v>
+        <v>34.2</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr"/>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="BB4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -1355,14 +1355,14 @@
       </c>
       <c r="Q5" s="3" t="inlineStr"/>
       <c r="R5" s="3" t="n">
-        <v>32.5</v>
+        <v>34.5</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr"/>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="BB5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -1531,14 +1531,14 @@
       </c>
       <c r="Q6" s="3" t="inlineStr"/>
       <c r="R6" s="3" t="n">
-        <v>40.4</v>
+        <v>42.4</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr"/>
@@ -1546,7 +1546,7 @@
       <c r="W6" s="3" t="inlineStr"/>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>🟡 WAIT (Δ+5.9%) · Rank ↑ 8→5 · Conf 43% · band STRONG · 16d left · → HOLD</t>
+          <t>🟢 BUY (Δ-0.6%) · Rank ↑ 8→5 · Conf 43% · band STRONG · 16d left · → HOLD</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr"/>
@@ -1582,28 +1582,28 @@
         <v>1351.3</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>1263.5</v>
+        <v>1346.6</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>1250.87</v>
+        <v>1333.13</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>1276.13</v>
+        <v>1360.07</v>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>1200.33</v>
+        <v>1279.27</v>
       </c>
       <c r="AM6" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>1364.58</v>
+        <v>1454.33</v>
       </c>
       <c r="AO6" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AP6" s="3" t="n">
-        <v>1453.02</v>
+        <v>1548.59</v>
       </c>
       <c r="AQ6" s="3" t="n">
         <v>15</v>
@@ -1615,13 +1615,13 @@
         <v>-1.36</v>
       </c>
       <c r="AT6" s="3" t="n">
-        <v>6.95</v>
+        <v>0.35</v>
       </c>
       <c r="AU6" s="3" t="n">
-        <v>6.58</v>
+        <v>1.73</v>
       </c>
       <c r="AV6" s="3" t="n">
-        <v>0</v>
+        <v>-2.03</v>
       </c>
       <c r="AW6" s="3" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BB6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -1703,14 +1703,14 @@
       </c>
       <c r="Q7" s="3" t="inlineStr"/>
       <c r="R7" s="3" t="n">
-        <v>36.6</v>
+        <v>38.6</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr"/>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="BB7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-3.34</v>
+        <v>0.65</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>7</v>
@@ -1877,14 +1877,14 @@
       </c>
       <c r="Q8" s="3" t="inlineStr"/>
       <c r="R8" s="3" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr"/>
@@ -1928,28 +1928,28 @@
         <v>443.9</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>459.25</v>
+        <v>441.05</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>454.66</v>
+        <v>436.64</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>463.84</v>
+        <v>445.46</v>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>436.29</v>
+        <v>419</v>
       </c>
       <c r="AM8" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AN8" s="3" t="n">
-        <v>495.99</v>
+        <v>476.33</v>
       </c>
       <c r="AO8" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AP8" s="3" t="n">
-        <v>528.14</v>
+        <v>507.21</v>
       </c>
       <c r="AQ8" s="3" t="n">
         <v>15</v>
@@ -1961,7 +1961,7 @@
         <v>-1.36</v>
       </c>
       <c r="AT8" s="3" t="n">
-        <v>-3.34</v>
+        <v>0.65</v>
       </c>
       <c r="AU8" s="3" t="n">
         <v>0</v>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="BB8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="J9" s="3" t="n">
-        <v>11.75</v>
+        <v>8.75</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>8</v>
@@ -2063,14 +2063,14 @@
       </c>
       <c r="Q9" s="3" t="inlineStr"/>
       <c r="R9" s="3" t="n">
-        <v>35.6</v>
+        <v>37.6</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr"/>
@@ -2114,28 +2114,28 @@
         <v>5651.5</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>5057.4</v>
+        <v>5196.6</v>
       </c>
       <c r="AJ9" s="3" t="n">
-        <v>5006.83</v>
+        <v>5144.63</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>5107.97</v>
+        <v>5248.57</v>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>4804.53</v>
+        <v>4936.77</v>
       </c>
       <c r="AM9" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AN9" s="3" t="n">
-        <v>5461.99</v>
+        <v>5612.33</v>
       </c>
       <c r="AO9" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AP9" s="3" t="n">
-        <v>5816.01</v>
+        <v>5976.09</v>
       </c>
       <c r="AQ9" s="3" t="n">
         <v>15</v>
@@ -2147,13 +2147,13 @@
         <v>1.87</v>
       </c>
       <c r="AT9" s="3" t="n">
-        <v>11.75</v>
+        <v>8.75</v>
       </c>
       <c r="AU9" s="3" t="n">
-        <v>5.66</v>
+        <v>6.76</v>
       </c>
       <c r="AV9" s="3" t="n">
-        <v>0</v>
+        <v>-0.91</v>
       </c>
       <c r="AW9" s="3" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="BB9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="J10" s="3" t="n">
-        <v>6.82</v>
+        <v>5.81</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>9</v>
@@ -2249,14 +2249,14 @@
       </c>
       <c r="Q10" s="3" t="inlineStr"/>
       <c r="R10" s="3" t="n">
-        <v>30.6</v>
+        <v>32.6</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr"/>
@@ -2300,28 +2300,28 @@
         <v>278.8</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>261</v>
+        <v>263.5</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>258.39</v>
+        <v>260.87</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>263.61</v>
+        <v>266.13</v>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>247.95</v>
+        <v>250.32</v>
       </c>
       <c r="AM10" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AN10" s="3" t="n">
-        <v>281.88</v>
+        <v>284.58</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AP10" s="3" t="n">
-        <v>300.15</v>
+        <v>303.02</v>
       </c>
       <c r="AQ10" s="3" t="n">
         <v>15</v>
@@ -2333,10 +2333,10 @@
         <v>3.64</v>
       </c>
       <c r="AT10" s="3" t="n">
-        <v>6.82</v>
+        <v>5.81</v>
       </c>
       <c r="AU10" s="3" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="AV10" s="3" t="n">
         <v>0</v>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="BB10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -2427,14 +2427,14 @@
       </c>
       <c r="Q11" s="3" t="inlineStr"/>
       <c r="R11" s="3" t="n">
-        <v>37.9</v>
+        <v>39.9</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr"/>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="BB11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>2.63</v>
+        <v>1.94</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>11</v>
@@ -2609,14 +2609,14 @@
       </c>
       <c r="Q12" s="3" t="inlineStr"/>
       <c r="R12" s="3" t="n">
-        <v>21.3</v>
+        <v>23.3</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr"/>
@@ -2660,28 +2660,28 @@
         <v>7531.5</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>7338.5</v>
+        <v>7388.5</v>
       </c>
       <c r="AJ12" s="3" t="n">
-        <v>7265.11</v>
+        <v>7314.61</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>7411.89</v>
+        <v>7462.39</v>
       </c>
       <c r="AL12" s="3" t="n">
-        <v>6971.57</v>
+        <v>7019.07</v>
       </c>
       <c r="AM12" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AN12" s="3" t="n">
-        <v>7925.58</v>
+        <v>7979.58</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AP12" s="3" t="n">
-        <v>8439.27</v>
+        <v>8496.77</v>
       </c>
       <c r="AQ12" s="3" t="n">
         <v>15</v>
@@ -2693,10 +2693,10 @@
         <v>1.85</v>
       </c>
       <c r="AT12" s="3" t="n">
-        <v>2.63</v>
+        <v>1.94</v>
       </c>
       <c r="AU12" s="3" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="AV12" s="3" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="BB12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.74</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>12</v>
@@ -2795,14 +2795,14 @@
       </c>
       <c r="Q13" s="3" t="inlineStr"/>
       <c r="R13" s="3" t="n">
-        <v>27.2</v>
+        <v>29.2</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr"/>
@@ -2846,28 +2846,28 @@
         <v>428.2</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>429.4</v>
+        <v>431.4</v>
       </c>
       <c r="AJ13" s="3" t="n">
-        <v>425.11</v>
+        <v>427.09</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>433.69</v>
+        <v>435.71</v>
       </c>
       <c r="AL13" s="3" t="n">
-        <v>407.93</v>
+        <v>409.83</v>
       </c>
       <c r="AM13" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AN13" s="3" t="n">
-        <v>463.75</v>
+        <v>465.91</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AP13" s="3" t="n">
-        <v>493.81</v>
+        <v>496.11</v>
       </c>
       <c r="AQ13" s="3" t="n">
         <v>15</v>
@@ -2879,13 +2879,13 @@
         <v>1.47</v>
       </c>
       <c r="AT13" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.74</v>
       </c>
       <c r="AU13" s="3" t="n">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="AV13" s="3" t="n">
-        <v>-0.91</v>
+        <v>-2.18</v>
       </c>
       <c r="AW13" s="3" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="BB13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -2973,14 +2973,14 @@
       </c>
       <c r="Q14" s="3" t="inlineStr"/>
       <c r="R14" s="3" t="n">
-        <v>22.1</v>
+        <v>24.1</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr"/>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="BB14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -3147,14 +3147,14 @@
       </c>
       <c r="Q15" s="3" t="inlineStr"/>
       <c r="R15" s="3" t="n">
-        <v>22.1</v>
+        <v>24.1</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr"/>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="BB15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.63</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>15</v>
@@ -3321,14 +3321,14 @@
       </c>
       <c r="Q16" s="3" t="inlineStr"/>
       <c r="R16" s="3" t="n">
-        <v>21.3</v>
+        <v>23.3</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr"/>
@@ -3372,28 +3372,28 @@
         <v>1296.8</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>1298.9</v>
+        <v>1305</v>
       </c>
       <c r="AJ16" s="3" t="n">
-        <v>1285.91</v>
+        <v>1291.95</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>1311.89</v>
+        <v>1318.05</v>
       </c>
       <c r="AL16" s="3" t="n">
-        <v>1233.95</v>
+        <v>1239.75</v>
       </c>
       <c r="AM16" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AN16" s="3" t="n">
-        <v>1402.81</v>
+        <v>1409.4</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AP16" s="3" t="n">
-        <v>1493.73</v>
+        <v>1500.75</v>
       </c>
       <c r="AQ16" s="3" t="n">
         <v>15</v>
@@ -3405,7 +3405,7 @@
         <v>-2.33</v>
       </c>
       <c r="AT16" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.63</v>
       </c>
       <c r="AU16" s="3" t="n">
         <v>0</v>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="BB16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="BB17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BB18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
         <v>2390.4</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>2376.2</v>
+        <v>2443.4</v>
       </c>
       <c r="AJ19" s="3" t="n">
         <v>2329</v>
@@ -3866,19 +3866,19 @@
         <v>2270.88</v>
       </c>
       <c r="AM19" s="3" t="n">
-        <v>-4.43</v>
+        <v>-7.06</v>
       </c>
       <c r="AN19" s="3" t="n">
         <v>2581.632</v>
       </c>
       <c r="AO19" s="3" t="n">
-        <v>8.65</v>
+        <v>5.66</v>
       </c>
       <c r="AP19" s="3" t="n">
         <v>2762.34624</v>
       </c>
       <c r="AQ19" s="3" t="n">
-        <v>16.25</v>
+        <v>13.05</v>
       </c>
       <c r="AR19" s="3" t="n">
         <v>2410</v>
@@ -3887,10 +3887,10 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="AT19" s="3" t="n">
-        <v>0.6</v>
+        <v>-2.17</v>
       </c>
       <c r="AU19" s="3" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="AV19" s="3" t="n">
         <v>0</v>
@@ -3910,11 +3910,11 @@
         <v>5</v>
       </c>
       <c r="BA19" s="3" t="n">
-        <v>8.65</v>
+        <v>5.66</v>
       </c>
       <c r="BB19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="BB20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="BB21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="BB22" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="BB23" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
         <v>285.8</v>
       </c>
       <c r="AI24" s="3" t="n">
-        <v>280.95</v>
+        <v>287.2</v>
       </c>
       <c r="AJ24" s="3" t="n">
         <v>279</v>
@@ -4666,19 +4666,19 @@
         <v>271.51</v>
       </c>
       <c r="AM24" s="3" t="n">
-        <v>-3.36</v>
+        <v>-5.46</v>
       </c>
       <c r="AN24" s="3" t="n">
         <v>287</v>
       </c>
       <c r="AO24" s="3" t="n">
-        <v>2.15</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AP24" s="3" t="n">
         <v>307.09</v>
       </c>
       <c r="AQ24" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>6.93</v>
       </c>
       <c r="AR24" s="3" t="n">
         <v>289</v>
@@ -4687,13 +4687,13 @@
         <v>-1.11</v>
       </c>
       <c r="AT24" s="3" t="n">
-        <v>1.73</v>
+        <v>-0.49</v>
       </c>
       <c r="AU24" s="3" t="n">
-        <v>2.22</v>
+        <v>1.64</v>
       </c>
       <c r="AV24" s="3" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="AW24" s="3" t="inlineStr">
         <is>
@@ -4710,11 +4710,11 @@
         <v>5</v>
       </c>
       <c r="BA24" s="3" t="n">
-        <v>2.15</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="BB24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -4874,7 +4874,7 @@
       </c>
       <c r="BB25" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="BB26" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -5138,7 +5138,7 @@
         <v>414</v>
       </c>
       <c r="AI27" s="3" t="n">
-        <v>426.65</v>
+        <v>410.5</v>
       </c>
       <c r="AJ27" s="3" t="n">
         <v>401</v>
@@ -5150,19 +5150,19 @@
         <v>393.3</v>
       </c>
       <c r="AM27" s="3" t="n">
-        <v>-7.82</v>
+        <v>-4.19</v>
       </c>
       <c r="AN27" s="3" t="n">
         <v>447.12</v>
       </c>
       <c r="AO27" s="3" t="n">
-        <v>4.8</v>
+        <v>8.92</v>
       </c>
       <c r="AP27" s="3" t="n">
         <v>478.4184</v>
       </c>
       <c r="AQ27" s="3" t="n">
-        <v>12.13</v>
+        <v>16.55</v>
       </c>
       <c r="AR27" s="3" t="n">
         <v>417.6</v>
@@ -5171,13 +5171,13 @@
         <v>-0.85</v>
       </c>
       <c r="AT27" s="3" t="n">
-        <v>-2.96</v>
+        <v>0.85</v>
       </c>
       <c r="AU27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AV27" s="3" t="n">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="AW27" s="3" t="inlineStr">
         <is>
@@ -5194,11 +5194,11 @@
         <v>5</v>
       </c>
       <c r="BA27" s="3" t="n">
-        <v>4.8</v>
+        <v>8.92</v>
       </c>
       <c r="BB27" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="BB28" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
       <c r="W29" s="3" t="inlineStr"/>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank ↑ 3→1 · Conf 52% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-0.8%) · Rank ↑ 3→1 · Conf 52% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr"/>
@@ -5453,31 +5453,31 @@
         </is>
       </c>
       <c r="AH29" s="3" t="n">
-        <v>2376.2</v>
+        <v>2447</v>
       </c>
       <c r="AI29" s="3" t="n">
-        <v>2376.2</v>
+        <v>2443.4</v>
       </c>
       <c r="AJ29" s="3" t="n">
-        <v>2352.44</v>
+        <v>2418.97</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>2399.96</v>
+        <v>2467.83</v>
       </c>
       <c r="AL29" s="3" t="n">
-        <v>2257.39</v>
+        <v>2321.23</v>
       </c>
       <c r="AM29" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AN29" s="3" t="n">
-        <v>2566.296</v>
+        <v>2638.872</v>
       </c>
       <c r="AO29" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AP29" s="3" t="n">
-        <v>2732.63</v>
+        <v>2809.91</v>
       </c>
       <c r="AQ29" s="3" t="n">
         <v>15</v>
@@ -5489,10 +5489,10 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="AT29" s="3" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="AU29" s="3" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="AV29" s="3" t="n">
         <v>0</v>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="BB29" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -5574,7 +5574,7 @@
       <c r="W30" s="3" t="inlineStr"/>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #4 · Conf 32% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.3%) · Rank #4 · Conf 32% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr"/>
@@ -5605,31 +5605,31 @@
         </is>
       </c>
       <c r="AH30" s="3" t="n">
-        <v>109.29</v>
+        <v>111.08</v>
       </c>
       <c r="AI30" s="3" t="n">
-        <v>109.29</v>
+        <v>111.44</v>
       </c>
       <c r="AJ30" s="3" t="n">
-        <v>108.2</v>
+        <v>110.33</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>110.38</v>
+        <v>112.55</v>
       </c>
       <c r="AL30" s="3" t="n">
-        <v>103.8255</v>
+        <v>105.868</v>
       </c>
       <c r="AM30" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AN30" s="3" t="n">
-        <v>118.0332</v>
+        <v>120.3552</v>
       </c>
       <c r="AO30" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AP30" s="3" t="n">
-        <v>125.6835</v>
+        <v>128.156</v>
       </c>
       <c r="AQ30" s="3" t="n">
         <v>15</v>
@@ -5641,13 +5641,13 @@
         <v>-0.39</v>
       </c>
       <c r="AT30" s="3" t="n">
-        <v>0</v>
+        <v>-0.32</v>
       </c>
       <c r="AU30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AV30" s="3" t="n">
-        <v>0</v>
+        <v>-0.32</v>
       </c>
       <c r="AW30" s="3" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
       </c>
       <c r="BB30" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -5730,7 +5730,7 @@
       <c r="W31" s="3" t="inlineStr"/>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank ↑ 10→5 · Conf 36% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.1%) · Rank ↑ 10→5 · Conf 36% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr"/>
@@ -5761,31 +5761,31 @@
         </is>
       </c>
       <c r="AH31" s="3" t="n">
-        <v>426.65</v>
+        <v>410.05</v>
       </c>
       <c r="AI31" s="3" t="n">
-        <v>426.65</v>
+        <v>410.5</v>
       </c>
       <c r="AJ31" s="3" t="n">
-        <v>422.38</v>
+        <v>406.39</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>430.92</v>
+        <v>414.61</v>
       </c>
       <c r="AL31" s="3" t="n">
-        <v>405.3174999999999</v>
+        <v>389.975</v>
       </c>
       <c r="AM31" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AN31" s="3" t="n">
-        <v>460.782</v>
+        <v>443.34</v>
       </c>
       <c r="AO31" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AP31" s="3" t="n">
-        <v>490.6474999999999</v>
+        <v>472.075</v>
       </c>
       <c r="AQ31" s="3" t="n">
         <v>15</v>
@@ -5797,13 +5797,13 @@
         <v>-0.85</v>
       </c>
       <c r="AT31" s="3" t="n">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="AU31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AV31" s="3" t="n">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="AW31" s="3" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="BB31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -5882,7 +5882,7 @@
       <c r="W32" s="3" t="inlineStr"/>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #10 · Conf 38% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-0.1%) · Rank #10 · Conf 38% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr"/>
@@ -5913,31 +5913,31 @@
         </is>
       </c>
       <c r="AH32" s="3" t="n">
-        <v>526.45</v>
+        <v>536.7</v>
       </c>
       <c r="AI32" s="3" t="n">
-        <v>526.45</v>
+        <v>531.9</v>
       </c>
       <c r="AJ32" s="3" t="n">
-        <v>521.1900000000001</v>
+        <v>526.58</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>531.71</v>
+        <v>537.22</v>
       </c>
       <c r="AL32" s="3" t="n">
-        <v>500.1275</v>
+        <v>505.3049999999999</v>
       </c>
       <c r="AM32" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AN32" s="3" t="n">
-        <v>568.566</v>
+        <v>574.452</v>
       </c>
       <c r="AO32" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AP32" s="3" t="n">
-        <v>605.4175</v>
+        <v>611.6849999999999</v>
       </c>
       <c r="AQ32" s="3" t="n">
         <v>15</v>
@@ -5949,10 +5949,10 @@
         <v>6.16</v>
       </c>
       <c r="AT32" s="3" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="AU32" s="3" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="AV32" s="3" t="n">
         <v>0</v>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="BB32" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       <c r="W33" s="3" t="inlineStr"/>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #15 · Conf 24% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.2%) · Rank #15 · Conf 24% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr"/>
@@ -6065,31 +6065,31 @@
         </is>
       </c>
       <c r="AH33" s="3" t="n">
-        <v>673.7</v>
+        <v>698.35</v>
       </c>
       <c r="AI33" s="3" t="n">
-        <v>673.7</v>
+        <v>700</v>
       </c>
       <c r="AJ33" s="3" t="n">
-        <v>666.96</v>
+        <v>693</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>680.4400000000001</v>
+        <v>707</v>
       </c>
       <c r="AL33" s="3" t="n">
-        <v>640.015</v>
+        <v>665</v>
       </c>
       <c r="AM33" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AN33" s="3" t="n">
-        <v>727.5960000000001</v>
+        <v>756</v>
       </c>
       <c r="AO33" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AP33" s="3" t="n">
-        <v>774.755</v>
+        <v>804.9999999999999</v>
       </c>
       <c r="AQ33" s="3" t="n">
         <v>15</v>
@@ -6101,13 +6101,13 @@
         <v>3.02</v>
       </c>
       <c r="AT33" s="3" t="n">
-        <v>0</v>
+        <v>-0.24</v>
       </c>
       <c r="AU33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AV33" s="3" t="n">
-        <v>0</v>
+        <v>-0.24</v>
       </c>
       <c r="AW33" s="3" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="BB33" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       <c r="BA34" s="3" t="inlineStr"/>
       <c r="BB34" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -6354,7 +6354,7 @@
       <c r="BA35" s="3" t="inlineStr"/>
       <c r="BB35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -6478,7 +6478,7 @@
       <c r="BA36" s="3" t="inlineStr"/>
       <c r="BB36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -6602,7 +6602,7 @@
       <c r="BA37" s="3" t="inlineStr"/>
       <c r="BB37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -6670,7 +6670,7 @@
       <c r="W38" s="3" t="inlineStr"/>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 3→3 · Conf 72% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-0.8%) · Rank → 3→3 · Conf 72% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr"/>
@@ -6701,31 +6701,31 @@
         </is>
       </c>
       <c r="AH38" s="3" t="n">
-        <v>2376.2</v>
+        <v>2447</v>
       </c>
       <c r="AI38" s="3" t="n">
-        <v>2376.2</v>
+        <v>2443.4</v>
       </c>
       <c r="AJ38" s="3" t="n">
-        <v>2352.44</v>
+        <v>2418.97</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>2399.96</v>
+        <v>2467.83</v>
       </c>
       <c r="AL38" s="3" t="n">
-        <v>2257.39</v>
+        <v>2321.23</v>
       </c>
       <c r="AM38" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AN38" s="3" t="n">
-        <v>2566.296</v>
+        <v>2638.872</v>
       </c>
       <c r="AO38" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AP38" s="3" t="n">
-        <v>2732.63</v>
+        <v>2809.91</v>
       </c>
       <c r="AQ38" s="3" t="n">
         <v>15</v>
@@ -6737,10 +6737,10 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="AT38" s="3" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="AU38" s="3" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="AV38" s="3" t="n">
         <v>0</v>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="BB38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -6882,7 +6882,7 @@
       <c r="BA39" s="3" t="inlineStr"/>
       <c r="BB39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -7006,7 +7006,7 @@
       <c r="BA40" s="3" t="inlineStr"/>
       <c r="BB40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       <c r="BA41" s="3" t="inlineStr"/>
       <c r="BB41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -7254,7 +7254,7 @@
       <c r="BA42" s="3" t="inlineStr"/>
       <c r="BB42" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -7378,7 +7378,7 @@
       <c r="BA43" s="3" t="inlineStr"/>
       <c r="BB43" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -7502,7 +7502,7 @@
       <c r="BA44" s="3" t="inlineStr"/>
       <c r="BB44" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -7570,7 +7570,7 @@
       <c r="W45" s="3" t="inlineStr"/>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 10→10 · Conf 66% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.1%) · Rank → 10→10 · Conf 66% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr"/>
@@ -7601,31 +7601,31 @@
         </is>
       </c>
       <c r="AH45" s="3" t="n">
-        <v>426.65</v>
+        <v>410.05</v>
       </c>
       <c r="AI45" s="3" t="n">
-        <v>426.65</v>
+        <v>410.5</v>
       </c>
       <c r="AJ45" s="3" t="n">
-        <v>422.38</v>
+        <v>406.39</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>430.92</v>
+        <v>414.61</v>
       </c>
       <c r="AL45" s="3" t="n">
-        <v>405.3174999999999</v>
+        <v>389.975</v>
       </c>
       <c r="AM45" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AN45" s="3" t="n">
-        <v>460.782</v>
+        <v>443.34</v>
       </c>
       <c r="AO45" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AP45" s="3" t="n">
-        <v>490.6474999999999</v>
+        <v>472.075</v>
       </c>
       <c r="AQ45" s="3" t="n">
         <v>15</v>
@@ -7637,13 +7637,13 @@
         <v>-0.85</v>
       </c>
       <c r="AT45" s="3" t="n">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="AU45" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AV45" s="3" t="n">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="AW45" s="3" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="BB45" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -7778,7 +7778,7 @@
       <c r="BA46" s="3" t="inlineStr"/>
       <c r="BB46" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       <c r="BA47" s="3" t="inlineStr"/>
       <c r="BB47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -8026,7 +8026,7 @@
         <v>368.98</v>
       </c>
       <c r="AI48" s="3" t="n">
-        <v>368.98</v>
+        <v>389.01</v>
       </c>
       <c r="AJ48" s="3" t="n">
         <v>365.29</v>
@@ -8038,30 +8038,34 @@
         <v>346.84</v>
       </c>
       <c r="AM48" s="3" t="n">
-        <v>-6</v>
+        <v>-10.84</v>
       </c>
       <c r="AN48" s="3" t="n">
         <v>413.26</v>
       </c>
       <c r="AO48" s="3" t="n">
-        <v>12</v>
+        <v>6.23</v>
       </c>
       <c r="AP48" s="3" t="n">
         <v>457.54</v>
       </c>
       <c r="AQ48" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AR48" s="3" t="inlineStr"/>
-      <c r="AS48" s="3" t="inlineStr"/>
+        <v>17.62</v>
+      </c>
+      <c r="AR48" s="3" t="n">
+        <v>377.15</v>
+      </c>
+      <c r="AS48" s="3" t="n">
+        <v>1.41</v>
+      </c>
       <c r="AT48" s="3" t="n">
-        <v>0</v>
+        <v>-5.15</v>
       </c>
       <c r="AU48" s="3" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AV48" s="3" t="n">
-        <v>0</v>
+        <v>-3.77</v>
       </c>
       <c r="AW48" s="3" t="inlineStr">
         <is>
@@ -8078,11 +8082,11 @@
         <v>3</v>
       </c>
       <c r="BA48" s="3" t="n">
-        <v>12</v>
+        <v>6.23</v>
       </c>
       <c r="BB48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -8166,13 +8170,11 @@
       <c r="U49" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="V49" s="3" t="n">
-        <v>0.184</v>
-      </c>
+      <c r="V49" s="3" t="inlineStr"/>
       <c r="W49" s="3" t="inlineStr"/>
       <c r="X49" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 2→2 · Conf 54% · band STRONG · 14d left · → HOLD</t>
+          <t>🟢 BUY (Δ-3.7%) · Rank → 2→2 · Conf 54% · band STRONG · 14d left · → HOLD</t>
         </is>
       </c>
       <c r="Y49" s="3" t="inlineStr"/>
@@ -8208,42 +8210,46 @@
         <v>358.56</v>
       </c>
       <c r="AI49" s="3" t="n">
-        <v>358.56</v>
+        <v>368.73</v>
       </c>
       <c r="AJ49" s="3" t="n">
-        <v>354.97</v>
+        <v>365.04</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>362.15</v>
+        <v>372.42</v>
       </c>
       <c r="AL49" s="3" t="n">
-        <v>340.63</v>
+        <v>350.29</v>
       </c>
       <c r="AM49" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AN49" s="3" t="n">
-        <v>387.24</v>
+        <v>398.23</v>
       </c>
       <c r="AO49" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AP49" s="3" t="n">
-        <v>412.34</v>
+        <v>424.04</v>
       </c>
       <c r="AQ49" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="AR49" s="3" t="inlineStr"/>
-      <c r="AS49" s="3" t="inlineStr"/>
+      <c r="AR49" s="3" t="n">
+        <v>369.59</v>
+      </c>
+      <c r="AS49" s="3" t="n">
+        <v>-0.28</v>
+      </c>
       <c r="AT49" s="3" t="n">
-        <v>0</v>
+        <v>-2.76</v>
       </c>
       <c r="AU49" s="3" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AV49" s="3" t="n">
-        <v>0</v>
+        <v>-0.71</v>
       </c>
       <c r="AW49" s="3" t="inlineStr">
         <is>
@@ -8262,7 +8268,7 @@
       </c>
       <c r="BB49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -8313,7 +8319,7 @@
         </is>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0</v>
+        <v>6.74</v>
       </c>
       <c r="K50" s="3" t="n">
         <v>3</v>
@@ -8392,42 +8398,46 @@
         <v>202.81</v>
       </c>
       <c r="AI50" s="3" t="n">
-        <v>202.81</v>
+        <v>190.01</v>
       </c>
       <c r="AJ50" s="3" t="n">
-        <v>200.78</v>
+        <v>188.11</v>
       </c>
       <c r="AK50" s="3" t="n">
-        <v>204.84</v>
+        <v>191.91</v>
       </c>
       <c r="AL50" s="3" t="n">
-        <v>192.67</v>
+        <v>180.51</v>
       </c>
       <c r="AM50" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AN50" s="3" t="n">
-        <v>219.03</v>
+        <v>205.21</v>
       </c>
       <c r="AO50" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AP50" s="3" t="n">
-        <v>233.23</v>
+        <v>218.51</v>
       </c>
       <c r="AQ50" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="AR50" s="3" t="inlineStr"/>
-      <c r="AS50" s="3" t="inlineStr"/>
+      <c r="AR50" s="3" t="n">
+        <v>211.94</v>
+      </c>
+      <c r="AS50" s="3" t="n">
+        <v>3.43</v>
+      </c>
       <c r="AT50" s="3" t="n">
-        <v>0</v>
+        <v>6.74</v>
       </c>
       <c r="AU50" s="3" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AV50" s="3" t="n">
-        <v>-1.02</v>
+        <v>0</v>
       </c>
       <c r="AW50" s="3" t="inlineStr">
         <is>
@@ -8446,7 +8456,7 @@
       </c>
       <c r="BB50" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -8497,7 +8507,7 @@
         </is>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0</v>
+        <v>-1.05</v>
       </c>
       <c r="K51" s="3" t="n">
         <v>4</v>
@@ -8576,39 +8586,43 @@
         <v>341.1</v>
       </c>
       <c r="AI51" s="3" t="n">
-        <v>341.1</v>
+        <v>344.71</v>
       </c>
       <c r="AJ51" s="3" t="n">
-        <v>337.69</v>
+        <v>341.26</v>
       </c>
       <c r="AK51" s="3" t="n">
-        <v>344.51</v>
+        <v>348.16</v>
       </c>
       <c r="AL51" s="3" t="n">
-        <v>324.05</v>
+        <v>327.47</v>
       </c>
       <c r="AM51" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AN51" s="3" t="n">
-        <v>368.39</v>
+        <v>372.29</v>
       </c>
       <c r="AO51" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AP51" s="3" t="n">
-        <v>392.26</v>
+        <v>396.42</v>
       </c>
       <c r="AQ51" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="AR51" s="3" t="inlineStr"/>
-      <c r="AS51" s="3" t="inlineStr"/>
+      <c r="AR51" s="3" t="n">
+        <v>357.52</v>
+      </c>
+      <c r="AS51" s="3" t="n">
+        <v>0.48</v>
+      </c>
       <c r="AT51" s="3" t="n">
-        <v>0</v>
+        <v>-1.05</v>
       </c>
       <c r="AU51" s="3" t="n">
-        <v>3.13</v>
+        <v>2.05</v>
       </c>
       <c r="AV51" s="3" t="n">
         <v>0</v>
@@ -8630,7 +8644,7 @@
       </c>
       <c r="BB51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -8681,7 +8695,7 @@
         </is>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0</v>
+        <v>-6.68</v>
       </c>
       <c r="K52" s="3" t="n">
         <v>5</v>
@@ -8720,9 +8734,7 @@
       <c r="U52" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="V52" s="3" t="n">
-        <v>0.127</v>
-      </c>
+      <c r="V52" s="3" t="inlineStr"/>
       <c r="W52" s="3" t="inlineStr"/>
       <c r="X52" s="3" t="inlineStr">
         <is>
@@ -8762,39 +8774,43 @@
         <v>225.02</v>
       </c>
       <c r="AI52" s="3" t="n">
-        <v>225.02</v>
+        <v>241.12</v>
       </c>
       <c r="AJ52" s="3" t="n">
-        <v>222.77</v>
+        <v>238.71</v>
       </c>
       <c r="AK52" s="3" t="n">
-        <v>227.27</v>
+        <v>243.53</v>
       </c>
       <c r="AL52" s="3" t="n">
-        <v>213.77</v>
+        <v>229.06</v>
       </c>
       <c r="AM52" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AN52" s="3" t="n">
-        <v>243.02</v>
+        <v>260.41</v>
       </c>
       <c r="AO52" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AP52" s="3" t="n">
-        <v>258.77</v>
+        <v>277.29</v>
       </c>
       <c r="AQ52" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="AR52" s="3" t="inlineStr"/>
-      <c r="AS52" s="3" t="inlineStr"/>
+      <c r="AR52" s="3" t="n">
+        <v>248.79</v>
+      </c>
+      <c r="AS52" s="3" t="n">
+        <v>-0.27</v>
+      </c>
       <c r="AT52" s="3" t="n">
-        <v>0</v>
+        <v>-6.68</v>
       </c>
       <c r="AU52" s="3" t="n">
-        <v>8.01</v>
+        <v>0.8</v>
       </c>
       <c r="AV52" s="3" t="n">
         <v>0</v>
@@ -8816,7 +8832,7 @@
       </c>
       <c r="BB52" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -8867,7 +8883,7 @@
         </is>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="K53" s="3" t="n">
         <v>6</v>
@@ -8946,42 +8962,46 @@
         <v>1065.22</v>
       </c>
       <c r="AI53" s="3" t="n">
-        <v>1065.22</v>
+        <v>980.75</v>
       </c>
       <c r="AJ53" s="3" t="n">
-        <v>1054.57</v>
+        <v>970.9400000000001</v>
       </c>
       <c r="AK53" s="3" t="n">
-        <v>1075.87</v>
+        <v>990.5599999999999</v>
       </c>
       <c r="AL53" s="3" t="n">
-        <v>1011.96</v>
+        <v>931.71</v>
       </c>
       <c r="AM53" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AN53" s="3" t="n">
-        <v>1150.44</v>
+        <v>1059.21</v>
       </c>
       <c r="AO53" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AP53" s="3" t="n">
-        <v>1225</v>
+        <v>1127.86</v>
       </c>
       <c r="AQ53" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="AR53" s="3" t="inlineStr"/>
-      <c r="AS53" s="3" t="inlineStr"/>
+      <c r="AR53" s="3" t="n">
+        <v>1052.98</v>
+      </c>
+      <c r="AS53" s="3" t="n">
+        <v>0.7</v>
+      </c>
       <c r="AT53" s="3" t="n">
-        <v>0</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="AU53" s="3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AV53" s="3" t="n">
-        <v>-4.4</v>
+        <v>0</v>
       </c>
       <c r="AW53" s="3" t="inlineStr">
         <is>
@@ -9000,7 +9020,7 @@
       </c>
       <c r="BB53" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -9051,7 +9071,7 @@
         </is>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0</v>
+        <v>-1.32</v>
       </c>
       <c r="K54" s="3" t="n">
         <v>7</v>
@@ -9090,9 +9110,7 @@
       <c r="U54" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="V54" s="3" t="n">
-        <v>0.109</v>
-      </c>
+      <c r="V54" s="3" t="inlineStr"/>
       <c r="W54" s="3" t="inlineStr"/>
       <c r="X54" s="3" t="inlineStr">
         <is>
@@ -9132,42 +9150,46 @@
         <v>333.74</v>
       </c>
       <c r="AI54" s="3" t="n">
-        <v>333.74</v>
+        <v>338.19</v>
       </c>
       <c r="AJ54" s="3" t="n">
-        <v>330.4</v>
+        <v>334.81</v>
       </c>
       <c r="AK54" s="3" t="n">
-        <v>337.08</v>
+        <v>341.57</v>
       </c>
       <c r="AL54" s="3" t="n">
-        <v>317.05</v>
+        <v>321.28</v>
       </c>
       <c r="AM54" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AN54" s="3" t="n">
-        <v>360.44</v>
+        <v>365.25</v>
       </c>
       <c r="AO54" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AP54" s="3" t="n">
-        <v>383.8</v>
+        <v>388.92</v>
       </c>
       <c r="AQ54" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="AR54" s="3" t="inlineStr"/>
-      <c r="AS54" s="3" t="inlineStr"/>
+      <c r="AR54" s="3" t="n">
+        <v>309.38</v>
+      </c>
+      <c r="AS54" s="3" t="n">
+        <v>0.52</v>
+      </c>
       <c r="AT54" s="3" t="n">
-        <v>0</v>
+        <v>-1.32</v>
       </c>
       <c r="AU54" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AV54" s="3" t="n">
-        <v>-7.44</v>
+        <v>-8.66</v>
       </c>
       <c r="AW54" s="3" t="inlineStr">
         <is>
@@ -9186,7 +9208,7 @@
       </c>
       <c r="BB54" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -9237,7 +9259,7 @@
         </is>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0</v>
+        <v>-12.7</v>
       </c>
       <c r="K55" s="3" t="n">
         <v>8</v>
@@ -9276,9 +9298,7 @@
       <c r="U55" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="V55" s="3" t="n">
-        <v>0.15</v>
-      </c>
+      <c r="V55" s="3" t="inlineStr"/>
       <c r="W55" s="3" t="inlineStr"/>
       <c r="X55" s="3" t="inlineStr">
         <is>
@@ -9318,39 +9338,43 @@
         <v>393.82</v>
       </c>
       <c r="AI55" s="3" t="n">
-        <v>393.82</v>
+        <v>451.1</v>
       </c>
       <c r="AJ55" s="3" t="n">
-        <v>389.88</v>
+        <v>446.59</v>
       </c>
       <c r="AK55" s="3" t="n">
-        <v>397.76</v>
+        <v>455.61</v>
       </c>
       <c r="AL55" s="3" t="n">
-        <v>374.13</v>
+        <v>428.55</v>
       </c>
       <c r="AM55" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AN55" s="3" t="n">
-        <v>425.33</v>
+        <v>487.19</v>
       </c>
       <c r="AO55" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AP55" s="3" t="n">
-        <v>452.89</v>
+        <v>518.76</v>
       </c>
       <c r="AQ55" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="AR55" s="3" t="inlineStr"/>
-      <c r="AS55" s="3" t="inlineStr"/>
+      <c r="AR55" s="3" t="n">
+        <v>492.81</v>
+      </c>
+      <c r="AS55" s="3" t="n">
+        <v>-1.09</v>
+      </c>
       <c r="AT55" s="3" t="n">
-        <v>0</v>
+        <v>-12.7</v>
       </c>
       <c r="AU55" s="3" t="n">
-        <v>18</v>
+        <v>3.02</v>
       </c>
       <c r="AV55" s="3" t="n">
         <v>0</v>
@@ -9372,7 +9396,7 @@
       </c>
       <c r="BB55" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -9423,7 +9447,7 @@
         </is>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0</v>
+        <v>-8.44</v>
       </c>
       <c r="K56" s="3" t="n">
         <v>9</v>
@@ -9462,9 +9486,7 @@
       <c r="U56" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V56" s="3" t="n">
-        <v>0.08500000000000001</v>
-      </c>
+      <c r="V56" s="3" t="inlineStr"/>
       <c r="W56" s="3" t="inlineStr"/>
       <c r="X56" s="3" t="inlineStr">
         <is>
@@ -9504,42 +9526,46 @@
         <v>81.56</v>
       </c>
       <c r="AI56" s="3" t="n">
-        <v>81.56</v>
+        <v>89.08</v>
       </c>
       <c r="AJ56" s="3" t="n">
-        <v>80.73999999999999</v>
+        <v>88.19</v>
       </c>
       <c r="AK56" s="3" t="n">
-        <v>82.38</v>
+        <v>89.97</v>
       </c>
       <c r="AL56" s="3" t="n">
-        <v>77.48</v>
+        <v>84.63</v>
       </c>
       <c r="AM56" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AN56" s="3" t="n">
-        <v>88.08</v>
+        <v>96.20999999999999</v>
       </c>
       <c r="AO56" s="3" t="n">
-        <v>7.99</v>
+        <v>8</v>
       </c>
       <c r="AP56" s="3" t="n">
-        <v>93.79000000000001</v>
+        <v>102.44</v>
       </c>
       <c r="AQ56" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="AR56" s="3" t="inlineStr"/>
-      <c r="AS56" s="3" t="inlineStr"/>
+      <c r="AR56" s="3" t="n">
+        <v>86.56</v>
+      </c>
+      <c r="AS56" s="3" t="n">
+        <v>0.31</v>
+      </c>
       <c r="AT56" s="3" t="n">
-        <v>0</v>
+        <v>-8.44</v>
       </c>
       <c r="AU56" s="3" t="n">
-        <v>7.39</v>
+        <v>0</v>
       </c>
       <c r="AV56" s="3" t="n">
-        <v>0</v>
+        <v>-1.67</v>
       </c>
       <c r="AW56" s="3" t="inlineStr">
         <is>
@@ -9558,7 +9584,7 @@
       </c>
       <c r="BB56" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9635,7 @@
         </is>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="K57" s="3" t="n">
         <v>10</v>
@@ -9688,39 +9714,43 @@
         <v>159.84</v>
       </c>
       <c r="AI57" s="3" t="n">
-        <v>159.84</v>
+        <v>176.07</v>
       </c>
       <c r="AJ57" s="3" t="n">
-        <v>158.24</v>
+        <v>174.31</v>
       </c>
       <c r="AK57" s="3" t="n">
-        <v>161.44</v>
+        <v>177.83</v>
       </c>
       <c r="AL57" s="3" t="n">
-        <v>151.85</v>
+        <v>167.27</v>
       </c>
       <c r="AM57" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AN57" s="3" t="n">
-        <v>172.63</v>
+        <v>190.16</v>
       </c>
       <c r="AO57" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AP57" s="3" t="n">
-        <v>183.82</v>
+        <v>202.48</v>
       </c>
       <c r="AQ57" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="AR57" s="3" t="inlineStr"/>
-      <c r="AS57" s="3" t="inlineStr"/>
+      <c r="AR57" s="3" t="n">
+        <v>181.45</v>
+      </c>
+      <c r="AS57" s="3" t="n">
+        <v>0.35</v>
+      </c>
       <c r="AT57" s="3" t="n">
-        <v>0</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="AU57" s="3" t="n">
-        <v>10.29</v>
+        <v>0.12</v>
       </c>
       <c r="AV57" s="3" t="n">
         <v>0</v>
@@ -9742,7 +9772,7 @@
       </c>
       <c r="BB57" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -9793,7 +9823,7 @@
         </is>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0</v>
+        <v>16.07</v>
       </c>
       <c r="K58" s="3" t="n">
         <v>11</v>
@@ -9872,42 +9902,46 @@
         <v>95.04000000000001</v>
       </c>
       <c r="AI58" s="3" t="n">
-        <v>95.04000000000001</v>
+        <v>81.88</v>
       </c>
       <c r="AJ58" s="3" t="n">
-        <v>94.09</v>
+        <v>81.06</v>
       </c>
       <c r="AK58" s="3" t="n">
-        <v>95.98999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="AL58" s="3" t="n">
-        <v>90.29000000000001</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="AM58" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AN58" s="3" t="n">
-        <v>102.64</v>
+        <v>88.43000000000001</v>
       </c>
       <c r="AO58" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AP58" s="3" t="n">
-        <v>109.3</v>
+        <v>94.16</v>
       </c>
       <c r="AQ58" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="AR58" s="3" t="inlineStr"/>
-      <c r="AS58" s="3" t="inlineStr"/>
+      <c r="AR58" s="3" t="n">
+        <v>100.86</v>
+      </c>
+      <c r="AS58" s="3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="AT58" s="3" t="n">
-        <v>0</v>
+        <v>16.07</v>
       </c>
       <c r="AU58" s="3" t="n">
-        <v>0</v>
+        <v>11.3</v>
       </c>
       <c r="AV58" s="3" t="n">
-        <v>-5.09</v>
+        <v>0</v>
       </c>
       <c r="AW58" s="3" t="inlineStr">
         <is>
@@ -9926,7 +9960,7 @@
       </c>
       <c r="BB58" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -9977,7 +10011,7 @@
         </is>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0</v>
+        <v>-3.11</v>
       </c>
       <c r="K59" s="3" t="n">
         <v>12</v>
@@ -10016,9 +10050,7 @@
       <c r="U59" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="V59" s="3" t="n">
-        <v>0.122</v>
-      </c>
+      <c r="V59" s="3" t="inlineStr"/>
       <c r="W59" s="3" t="inlineStr"/>
       <c r="X59" s="3" t="inlineStr">
         <is>
@@ -10058,42 +10090,46 @@
         <v>214.03</v>
       </c>
       <c r="AI59" s="3" t="n">
-        <v>214.03</v>
+        <v>220.9</v>
       </c>
       <c r="AJ59" s="3" t="n">
-        <v>211.89</v>
+        <v>218.69</v>
       </c>
       <c r="AK59" s="3" t="n">
-        <v>216.17</v>
+        <v>223.11</v>
       </c>
       <c r="AL59" s="3" t="n">
-        <v>203.33</v>
+        <v>209.85</v>
       </c>
       <c r="AM59" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AN59" s="3" t="n">
-        <v>231.15</v>
+        <v>238.57</v>
       </c>
       <c r="AO59" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AP59" s="3" t="n">
-        <v>246.13</v>
+        <v>254.03</v>
       </c>
       <c r="AQ59" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="AR59" s="3" t="inlineStr"/>
-      <c r="AS59" s="3" t="inlineStr"/>
+      <c r="AR59" s="3" t="n">
+        <v>237.16</v>
+      </c>
+      <c r="AS59" s="3" t="n">
+        <v>1.28</v>
+      </c>
       <c r="AT59" s="3" t="n">
-        <v>0</v>
+        <v>-3.11</v>
       </c>
       <c r="AU59" s="3" t="n">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="AV59" s="3" t="n">
-        <v>0</v>
+        <v>-2.15</v>
       </c>
       <c r="AW59" s="3" t="inlineStr">
         <is>
@@ -10112,7 +10148,7 @@
       </c>
       <c r="BB59" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -10163,7 +10199,7 @@
         </is>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="K60" s="3" t="n">
         <v>13</v>
@@ -10203,7 +10239,7 @@
         <v>13</v>
       </c>
       <c r="V60" s="3" t="n">
-        <v>0.156</v>
+        <v>0.237</v>
       </c>
       <c r="W60" s="3" t="inlineStr"/>
       <c r="X60" s="3" t="inlineStr">
@@ -10244,42 +10280,46 @@
         <v>338.87</v>
       </c>
       <c r="AI60" s="3" t="n">
-        <v>338.87</v>
+        <v>338.27</v>
       </c>
       <c r="AJ60" s="3" t="n">
-        <v>335.48</v>
+        <v>334.89</v>
       </c>
       <c r="AK60" s="3" t="n">
-        <v>342.26</v>
+        <v>341.65</v>
       </c>
       <c r="AL60" s="3" t="n">
-        <v>321.93</v>
+        <v>321.36</v>
       </c>
       <c r="AM60" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AN60" s="3" t="n">
-        <v>365.98</v>
+        <v>365.33</v>
       </c>
       <c r="AO60" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AP60" s="3" t="n">
-        <v>389.7</v>
+        <v>389.01</v>
       </c>
       <c r="AQ60" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="AR60" s="3" t="inlineStr"/>
-      <c r="AS60" s="3" t="inlineStr"/>
+      <c r="AR60" s="3" t="n">
+        <v>348.24</v>
+      </c>
+      <c r="AS60" s="3" t="n">
+        <v>1.41</v>
+      </c>
       <c r="AT60" s="3" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="AU60" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AV60" s="3" t="n">
-        <v>-2.04</v>
+        <v>-1.87</v>
       </c>
       <c r="AW60" s="3" t="inlineStr">
         <is>
@@ -10298,7 +10338,7 @@
       </c>
       <c r="BB60" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -10349,7 +10389,7 @@
         </is>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0</v>
+        <v>-0.82</v>
       </c>
       <c r="K61" s="3" t="n">
         <v>14</v>
@@ -10388,9 +10428,7 @@
       <c r="U61" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="V61" s="3" t="n">
-        <v>0.193</v>
-      </c>
+      <c r="V61" s="3" t="inlineStr"/>
       <c r="W61" s="3" t="inlineStr"/>
       <c r="X61" s="3" t="inlineStr">
         <is>
@@ -10430,42 +10468,46 @@
         <v>97.67</v>
       </c>
       <c r="AI61" s="3" t="n">
-        <v>97.67</v>
+        <v>98.48</v>
       </c>
       <c r="AJ61" s="3" t="n">
-        <v>96.69</v>
+        <v>97.5</v>
       </c>
       <c r="AK61" s="3" t="n">
-        <v>98.65000000000001</v>
+        <v>99.45999999999999</v>
       </c>
       <c r="AL61" s="3" t="n">
-        <v>92.79000000000001</v>
+        <v>93.56</v>
       </c>
       <c r="AM61" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AN61" s="3" t="n">
-        <v>105.48</v>
+        <v>106.36</v>
       </c>
       <c r="AO61" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AP61" s="3" t="n">
-        <v>112.32</v>
+        <v>113.25</v>
       </c>
       <c r="AQ61" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="AR61" s="3" t="inlineStr"/>
-      <c r="AS61" s="3" t="inlineStr"/>
+      <c r="AR61" s="3" t="n">
+        <v>98.18000000000001</v>
+      </c>
+      <c r="AS61" s="3" t="n">
+        <v>3.65</v>
+      </c>
       <c r="AT61" s="3" t="n">
-        <v>0</v>
+        <v>-0.82</v>
       </c>
       <c r="AU61" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AV61" s="3" t="n">
-        <v>-1.52</v>
+        <v>-2.36</v>
       </c>
       <c r="AW61" s="3" t="inlineStr">
         <is>
@@ -10484,7 +10526,7 @@
       </c>
       <c r="BB61" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -10535,7 +10577,7 @@
         </is>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0</v>
+        <v>-1.4</v>
       </c>
       <c r="K62" s="3" t="n">
         <v>15</v>
@@ -10574,9 +10616,7 @@
       <c r="U62" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="V62" s="3" t="n">
-        <v>0.192</v>
-      </c>
+      <c r="V62" s="3" t="inlineStr"/>
       <c r="W62" s="3" t="inlineStr"/>
       <c r="X62" s="3" t="inlineStr">
         <is>
@@ -10616,42 +10656,46 @@
         <v>267.71</v>
       </c>
       <c r="AI62" s="3" t="n">
-        <v>267.71</v>
+        <v>271.52</v>
       </c>
       <c r="AJ62" s="3" t="n">
-        <v>265.03</v>
+        <v>268.8</v>
       </c>
       <c r="AK62" s="3" t="n">
-        <v>270.39</v>
+        <v>274.24</v>
       </c>
       <c r="AL62" s="3" t="n">
-        <v>254.32</v>
+        <v>257.94</v>
       </c>
       <c r="AM62" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AN62" s="3" t="n">
-        <v>289.13</v>
+        <v>293.24</v>
       </c>
       <c r="AO62" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AP62" s="3" t="n">
-        <v>307.87</v>
+        <v>312.25</v>
       </c>
       <c r="AQ62" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="AR62" s="3" t="inlineStr"/>
-      <c r="AS62" s="3" t="inlineStr"/>
+      <c r="AR62" s="3" t="n">
+        <v>268.34</v>
+      </c>
+      <c r="AS62" s="3" t="n">
+        <v>2.11</v>
+      </c>
       <c r="AT62" s="3" t="n">
-        <v>0</v>
+        <v>-1.4</v>
       </c>
       <c r="AU62" s="3" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AV62" s="3" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="AW62" s="3" t="inlineStr">
         <is>
@@ -10670,7 +10714,7 @@
       </c>
       <c r="BB62" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -10752,9 +10796,7 @@
       <c r="U63" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="V63" s="3" t="n">
-        <v>0.184</v>
-      </c>
+      <c r="V63" s="3" t="inlineStr"/>
       <c r="W63" s="3" t="inlineStr"/>
       <c r="X63" s="3" t="inlineStr">
         <is>
@@ -10792,7 +10834,7 @@
         <v>358.56</v>
       </c>
       <c r="AI63" s="3" t="n">
-        <v>358.56</v>
+        <v>368.73</v>
       </c>
       <c r="AJ63" s="3" t="n">
         <v>351.39</v>
@@ -10804,30 +10846,34 @@
         <v>340.632</v>
       </c>
       <c r="AM63" s="3" t="n">
-        <v>-5</v>
+        <v>-7.62</v>
       </c>
       <c r="AN63" s="3" t="n">
         <v>387.2448000000001</v>
       </c>
       <c r="AO63" s="3" t="n">
-        <v>8</v>
+        <v>5.02</v>
       </c>
       <c r="AP63" s="3" t="n">
         <v>414.3519360000001</v>
       </c>
       <c r="AQ63" s="3" t="n">
-        <v>15.56</v>
-      </c>
-      <c r="AR63" s="3" t="inlineStr"/>
-      <c r="AS63" s="3" t="inlineStr"/>
+        <v>12.37</v>
+      </c>
+      <c r="AR63" s="3" t="n">
+        <v>369.59</v>
+      </c>
+      <c r="AS63" s="3" t="n">
+        <v>-0.28</v>
+      </c>
       <c r="AT63" s="3" t="n">
-        <v>0</v>
+        <v>-2.76</v>
       </c>
       <c r="AU63" s="3" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AV63" s="3" t="n">
-        <v>0</v>
+        <v>-0.71</v>
       </c>
       <c r="AW63" s="3" t="inlineStr">
         <is>
@@ -10844,11 +10890,11 @@
         <v>5</v>
       </c>
       <c r="BA63" s="3" t="n">
-        <v>8</v>
+        <v>5.02</v>
       </c>
       <c r="BB63" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -10968,7 +11014,7 @@
         <v>368.98</v>
       </c>
       <c r="AI64" s="3" t="n">
-        <v>368.98</v>
+        <v>389.01</v>
       </c>
       <c r="AJ64" s="3" t="n">
         <v>365.29</v>
@@ -10980,30 +11026,34 @@
         <v>350.531</v>
       </c>
       <c r="AM64" s="3" t="n">
-        <v>-5</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="AN64" s="3" t="n">
         <v>413.26</v>
       </c>
       <c r="AO64" s="3" t="n">
-        <v>12</v>
+        <v>6.23</v>
       </c>
       <c r="AP64" s="3" t="n">
         <v>442.1882</v>
       </c>
       <c r="AQ64" s="3" t="n">
-        <v>19.84</v>
-      </c>
-      <c r="AR64" s="3" t="inlineStr"/>
-      <c r="AS64" s="3" t="inlineStr"/>
+        <v>13.67</v>
+      </c>
+      <c r="AR64" s="3" t="n">
+        <v>377.15</v>
+      </c>
+      <c r="AS64" s="3" t="n">
+        <v>1.41</v>
+      </c>
       <c r="AT64" s="3" t="n">
-        <v>0</v>
+        <v>-5.15</v>
       </c>
       <c r="AU64" s="3" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AV64" s="3" t="n">
-        <v>0</v>
+        <v>-3.77</v>
       </c>
       <c r="AW64" s="3" t="inlineStr">
         <is>
@@ -11020,11 +11070,11 @@
         <v>5</v>
       </c>
       <c r="BA64" s="3" t="n">
-        <v>12</v>
+        <v>6.23</v>
       </c>
       <c r="BB64" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -11144,7 +11194,7 @@
         <v>202.81</v>
       </c>
       <c r="AI65" s="3" t="n">
-        <v>202.81</v>
+        <v>190.01</v>
       </c>
       <c r="AJ65" s="3" t="n">
         <v>198.75</v>
@@ -11156,30 +11206,34 @@
         <v>192.6695</v>
       </c>
       <c r="AM65" s="3" t="n">
-        <v>-5</v>
+        <v>1.4</v>
       </c>
       <c r="AN65" s="3" t="n">
         <v>219.0348</v>
       </c>
       <c r="AO65" s="3" t="n">
-        <v>8</v>
+        <v>15.28</v>
       </c>
       <c r="AP65" s="3" t="n">
         <v>234.367236</v>
       </c>
       <c r="AQ65" s="3" t="n">
-        <v>15.56</v>
-      </c>
-      <c r="AR65" s="3" t="inlineStr"/>
-      <c r="AS65" s="3" t="inlineStr"/>
+        <v>23.34</v>
+      </c>
+      <c r="AR65" s="3" t="n">
+        <v>211.94</v>
+      </c>
+      <c r="AS65" s="3" t="n">
+        <v>3.43</v>
+      </c>
       <c r="AT65" s="3" t="n">
-        <v>0</v>
+        <v>6.74</v>
       </c>
       <c r="AU65" s="3" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AV65" s="3" t="n">
-        <v>-1.02</v>
+        <v>0</v>
       </c>
       <c r="AW65" s="3" t="inlineStr">
         <is>
@@ -11196,11 +11250,11 @@
         <v>5</v>
       </c>
       <c r="BA65" s="3" t="n">
-        <v>8</v>
+        <v>15.28</v>
       </c>
       <c r="BB65" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -11282,9 +11336,7 @@
       <c r="U66" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="V66" s="3" t="n">
-        <v>0.15</v>
-      </c>
+      <c r="V66" s="3" t="inlineStr"/>
       <c r="W66" s="3" t="inlineStr"/>
       <c r="X66" s="3" t="inlineStr">
         <is>
@@ -11322,7 +11374,7 @@
         <v>393.82</v>
       </c>
       <c r="AI66" s="3" t="n">
-        <v>393.82</v>
+        <v>451.1</v>
       </c>
       <c r="AJ66" s="3" t="n">
         <v>385.94</v>
@@ -11334,27 +11386,31 @@
         <v>374.129</v>
       </c>
       <c r="AM66" s="3" t="n">
-        <v>-5</v>
+        <v>-17.06</v>
       </c>
       <c r="AN66" s="3" t="n">
         <v>425.3256</v>
       </c>
       <c r="AO66" s="3" t="n">
-        <v>8</v>
+        <v>-5.71</v>
       </c>
       <c r="AP66" s="3" t="n">
         <v>455.098392</v>
       </c>
       <c r="AQ66" s="3" t="n">
-        <v>15.56</v>
-      </c>
-      <c r="AR66" s="3" t="inlineStr"/>
-      <c r="AS66" s="3" t="inlineStr"/>
+        <v>0.89</v>
+      </c>
+      <c r="AR66" s="3" t="n">
+        <v>492.81</v>
+      </c>
+      <c r="AS66" s="3" t="n">
+        <v>-1.09</v>
+      </c>
       <c r="AT66" s="3" t="n">
-        <v>0</v>
+        <v>-12.7</v>
       </c>
       <c r="AU66" s="3" t="n">
-        <v>18</v>
+        <v>3.02</v>
       </c>
       <c r="AV66" s="3" t="n">
         <v>0</v>
@@ -11374,11 +11430,11 @@
         <v>5</v>
       </c>
       <c r="BA66" s="3" t="n">
-        <v>8</v>
+        <v>-5.71</v>
       </c>
       <c r="BB66" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -11460,9 +11516,7 @@
       <c r="U67" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V67" s="3" t="n">
-        <v>0.08500000000000001</v>
-      </c>
+      <c r="V67" s="3" t="inlineStr"/>
       <c r="W67" s="3" t="inlineStr"/>
       <c r="X67" s="3" t="inlineStr">
         <is>
@@ -11500,7 +11554,7 @@
         <v>81.56</v>
       </c>
       <c r="AI67" s="3" t="n">
-        <v>81.56</v>
+        <v>89.08</v>
       </c>
       <c r="AJ67" s="3" t="n">
         <v>79.93000000000001</v>
@@ -11512,30 +11566,34 @@
         <v>77.482</v>
       </c>
       <c r="AM67" s="3" t="n">
-        <v>-5</v>
+        <v>-13.02</v>
       </c>
       <c r="AN67" s="3" t="n">
         <v>88.0848</v>
       </c>
       <c r="AO67" s="3" t="n">
-        <v>8</v>
+        <v>-1.12</v>
       </c>
       <c r="AP67" s="3" t="n">
         <v>94.250736</v>
       </c>
       <c r="AQ67" s="3" t="n">
-        <v>15.56</v>
-      </c>
-      <c r="AR67" s="3" t="inlineStr"/>
-      <c r="AS67" s="3" t="inlineStr"/>
+        <v>5.8</v>
+      </c>
+      <c r="AR67" s="3" t="n">
+        <v>86.56</v>
+      </c>
+      <c r="AS67" s="3" t="n">
+        <v>0.31</v>
+      </c>
       <c r="AT67" s="3" t="n">
-        <v>0</v>
+        <v>-8.44</v>
       </c>
       <c r="AU67" s="3" t="n">
-        <v>7.39</v>
+        <v>0</v>
       </c>
       <c r="AV67" s="3" t="n">
-        <v>0</v>
+        <v>-1.67</v>
       </c>
       <c r="AW67" s="3" t="inlineStr">
         <is>
@@ -11552,11 +11610,11 @@
         <v>5</v>
       </c>
       <c r="BA67" s="3" t="n">
-        <v>8</v>
+        <v>-1.12</v>
       </c>
       <c r="BB67" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -11638,9 +11696,7 @@
       <c r="U68" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="V68" s="3" t="n">
-        <v>0.127</v>
-      </c>
+      <c r="V68" s="3" t="inlineStr"/>
       <c r="W68" s="3" t="inlineStr"/>
       <c r="X68" s="3" t="inlineStr">
         <is>
@@ -11678,7 +11734,7 @@
         <v>225.02</v>
       </c>
       <c r="AI68" s="3" t="n">
-        <v>225.02</v>
+        <v>241.12</v>
       </c>
       <c r="AJ68" s="3" t="n">
         <v>220.52</v>
@@ -11690,27 +11746,31 @@
         <v>213.769</v>
       </c>
       <c r="AM68" s="3" t="n">
-        <v>-5</v>
+        <v>-11.34</v>
       </c>
       <c r="AN68" s="3" t="n">
         <v>243.0216</v>
       </c>
       <c r="AO68" s="3" t="n">
-        <v>8</v>
+        <v>0.79</v>
       </c>
       <c r="AP68" s="3" t="n">
         <v>260.0331120000001</v>
       </c>
       <c r="AQ68" s="3" t="n">
-        <v>15.56</v>
-      </c>
-      <c r="AR68" s="3" t="inlineStr"/>
-      <c r="AS68" s="3" t="inlineStr"/>
+        <v>7.84</v>
+      </c>
+      <c r="AR68" s="3" t="n">
+        <v>248.79</v>
+      </c>
+      <c r="AS68" s="3" t="n">
+        <v>-0.27</v>
+      </c>
       <c r="AT68" s="3" t="n">
-        <v>0</v>
+        <v>-6.68</v>
       </c>
       <c r="AU68" s="3" t="n">
-        <v>8.01</v>
+        <v>0.8</v>
       </c>
       <c r="AV68" s="3" t="n">
         <v>0</v>
@@ -11730,11 +11790,11 @@
         <v>5</v>
       </c>
       <c r="BA68" s="3" t="n">
-        <v>8</v>
+        <v>0.79</v>
       </c>
       <c r="BB68" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -11816,9 +11876,7 @@
       <c r="U69" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="V69" s="3" t="n">
-        <v>0.109</v>
-      </c>
+      <c r="V69" s="3" t="inlineStr"/>
       <c r="W69" s="3" t="inlineStr"/>
       <c r="X69" s="3" t="inlineStr">
         <is>
@@ -11856,7 +11914,7 @@
         <v>333.74</v>
       </c>
       <c r="AI69" s="3" t="n">
-        <v>333.74</v>
+        <v>338.19</v>
       </c>
       <c r="AJ69" s="3" t="n">
         <v>327.07</v>
@@ -11868,30 +11926,34 @@
         <v>317.053</v>
       </c>
       <c r="AM69" s="3" t="n">
-        <v>-5</v>
+        <v>-6.25</v>
       </c>
       <c r="AN69" s="3" t="n">
         <v>360.4392</v>
       </c>
       <c r="AO69" s="3" t="n">
-        <v>8</v>
+        <v>6.58</v>
       </c>
       <c r="AP69" s="3" t="n">
         <v>385.669944</v>
       </c>
       <c r="AQ69" s="3" t="n">
-        <v>15.56</v>
-      </c>
-      <c r="AR69" s="3" t="inlineStr"/>
-      <c r="AS69" s="3" t="inlineStr"/>
+        <v>14.04</v>
+      </c>
+      <c r="AR69" s="3" t="n">
+        <v>309.38</v>
+      </c>
+      <c r="AS69" s="3" t="n">
+        <v>0.52</v>
+      </c>
       <c r="AT69" s="3" t="n">
-        <v>0</v>
+        <v>-1.32</v>
       </c>
       <c r="AU69" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AV69" s="3" t="n">
-        <v>-7.44</v>
+        <v>-8.66</v>
       </c>
       <c r="AW69" s="3" t="inlineStr">
         <is>
@@ -11908,11 +11970,11 @@
         <v>5</v>
       </c>
       <c r="BA69" s="3" t="n">
-        <v>8</v>
+        <v>6.58</v>
       </c>
       <c r="BB69" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -12032,7 +12094,7 @@
         <v>341.1</v>
       </c>
       <c r="AI70" s="3" t="n">
-        <v>341.1</v>
+        <v>344.71</v>
       </c>
       <c r="AJ70" s="3" t="n">
         <v>334.28</v>
@@ -12044,27 +12106,31 @@
         <v>324.045</v>
       </c>
       <c r="AM70" s="3" t="n">
-        <v>-5</v>
+        <v>-5.99</v>
       </c>
       <c r="AN70" s="3" t="n">
         <v>368.388</v>
       </c>
       <c r="AO70" s="3" t="n">
-        <v>8</v>
+        <v>6.87</v>
       </c>
       <c r="AP70" s="3" t="n">
         <v>394.1751600000001</v>
       </c>
       <c r="AQ70" s="3" t="n">
-        <v>15.56</v>
-      </c>
-      <c r="AR70" s="3" t="inlineStr"/>
-      <c r="AS70" s="3" t="inlineStr"/>
+        <v>14.35</v>
+      </c>
+      <c r="AR70" s="3" t="n">
+        <v>357.52</v>
+      </c>
+      <c r="AS70" s="3" t="n">
+        <v>0.48</v>
+      </c>
       <c r="AT70" s="3" t="n">
-        <v>0</v>
+        <v>-1.05</v>
       </c>
       <c r="AU70" s="3" t="n">
-        <v>3.13</v>
+        <v>2.05</v>
       </c>
       <c r="AV70" s="3" t="n">
         <v>0</v>
@@ -12084,11 +12150,11 @@
         <v>5</v>
       </c>
       <c r="BA70" s="3" t="n">
-        <v>8</v>
+        <v>6.87</v>
       </c>
       <c r="BB70" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -12208,7 +12274,7 @@
         <v>1065.22</v>
       </c>
       <c r="AI71" s="3" t="n">
-        <v>1065.22</v>
+        <v>980.75</v>
       </c>
       <c r="AJ71" s="3" t="n">
         <v>1043.92</v>
@@ -12220,30 +12286,34 @@
         <v>1011.959</v>
       </c>
       <c r="AM71" s="3" t="n">
-        <v>-5</v>
+        <v>3.18</v>
       </c>
       <c r="AN71" s="3" t="n">
         <v>1150.4376</v>
       </c>
       <c r="AO71" s="3" t="n">
-        <v>8</v>
+        <v>17.3</v>
       </c>
       <c r="AP71" s="3" t="n">
         <v>1230.968232</v>
       </c>
       <c r="AQ71" s="3" t="n">
-        <v>15.56</v>
-      </c>
-      <c r="AR71" s="3" t="inlineStr"/>
-      <c r="AS71" s="3" t="inlineStr"/>
+        <v>25.51</v>
+      </c>
+      <c r="AR71" s="3" t="n">
+        <v>1052.98</v>
+      </c>
+      <c r="AS71" s="3" t="n">
+        <v>0.7</v>
+      </c>
       <c r="AT71" s="3" t="n">
-        <v>0</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="AU71" s="3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AV71" s="3" t="n">
-        <v>-4.4</v>
+        <v>0</v>
       </c>
       <c r="AW71" s="3" t="inlineStr">
         <is>
@@ -12260,11 +12330,11 @@
         <v>5</v>
       </c>
       <c r="BA71" s="3" t="n">
-        <v>8</v>
+        <v>17.3</v>
       </c>
       <c r="BB71" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -12384,7 +12454,7 @@
         <v>159.84</v>
       </c>
       <c r="AI72" s="3" t="n">
-        <v>159.84</v>
+        <v>176.07</v>
       </c>
       <c r="AJ72" s="3" t="n">
         <v>156.64</v>
@@ -12396,27 +12466,31 @@
         <v>151.848</v>
       </c>
       <c r="AM72" s="3" t="n">
-        <v>-5</v>
+        <v>-13.76</v>
       </c>
       <c r="AN72" s="3" t="n">
         <v>172.6272</v>
       </c>
       <c r="AO72" s="3" t="n">
-        <v>8</v>
+        <v>-1.96</v>
       </c>
       <c r="AP72" s="3" t="n">
         <v>184.711104</v>
       </c>
       <c r="AQ72" s="3" t="n">
-        <v>15.56</v>
-      </c>
-      <c r="AR72" s="3" t="inlineStr"/>
-      <c r="AS72" s="3" t="inlineStr"/>
+        <v>4.91</v>
+      </c>
+      <c r="AR72" s="3" t="n">
+        <v>181.45</v>
+      </c>
+      <c r="AS72" s="3" t="n">
+        <v>0.35</v>
+      </c>
       <c r="AT72" s="3" t="n">
-        <v>0</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="AU72" s="3" t="n">
-        <v>10.29</v>
+        <v>0.12</v>
       </c>
       <c r="AV72" s="3" t="n">
         <v>0</v>
@@ -12436,11 +12510,11 @@
         <v>5</v>
       </c>
       <c r="BA72" s="3" t="n">
-        <v>8</v>
+        <v>-1.96</v>
       </c>
       <c r="BB72" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_daily_2026-08-06.xlsx
+++ b/reports/telegram/aegis_daily_2026-08-06.xlsx
@@ -944,7 +944,7 @@
       </c>
       <c r="BB2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="BB3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="BB4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="BB5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BB6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="BB7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="BB8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="BB9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="BB10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="BB11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="BB12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="BB13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="BB14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="BB15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="BB16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="BB17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BB18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="BB19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="BB20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="BB21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="BB22" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="BB23" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="BB24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -4874,7 +4874,7 @@
       </c>
       <c r="BB25" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="BB26" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="BB27" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="BB28" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="BB29" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -5662,7 +5662,7 @@
       </c>
       <c r="BB30" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="BB31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="BB32" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="BB33" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       <c r="BA34" s="3" t="inlineStr"/>
       <c r="BB34" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -6354,7 +6354,7 @@
       <c r="BA35" s="3" t="inlineStr"/>
       <c r="BB35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -6478,7 +6478,7 @@
       <c r="BA36" s="3" t="inlineStr"/>
       <c r="BB36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -6602,7 +6602,7 @@
       <c r="BA37" s="3" t="inlineStr"/>
       <c r="BB37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="BB38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -6882,7 +6882,7 @@
       <c r="BA39" s="3" t="inlineStr"/>
       <c r="BB39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -7006,7 +7006,7 @@
       <c r="BA40" s="3" t="inlineStr"/>
       <c r="BB40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       <c r="BA41" s="3" t="inlineStr"/>
       <c r="BB41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -7254,7 +7254,7 @@
       <c r="BA42" s="3" t="inlineStr"/>
       <c r="BB42" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -7378,7 +7378,7 @@
       <c r="BA43" s="3" t="inlineStr"/>
       <c r="BB43" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -7502,7 +7502,7 @@
       <c r="BA44" s="3" t="inlineStr"/>
       <c r="BB44" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="BB45" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -7778,7 +7778,7 @@
       <c r="BA46" s="3" t="inlineStr"/>
       <c r="BB46" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       <c r="BA47" s="3" t="inlineStr"/>
       <c r="BB47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -8086,7 +8086,7 @@
       </c>
       <c r="BB48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -8268,7 +8268,7 @@
       </c>
       <c r="BB49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -8456,7 +8456,7 @@
       </c>
       <c r="BB50" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BB51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="BB52" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -9020,7 +9020,7 @@
       </c>
       <c r="BB53" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="BB54" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BB55" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -9584,7 +9584,7 @@
       </c>
       <c r="BB56" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BB57" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="BB58" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -10148,7 +10148,7 @@
       </c>
       <c r="BB59" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -10338,7 +10338,7 @@
       </c>
       <c r="BB60" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -10526,7 +10526,7 @@
       </c>
       <c r="BB61" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -10714,7 +10714,7 @@
       </c>
       <c r="BB62" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -10894,7 +10894,7 @@
       </c>
       <c r="BB63" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -11074,7 +11074,7 @@
       </c>
       <c r="BB64" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -11254,7 +11254,7 @@
       </c>
       <c r="BB65" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -11434,7 +11434,7 @@
       </c>
       <c r="BB66" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -11614,7 +11614,7 @@
       </c>
       <c r="BB67" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="BB68" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -11974,7 +11974,7 @@
       </c>
       <c r="BB69" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -12154,7 +12154,7 @@
       </c>
       <c r="BB70" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -12334,7 +12334,7 @@
       </c>
       <c r="BB71" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -12514,7 +12514,7 @@
       </c>
       <c r="BB72" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_daily_2026-08-06.xlsx
+++ b/reports/telegram/aegis_daily_2026-08-06.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AX$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AW$72</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX72"/>
+  <dimension ref="A1:AW72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -458,7 +458,7 @@
     <col width="10" customWidth="1" min="18" max="18"/>
     <col width="50" customWidth="1" min="19" max="19"/>
     <col width="60" customWidth="1" min="20" max="20"/>
-    <col width="34" customWidth="1" min="21" max="21"/>
+    <col width="44" customWidth="1" min="21" max="21"/>
     <col width="13" customWidth="1" min="22" max="22"/>
     <col width="11" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -482,12 +482,11 @@
     <col width="15" customWidth="1" min="42" max="42"/>
     <col width="12" customWidth="1" min="43" max="43"/>
     <col width="11" customWidth="1" min="44" max="44"/>
-    <col width="16" customWidth="1" min="45" max="45"/>
-    <col width="32" customWidth="1" min="46" max="46"/>
-    <col width="20" customWidth="1" min="47" max="47"/>
-    <col width="18" customWidth="1" min="48" max="48"/>
-    <col width="17" customWidth="1" min="49" max="49"/>
-    <col width="20" customWidth="1" min="50" max="50"/>
+    <col width="32" customWidth="1" min="45" max="45"/>
+    <col width="20" customWidth="1" min="46" max="46"/>
+    <col width="18" customWidth="1" min="47" max="47"/>
+    <col width="17" customWidth="1" min="48" max="48"/>
+    <col width="20" customWidth="1" min="49" max="49"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -593,7 +592,7 @@
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Alerts</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
@@ -713,30 +712,25 @@
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>Lifecycle State</t>
+          <t>Top Drivers</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>Top Drivers</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Portfolio Weight %</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>Portfolio Weight %</t>
+          <t>Expected Alpha %</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>Expected Alpha %</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Last Updated (UTC)</t>
         </is>
@@ -745,7 +739,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TCS_IND_20260729</t>
+          <t>GNFC_IND_20260806</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -760,19 +754,15 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R2_NEW</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>TCS</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>TCS</t>
-        </is>
-      </c>
+          <t>GNFC</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>STRONG BUY</t>
@@ -788,14 +778,10 @@
       <c r="K2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L2" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="M2" s="3" t="n">
-        <v>-8</v>
-      </c>
+      <c r="L2" s="3" t="inlineStr"/>
+      <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="3" t="n">
-        <v>75.90000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
@@ -808,7 +794,7 @@
         </is>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>38.6</v>
+        <v>33.3</v>
       </c>
       <c r="R2" s="3" t="n">
         <v>-0.8</v>
@@ -820,12 +806,12 @@
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank ↑ 9→1 · Conf 39% · band HOLD · 16d left · → STRONG BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #1 · Conf 34% · band HOLD · 17d left · → STRONG BUY</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr"/>
       <c r="V2" s="3" t="n">
-        <v>39.3</v>
+        <v>34.1</v>
       </c>
       <c r="W2" s="3" t="inlineStr">
         <is>
@@ -833,97 +819,88 @@
         </is>
       </c>
       <c r="X2" s="3" t="n">
-        <v>28.4</v>
+        <v>32.8</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA2" s="3" t="n">
         <v>17</v>
       </c>
       <c r="AB2" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AC2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="AD2" s="3" t="n">
-        <v>2421.9</v>
+        <v>553.3</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>2452.2</v>
+        <v>553.2999877929688</v>
       </c>
       <c r="AF2" s="3" t="n">
-        <v>2397.68</v>
+        <v>547.77</v>
       </c>
       <c r="AG2" s="3" t="n">
-        <v>2446.12</v>
+        <v>558.83</v>
       </c>
       <c r="AH2" s="3" t="n">
-        <v>2276.59</v>
+        <v>520.1</v>
       </c>
       <c r="AI2" s="3" t="n">
-        <v>-7.16</v>
+        <v>-6</v>
       </c>
       <c r="AJ2" s="3" t="n">
-        <v>2712.53</v>
+        <v>619.7</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>10.62</v>
+        <v>12</v>
       </c>
       <c r="AL2" s="3" t="n">
-        <v>3003.16</v>
+        <v>686.09</v>
       </c>
       <c r="AM2" s="3" t="n">
-        <v>22.47</v>
+        <v>24</v>
       </c>
       <c r="AN2" s="3" t="n">
-        <v>2460</v>
+        <v>519.75</v>
       </c>
       <c r="AO2" s="3" t="n">
-        <v>-1.55</v>
+        <v>6.46</v>
       </c>
       <c r="AP2" s="3" t="n">
-        <v>-1.24</v>
-      </c>
-      <c r="AQ2" s="3" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="AR2" s="3" t="n">
-        <v>-4.11</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AQ2" s="3" t="inlineStr"/>
+      <c r="AR2" s="3" t="inlineStr"/>
       <c r="AS2" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT2" s="3" t="inlineStr">
-        <is>
-          <t>Quality · Mean Reversion · Ai Hybrid</t>
-        </is>
-      </c>
-      <c r="AU2" s="3" t="inlineStr"/>
+          <t>Value · Growth · Ai Hybrid</t>
+        </is>
+      </c>
+      <c r="AT2" s="3" t="inlineStr"/>
+      <c r="AU2" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AV2" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AX2" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW2" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>OFSS_IND_20260730</t>
+          <t>TCS_IND_20260729</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -943,10 +920,14 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>OFSS</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
           <t>STRONG BUY</t>
@@ -963,13 +944,13 @@
         <v>2</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
@@ -982,7 +963,7 @@
         </is>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>45.6</v>
+        <v>38.6</v>
       </c>
       <c r="R3" s="3" t="n">
         <v>-0.8</v>
@@ -994,12 +975,12 @@
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank ↑ 6→2 · Conf 46% · band HOLD · 16d left · → STRONG BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank ↑ 9→2 · Conf 39% · band HOLD · 16d left · → STRONG BUY</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr"/>
       <c r="V3" s="3" t="n">
-        <v>46.4</v>
+        <v>39.3</v>
       </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
@@ -1007,13 +988,13 @@
         </is>
       </c>
       <c r="X3" s="3" t="n">
-        <v>27.2</v>
+        <v>28.4</v>
       </c>
       <c r="Y3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA3" s="3" t="n">
         <v>17</v>
@@ -1023,81 +1004,76 @@
       </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD3" s="3" t="n">
-        <v>11727</v>
+        <v>2421.9</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>11427</v>
+        <v>2452.2</v>
       </c>
       <c r="AF3" s="3" t="n">
-        <v>11609.73</v>
+        <v>2397.68</v>
       </c>
       <c r="AG3" s="3" t="n">
-        <v>11844.27</v>
+        <v>2446.12</v>
       </c>
       <c r="AH3" s="3" t="n">
-        <v>11023.38</v>
+        <v>2276.59</v>
       </c>
       <c r="AI3" s="3" t="n">
-        <v>-3.53</v>
+        <v>-7.16</v>
       </c>
       <c r="AJ3" s="3" t="n">
-        <v>13134.24</v>
+        <v>2712.53</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>14.94</v>
+        <v>10.62</v>
       </c>
       <c r="AL3" s="3" t="n">
-        <v>14541.48</v>
+        <v>3003.16</v>
       </c>
       <c r="AM3" s="3" t="n">
-        <v>27.26</v>
+        <v>22.47</v>
       </c>
       <c r="AN3" s="3" t="n">
-        <v>11600</v>
+        <v>2460</v>
       </c>
       <c r="AO3" s="3" t="n">
-        <v>1.09</v>
+        <v>-1.55</v>
       </c>
       <c r="AP3" s="3" t="n">
-        <v>2.63</v>
+        <v>-1.24</v>
       </c>
       <c r="AQ3" s="3" t="n">
-        <v>1.51</v>
+        <v>0.32</v>
       </c>
       <c r="AR3" s="3" t="n">
-        <v>-3.08</v>
+        <v>-4.11</v>
       </c>
       <c r="AS3" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT3" s="3" t="inlineStr">
-        <is>
-          <t>Quality · Growth · Momentum</t>
-        </is>
-      </c>
-      <c r="AU3" s="3" t="inlineStr"/>
+          <t>Quality · Mean Reversion · Ai Hybrid</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr"/>
+      <c r="AU3" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AV3" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AX3" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>INDIANB_IND_20260806</t>
+          <t>OFSS_IND_20260730</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -1117,7 +1093,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
@@ -1136,10 +1112,14 @@
       <c r="K4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="L4" s="3" t="inlineStr"/>
-      <c r="M4" s="3" t="inlineStr"/>
+      <c r="L4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>-3</v>
+      </c>
       <c r="N4" s="3" t="n">
-        <v>68.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
@@ -1152,7 +1132,7 @@
         </is>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>34.2</v>
+        <v>45.6</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>-0.8</v>
@@ -1164,12 +1144,12 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #3 · Conf 35% · band HOLD · 17d left · → BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank ↑ 6→3 · Conf 46% · band HOLD · 16d left · → BUY</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr"/>
       <c r="V4" s="3" t="n">
-        <v>35</v>
+        <v>46.4</v>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
@@ -1177,93 +1157,92 @@
         </is>
       </c>
       <c r="X4" s="3" t="n">
-        <v>25.4</v>
+        <v>27.1</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA4" s="3" t="n">
         <v>17</v>
       </c>
       <c r="AB4" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>853.4</v>
+        <v>11727</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>853.4000244140625</v>
+        <v>11427</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>844.87</v>
+        <v>11609.73</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>861.9299999999999</v>
+        <v>11844.27</v>
       </c>
       <c r="AH4" s="3" t="n">
-        <v>802.2</v>
+        <v>11023.38</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>-6</v>
+        <v>-3.53</v>
       </c>
       <c r="AJ4" s="3" t="n">
-        <v>955.8099999999999</v>
+        <v>13134.24</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>12</v>
+        <v>14.94</v>
       </c>
       <c r="AL4" s="3" t="n">
-        <v>1058.22</v>
+        <v>14541.48</v>
       </c>
       <c r="AM4" s="3" t="n">
-        <v>24</v>
+        <v>27.26</v>
       </c>
       <c r="AN4" s="3" t="n">
-        <v>845</v>
+        <v>11600</v>
       </c>
       <c r="AO4" s="3" t="n">
-        <v>0.99</v>
+        <v>1.09</v>
       </c>
       <c r="AP4" s="3" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AQ4" s="3" t="inlineStr"/>
-      <c r="AR4" s="3" t="inlineStr"/>
+        <v>2.63</v>
+      </c>
+      <c r="AQ4" s="3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AR4" s="3" t="n">
+        <v>-3.08</v>
+      </c>
       <c r="AS4" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT4" s="3" t="inlineStr">
-        <is>
-          <t>Value · Mean Reversion · Ai Hybrid</t>
-        </is>
-      </c>
-      <c r="AU4" s="3" t="inlineStr"/>
+          <t>Quality · Growth · Momentum</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr"/>
+      <c r="AU4" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="AV4" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AX4" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ATUL_IND_20260806</t>
+          <t>INDIANB_IND_20260806</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -1283,29 +1262,35 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>ATUL</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>EXIT</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +7.4pp alpha</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>-0</v>
+      </c>
       <c r="K5" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="n">
-        <v>75.8</v>
+        <v>68.7</v>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
@@ -1318,7 +1303,7 @@
         </is>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>34.5</v>
+        <v>34.2</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>-0.8</v>
@@ -1330,12 +1315,12 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #4 · Conf 35% · band HOLD · 17d left · → HOLD</t>
+          <t>🔴 AVOID · Rank #4 · Conf 35% · band HOLD · 17d left · → EXIT (rotate to GNFC.NS)</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr"/>
       <c r="V5" s="3" t="n">
-        <v>35.2</v>
+        <v>35</v>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
@@ -1343,7 +1328,7 @@
         </is>
       </c>
       <c r="X5" s="3" t="n">
-        <v>25</v>
+        <v>25.4</v>
       </c>
       <c r="Y5" s="3" t="n">
         <v>1</v>
@@ -1363,64 +1348,59 @@
         </is>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>6834</v>
+        <v>853.4</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>6834</v>
+        <v>853.4000244140625</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>6765.66</v>
+        <v>844.87</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>6902.34</v>
+        <v>861.9299999999999</v>
       </c>
       <c r="AH5" s="3" t="n">
-        <v>6492.3</v>
+        <v>810.73</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AJ5" s="3" t="n">
-        <v>7380.72</v>
+        <v>921.67</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>7859.1</v>
+        <v>981.41</v>
       </c>
       <c r="AM5" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AN5" s="3" t="n">
-        <v>6793.5</v>
+        <v>845</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>0.6</v>
+        <v>0.99</v>
       </c>
       <c r="AP5" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr"/>
       <c r="AS5" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT5" s="3" t="inlineStr">
-        <is>
-          <t>Trend · Growth · Mean Reversion</t>
-        </is>
-      </c>
+          <t>Value · Mean Reversion · Ai Hybrid</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr"/>
       <c r="AU5" s="3" t="inlineStr"/>
-      <c r="AV5" s="3" t="inlineStr"/>
-      <c r="AW5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AV5" s="3" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -1457,16 +1437,22 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>EXIT</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr"/>
-      <c r="J6" s="3" t="inlineStr"/>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +7.8pp alpha</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0.35</v>
+      </c>
       <c r="K6" s="3" t="n">
         <v>5</v>
       </c>
@@ -1477,7 +1463,7 @@
         <v>-3</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>80.59999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
@@ -1502,7 +1488,7 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-0.6%) · Rank ↑ 8→5 · Conf 43% · band STRONG · 16d left · → HOLD</t>
+          <t>🔴 AVOID · Rank ↑ 8→5 · Conf 43% · band STRONG · 16d left · → EXIT (rotate to GNFC.NS)</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr"/>
@@ -1515,7 +1501,7 @@
         </is>
       </c>
       <c r="X6" s="3" t="n">
-        <v>24.8</v>
+        <v>25.1</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>2</v>
@@ -1581,29 +1567,24 @@
       </c>
       <c r="AS6" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT6" s="3" t="inlineStr">
-        <is>
-          <t>Trend · Quality · Mean Reversion</t>
-        </is>
-      </c>
+          <t>Quality · Trend · Mean Reversion</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr"/>
       <c r="AU6" s="3" t="inlineStr"/>
-      <c r="AV6" s="3" t="inlineStr"/>
-      <c r="AW6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AV6" s="3" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>GNFC_IND_20260806</t>
+          <t>ATUL_IND_20260806</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -1618,34 +1599,40 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>R2_NEW</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>ATUL</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>EXIT</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr"/>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +8.0pp alpha</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="K7" s="3" t="n">
         <v>6</v>
       </c>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="n">
-        <v>77</v>
+        <v>75.8</v>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
@@ -1658,7 +1645,7 @@
         </is>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>38.6</v>
+        <v>34.5</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>-0.8</v>
@@ -1670,12 +1657,12 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #6 · Conf 39% · band HOLD · 60d left · → HOLD</t>
+          <t>🔴 AVOID · Rank #6 · Conf 35% · band HOLD · 17d left · → EXIT (rotate to GNFC.NS)</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr"/>
       <c r="V7" s="3" t="n">
-        <v>39.3</v>
+        <v>35.2</v>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
@@ -1683,7 +1670,7 @@
         </is>
       </c>
       <c r="X7" s="3" t="n">
-        <v>24.3</v>
+        <v>24.9</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>1</v>
@@ -1692,10 +1679,10 @@
         <v>0</v>
       </c>
       <c r="AA7" s="3" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="AB7" s="3" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
@@ -1703,40 +1690,40 @@
         </is>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>553.3</v>
+        <v>6834</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>553.2999877929688</v>
+        <v>6834</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>547.77</v>
+        <v>6765.66</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>558.83</v>
+        <v>6902.34</v>
       </c>
       <c r="AH7" s="3" t="n">
-        <v>525.63</v>
+        <v>6492.3</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AJ7" s="3" t="n">
-        <v>597.5599999999999</v>
+        <v>7380.72</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>636.29</v>
+        <v>7859.1</v>
       </c>
       <c r="AM7" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AN7" s="3" t="n">
-        <v>519.75</v>
+        <v>6793.5</v>
       </c>
       <c r="AO7" s="3" t="n">
-        <v>6.46</v>
+        <v>0.6</v>
       </c>
       <c r="AP7" s="3" t="n">
         <v>0</v>
@@ -1745,22 +1732,17 @@
       <c r="AR7" s="3" t="inlineStr"/>
       <c r="AS7" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT7" s="3" t="inlineStr">
-        <is>
-          <t>Value · Momentum · Ai Hybrid</t>
-        </is>
-      </c>
+          <t>Trend · Growth · Mean Reversion</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr"/>
       <c r="AU7" s="3" t="inlineStr"/>
-      <c r="AV7" s="3" t="inlineStr"/>
-      <c r="AW7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AV7" s="3" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1785,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>→ TCS.NS · +5.5pp alpha</t>
+          <t>→ GNFC.NS · +10.3pp alpha</t>
         </is>
       </c>
       <c r="J8" s="3" t="n">
@@ -1815,7 +1797,7 @@
       <c r="L8" s="3" t="inlineStr"/>
       <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="3" t="n">
-        <v>63.4</v>
+        <v>63.1</v>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
@@ -1840,7 +1822,7 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank #7 · Conf 41% · band HOLD · 17d left · → EXIT (rotate to TCS.NS)</t>
+          <t>🔴 AVOID · Rank #7 · Conf 41% · band HOLD · 17d left · → EXIT (rotate to GNFC.NS)</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr"/>
@@ -1853,7 +1835,7 @@
         </is>
       </c>
       <c r="X8" s="3" t="n">
-        <v>22.9</v>
+        <v>22.5</v>
       </c>
       <c r="Y8" s="3" t="n">
         <v>1</v>
@@ -1919,22 +1901,17 @@
       </c>
       <c r="AS8" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT8" s="3" t="inlineStr">
-        <is>
           <t>Mean Reversion · Value · Ai Hybrid</t>
         </is>
       </c>
+      <c r="AT8" s="3" t="inlineStr"/>
       <c r="AU8" s="3" t="inlineStr"/>
-      <c r="AV8" s="3" t="inlineStr"/>
-      <c r="AW8" s="3" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="AX8" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AV8" s="3" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1958,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>→ TCS.NS · +6.4pp alpha</t>
+          <t>→ GNFC.NS · +10.6pp alpha</t>
         </is>
       </c>
       <c r="J9" s="3" t="n">
@@ -2022,7 +1999,7 @@
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank ↓ 2→8 · Conf 38% · band STRONG · 16d left · → EXIT (rotate to TCS.NS)</t>
+          <t>🔴 AVOID · Rank ↓ 2→8 · Conf 38% · band STRONG · 16d left · → EXIT (rotate to GNFC.NS)</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr"/>
@@ -2035,7 +2012,7 @@
         </is>
       </c>
       <c r="X9" s="3" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="Y9" s="3" t="n">
         <v>2</v>
@@ -2101,22 +2078,17 @@
       </c>
       <c r="AS9" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT9" s="3" t="inlineStr">
-        <is>
           <t>Trend · Quality · Growth</t>
         </is>
       </c>
+      <c r="AT9" s="3" t="inlineStr"/>
       <c r="AU9" s="3" t="inlineStr"/>
-      <c r="AV9" s="3" t="inlineStr"/>
-      <c r="AW9" s="3" t="n">
-        <v>6.42</v>
-      </c>
-      <c r="AX9" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AV9" s="3" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2135,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>→ TCS.NS · +7.1pp alpha</t>
+          <t>→ GNFC.NS · +11.6pp alpha</t>
         </is>
       </c>
       <c r="J10" s="3" t="n">
@@ -2179,7 +2151,7 @@
         <v>3</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>64</v>
+        <v>63.9</v>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
@@ -2204,7 +2176,7 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank ↓ 6→9 · Conf 33% · band HOLD · 60d left · → EXIT (rotate to TCS.NS)</t>
+          <t>🔴 AVOID · Rank ↓ 6→9 · Conf 33% · band HOLD · 17d left · → EXIT (rotate to GNFC.NS)</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr"/>
@@ -2217,7 +2189,7 @@
         </is>
       </c>
       <c r="X10" s="3" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="Y10" s="3" t="n">
         <v>1</v>
@@ -2226,10 +2198,10 @@
         <v>6</v>
       </c>
       <c r="AA10" s="3" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="AB10" s="3" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
@@ -2283,29 +2255,24 @@
       </c>
       <c r="AS10" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT10" s="3" t="inlineStr">
-        <is>
           <t>Mean Reversion · Value · Growth</t>
         </is>
       </c>
+      <c r="AT10" s="3" t="inlineStr"/>
       <c r="AU10" s="3" t="inlineStr"/>
-      <c r="AV10" s="3" t="inlineStr"/>
-      <c r="AW10" s="3" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AX10" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AV10" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>NATIONALUM_IND_20260806</t>
+          <t>INFY_IND_20260730</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -2325,7 +2292,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
@@ -2341,19 +2308,23 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>→ TCS.NS · +7.3pp alpha</t>
+          <t>→ GNFC.NS · +11.7pp alpha</t>
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>1.85</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="N11" s="3" t="n">
-        <v>74</v>
+        <v>75.5</v>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
@@ -2366,7 +2337,7 @@
         </is>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>39.9</v>
+        <v>40</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>-0.8</v>
@@ -2378,12 +2349,12 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank #10 · Conf 41% · band HOLD · 17d left · → EXIT (rotate to TCS.NS)</t>
+          <t>🔴 AVOID · Rank ↓ 7→10 · Conf 41% · band HOLD · 59d left · → EXIT (rotate to GNFC.NS)</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr"/>
       <c r="V11" s="3" t="n">
-        <v>40.6</v>
+        <v>40.7</v>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
@@ -2394,88 +2365,87 @@
         <v>21.1</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA11" s="3" t="n">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="AB11" s="3" t="n">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD11" s="3" t="n">
-        <v>380.35</v>
+        <v>1177</v>
       </c>
       <c r="AE11" s="3" t="n">
-        <v>380.3500061035156</v>
+        <v>1155.6</v>
       </c>
       <c r="AF11" s="3" t="n">
-        <v>376.55</v>
+        <v>1144.04</v>
       </c>
       <c r="AG11" s="3" t="n">
-        <v>384.15</v>
+        <v>1167.16</v>
       </c>
       <c r="AH11" s="3" t="n">
-        <v>361.33</v>
+        <v>1097.82</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AJ11" s="3" t="n">
-        <v>410.78</v>
+        <v>1248.05</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AL11" s="3" t="n">
-        <v>437.4</v>
+        <v>1328.94</v>
       </c>
       <c r="AM11" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AN11" s="3" t="n">
-        <v>377</v>
+        <v>1167.5</v>
       </c>
       <c r="AO11" s="3" t="n">
-        <v>0.89</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AP11" s="3" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AQ11" s="3" t="inlineStr"/>
-      <c r="AR11" s="3" t="inlineStr"/>
+        <v>1.85</v>
+      </c>
+      <c r="AQ11" s="3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR11" s="3" t="n">
+        <v>-3.51</v>
+      </c>
       <c r="AS11" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT11" s="3" t="inlineStr">
-        <is>
-          <t>Mean Reversion · Quality · Value</t>
-        </is>
-      </c>
+          <t>Mean Reversion · Quality · Momentum</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr"/>
       <c r="AU11" s="3" t="inlineStr"/>
-      <c r="AV11" s="3" t="inlineStr"/>
-      <c r="AW11" s="3" t="n">
-        <v>7.31</v>
-      </c>
-      <c r="AX11" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AV11" s="3" t="n">
+        <v>11.69</v>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>AMBER_IND_20260729</t>
+          <t>BHARATFORG_IND_20260730</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -2495,14 +2465,10 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>AMBER</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Amber Ent.</t>
-        </is>
-      </c>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="3" t="inlineStr">
         <is>
           <t>EXIT</t>
@@ -2515,23 +2481,23 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>→ TCS.NS · +55.4pp alpha</t>
+          <t>→ GNFC.NS · +59.7pp alpha</t>
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>1.94</v>
+        <v>0.48</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>11</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>52.2</v>
+        <v>52.5</v>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
@@ -2544,7 +2510,7 @@
         </is>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>23.3</v>
+        <v>29.2</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>-0.8</v>
@@ -2556,12 +2522,12 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank ↑ 14→11 · Conf 24% · band EXIT · 60d left · → EXIT (rotate to TCS.NS)</t>
+          <t>🔴 AVOID · Rank ↑ 13→11 · Conf 30% · band EXIT · 59d left · → EXIT (rotate to GNFC.NS)</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr"/>
       <c r="V12" s="3" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
@@ -2569,88 +2535,83 @@
         </is>
       </c>
       <c r="X12" s="3" t="n">
-        <v>-27</v>
+        <v>-26.9</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA12" s="3" t="n">
         <v>60</v>
       </c>
       <c r="AB12" s="3" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD12" s="3" t="n">
-        <v>7531.5</v>
+        <v>2182</v>
       </c>
       <c r="AE12" s="3" t="n">
-        <v>7388.5</v>
+        <v>2171.5</v>
       </c>
       <c r="AF12" s="3" t="n">
-        <v>7314.61</v>
+        <v>2149.78</v>
       </c>
       <c r="AG12" s="3" t="n">
-        <v>7462.39</v>
+        <v>2193.22</v>
       </c>
       <c r="AH12" s="3" t="n">
-        <v>7019.07</v>
+        <v>2062.92</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AJ12" s="3" t="n">
-        <v>7979.58</v>
+        <v>2345.22</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AL12" s="3" t="n">
-        <v>8496.77</v>
+        <v>2497.22</v>
       </c>
       <c r="AM12" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AN12" s="3" t="n">
-        <v>7395</v>
+        <v>2195</v>
       </c>
       <c r="AO12" s="3" t="n">
-        <v>1.85</v>
+        <v>-0.59</v>
       </c>
       <c r="AP12" s="3" t="n">
-        <v>1.94</v>
+        <v>0.48</v>
       </c>
       <c r="AQ12" s="3" t="n">
-        <v>0.31</v>
+        <v>2.22</v>
       </c>
       <c r="AR12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AS12" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT12" s="3" t="inlineStr">
-        <is>
-          <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Fund Debt To Equity</t>
-        </is>
-      </c>
+          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Distance From 52W High Pct</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr"/>
       <c r="AU12" s="3" t="inlineStr"/>
-      <c r="AV12" s="3" t="inlineStr"/>
-      <c r="AW12" s="3" t="n">
-        <v>55.4</v>
-      </c>
-      <c r="AX12" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AV12" s="3" t="n">
+        <v>59.69</v>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2658,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>→ TCS.NS · +55.4pp alpha</t>
+          <t>→ GNFC.NS · +59.9pp alpha</t>
         </is>
       </c>
       <c r="J13" s="3" t="n">
@@ -2738,7 +2699,7 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank ↓ 11→12 · Conf 30% · band EXIT · 16d left · → EXIT (rotate to TCS.NS)</t>
+          <t>🔴 AVOID · Rank ↓ 11→12 · Conf 30% · band EXIT · 16d left · → EXIT (rotate to GNFC.NS)</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr"/>
@@ -2751,7 +2712,7 @@
         </is>
       </c>
       <c r="X13" s="3" t="n">
-        <v>-27.1</v>
+        <v>-27</v>
       </c>
       <c r="Y13" s="3" t="n">
         <v>2</v>
@@ -2817,22 +2778,17 @@
       </c>
       <c r="AS13" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT13" s="3" t="inlineStr">
-        <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Distance From 52W High Pct</t>
         </is>
       </c>
+      <c r="AT13" s="3" t="inlineStr"/>
       <c r="AU13" s="3" t="inlineStr"/>
-      <c r="AV13" s="3" t="inlineStr"/>
-      <c r="AW13" s="3" t="n">
-        <v>55.43</v>
-      </c>
-      <c r="AX13" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AV13" s="3" t="n">
+        <v>59.88</v>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -2875,7 +2831,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>→ TCS.NS · +56.3pp alpha</t>
+          <t>→ GNFC.NS · +60.7pp alpha</t>
         </is>
       </c>
       <c r="J14" s="3" t="n">
@@ -2912,7 +2868,7 @@
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank #13 · Conf 25% · band EXIT · 60d left · → EXIT (rotate to TCS.NS)</t>
+          <t>🔴 AVOID · Rank #13 · Conf 25% · band EXIT · 17d left · → EXIT (rotate to GNFC.NS)</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr"/>
@@ -2925,7 +2881,7 @@
         </is>
       </c>
       <c r="X14" s="3" t="n">
-        <v>-28</v>
+        <v>-27.8</v>
       </c>
       <c r="Y14" s="3" t="n">
         <v>1</v>
@@ -2934,10 +2890,10 @@
         <v>0</v>
       </c>
       <c r="AA14" s="3" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="AB14" s="3" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
@@ -2987,22 +2943,17 @@
       <c r="AR14" s="3" t="inlineStr"/>
       <c r="AS14" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT14" s="3" t="inlineStr">
-        <is>
           <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
         </is>
       </c>
+      <c r="AT14" s="3" t="inlineStr"/>
       <c r="AU14" s="3" t="inlineStr"/>
-      <c r="AV14" s="3" t="inlineStr"/>
-      <c r="AW14" s="3" t="n">
-        <v>56.33</v>
-      </c>
-      <c r="AX14" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AV14" s="3" t="n">
+        <v>60.67</v>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -3045,7 +2996,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>→ TCS.NS · +58.3pp alpha</t>
+          <t>→ GNFC.NS · +62.5pp alpha</t>
         </is>
       </c>
       <c r="J15" s="3" t="n">
@@ -3082,7 +3033,7 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank #14 · Conf 25% · band EXIT · 17d left · → EXIT (rotate to TCS.NS)</t>
+          <t>🔴 AVOID · Rank #14 · Conf 25% · band EXIT · 17d left · → EXIT (rotate to GNFC.NS)</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr"/>
@@ -3095,7 +3046,7 @@
         </is>
       </c>
       <c r="X15" s="3" t="n">
-        <v>-29.9</v>
+        <v>-29.7</v>
       </c>
       <c r="Y15" s="3" t="n">
         <v>1</v>
@@ -3157,22 +3108,17 @@
       <c r="AR15" s="3" t="inlineStr"/>
       <c r="AS15" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT15" s="3" t="inlineStr">
-        <is>
           <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
         </is>
       </c>
+      <c r="AT15" s="3" t="inlineStr"/>
       <c r="AU15" s="3" t="inlineStr"/>
-      <c r="AV15" s="3" t="inlineStr"/>
-      <c r="AW15" s="3" t="n">
-        <v>58.32</v>
-      </c>
-      <c r="AX15" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AV15" s="3" t="n">
+        <v>62.51</v>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -3215,7 +3161,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>→ TCS.NS · +60.5pp alpha</t>
+          <t>→ GNFC.NS · +64.8pp alpha</t>
         </is>
       </c>
       <c r="J16" s="3" t="n">
@@ -3252,7 +3198,7 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank #15 · Conf 24% · band EXIT · 17d left · → EXIT (rotate to TCS.NS)</t>
+          <t>🔴 AVOID · Rank #15 · Conf 24% · band EXIT · 17d left · → EXIT (rotate to GNFC.NS)</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr"/>
@@ -3265,7 +3211,7 @@
         </is>
       </c>
       <c r="X16" s="3" t="n">
-        <v>-32.1</v>
+        <v>-32</v>
       </c>
       <c r="Y16" s="3" t="n">
         <v>1</v>
@@ -3331,22 +3277,17 @@
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT16" s="3" t="inlineStr">
-        <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Distance From 52W High Pct</t>
         </is>
       </c>
+      <c r="AT16" s="3" t="inlineStr"/>
       <c r="AU16" s="3" t="inlineStr"/>
-      <c r="AV16" s="3" t="inlineStr"/>
-      <c r="AW16" s="3" t="n">
-        <v>60.46</v>
-      </c>
-      <c r="AX16" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AV16" s="3" t="n">
+        <v>64.81999999999999</v>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -3481,26 +3422,21 @@
       </c>
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr"/>
-      <c r="AS17" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT17" s="3" t="inlineStr"/>
-      <c r="AU17" s="3" t="inlineStr">
+      <c r="AS17" s="3" t="inlineStr"/>
+      <c r="AT17" s="3" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
+      <c r="AU17" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AV17" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW17" s="3" t="n">
         <v>5.34</v>
       </c>
-      <c r="AX17" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -3635,26 +3571,21 @@
       </c>
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr"/>
-      <c r="AS18" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT18" s="3" t="inlineStr"/>
-      <c r="AU18" s="3" t="inlineStr">
+      <c r="AS18" s="3" t="inlineStr"/>
+      <c r="AT18" s="3" t="inlineStr">
         <is>
           <t>Pharma</t>
         </is>
       </c>
+      <c r="AU18" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AV18" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW18" s="3" t="n">
         <v>4.57</v>
       </c>
-      <c r="AX18" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -3793,26 +3724,21 @@
       <c r="AR19" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AS19" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT19" s="3" t="inlineStr"/>
-      <c r="AU19" s="3" t="inlineStr">
+      <c r="AS19" s="3" t="inlineStr"/>
+      <c r="AT19" s="3" t="inlineStr">
         <is>
           <t>Pharma</t>
         </is>
       </c>
+      <c r="AU19" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AV19" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW19" s="3" t="n">
         <v>5.66</v>
       </c>
-      <c r="AX19" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -3947,26 +3873,21 @@
       </c>
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr"/>
-      <c r="AS20" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT20" s="3" t="inlineStr"/>
-      <c r="AU20" s="3" t="inlineStr">
+      <c r="AS20" s="3" t="inlineStr"/>
+      <c r="AT20" s="3" t="inlineStr">
         <is>
           <t>Chemicals</t>
         </is>
       </c>
+      <c r="AU20" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AV20" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW20" s="3" t="n">
         <v>1.39</v>
       </c>
-      <c r="AX20" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -4101,26 +4022,21 @@
       </c>
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr"/>
-      <c r="AS21" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT21" s="3" t="inlineStr"/>
-      <c r="AU21" s="3" t="inlineStr">
+      <c r="AS21" s="3" t="inlineStr"/>
+      <c r="AT21" s="3" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
+      <c r="AU21" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AV21" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW21" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AX21" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -4255,26 +4171,21 @@
       </c>
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr"/>
-      <c r="AS22" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT22" s="3" t="inlineStr"/>
-      <c r="AU22" s="3" t="inlineStr">
+      <c r="AS22" s="3" t="inlineStr"/>
+      <c r="AT22" s="3" t="inlineStr">
         <is>
           <t>Power</t>
         </is>
       </c>
+      <c r="AU22" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AV22" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW22" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AX22" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -4409,26 +4320,21 @@
       </c>
       <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr"/>
-      <c r="AS23" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT23" s="3" t="inlineStr"/>
-      <c r="AU23" s="3" t="inlineStr">
+      <c r="AS23" s="3" t="inlineStr"/>
+      <c r="AT23" s="3" t="inlineStr">
         <is>
           <t>Power</t>
         </is>
       </c>
+      <c r="AU23" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AV23" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW23" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AX23" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -4563,26 +4469,21 @@
       <c r="AR24" s="3" t="n">
         <v>-1.5</v>
       </c>
-      <c r="AS24" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT24" s="3" t="inlineStr"/>
-      <c r="AU24" s="3" t="inlineStr">
+      <c r="AS24" s="3" t="inlineStr"/>
+      <c r="AT24" s="3" t="inlineStr">
         <is>
           <t>FMCG</t>
         </is>
       </c>
+      <c r="AU24" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AV24" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW24" s="3" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="AX24" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -4717,26 +4618,21 @@
       </c>
       <c r="AQ25" s="3" t="inlineStr"/>
       <c r="AR25" s="3" t="inlineStr"/>
-      <c r="AS25" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT25" s="3" t="inlineStr"/>
-      <c r="AU25" s="3" t="inlineStr">
+      <c r="AS25" s="3" t="inlineStr"/>
+      <c r="AT25" s="3" t="inlineStr">
         <is>
           <t>Transport</t>
         </is>
       </c>
+      <c r="AU25" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AV25" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW25" s="3" t="n">
         <v>8.01</v>
       </c>
-      <c r="AX25" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -4871,26 +4767,21 @@
       </c>
       <c r="AQ26" s="3" t="inlineStr"/>
       <c r="AR26" s="3" t="inlineStr"/>
-      <c r="AS26" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT26" s="3" t="inlineStr"/>
-      <c r="AU26" s="3" t="inlineStr">
+      <c r="AS26" s="3" t="inlineStr"/>
+      <c r="AT26" s="3" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
+      <c r="AU26" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AV26" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW26" s="3" t="n">
         <v>7.99</v>
       </c>
-      <c r="AX26" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW26" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -5029,26 +4920,21 @@
       <c r="AR27" s="3" t="n">
         <v>-0.11</v>
       </c>
-      <c r="AS27" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT27" s="3" t="inlineStr"/>
-      <c r="AU27" s="3" t="inlineStr">
+      <c r="AS27" s="3" t="inlineStr"/>
+      <c r="AT27" s="3" t="inlineStr">
         <is>
           <t>Metal</t>
         </is>
       </c>
+      <c r="AU27" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AV27" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW27" s="3" t="n">
         <v>8.92</v>
       </c>
-      <c r="AX27" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW27" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -5179,26 +5065,21 @@
       </c>
       <c r="AQ28" s="3" t="inlineStr"/>
       <c r="AR28" s="3" t="inlineStr"/>
-      <c r="AS28" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT28" s="3" t="inlineStr"/>
-      <c r="AU28" s="3" t="inlineStr">
+      <c r="AS28" s="3" t="inlineStr"/>
+      <c r="AT28" s="3" t="inlineStr">
         <is>
           <t>FMCG</t>
         </is>
       </c>
+      <c r="AU28" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AV28" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW28" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AX28" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -5337,20 +5218,15 @@
       <c r="AR29" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AS29" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS29" s="3" t="inlineStr"/>
       <c r="AT29" s="3" t="inlineStr"/>
       <c r="AU29" s="3" t="inlineStr"/>
-      <c r="AV29" s="3" t="inlineStr"/>
-      <c r="AW29" s="3" t="n">
+      <c r="AV29" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AX29" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW29" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -5485,20 +5361,15 @@
       <c r="AR30" s="3" t="n">
         <v>-0.32</v>
       </c>
-      <c r="AS30" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS30" s="3" t="inlineStr"/>
       <c r="AT30" s="3" t="inlineStr"/>
       <c r="AU30" s="3" t="inlineStr"/>
-      <c r="AV30" s="3" t="inlineStr"/>
-      <c r="AW30" s="3" t="n">
+      <c r="AV30" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AX30" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -5637,20 +5508,15 @@
       <c r="AR31" s="3" t="n">
         <v>-0.11</v>
       </c>
-      <c r="AS31" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS31" s="3" t="inlineStr"/>
       <c r="AT31" s="3" t="inlineStr"/>
       <c r="AU31" s="3" t="inlineStr"/>
-      <c r="AV31" s="3" t="inlineStr"/>
-      <c r="AW31" s="3" t="n">
+      <c r="AV31" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AX31" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW31" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -5785,20 +5651,15 @@
       <c r="AR32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AS32" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS32" s="3" t="inlineStr"/>
       <c r="AT32" s="3" t="inlineStr"/>
       <c r="AU32" s="3" t="inlineStr"/>
-      <c r="AV32" s="3" t="inlineStr"/>
-      <c r="AW32" s="3" t="n">
+      <c r="AV32" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AX32" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW32" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -5933,20 +5794,15 @@
       <c r="AR33" s="3" t="n">
         <v>-0.24</v>
       </c>
-      <c r="AS33" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS33" s="3" t="inlineStr"/>
       <c r="AT33" s="3" t="inlineStr"/>
       <c r="AU33" s="3" t="inlineStr"/>
-      <c r="AV33" s="3" t="inlineStr"/>
-      <c r="AW33" s="3" t="n">
+      <c r="AV33" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AX33" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW33" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -6047,18 +5903,13 @@
       <c r="AP34" s="3" t="inlineStr"/>
       <c r="AQ34" s="3" t="inlineStr"/>
       <c r="AR34" s="3" t="inlineStr"/>
-      <c r="AS34" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS34" s="3" t="inlineStr"/>
       <c r="AT34" s="3" t="inlineStr"/>
       <c r="AU34" s="3" t="inlineStr"/>
       <c r="AV34" s="3" t="inlineStr"/>
-      <c r="AW34" s="3" t="inlineStr"/>
-      <c r="AX34" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -6159,18 +6010,13 @@
       <c r="AP35" s="3" t="inlineStr"/>
       <c r="AQ35" s="3" t="inlineStr"/>
       <c r="AR35" s="3" t="inlineStr"/>
-      <c r="AS35" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS35" s="3" t="inlineStr"/>
       <c r="AT35" s="3" t="inlineStr"/>
       <c r="AU35" s="3" t="inlineStr"/>
       <c r="AV35" s="3" t="inlineStr"/>
-      <c r="AW35" s="3" t="inlineStr"/>
-      <c r="AX35" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -6279,18 +6125,13 @@
       <c r="AP36" s="3" t="inlineStr"/>
       <c r="AQ36" s="3" t="inlineStr"/>
       <c r="AR36" s="3" t="inlineStr"/>
-      <c r="AS36" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS36" s="3" t="inlineStr"/>
       <c r="AT36" s="3" t="inlineStr"/>
       <c r="AU36" s="3" t="inlineStr"/>
       <c r="AV36" s="3" t="inlineStr"/>
-      <c r="AW36" s="3" t="inlineStr"/>
-      <c r="AX36" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW36" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -6399,18 +6240,13 @@
       <c r="AP37" s="3" t="inlineStr"/>
       <c r="AQ37" s="3" t="inlineStr"/>
       <c r="AR37" s="3" t="inlineStr"/>
-      <c r="AS37" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS37" s="3" t="inlineStr"/>
       <c r="AT37" s="3" t="inlineStr"/>
       <c r="AU37" s="3" t="inlineStr"/>
       <c r="AV37" s="3" t="inlineStr"/>
-      <c r="AW37" s="3" t="inlineStr"/>
-      <c r="AX37" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW37" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -6549,20 +6385,15 @@
       <c r="AR38" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AS38" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS38" s="3" t="inlineStr"/>
       <c r="AT38" s="3" t="inlineStr"/>
       <c r="AU38" s="3" t="inlineStr"/>
-      <c r="AV38" s="3" t="inlineStr"/>
-      <c r="AW38" s="3" t="n">
+      <c r="AV38" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AX38" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW38" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -6671,18 +6502,13 @@
       <c r="AP39" s="3" t="inlineStr"/>
       <c r="AQ39" s="3" t="inlineStr"/>
       <c r="AR39" s="3" t="inlineStr"/>
-      <c r="AS39" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS39" s="3" t="inlineStr"/>
       <c r="AT39" s="3" t="inlineStr"/>
       <c r="AU39" s="3" t="inlineStr"/>
       <c r="AV39" s="3" t="inlineStr"/>
-      <c r="AW39" s="3" t="inlineStr"/>
-      <c r="AX39" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW39" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -6791,18 +6617,13 @@
       <c r="AP40" s="3" t="inlineStr"/>
       <c r="AQ40" s="3" t="inlineStr"/>
       <c r="AR40" s="3" t="inlineStr"/>
-      <c r="AS40" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS40" s="3" t="inlineStr"/>
       <c r="AT40" s="3" t="inlineStr"/>
       <c r="AU40" s="3" t="inlineStr"/>
       <c r="AV40" s="3" t="inlineStr"/>
-      <c r="AW40" s="3" t="inlineStr"/>
-      <c r="AX40" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW40" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -6911,18 +6732,13 @@
       <c r="AP41" s="3" t="inlineStr"/>
       <c r="AQ41" s="3" t="inlineStr"/>
       <c r="AR41" s="3" t="inlineStr"/>
-      <c r="AS41" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS41" s="3" t="inlineStr"/>
       <c r="AT41" s="3" t="inlineStr"/>
       <c r="AU41" s="3" t="inlineStr"/>
       <c r="AV41" s="3" t="inlineStr"/>
-      <c r="AW41" s="3" t="inlineStr"/>
-      <c r="AX41" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW41" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -7031,18 +6847,13 @@
       <c r="AP42" s="3" t="inlineStr"/>
       <c r="AQ42" s="3" t="inlineStr"/>
       <c r="AR42" s="3" t="inlineStr"/>
-      <c r="AS42" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS42" s="3" t="inlineStr"/>
       <c r="AT42" s="3" t="inlineStr"/>
       <c r="AU42" s="3" t="inlineStr"/>
       <c r="AV42" s="3" t="inlineStr"/>
-      <c r="AW42" s="3" t="inlineStr"/>
-      <c r="AX42" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW42" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -7151,18 +6962,13 @@
       <c r="AP43" s="3" t="inlineStr"/>
       <c r="AQ43" s="3" t="inlineStr"/>
       <c r="AR43" s="3" t="inlineStr"/>
-      <c r="AS43" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS43" s="3" t="inlineStr"/>
       <c r="AT43" s="3" t="inlineStr"/>
       <c r="AU43" s="3" t="inlineStr"/>
       <c r="AV43" s="3" t="inlineStr"/>
-      <c r="AW43" s="3" t="inlineStr"/>
-      <c r="AX43" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -7271,18 +7077,13 @@
       <c r="AP44" s="3" t="inlineStr"/>
       <c r="AQ44" s="3" t="inlineStr"/>
       <c r="AR44" s="3" t="inlineStr"/>
-      <c r="AS44" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS44" s="3" t="inlineStr"/>
       <c r="AT44" s="3" t="inlineStr"/>
       <c r="AU44" s="3" t="inlineStr"/>
       <c r="AV44" s="3" t="inlineStr"/>
-      <c r="AW44" s="3" t="inlineStr"/>
-      <c r="AX44" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW44" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -7421,20 +7222,15 @@
       <c r="AR45" s="3" t="n">
         <v>-0.11</v>
       </c>
-      <c r="AS45" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS45" s="3" t="inlineStr"/>
       <c r="AT45" s="3" t="inlineStr"/>
       <c r="AU45" s="3" t="inlineStr"/>
-      <c r="AV45" s="3" t="inlineStr"/>
-      <c r="AW45" s="3" t="n">
+      <c r="AV45" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AX45" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -7539,18 +7335,13 @@
       <c r="AP46" s="3" t="inlineStr"/>
       <c r="AQ46" s="3" t="inlineStr"/>
       <c r="AR46" s="3" t="inlineStr"/>
-      <c r="AS46" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS46" s="3" t="inlineStr"/>
       <c r="AT46" s="3" t="inlineStr"/>
       <c r="AU46" s="3" t="inlineStr"/>
       <c r="AV46" s="3" t="inlineStr"/>
-      <c r="AW46" s="3" t="inlineStr"/>
-      <c r="AX46" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW46" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -7659,18 +7450,13 @@
       <c r="AP47" s="3" t="inlineStr"/>
       <c r="AQ47" s="3" t="inlineStr"/>
       <c r="AR47" s="3" t="inlineStr"/>
-      <c r="AS47" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS47" s="3" t="inlineStr"/>
       <c r="AT47" s="3" t="inlineStr"/>
       <c r="AU47" s="3" t="inlineStr"/>
       <c r="AV47" s="3" t="inlineStr"/>
-      <c r="AW47" s="3" t="inlineStr"/>
-      <c r="AX47" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW47" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7541,11 @@
           <t>🟢 BUY (Δ-1.0%) · Rank → 1→1 · Conf 57% · band HOLD · 14d left · → BUY</t>
         </is>
       </c>
-      <c r="U48" s="3" t="inlineStr"/>
+      <c r="U48" s="3" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-5.2% ≤ -5% · exit</t>
+        </is>
+      </c>
       <c r="V48" s="3" t="n">
         <v>56.8</v>
       </c>
@@ -7831,24 +7621,19 @@
       </c>
       <c r="AS48" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT48" s="3" t="inlineStr">
-        <is>
           <t>Momentum · Value · Trend</t>
         </is>
       </c>
-      <c r="AU48" s="3" t="inlineStr"/>
+      <c r="AT48" s="3" t="inlineStr"/>
+      <c r="AU48" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="AV48" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW48" s="3" t="n">
         <v>6.23</v>
       </c>
-      <c r="AX48" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW48" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -8009,22 +7794,17 @@
       </c>
       <c r="AS49" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT49" s="3" t="inlineStr">
-        <is>
           <t>Momentum · Trend · Quality</t>
         </is>
       </c>
+      <c r="AT49" s="3" t="inlineStr"/>
       <c r="AU49" s="3" t="inlineStr"/>
-      <c r="AV49" s="3" t="inlineStr"/>
-      <c r="AW49" s="3" t="n">
+      <c r="AV49" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AX49" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW49" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -8191,22 +7971,17 @@
       </c>
       <c r="AS50" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT50" s="3" t="inlineStr">
-        <is>
           <t>Quality · Growth · Mean Reversion</t>
         </is>
       </c>
+      <c r="AT50" s="3" t="inlineStr"/>
       <c r="AU50" s="3" t="inlineStr"/>
-      <c r="AV50" s="3" t="inlineStr"/>
-      <c r="AW50" s="3" t="n">
+      <c r="AV50" s="3" t="n">
         <v>12.15</v>
       </c>
-      <c r="AX50" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW50" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -8373,22 +8148,17 @@
       </c>
       <c r="AS51" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT51" s="3" t="inlineStr">
-        <is>
           <t>Momentum · Value · Mean Reversion</t>
         </is>
       </c>
+      <c r="AT51" s="3" t="inlineStr"/>
       <c r="AU51" s="3" t="inlineStr"/>
-      <c r="AV51" s="3" t="inlineStr"/>
-      <c r="AW51" s="3" t="n">
+      <c r="AV51" s="3" t="n">
         <v>12.97</v>
       </c>
-      <c r="AX51" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW51" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -8479,7 +8249,11 @@
           <t>🔴 AVOID · Rank → 5→5 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
-      <c r="U52" s="3" t="inlineStr"/>
+      <c r="U52" s="3" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-6.7% ≤ -5% · exit</t>
+        </is>
+      </c>
       <c r="V52" s="3" t="n">
         <v>50.5</v>
       </c>
@@ -8555,22 +8329,17 @@
       </c>
       <c r="AS52" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT52" s="3" t="inlineStr">
-        <is>
           <t>Mean Reversion · Growth · Value</t>
         </is>
       </c>
+      <c r="AT52" s="3" t="inlineStr"/>
       <c r="AU52" s="3" t="inlineStr"/>
-      <c r="AV52" s="3" t="inlineStr"/>
-      <c r="AW52" s="3" t="n">
+      <c r="AV52" s="3" t="n">
         <v>14.45</v>
       </c>
-      <c r="AX52" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW52" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -8737,22 +8506,17 @@
       </c>
       <c r="AS53" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT53" s="3" t="inlineStr">
-        <is>
           <t>Value · News · Event Driven</t>
         </is>
       </c>
+      <c r="AT53" s="3" t="inlineStr"/>
       <c r="AU53" s="3" t="inlineStr"/>
-      <c r="AV53" s="3" t="inlineStr"/>
-      <c r="AW53" s="3" t="n">
+      <c r="AV53" s="3" t="n">
         <v>14.77</v>
       </c>
-      <c r="AX53" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW53" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -8919,22 +8683,17 @@
       </c>
       <c r="AS54" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT54" s="3" t="inlineStr">
-        <is>
           <t>Value · Trend · Momentum</t>
         </is>
       </c>
+      <c r="AT54" s="3" t="inlineStr"/>
       <c r="AU54" s="3" t="inlineStr"/>
-      <c r="AV54" s="3" t="inlineStr"/>
-      <c r="AW54" s="3" t="n">
+      <c r="AV54" s="3" t="n">
         <v>14.87</v>
       </c>
-      <c r="AX54" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW54" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -9025,7 +8784,11 @@
           <t>🔴 AVOID · Rank → 8→8 · Conf 54% · band HOLD · 58d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
-      <c r="U55" s="3" t="inlineStr"/>
+      <c r="U55" s="3" t="inlineStr">
+        <is>
+          <t>CRITICAL·DEEP_LOSS·-12.7% ≤ -8% · EXIT URGENT</t>
+        </is>
+      </c>
       <c r="V55" s="3" t="n">
         <v>53.6</v>
       </c>
@@ -9101,22 +8864,17 @@
       </c>
       <c r="AS55" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT55" s="3" t="inlineStr">
-        <is>
           <t>Quality · Mean Reversion · Trend</t>
         </is>
       </c>
+      <c r="AT55" s="3" t="inlineStr"/>
       <c r="AU55" s="3" t="inlineStr"/>
-      <c r="AV55" s="3" t="inlineStr"/>
-      <c r="AW55" s="3" t="n">
+      <c r="AV55" s="3" t="n">
         <v>15.21</v>
       </c>
-      <c r="AX55" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW55" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -9207,7 +8965,11 @@
           <t>🔴 AVOID · Rank → 9→9 · Conf 50% · band STRONG · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
-      <c r="U56" s="3" t="inlineStr"/>
+      <c r="U56" s="3" t="inlineStr">
+        <is>
+          <t>CRITICAL·DEEP_LOSS·-8.4% ≤ -8% · EXIT URGENT</t>
+        </is>
+      </c>
       <c r="V56" s="3" t="n">
         <v>50.5</v>
       </c>
@@ -9283,22 +9045,17 @@
       </c>
       <c r="AS56" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT56" s="3" t="inlineStr">
-        <is>
           <t>Momentum · News · Quality</t>
         </is>
       </c>
+      <c r="AT56" s="3" t="inlineStr"/>
       <c r="AU56" s="3" t="inlineStr"/>
-      <c r="AV56" s="3" t="inlineStr"/>
-      <c r="AW56" s="3" t="n">
+      <c r="AV56" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="AX56" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW56" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -9389,7 +9146,11 @@
           <t>🔴 AVOID · Rank → 10→10 · Conf 54% · band HOLD · 58d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
-      <c r="U57" s="3" t="inlineStr"/>
+      <c r="U57" s="3" t="inlineStr">
+        <is>
+          <t>CRITICAL·DEEP_LOSS·-9.2% ≤ -8% · EXIT URGENT</t>
+        </is>
+      </c>
       <c r="V57" s="3" t="n">
         <v>53.6</v>
       </c>
@@ -9465,22 +9226,17 @@
       </c>
       <c r="AS57" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT57" s="3" t="inlineStr">
-        <is>
           <t>Momentum · News · Value</t>
         </is>
       </c>
+      <c r="AT57" s="3" t="inlineStr"/>
       <c r="AU57" s="3" t="inlineStr"/>
-      <c r="AV57" s="3" t="inlineStr"/>
-      <c r="AW57" s="3" t="n">
+      <c r="AV57" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="AX57" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW57" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -9571,7 +9327,11 @@
           <t>🔴 AVOID · Rank → 11→11 · Conf 29% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
-      <c r="U58" s="3" t="inlineStr"/>
+      <c r="U58" s="3" t="inlineStr">
+        <is>
+          <t>WARNING·RAPID_APPRECIATION·+16.1% ≥ +12% · take profit</t>
+        </is>
+      </c>
       <c r="V58" s="3" t="n">
         <v>28.7</v>
       </c>
@@ -9647,22 +9407,17 @@
       </c>
       <c r="AS58" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT58" s="3" t="inlineStr">
-        <is>
           <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
+      <c r="AT58" s="3" t="inlineStr"/>
       <c r="AU58" s="3" t="inlineStr"/>
-      <c r="AV58" s="3" t="inlineStr"/>
-      <c r="AW58" s="3" t="n">
+      <c r="AV58" s="3" t="n">
         <v>37.17</v>
       </c>
-      <c r="AX58" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW58" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -9829,22 +9584,17 @@
       </c>
       <c r="AS59" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT59" s="3" t="inlineStr">
-        <is>
           <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
+      <c r="AT59" s="3" t="inlineStr"/>
       <c r="AU59" s="3" t="inlineStr"/>
-      <c r="AV59" s="3" t="inlineStr"/>
-      <c r="AW59" s="3" t="n">
+      <c r="AV59" s="3" t="n">
         <v>37.79</v>
       </c>
-      <c r="AX59" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW59" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -10011,22 +9761,17 @@
       </c>
       <c r="AS60" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT60" s="3" t="inlineStr">
-        <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
+      <c r="AT60" s="3" t="inlineStr"/>
       <c r="AU60" s="3" t="inlineStr"/>
-      <c r="AV60" s="3" t="inlineStr"/>
-      <c r="AW60" s="3" t="n">
+      <c r="AV60" s="3" t="n">
         <v>43.85</v>
       </c>
-      <c r="AX60" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW60" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -10193,22 +9938,17 @@
       </c>
       <c r="AS61" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT61" s="3" t="inlineStr">
-        <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
+      <c r="AT61" s="3" t="inlineStr"/>
       <c r="AU61" s="3" t="inlineStr"/>
-      <c r="AV61" s="3" t="inlineStr"/>
-      <c r="AW61" s="3" t="n">
+      <c r="AV61" s="3" t="n">
         <v>45.62</v>
       </c>
-      <c r="AX61" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW61" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -10375,22 +10115,17 @@
       </c>
       <c r="AS62" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT62" s="3" t="inlineStr">
-        <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
+      <c r="AT62" s="3" t="inlineStr"/>
       <c r="AU62" s="3" t="inlineStr"/>
-      <c r="AV62" s="3" t="inlineStr"/>
-      <c r="AW62" s="3" t="n">
+      <c r="AV62" s="3" t="n">
         <v>45.94</v>
       </c>
-      <c r="AX62" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW62" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -10543,26 +10278,21 @@
       <c r="AR63" s="3" t="n">
         <v>-0.71</v>
       </c>
-      <c r="AS63" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT63" s="3" t="inlineStr"/>
-      <c r="AU63" s="3" t="inlineStr">
+      <c r="AS63" s="3" t="inlineStr"/>
+      <c r="AT63" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="AU63" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AV63" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW63" s="3" t="n">
         <v>5.02</v>
       </c>
-      <c r="AX63" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW63" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -10643,7 +10373,11 @@
           <t>🟢 BUY (Δ-1.0%) · Rank #2 · Conf 57% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
-      <c r="U64" s="3" t="inlineStr"/>
+      <c r="U64" s="3" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-5.2% ≤ -5% · exit</t>
+        </is>
+      </c>
       <c r="V64" s="3" t="n">
         <v>56.8</v>
       </c>
@@ -10715,26 +10449,21 @@
       <c r="AR64" s="3" t="n">
         <v>-3.77</v>
       </c>
-      <c r="AS64" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT64" s="3" t="inlineStr"/>
-      <c r="AU64" s="3" t="inlineStr">
+      <c r="AS64" s="3" t="inlineStr"/>
+      <c r="AT64" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="AU64" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AV64" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW64" s="3" t="n">
         <v>6.23</v>
       </c>
-      <c r="AX64" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW64" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -10887,26 +10616,21 @@
       <c r="AR65" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AS65" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT65" s="3" t="inlineStr"/>
-      <c r="AU65" s="3" t="inlineStr">
+      <c r="AS65" s="3" t="inlineStr"/>
+      <c r="AT65" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="AU65" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AV65" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW65" s="3" t="n">
         <v>15.28</v>
       </c>
-      <c r="AX65" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW65" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -10987,7 +10711,11 @@
           <t>🟢 BUY (Δ-2.0%) · Rank #4 · Conf 54% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
-      <c r="U66" s="3" t="inlineStr"/>
+      <c r="U66" s="3" t="inlineStr">
+        <is>
+          <t>CRITICAL·DEEP_LOSS·-12.7% ≤ -8% · EXIT URGENT</t>
+        </is>
+      </c>
       <c r="V66" s="3" t="n">
         <v>53.6</v>
       </c>
@@ -11059,26 +10787,21 @@
       <c r="AR66" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AS66" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT66" s="3" t="inlineStr"/>
-      <c r="AU66" s="3" t="inlineStr">
+      <c r="AS66" s="3" t="inlineStr"/>
+      <c r="AT66" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="AU66" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AV66" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW66" s="3" t="n">
         <v>-5.71</v>
       </c>
-      <c r="AX66" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW66" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -11159,7 +10882,11 @@
           <t>🟢 BUY (Δ-2.0%) · Rank #5 · Conf 50% · momentum → · band STRONG · 91d left · → HOLD</t>
         </is>
       </c>
-      <c r="U67" s="3" t="inlineStr"/>
+      <c r="U67" s="3" t="inlineStr">
+        <is>
+          <t>CRITICAL·DEEP_LOSS·-8.4% ≤ -8% · EXIT URGENT</t>
+        </is>
+      </c>
       <c r="V67" s="3" t="n">
         <v>50.5</v>
       </c>
@@ -11231,26 +10958,21 @@
       <c r="AR67" s="3" t="n">
         <v>-1.67</v>
       </c>
-      <c r="AS67" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT67" s="3" t="inlineStr"/>
-      <c r="AU67" s="3" t="inlineStr">
+      <c r="AS67" s="3" t="inlineStr"/>
+      <c r="AT67" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="AU67" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AV67" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW67" s="3" t="n">
         <v>-1.12</v>
       </c>
-      <c r="AX67" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW67" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -11331,7 +11053,11 @@
           <t>🟢 BUY (Δ-2.0%) · Rank #6 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
-      <c r="U68" s="3" t="inlineStr"/>
+      <c r="U68" s="3" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-6.7% ≤ -5% · exit</t>
+        </is>
+      </c>
       <c r="V68" s="3" t="n">
         <v>50.5</v>
       </c>
@@ -11403,26 +11129,21 @@
       <c r="AR68" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AS68" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT68" s="3" t="inlineStr"/>
-      <c r="AU68" s="3" t="inlineStr">
+      <c r="AS68" s="3" t="inlineStr"/>
+      <c r="AT68" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="AU68" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AV68" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW68" s="3" t="n">
         <v>0.79</v>
       </c>
-      <c r="AX68" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW68" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -11575,26 +11296,21 @@
       <c r="AR69" s="3" t="n">
         <v>-8.66</v>
       </c>
-      <c r="AS69" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT69" s="3" t="inlineStr"/>
-      <c r="AU69" s="3" t="inlineStr">
+      <c r="AS69" s="3" t="inlineStr"/>
+      <c r="AT69" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="AU69" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AV69" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW69" s="3" t="n">
         <v>6.58</v>
       </c>
-      <c r="AX69" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW69" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -11747,26 +11463,21 @@
       <c r="AR70" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AS70" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT70" s="3" t="inlineStr"/>
-      <c r="AU70" s="3" t="inlineStr">
+      <c r="AS70" s="3" t="inlineStr"/>
+      <c r="AT70" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="AU70" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AV70" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW70" s="3" t="n">
         <v>6.87</v>
       </c>
-      <c r="AX70" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW70" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -11919,26 +11630,21 @@
       <c r="AR71" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AS71" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT71" s="3" t="inlineStr"/>
-      <c r="AU71" s="3" t="inlineStr">
+      <c r="AS71" s="3" t="inlineStr"/>
+      <c r="AT71" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="AU71" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AV71" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW71" s="3" t="n">
         <v>17.3</v>
       </c>
-      <c r="AX71" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW71" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
@@ -12019,7 +11725,11 @@
           <t>🟢 BUY (Δ-2.0%) · Rank #10 · Conf 54% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
-      <c r="U72" s="3" t="inlineStr"/>
+      <c r="U72" s="3" t="inlineStr">
+        <is>
+          <t>CRITICAL·DEEP_LOSS·-9.2% ≤ -8% · EXIT URGENT</t>
+        </is>
+      </c>
       <c r="V72" s="3" t="n">
         <v>53.6</v>
       </c>
@@ -12091,31 +11801,26 @@
       <c r="AR72" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AS72" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT72" s="3" t="inlineStr"/>
-      <c r="AU72" s="3" t="inlineStr">
+      <c r="AS72" s="3" t="inlineStr"/>
+      <c r="AT72" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="AU72" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AV72" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW72" s="3" t="n">
         <v>-1.96</v>
       </c>
-      <c r="AX72" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:51</t>
+      <c r="AW72" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:01</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AX72"/>
+  <autoFilter ref="A1:AW72"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>